--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{80813F1C-CE7F-4B1A-91C5-8C400A32977F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6AEA668-0A33-4479-A1A4-EE62E3DFE2CC}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{80813F1C-CE7F-4B1A-91C5-8C400A32977F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74553B82-B268-4C1F-8F94-DCC6A5958B7A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="(2)" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$B$1:$J$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$B$1:$J$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="912">
   <si>
     <t>fx.MenuPane.020</t>
   </si>
@@ -3213,63 +3213,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>MSG_128</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_129</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_130</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CompareSheetsTask.030</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_131</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_132</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_133</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_136</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_134</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_135</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_141</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_142</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_139</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_140</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MSG_137</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3313,6 +3257,422 @@
   </si>
   <si>
     <t>fx.ExecutePane.010</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_0010</t>
+  </si>
+  <si>
+    <t>APP_0020</t>
+  </si>
+  <si>
+    <t>APP_0030</t>
+  </si>
+  <si>
+    <t>APP_0040</t>
+  </si>
+  <si>
+    <t>APP_0050</t>
+  </si>
+  <si>
+    <t>APP_0060</t>
+  </si>
+  <si>
+    <t>APP_0070</t>
+  </si>
+  <si>
+    <t>APP_0080</t>
+  </si>
+  <si>
+    <t>APP_0090</t>
+  </si>
+  <si>
+    <t>APP_0100</t>
+  </si>
+  <si>
+    <t>APP_0110</t>
+  </si>
+  <si>
+    <t>APP_0120</t>
+  </si>
+  <si>
+    <t>APP_0130</t>
+  </si>
+  <si>
+    <t>APP_0140</t>
+  </si>
+  <si>
+    <t>APP_0150</t>
+  </si>
+  <si>
+    <t>APP_0160</t>
+  </si>
+  <si>
+    <t>APP_0170</t>
+  </si>
+  <si>
+    <t>APP_0180</t>
+  </si>
+  <si>
+    <t>APP_0190</t>
+  </si>
+  <si>
+    <t>APP_0200</t>
+  </si>
+  <si>
+    <t>APP_0210</t>
+  </si>
+  <si>
+    <t>APP_0220</t>
+  </si>
+  <si>
+    <t>APP_0230</t>
+  </si>
+  <si>
+    <t>APP_0240</t>
+  </si>
+  <si>
+    <t>APP_0250</t>
+  </si>
+  <si>
+    <t>APP_0260</t>
+  </si>
+  <si>
+    <t>APP_0270</t>
+  </si>
+  <si>
+    <t>APP_0280</t>
+  </si>
+  <si>
+    <t>APP_0290</t>
+  </si>
+  <si>
+    <t>APP_0300</t>
+  </si>
+  <si>
+    <t>APP_0310</t>
+  </si>
+  <si>
+    <t>APP_0320</t>
+  </si>
+  <si>
+    <t>APP_0330</t>
+  </si>
+  <si>
+    <t>APP_0340</t>
+  </si>
+  <si>
+    <t>APP_0350</t>
+  </si>
+  <si>
+    <t>APP_0360</t>
+  </si>
+  <si>
+    <t>APP_0370</t>
+  </si>
+  <si>
+    <t>APP_0380</t>
+  </si>
+  <si>
+    <t>APP_0390</t>
+  </si>
+  <si>
+    <t>APP_0400</t>
+  </si>
+  <si>
+    <t>APP_0410</t>
+  </si>
+  <si>
+    <t>APP_0420</t>
+  </si>
+  <si>
+    <t>APP_0430</t>
+  </si>
+  <si>
+    <t>APP_0440</t>
+  </si>
+  <si>
+    <t>APP_0450</t>
+  </si>
+  <si>
+    <t>APP_0460</t>
+  </si>
+  <si>
+    <t>APP_0470</t>
+  </si>
+  <si>
+    <t>APP_0480</t>
+  </si>
+  <si>
+    <t>APP_0490</t>
+  </si>
+  <si>
+    <t>APP_0500</t>
+  </si>
+  <si>
+    <t>APP_0510</t>
+  </si>
+  <si>
+    <t>APP_0520</t>
+  </si>
+  <si>
+    <t>APP_0530</t>
+  </si>
+  <si>
+    <t>APP_0540</t>
+  </si>
+  <si>
+    <t>APP_0550</t>
+  </si>
+  <si>
+    <t>APP_0560</t>
+  </si>
+  <si>
+    <t>APP_0570</t>
+  </si>
+  <si>
+    <t>APP_0580</t>
+  </si>
+  <si>
+    <t>APP_0590</t>
+  </si>
+  <si>
+    <t>APP_0600</t>
+  </si>
+  <si>
+    <t>APP_0610</t>
+  </si>
+  <si>
+    <t>APP_0620</t>
+  </si>
+  <si>
+    <t>APP_0630</t>
+  </si>
+  <si>
+    <t>APP_0640</t>
+  </si>
+  <si>
+    <t>APP_0650</t>
+  </si>
+  <si>
+    <t>APP_0660</t>
+  </si>
+  <si>
+    <t>APP_0670</t>
+  </si>
+  <si>
+    <t>APP_0680</t>
+  </si>
+  <si>
+    <t>APP_0690</t>
+  </si>
+  <si>
+    <t>APP_0700</t>
+  </si>
+  <si>
+    <t>APP_0710</t>
+  </si>
+  <si>
+    <t>APP_0720</t>
+  </si>
+  <si>
+    <t>APP_0730</t>
+  </si>
+  <si>
+    <t>APP_0740</t>
+  </si>
+  <si>
+    <t>APP_0750</t>
+  </si>
+  <si>
+    <t>APP_0760</t>
+  </si>
+  <si>
+    <t>APP_0770</t>
+  </si>
+  <si>
+    <t>APP_0780</t>
+  </si>
+  <si>
+    <t>APP_0790</t>
+  </si>
+  <si>
+    <t>APP_0800</t>
+  </si>
+  <si>
+    <t>APP_0810</t>
+  </si>
+  <si>
+    <t>APP_0820</t>
+  </si>
+  <si>
+    <t>APP_0830</t>
+  </si>
+  <si>
+    <t>APP_0840</t>
+  </si>
+  <si>
+    <t>APP_0850</t>
+  </si>
+  <si>
+    <t>APP_0860</t>
+  </si>
+  <si>
+    <t>APP_0870</t>
+  </si>
+  <si>
+    <t>APP_0880</t>
+  </si>
+  <si>
+    <t>APP_0890</t>
+  </si>
+  <si>
+    <t>APP_0900</t>
+  </si>
+  <si>
+    <t>APP_0910</t>
+  </si>
+  <si>
+    <t>APP_0920</t>
+  </si>
+  <si>
+    <t>APP_0930</t>
+  </si>
+  <si>
+    <t>APP_0940</t>
+  </si>
+  <si>
+    <t>APP_0950</t>
+  </si>
+  <si>
+    <t>APP_0960</t>
+  </si>
+  <si>
+    <t>APP_0970</t>
+  </si>
+  <si>
+    <t>APP_0980</t>
+  </si>
+  <si>
+    <t>APP_0990</t>
+  </si>
+  <si>
+    <t>APP_1000</t>
+  </si>
+  <si>
+    <t>APP_1010</t>
+  </si>
+  <si>
+    <t>APP_1020</t>
+  </si>
+  <si>
+    <t>APP_1030</t>
+  </si>
+  <si>
+    <t>APP_1040</t>
+  </si>
+  <si>
+    <t>APP_1050</t>
+  </si>
+  <si>
+    <t>APP_1060</t>
+  </si>
+  <si>
+    <t>APP_1070</t>
+  </si>
+  <si>
+    <t>APP_1080</t>
+  </si>
+  <si>
+    <t>APP_1091</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1092</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1093</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1100</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1110</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1120</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1130</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1140</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1150</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1160</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1170</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1180</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1190</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1200</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1210</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1220</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1230</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1240</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1250</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1260</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1270</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1280</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_1290</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3473,6 +3833,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3738,7 +4102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:J195"/>
+  <dimension ref="B1:J177"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="1"/>
@@ -3779,10 +4143,10 @@
     </row>
     <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -3808,10 +4172,10 @@
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1</v>
@@ -3837,10 +4201,10 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>236</v>
@@ -3866,7 +4230,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>0</v>
@@ -3895,7 +4259,7 @@
     </row>
     <row r="6" spans="2:10">
       <c r="B6" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>207</v>
@@ -3924,7 +4288,7 @@
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>208</v>
@@ -3953,7 +4317,7 @@
     </row>
     <row r="8" spans="2:10">
       <c r="B8" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>234</v>
@@ -3982,10 +4346,10 @@
     </row>
     <row r="9" spans="2:10">
       <c r="B9" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>29</v>
@@ -4011,7 +4375,7 @@
     </row>
     <row r="10" spans="2:10">
       <c r="B10" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>30</v>
@@ -4040,7 +4404,7 @@
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -4069,7 +4433,7 @@
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
@@ -4098,7 +4462,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
@@ -4127,7 +4491,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="B14" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>11</v>
@@ -4156,7 +4520,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="B15" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>13</v>
@@ -4185,7 +4549,7 @@
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>462</v>
@@ -4214,7 +4578,7 @@
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>15</v>
@@ -4243,7 +4607,7 @@
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -4272,7 +4636,7 @@
     </row>
     <row r="19" spans="2:10">
       <c r="B19" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>18</v>
@@ -4301,10 +4665,10 @@
     </row>
     <row r="20" spans="2:10">
       <c r="B20" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>19</v>
@@ -4330,10 +4694,10 @@
     </row>
     <row r="21" spans="2:10">
       <c r="B21" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>20</v>
@@ -4359,7 +4723,7 @@
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>375</v>
@@ -4388,7 +4752,7 @@
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>376</v>
@@ -4417,10 +4781,10 @@
     </row>
     <row r="24" spans="2:10">
       <c r="B24" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>21</v>
@@ -4446,7 +4810,7 @@
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>22</v>
@@ -4475,7 +4839,7 @@
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>578</v>
@@ -4504,10 +4868,10 @@
     </row>
     <row r="27" spans="2:10">
       <c r="B27" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>24</v>
@@ -4533,7 +4897,7 @@
     </row>
     <row r="28" spans="2:10">
       <c r="B28" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
@@ -4562,7 +4926,7 @@
     </row>
     <row r="29" spans="2:10">
       <c r="B29" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>27</v>
@@ -4591,10 +4955,10 @@
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>292</v>
@@ -4620,7 +4984,7 @@
     </row>
     <row r="31" spans="2:10">
       <c r="B31" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>2</v>
@@ -4649,7 +5013,7 @@
     </row>
     <row r="32" spans="2:10">
       <c r="B32" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>209</v>
@@ -4678,7 +5042,7 @@
     </row>
     <row r="33" spans="2:10">
       <c r="B33" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>511</v>
@@ -4707,7 +5071,7 @@
     </row>
     <row r="34" spans="2:10">
       <c r="B34" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>514</v>
@@ -4736,7 +5100,7 @@
     </row>
     <row r="35" spans="2:10">
       <c r="B35" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>519</v>
@@ -4765,7 +5129,7 @@
     </row>
     <row r="36" spans="2:10">
       <c r="B36" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>521</v>
@@ -4794,7 +5158,7 @@
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>524</v>
@@ -4823,7 +5187,7 @@
     </row>
     <row r="38" spans="2:10">
       <c r="B38" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>581</v>
@@ -4852,7 +5216,7 @@
     </row>
     <row r="39" spans="2:10">
       <c r="B39" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>586</v>
@@ -4881,7 +5245,7 @@
     </row>
     <row r="40" spans="2:10">
       <c r="B40" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>592</v>
@@ -4910,7 +5274,7 @@
     </row>
     <row r="41" spans="2:10">
       <c r="B41" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>593</v>
@@ -4939,7 +5303,7 @@
     </row>
     <row r="42" spans="2:10">
       <c r="B42" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>599</v>
@@ -4968,7 +5332,7 @@
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>600</v>
@@ -4997,7 +5361,7 @@
     </row>
     <row r="44" spans="2:10">
       <c r="B44" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>531</v>
@@ -5026,7 +5390,7 @@
     </row>
     <row r="45" spans="2:10">
       <c r="B45" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>532</v>
@@ -5070,4072 +5434,3807 @@
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="1" t="s">
-        <v>695</v>
+        <v>781</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>396</v>
+        <v>471</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>397</v>
+        <v>124</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="H47" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.EditComparisonPane.010=組み合わせ編集</v>
+        <f xml:space="preserve"> IF($C47="", "", $C47 &amp; "=" &amp; D47)</f>
+        <v>AppMain.010=方眼Diff</v>
       </c>
       <c r="I47" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.EditComparisonPane.010=Edit Pairing</v>
+        <f xml:space="preserve"> IF($C47="", "", $C47 &amp; "=" &amp; E47)</f>
+        <v>AppMain.010=HoganDiff (方眼Diff)</v>
       </c>
       <c r="J47" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.EditComparisonPane.010=组合编辑</v>
+        <f xml:space="preserve"> IF($C47="", "", $C47 &amp; "=" &amp; F47)</f>
+        <v>AppMain.010=方眼Diff</v>
       </c>
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="1" t="s">
-        <v>697</v>
+        <v>782</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>542</v>
+        <v>60</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>544</v>
+        <v>125</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>546</v>
+        <v>343</v>
       </c>
       <c r="H48" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialog.010=方眼Diff  -  Googleドライブ リビジョン選択</v>
+        <f xml:space="preserve"> IF($C48="", "", $C48 &amp; "=" &amp; D48)</f>
+        <v>AppResource.010=設定の保存に失敗しました。</v>
       </c>
       <c r="I48" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialog.010=HoganDiff  -  Google Drive Revision Selection</v>
+        <f xml:space="preserve"> IF($C48="", "", $C48 &amp; "=" &amp; E48)</f>
+        <v>AppResource.010=Failed to save settings.</v>
       </c>
       <c r="J48" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialog.010=方眼Diff  -  Google Drive 版本选择</v>
+        <f xml:space="preserve"> IF($C48="", "", $C48 &amp; "=" &amp; F48)</f>
+        <v>AppResource.010=保存设置失败。</v>
       </c>
     </row>
     <row r="49" spans="2:10">
       <c r="B49" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>543</v>
+        <v>783</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>545</v>
+        <v>129</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>547</v>
+        <v>344</v>
       </c>
       <c r="H49" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialog.020=方眼Diff  -  Googleドライブ ファイル選択</v>
+        <f xml:space="preserve"> IF($C49="", "", $C49 &amp; "=" &amp; D49)</f>
+        <v>AppTaskBase.030=比較結果テキストを保存しています...</v>
       </c>
       <c r="I49" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialog.020=HoganDiff  -  Google Drive File Selection</v>
+        <f xml:space="preserve"> IF($C49="", "", $C49 &amp; "=" &amp; E49)</f>
+        <v>AppTaskBase.030=Saving result text...</v>
       </c>
       <c r="J49" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialog.020=方眼Diff  -  Google Drive 文件选择</v>
+        <f xml:space="preserve"> IF($C49="", "", $C49 &amp; "=" &amp; F49)</f>
+        <v>AppTaskBase.030=存储比较结果文本...</v>
       </c>
     </row>
     <row r="50" spans="2:10">
       <c r="B50" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>551</v>
+        <v>784</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>552</v>
+        <v>130</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>558</v>
+        <v>345</v>
       </c>
       <c r="H50" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialogPane.070=共有ドライブ</v>
+        <f xml:space="preserve"> IF($C50="", "", $C50 &amp; "=" &amp; D50)</f>
+        <v>AppTaskBase.050=比較結果テキストの保存と表示に失敗しました。</v>
       </c>
       <c r="I50" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialogPane.070=Shared drives</v>
+        <f xml:space="preserve"> IF($C50="", "", $C50 &amp; "=" &amp; E50)</f>
+        <v>AppTaskBase.050=Failed to save or open result text.</v>
       </c>
       <c r="J50" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialogPane.070=共享云端硬盘</v>
+        <f xml:space="preserve"> IF($C50="", "", $C50 &amp; "=" &amp; F50)</f>
+        <v>AppTaskBase.050=保存和显示比较结果文本失败。</v>
       </c>
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>555</v>
+        <v>785</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>553</v>
+        <v>131</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>554</v>
+        <v>346</v>
       </c>
       <c r="H51" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialogPane.080=すべてのファイル</v>
+        <f xml:space="preserve"> IF($C51="", "", $C51 &amp; "=" &amp; D51)</f>
+        <v>AppTaskBase.060=Excelブックに比較結果の色を付けて保存しています...</v>
       </c>
       <c r="I51" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialogPane.080=All files</v>
+        <f xml:space="preserve"> IF($C51="", "", $C51 &amp; "=" &amp; E51)</f>
+        <v>AppTaskBase.060=Painting and saving result book(s)...</v>
       </c>
       <c r="J51" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialogPane.080=所有文件</v>
+        <f xml:space="preserve"> IF($C51="", "", $C51 &amp; "=" &amp; F51)</f>
+        <v>AppTaskBase.060=着色和存储在工作簿...</v>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>556</v>
+        <v>786</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>557</v>
+        <v>132</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>559</v>
+        <v>347</v>
       </c>
       <c r="H52" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialogPane.090=スター付き</v>
+        <f xml:space="preserve"> IF($C52="", "", $C52 &amp; "=" &amp; D52)</f>
+        <v>AppTaskBase.070=Excelブックの着色・保存に失敗しました。</v>
       </c>
       <c r="I52" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialogPane.090=Starred</v>
+        <f xml:space="preserve"> IF($C52="", "", $C52 &amp; "=" &amp; E52)</f>
+        <v>AppTaskBase.070=Failed to paint or save result book(s).</v>
       </c>
       <c r="J52" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialogPane.090=已加星标</v>
+        <f xml:space="preserve"> IF($C52="", "", $C52 &amp; "=" &amp; F52)</f>
+        <v>AppTaskBase.070=着色和保存工作簿失败。</v>
       </c>
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>561</v>
+        <v>787</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>563</v>
+        <v>133</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>562</v>
+        <v>348</v>
       </c>
       <c r="H53" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleRevisionSelectorDialog.010=Googleドライブからのファイルダウンロードに失敗しました。</v>
+        <f xml:space="preserve"> IF($C53="", "", $C53 &amp; "=" &amp; D53)</f>
+        <v>AppTaskBase.080=比較結果のExcelブックを表示しています...</v>
       </c>
       <c r="I53" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleRevisionSelectorDialog.010=Failed to download the file from Google Drive.</v>
+        <f xml:space="preserve"> IF($C53="", "", $C53 &amp; "=" &amp; E53)</f>
+        <v>AppTaskBase.080=Opening result book(s)...</v>
       </c>
       <c r="J53" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleRevisionSelectorDialog.010=从Google云端硬盘下载文件失败。</v>
+        <f xml:space="preserve"> IF($C53="", "", $C53 &amp; "=" &amp; F53)</f>
+        <v>AppTaskBase.080=显示比较结果的工作簿...</v>
       </c>
     </row>
     <row r="54" spans="2:10">
+      <c r="B54" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>349</v>
+      </c>
       <c r="H54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f xml:space="preserve"> IF($C54="", "", $C54 &amp; "=" &amp; D54)</f>
+        <v>AppTaskBase.090=Excelブックの表示に失敗しました。</v>
       </c>
       <c r="I54" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <f xml:space="preserve"> IF($C54="", "", $C54 &amp; "=" &amp; E54)</f>
+        <v>AppTaskBase.090=Failed to open result book(s).</v>
       </c>
       <c r="J54" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f xml:space="preserve"> IF($C54="", "", $C54 &amp; "=" &amp; F54)</f>
+        <v>AppTaskBase.090=显示工作簿失败。</v>
       </c>
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>285</v>
+        <v>789</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="H55" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.TreeResultBookCreator.010=比較フォルダ%s：</v>
+        <f xml:space="preserve"> IF($C55="", "", $C55 &amp; "=" &amp; D55)</f>
+        <v>AppTaskBase.100=ExcelブックAの着色・保存に失敗しました。</v>
       </c>
       <c r="I55" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">excel.poi.usermodel.TreeResultBookCreator.010=Folder %s : </v>
+        <f xml:space="preserve"> IF($C55="", "", $C55 &amp; "=" &amp; E55)</f>
+        <v>AppTaskBase.100=Failed to paint or save result book A.</v>
       </c>
       <c r="J55" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.TreeResultBookCreator.010=文件夹%s：</v>
+        <f xml:space="preserve"> IF($C55="", "", $C55 &amp; "=" &amp; F55)</f>
+        <v>AppTaskBase.100=工作簿A的着色和保存失败。</v>
       </c>
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>286</v>
+        <v>790</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>411</v>
+        <v>136</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="H56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.TreeResultBookCreator.020=作業用フォルダ：</v>
+        <f xml:space="preserve"> IF($C56="", "", $C56 &amp; "=" &amp; D56)</f>
+        <v>AppTaskBase.110=ExcelブックBの着色・保存に失敗しました。</v>
       </c>
       <c r="I56" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">excel.poi.usermodel.TreeResultBookCreator.020=Working dir : </v>
+        <f xml:space="preserve"> IF($C56="", "", $C56 &amp; "=" &amp; E56)</f>
+        <v>AppTaskBase.110=Failed to paint or save result book B.</v>
       </c>
       <c r="J56" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.TreeResultBookCreator.020=工作文件夹：</v>
+        <f xml:space="preserve"> IF($C56="", "", $C56 &amp; "=" &amp; F56)</f>
+        <v>AppTaskBase.110=工作簿B的着色和保存失败。</v>
       </c>
     </row>
     <row r="57" spans="2:10">
+      <c r="B57" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>352</v>
+      </c>
       <c r="H57" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f xml:space="preserve"> IF($C57="", "", $C57 &amp; "=" &amp; D57)</f>
+        <v>AppTaskBase.120=処理が完了しました。</v>
       </c>
       <c r="I57" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <f xml:space="preserve"> IF($C57="", "", $C57 &amp; "=" &amp; E57)</f>
+        <v>AppTaskBase.120=Process completed.</v>
       </c>
       <c r="J57" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f xml:space="preserve"> IF($C57="", "", $C57 &amp; "=" &amp; F57)</f>
+        <v>AppTaskBase.120=过程完成。</v>
       </c>
     </row>
     <row r="58" spans="2:10">
       <c r="B58" s="1" t="s">
-        <v>644</v>
+        <v>792</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>416</v>
+        <v>247</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>424</v>
+        <v>194</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>438</v>
+        <v>220</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>425</v>
+        <v>353</v>
       </c>
       <c r="H58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.010=比較実行日時：</v>
+        <f xml:space="preserve"> IF($C58="", "", $C58 &amp; "=" &amp; D58)</f>
+        <v>AppTaskBase.150=★失敗しました</v>
       </c>
       <c r="I58" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">excel.poi.usermodel.BookResultBookCreator.010=Exec datetime : </v>
+        <f xml:space="preserve"> IF($C58="", "", $C58 &amp; "=" &amp; E58)</f>
+        <v>AppTaskBase.150=★Failed</v>
       </c>
       <c r="J58" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.010=执行日期和时间：</v>
+        <f xml:space="preserve"> IF($C58="", "", $C58 &amp; "=" &amp; F58)</f>
+        <v>AppTaskBase.150=★失败</v>
       </c>
     </row>
     <row r="59" spans="2:10">
       <c r="B59" s="1" t="s">
-        <v>646</v>
+        <v>793</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>417</v>
+        <v>248</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>411</v>
+        <v>277</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="H59" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.020=作業用フォルダ：</v>
+        <f xml:space="preserve"> IF($C59="", "", $C59 &amp; "=" &amp; D59)</f>
+        <v>AppTaskBase.160=(比較対象ファイルなし)</v>
       </c>
       <c r="I59" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">excel.poi.usermodel.BookResultBookCreator.020=Working dir : </v>
+        <f xml:space="preserve"> IF($C59="", "", $C59 &amp; "=" &amp; E59)</f>
+        <v>AppTaskBase.160=(No files to compare)</v>
       </c>
       <c r="J59" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.020=工作文件夹：</v>
+        <f xml:space="preserve"> IF($C59="", "", $C59 &amp; "=" &amp; F59)</f>
+        <v>AppTaskBase.160=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="60" spans="2:10">
       <c r="B60" s="1" t="s">
-        <v>648</v>
+        <v>794</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>423</v>
+        <v>374</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>224</v>
+        <v>383</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>298</v>
+        <v>479</v>
       </c>
       <c r="H60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.030=ブック%s：</v>
+        <f xml:space="preserve"> IF($C60="", "", $C60 &amp; "=" &amp; D60)</f>
+        <v>AppTaskBase.170=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="I60" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">excel.poi.usermodel.BookResultBookCreator.030=Book %s : </v>
+        <f xml:space="preserve"> IF($C60="", "", $C60 &amp; "=" &amp; E60)</f>
+        <v>AppTaskBase.170=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="J60" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.030=工作簿%s：</v>
+        <f xml:space="preserve"> IF($C60="", "", $C60 &amp; "=" &amp; F60)</f>
+        <v>AppTaskBase.170=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
     </row>
     <row r="61" spans="2:10">
       <c r="B61" s="1" t="s">
-        <v>650</v>
+        <v>795</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>431</v>
+        <v>381</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>433</v>
+        <v>121</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>434</v>
+        <v>156</v>
       </c>
       <c r="H61" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.040=差分なし</v>
+        <f xml:space="preserve"> IF($C61="", "", $C61 &amp; "=" &amp; D61)</f>
+        <v>AppTaskBase.180=予期せぬ例外が発生しました。</v>
       </c>
       <c r="I61" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.040=No Diffs</v>
+        <f xml:space="preserve"> IF($C61="", "", $C61 &amp; "=" &amp; E61)</f>
+        <v>AppTaskBase.180=Unexpected exception occurred.</v>
       </c>
       <c r="J61" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.040=没有区别</v>
+        <f xml:space="preserve"> IF($C61="", "", $C61 &amp; "=" &amp; F61)</f>
+        <v>AppTaskBase.180=意外的例外。</v>
       </c>
     </row>
     <row r="62" spans="2:10">
       <c r="B62" s="1" t="s">
-        <v>652</v>
+        <v>796</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
       <c r="H62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.050=比較失敗</v>
+        <f xml:space="preserve"> IF($C62="", "", $C62 &amp; "=" &amp; D62)</f>
+        <v xml:space="preserve">AppTaskBase.200=比較実行日時 : </v>
       </c>
       <c r="I62" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.050=Comparison Failed</v>
+        <f xml:space="preserve"> IF($C62="", "", $C62 &amp; "=" &amp; E62)</f>
+        <v xml:space="preserve">AppTaskBase.200=Exec datetime : </v>
       </c>
       <c r="J62" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.050=比较失败</v>
+        <f xml:space="preserve"> IF($C62="", "", $C62 &amp; "=" &amp; F62)</f>
+        <v xml:space="preserve">AppTaskBase.200=执行日期和时间 : </v>
       </c>
     </row>
     <row r="63" spans="2:10">
       <c r="B63" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>451</v>
+        <v>797</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>452</v>
+        <v>215</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>459</v>
+        <v>354</v>
       </c>
       <c r="H63" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.060=余剰行（A: %d, B: %d）</v>
+        <f xml:space="preserve"> IF($C63="", "", $C63 &amp; "=" &amp; D63)</f>
+        <v>CompareBooksTask.010=ブック同士の比較を開始します。</v>
       </c>
       <c r="I63" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.060=Redundant Rows (A: %d, B: %d)</v>
+        <f xml:space="preserve"> IF($C63="", "", $C63 &amp; "=" &amp; E63)</f>
+        <v>CompareBooksTask.010=Starting comparing books.</v>
       </c>
       <c r="J63" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.060=冗余行（A: %d, B: %d）</v>
+        <f xml:space="preserve"> IF($C63="", "", $C63 &amp; "=" &amp; F63)</f>
+        <v>CompareBooksTask.010=开始互相比较工作簿。</v>
       </c>
     </row>
     <row r="64" spans="2:10">
       <c r="B64" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>453</v>
+        <v>798</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>455</v>
+        <v>127</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>457</v>
+        <v>355</v>
       </c>
       <c r="H64" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.070=余剰列（A: %d, B: %d）</v>
+        <f xml:space="preserve"> IF($C64="", "", $C64 &amp; "=" &amp; D64)</f>
+        <v>CompareBooksTask.040=シートを比較しています...</v>
       </c>
       <c r="I64" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.070=Redundant Columns (A: %d, B: %d)</v>
+        <f xml:space="preserve"> IF($C64="", "", $C64 &amp; "=" &amp; E64)</f>
+        <v>CompareBooksTask.040=Comparing sheets...</v>
       </c>
       <c r="J64" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.070=冗余列（A: %d, B: %d）</v>
+        <f xml:space="preserve"> IF($C64="", "", $C64 &amp; "=" &amp; F64)</f>
+        <v>CompareBooksTask.040=比较工作表...</v>
       </c>
     </row>
     <row r="65" spans="2:10">
       <c r="B65" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>454</v>
+        <v>799</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>456</v>
+        <v>128</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>458</v>
+        <v>356</v>
       </c>
       <c r="H65" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.080=差分セル（%d）</v>
+        <f xml:space="preserve"> IF($C65="", "", $C65 &amp; "=" &amp; D65)</f>
+        <v>CompareBooksTask.050=シートの比較に失敗しました。</v>
       </c>
       <c r="I65" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.080=Diff Cells (%d)</v>
+        <f xml:space="preserve"> IF($C65="", "", $C65 &amp; "=" &amp; E65)</f>
+        <v>CompareBooksTask.050=Failed to compare sheets.</v>
       </c>
       <c r="J65" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.080=差异单元格（%d）</v>
+        <f xml:space="preserve"> IF($C65="", "", $C65 &amp; "=" &amp; F65)</f>
+        <v>CompareBooksTask.050=工作表比较失败。</v>
       </c>
     </row>
     <row r="66" spans="2:10">
       <c r="B66" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>437</v>
+        <v>800</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>138</v>
+        <v>440</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>363</v>
+        <v>441</v>
       </c>
       <c r="H66" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.090=(比較相手なし)</v>
+        <f xml:space="preserve"> IF($C66="", "", $C66 &amp; "=" &amp; D66)</f>
+        <v>CompareBooksTask.060=比較結果レポートを保存しています...</v>
       </c>
       <c r="I66" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.090=(no opponent)</v>
+        <f xml:space="preserve"> IF($C66="", "", $C66 &amp; "=" &amp; E66)</f>
+        <v>CompareBooksTask.060=Saving result report...</v>
       </c>
       <c r="J66" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>excel.poi.usermodel.BookResultBookCreator.090=(没有对比)</v>
+        <f xml:space="preserve"> IF($C66="", "", $C66 &amp; "=" &amp; F66)</f>
+        <v>CompareBooksTask.060=保存比较结果报告...</v>
       </c>
     </row>
     <row r="67" spans="2:10">
+      <c r="B67" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>444</v>
+      </c>
       <c r="H67" s="4" t="str">
-        <f t="shared" ref="H67:H130" si="3" xml:space="preserve"> IF($C67="", "", $C67 &amp; "=" &amp; D67)</f>
-        <v/>
+        <f xml:space="preserve"> IF($C67="", "", $C67 &amp; "=" &amp; D67)</f>
+        <v>CompareBooksTask.070=比較結果レポートの保存に失敗しました。</v>
       </c>
       <c r="I67" s="5" t="str">
-        <f t="shared" ref="I67:I130" si="4" xml:space="preserve"> IF($C67="", "", $C67 &amp; "=" &amp; E67)</f>
-        <v/>
+        <f xml:space="preserve"> IF($C67="", "", $C67 &amp; "=" &amp; E67)</f>
+        <v>CompareBooksTask.070=Failed to save result report.</v>
       </c>
       <c r="J67" s="6" t="str">
-        <f t="shared" ref="J67:J130" si="5" xml:space="preserve"> IF($C67="", "", $C67 &amp; "=" &amp; F67)</f>
-        <v/>
+        <f xml:space="preserve"> IF($C67="", "", $C67 &amp; "=" &amp; F67)</f>
+        <v>CompareBooksTask.070=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="68" spans="2:10">
       <c r="B68" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>169</v>
+        <v>802</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>211</v>
+        <v>446</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>331</v>
+        <v>447</v>
       </c>
       <c r="H68" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.010=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
+        <f xml:space="preserve"> IF($C68="", "", $C68 &amp; "=" &amp; D68)</f>
+        <v>CompareBooksTask.080=比較結果レポートを表示しています...</v>
       </c>
       <c r="I68" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.010=Please specify different folders/books/sheets.</v>
+        <f xml:space="preserve"> IF($C68="", "", $C68 &amp; "=" &amp; E68)</f>
+        <v>CompareBooksTask.080=Opening result report...</v>
       </c>
       <c r="J68" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.010=指定非相同的文件夹／工作簿／工作表。</v>
+        <f xml:space="preserve"> IF($C68="", "", $C68 &amp; "=" &amp; F68)</f>
+        <v>CompareBooksTask.080=显示比较结果报告...</v>
       </c>
     </row>
     <row r="69" spans="2:10">
       <c r="B69" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>52</v>
+        <v>803</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>422</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>166</v>
+        <v>450</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>167</v>
+        <v>449</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>332</v>
+        <v>448</v>
       </c>
       <c r="H69" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.020=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
+        <f xml:space="preserve"> IF($C69="", "", $C69 &amp; "=" &amp; D69)</f>
+        <v>CompareBooksTask.090=比較結果レポートの表示に失敗しました。</v>
       </c>
       <c r="I69" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.020=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
+        <f xml:space="preserve"> IF($C69="", "", $C69 &amp; "=" &amp; E69)</f>
+        <v>CompareBooksTask.090=Failed to open result report.</v>
       </c>
       <c r="J69" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.020=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
+        <f xml:space="preserve"> IF($C69="", "", $C69 &amp; "=" &amp; F69)</f>
+        <v>CompareBooksTask.090=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="70" spans="2:10">
       <c r="B70" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>54</v>
+        <v>804</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>156</v>
+        <v>357</v>
       </c>
       <c r="H70" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.030=予期せぬ例外が発生しました。</v>
+        <f xml:space="preserve"> IF($C70="", "", $C70 &amp; "=" &amp; D70)</f>
+        <v>CompareDirsTask.010=フォルダ同士の比較を開始します。</v>
       </c>
       <c r="I70" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.030=Unexpected exception occurred.</v>
+        <f xml:space="preserve"> IF($C70="", "", $C70 &amp; "=" &amp; E70)</f>
+        <v>CompareDirsTask.010=Starting comparing folders.</v>
       </c>
       <c r="J70" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.030=意外的例外。</v>
+        <f xml:space="preserve"> IF($C70="", "", $C70 &amp; "=" &amp; F70)</f>
+        <v>CompareDirsTask.010=开始互相比较文件夹。</v>
       </c>
     </row>
     <row r="71" spans="2:10">
       <c r="B71" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>64</v>
+        <v>805</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>309</v>
+        <v>221</v>
       </c>
       <c r="H71" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.040=作業用フォルダの作成に失敗しました。</v>
+        <f xml:space="preserve"> IF($C71="", "", $C71 &amp; "=" &amp; D71)</f>
+        <v>CompareDirsTask.020=出力フォルダの作成に失敗しました。</v>
       </c>
       <c r="I71" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.040=Failed to create working directory.</v>
+        <f xml:space="preserve"> IF($C71="", "", $C71 &amp; "=" &amp; E71)</f>
+        <v>CompareDirsTask.020=Failed to create output directory.</v>
       </c>
       <c r="J71" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.040=创建工作文件夹失败。</v>
+        <f xml:space="preserve"> IF($C71="", "", $C71 &amp; "=" &amp; F71)</f>
+        <v>CompareDirsTask.020=创建输出目的地文件夹失败。</v>
       </c>
     </row>
     <row r="72" spans="2:10">
       <c r="B72" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>306</v>
+        <v>806</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>307</v>
+        <v>219</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>308</v>
+        <v>358</v>
       </c>
       <c r="H72" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.050=別の場所を指定してください。</v>
+        <f xml:space="preserve"> IF($C72="", "", $C72 &amp; "=" &amp; D72)</f>
+        <v>CompareDirsTask.050=Excelブックを比較しています...</v>
       </c>
       <c r="I72" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.050=Please specify another location.</v>
+        <f xml:space="preserve"> IF($C72="", "", $C72 &amp; "=" &amp; E72)</f>
+        <v>CompareDirsTask.050=Comparing books...</v>
       </c>
       <c r="J72" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.050=请指定其他位置。</v>
+        <f xml:space="preserve"> IF($C72="", "", $C72 &amp; "=" &amp; F72)</f>
+        <v>CompareDirsTask.050=比较工作簿...</v>
       </c>
     </row>
     <row r="73" spans="2:10">
       <c r="B73" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>47</v>
+        <v>807</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>118</v>
+        <v>277</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="H73" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.060=作業用フォルダの変更</v>
+        <f xml:space="preserve"> IF($C73="", "", $C73 &amp; "=" &amp; D73)</f>
+        <v>CompareDirsTask.070=(比較対象ファイルなし)</v>
       </c>
       <c r="I73" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.060=Change working directory</v>
+        <f xml:space="preserve"> IF($C73="", "", $C73 &amp; "=" &amp; E73)</f>
+        <v>CompareDirsTask.070=(No files to compare)</v>
       </c>
       <c r="J73" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.060=改变工作文件夹</v>
+        <f xml:space="preserve"> IF($C73="", "", $C73 &amp; "=" &amp; F73)</f>
+        <v>CompareDirsTask.070=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="74" spans="2:10">
       <c r="B74" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>310</v>
+        <v>808</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>390</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>312</v>
+        <v>385</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>311</v>
+        <v>387</v>
       </c>
       <c r="H74" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.MainController.070=処理を中止しました。</v>
+        <f xml:space="preserve"> IF($C74="", "", $C74 &amp; "=" &amp; D74)</f>
+        <v>CompareDirsTask.080=フォルダの比較に失敗しました。</v>
       </c>
       <c r="I74" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.MainController.070=Processing has been canceled.</v>
+        <f xml:space="preserve"> IF($C74="", "", $C74 &amp; "=" &amp; E74)</f>
+        <v>CompareDirsTask.080=Failed to compare folders.</v>
       </c>
       <c r="J74" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.MainController.070=处理已被取消。</v>
+        <f xml:space="preserve"> IF($C74="", "", $C74 &amp; "=" &amp; F74)</f>
+        <v>CompareDirsTask.080=文件夹比较失败。</v>
       </c>
     </row>
     <row r="75" spans="2:10">
       <c r="B75" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>55</v>
+        <v>809</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>195</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="H75" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.PasswordDialog.010=パスワード指定</v>
+        <f xml:space="preserve"> IF($C75="", "", $C75 &amp; "=" &amp; D75)</f>
+        <v>CompareSheetsTask.010=シート同士の比較を開始します。</v>
       </c>
       <c r="I75" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.PasswordDialog.010=Enter Password</v>
+        <f xml:space="preserve"> IF($C75="", "", $C75 &amp; "=" &amp; E75)</f>
+        <v>CompareSheetsTask.010=Starting comparing sheets.</v>
       </c>
       <c r="J75" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.PasswordDialog.010=输入密码</v>
+        <f xml:space="preserve"> IF($C75="", "", $C75 &amp; "=" &amp; F75)</f>
+        <v>CompareSheetsTask.010=开始相互比较工作表。</v>
       </c>
     </row>
     <row r="76" spans="2:10">
       <c r="B76" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>57</v>
+        <v>810</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="H76" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.PasswordDialogPane.010=%s はパスワードで保護されています。</v>
+        <f xml:space="preserve"> IF($C76="", "", $C76 &amp; "=" &amp; D76)</f>
+        <v>CompareSheetsTask.020=シートを比較しています...</v>
       </c>
       <c r="I76" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.PasswordDialogPane.010=The book [%s] is password protected.</v>
+        <f xml:space="preserve"> IF($C76="", "", $C76 &amp; "=" &amp; E76)</f>
+        <v>CompareSheetsTask.020=Comparing sheets...</v>
       </c>
       <c r="J76" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.PasswordDialogPane.010=%s 是受密码保护的。</v>
+        <f xml:space="preserve"> IF($C76="", "", $C76 &amp; "=" &amp; F76)</f>
+        <v>CompareSheetsTask.020=比较工作表...</v>
       </c>
     </row>
     <row r="77" spans="2:10">
       <c r="B77" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>564</v>
+        <v>811</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>770</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>565</v>
+        <v>66</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>568</v>
+        <v>128</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>569</v>
+        <v>386</v>
       </c>
       <c r="H77" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.UpdateChecker.010=新しいバージョンが利用可能です。</v>
+        <f xml:space="preserve"> IF($C77="", "", $C77 &amp; "=" &amp; D77)</f>
+        <v>CompareSheetsTask.030=シートの比較に失敗しました。</v>
       </c>
       <c r="I77" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.UpdateChecker.010=A new version is available.</v>
+        <f xml:space="preserve"> IF($C77="", "", $C77 &amp; "=" &amp; E77)</f>
+        <v>CompareSheetsTask.030=Failed to compare sheets.</v>
       </c>
       <c r="J77" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.UpdateChecker.010=有新版本可用。</v>
+        <f xml:space="preserve"> IF($C77="", "", $C77 &amp; "=" &amp; F77)</f>
+        <v>CompareSheetsTask.030=工作表比较失败。</v>
       </c>
     </row>
     <row r="78" spans="2:10">
       <c r="B78" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>611</v>
+        <v>812</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>606</v>
+        <v>266</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>607</v>
+        <v>361</v>
       </c>
       <c r="H78" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.UpdateChecker.020=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+        <f xml:space="preserve"> IF($C78="", "", $C78 &amp; "=" &amp; D78)</f>
+        <v>CompareTreesTask.010=フォルダツリー同士の比較を開始します。</v>
       </c>
       <c r="I78" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.UpdateChecker.020=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+        <f xml:space="preserve"> IF($C78="", "", $C78 &amp; "=" &amp; E78)</f>
+        <v>CompareTreesTask.010=Starting comparing folder trees.</v>
       </c>
       <c r="J78" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.UpdateChecker.020=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+        <f xml:space="preserve"> IF($C78="", "", $C78 &amp; "=" &amp; F78)</f>
+        <v>CompareTreesTask.010=开始互相比较文件夹树。</v>
       </c>
     </row>
     <row r="79" spans="2:10">
       <c r="B79" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>567</v>
+        <v>813</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>608</v>
+        <v>252</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>609</v>
+        <v>268</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="H79" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.UpdateChecker.030=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
+        <f xml:space="preserve"> IF($C79="", "", $C79 &amp; "=" &amp; D79)</f>
+        <v>CompareTreesTask.040=フォルダツリーを比較しています...</v>
       </c>
       <c r="I79" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.UpdateChecker.030=Your application is up to date.\n    - Current version : %s</v>
+        <f xml:space="preserve"> IF($C79="", "", $C79 &amp; "=" &amp; E79)</f>
+        <v>CompareTreesTask.040=Comparing folders...</v>
       </c>
       <c r="J79" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.UpdateChecker.030=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
+        <f xml:space="preserve"> IF($C79="", "", $C79 &amp; "=" &amp; F79)</f>
+        <v>CompareTreesTask.040=比较文件夹...</v>
       </c>
     </row>
     <row r="80" spans="2:10">
-      <c r="C80" s="2"/>
-      <c r="D80" s="3"/>
+      <c r="B80" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>353</v>
+      </c>
       <c r="H80" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f xml:space="preserve"> IF($C80="", "", $C80 &amp; "=" &amp; D80)</f>
+        <v>CompareTreesTask.050=★失敗しました</v>
       </c>
       <c r="I80" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f xml:space="preserve"> IF($C80="", "", $C80 &amp; "=" &amp; E80)</f>
+        <v>CompareTreesTask.050=★Failed</v>
       </c>
       <c r="J80" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f xml:space="preserve"> IF($C80="", "", $C80 &amp; "=" &amp; F80)</f>
+        <v>CompareTreesTask.050=★失败</v>
       </c>
     </row>
     <row r="81" spans="2:10">
       <c r="B81" s="1" t="s">
-        <v>731</v>
+        <v>815</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>32</v>
+        <v>281</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>33</v>
+        <v>439</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>114</v>
+        <v>440</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>336</v>
+        <v>441</v>
       </c>
       <c r="H81" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.LinkPane.010=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
+        <f xml:space="preserve"> IF($C81="", "", $C81 &amp; "=" &amp; D81)</f>
+        <v>CompareTreesTask.070=比較結果レポートを保存しています...</v>
       </c>
       <c r="I81" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.LinkPane.010=Failed to open the website. Please try using your browser.</v>
+        <f xml:space="preserve"> IF($C81="", "", $C81 &amp; "=" &amp; E81)</f>
+        <v>CompareTreesTask.070=Saving result report...</v>
       </c>
       <c r="J81" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.LinkPane.010=网页未能显示。 请尝试使用你的浏览器。</v>
+        <f xml:space="preserve"> IF($C81="", "", $C81 &amp; "=" &amp; F81)</f>
+        <v>CompareTreesTask.070=保存比较结果报告...</v>
       </c>
     </row>
     <row r="82" spans="2:10">
       <c r="B82" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>170</v>
+        <v>816</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>45</v>
+        <v>442</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>117</v>
+        <v>443</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>337</v>
+        <v>444</v>
       </c>
       <c r="H82" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.010=作業用フォルダの表示に失敗しました。</v>
+        <f xml:space="preserve"> IF($C82="", "", $C82 &amp; "=" &amp; D82)</f>
+        <v>CompareTreesTask.080=比較結果レポートの保存に失敗しました。</v>
       </c>
       <c r="I82" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.010=Failed to open working directory.</v>
+        <f xml:space="preserve"> IF($C82="", "", $C82 &amp; "=" &amp; E82)</f>
+        <v>CompareTreesTask.080=Failed to save result report.</v>
       </c>
       <c r="J82" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.010=显示工作文件夹失败。</v>
+        <f xml:space="preserve"> IF($C82="", "", $C82 &amp; "=" &amp; F82)</f>
+        <v>CompareTreesTask.080=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="83" spans="2:10">
       <c r="B83" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>44</v>
+        <v>817</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>47</v>
+        <v>445</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>118</v>
+        <v>446</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>333</v>
+        <v>447</v>
       </c>
       <c r="H83" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.020=作業用フォルダの変更</v>
+        <f xml:space="preserve"> IF($C83="", "", $C83 &amp; "=" &amp; D83)</f>
+        <v>CompareTreesTask.090=比較結果レポートを表示しています...</v>
       </c>
       <c r="I83" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.020=Change working directory</v>
+        <f xml:space="preserve"> IF($C83="", "", $C83 &amp; "=" &amp; E83)</f>
+        <v>CompareTreesTask.090=Opening result report...</v>
       </c>
       <c r="J83" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.020=改变工作文件夹</v>
+        <f xml:space="preserve"> IF($C83="", "", $C83 &amp; "=" &amp; F83)</f>
+        <v>CompareTreesTask.090=显示比较结果报告...</v>
       </c>
     </row>
     <row r="84" spans="2:10">
       <c r="B84" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>46</v>
+        <v>818</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>450</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>338</v>
+        <v>448</v>
       </c>
       <c r="H84" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.030=作業用フォルダの変更に失敗しました。</v>
+        <f xml:space="preserve"> IF($C84="", "", $C84 &amp; "=" &amp; D84)</f>
+        <v>CompareTreesTask.100=比較結果レポートの表示に失敗しました。</v>
       </c>
       <c r="I84" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.030=Failed to change working directory.</v>
+        <f xml:space="preserve"> IF($C84="", "", $C84 &amp; "=" &amp; E84)</f>
+        <v>CompareTreesTask.100=Failed to open result report.</v>
       </c>
       <c r="J84" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.030=更改工作文件夹失败。</v>
+        <f xml:space="preserve"> IF($C84="", "", $C84 &amp; "=" &amp; F84)</f>
+        <v>CompareTreesTask.100=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="85" spans="2:10">
       <c r="B85" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>50</v>
+        <v>819</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>120</v>
+        <v>391</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="H85" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.040=次のフォルダの内容物を全て削除します。よろしいですか？</v>
+        <f xml:space="preserve"> IF($C85="", "", $C85 &amp; "=" &amp; D85)</f>
+        <v>CompareTreesTask.110=フォルダツリーの比較に失敗しました。</v>
       </c>
       <c r="I85" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.040=Delete all contents of the following directory. Are you sure?</v>
+        <f xml:space="preserve"> IF($C85="", "", $C85 &amp; "=" &amp; E85)</f>
+        <v>CompareTreesTask.110=Failed to compare folder trees.</v>
       </c>
       <c r="J85" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.040=删除以下文件夹的所有内容。你确定吗？</v>
+        <f xml:space="preserve"> IF($C85="", "", $C85 &amp; "=" &amp; F85)</f>
+        <v>CompareTreesTask.110=文件夹比较失败。</v>
       </c>
     </row>
     <row r="86" spans="2:10">
       <c r="B86" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>171</v>
+        <v>820</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>41</v>
+        <v>363</v>
       </c>
       <c r="H86" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.051=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f xml:space="preserve"> IF($C86="", "", $C86 &amp; "=" &amp; D86)</f>
+        <v>excel.BResult.010=(比較相手なし)</v>
       </c>
       <c r="I86" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.051=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f xml:space="preserve"> IF($C86="", "", $C86 &amp; "=" &amp; E86)</f>
+        <v>excel.BResult.010=(no opponent)</v>
       </c>
       <c r="J86" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.051=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f xml:space="preserve"> IF($C86="", "", $C86 &amp; "=" &amp; F86)</f>
+        <v>excel.BResult.010=(没有对比)</v>
       </c>
     </row>
     <row r="87" spans="2:10">
       <c r="B87" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>172</v>
+        <v>821</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>42</v>
+        <v>364</v>
       </c>
       <c r="H87" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.052=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f xml:space="preserve"> IF($C87="", "", $C87 &amp; "=" &amp; D87)</f>
+        <v>excel.BResult.020=(差分なし)</v>
       </c>
       <c r="I87" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.052=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f xml:space="preserve"> IF($C87="", "", $C87 &amp; "=" &amp; E87)</f>
+        <v>excel.BResult.020=(no diffs)</v>
       </c>
       <c r="J87" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.052=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f xml:space="preserve"> IF($C87="", "", $C87 &amp; "=" &amp; F87)</f>
+        <v>excel.BResult.020=(没有区别)</v>
       </c>
     </row>
     <row r="88" spans="2:10">
       <c r="B88" s="1" t="s">
-        <v>738</v>
+        <v>822</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="H88" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.053=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f xml:space="preserve"> IF($C88="", "", $C88 &amp; "=" &amp; D88)</f>
+        <v>excel.BResult.030=差異発生%dシート</v>
       </c>
       <c r="I88" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.053=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f xml:space="preserve"> IF($C88="", "", $C88 &amp; "=" &amp; E88)</f>
+        <v>excel.BResult.030=diff sheets:%d</v>
       </c>
       <c r="J88" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.053=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f xml:space="preserve"> IF($C88="", "", $C88 &amp; "=" &amp; F88)</f>
+        <v>excel.BResult.030=差异工作表%d</v>
       </c>
     </row>
     <row r="89" spans="2:10">
       <c r="B89" s="1" t="s">
-        <v>739</v>
+        <v>823</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>571</v>
+        <v>81</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>572</v>
+        <v>223</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>573</v>
+        <v>225</v>
       </c>
       <c r="H89" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.SettingsPane2.060=方眼Diff  -  詳細設定</v>
+        <f xml:space="preserve"> IF($C89="", "", $C89 &amp; "=" &amp; D89)</f>
+        <v>excel.BResult.040=余剰%dシート</v>
       </c>
       <c r="I89" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.SettingsPane2.060=HoganDiff  -  Advanced Settings</v>
+        <f xml:space="preserve"> IF($C89="", "", $C89 &amp; "=" &amp; E89)</f>
+        <v>excel.BResult.040=redundant sheets:%d</v>
       </c>
       <c r="J89" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.SettingsPane2.060=方眼Diff  -  详细设置</v>
+        <f xml:space="preserve"> IF($C89="", "", $C89 &amp; "=" &amp; F89)</f>
+        <v>excel.BResult.040=冗余工作表%d</v>
       </c>
     </row>
     <row r="90" spans="2:10">
       <c r="B90" s="1" t="s">
-        <v>741</v>
+        <v>824</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>174</v>
+        <v>83</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>340</v>
+        <v>298</v>
       </c>
       <c r="H90" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.TargetSelectionPane.010=比較対象フォルダの選択</v>
+        <f xml:space="preserve"> IF($C90="", "", $C90 &amp; "=" &amp; D90)</f>
+        <v xml:space="preserve">excel.BResult.050=ブック%s : </v>
       </c>
       <c r="I90" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.TargetSelectionPane.010=Select comparison folder</v>
+        <f xml:space="preserve"> IF($C90="", "", $C90 &amp; "=" &amp; E90)</f>
+        <v xml:space="preserve">excel.BResult.050=Book %s : </v>
       </c>
       <c r="J90" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.TargetSelectionPane.010=选择用于比较的文件夹</v>
+        <f xml:space="preserve"> IF($C90="", "", $C90 &amp; "=" &amp; F90)</f>
+        <v>excel.BResult.050=工作簿%s：</v>
       </c>
     </row>
     <row r="91" spans="2:10">
       <c r="B91" s="1" t="s">
-        <v>742</v>
+        <v>825</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>35</v>
+        <v>199</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
       <c r="H91" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.TargetSelectionPane.020=比較対象ブックの選択</v>
+        <f xml:space="preserve"> IF($C91="", "", $C91 &amp; "=" &amp; D91)</f>
+        <v>excel.BResult.060=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="I91" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.TargetSelectionPane.020=Select comparison book</v>
+        <f xml:space="preserve"> IF($C91="", "", $C91 &amp; "=" &amp; E91)</f>
+        <v>excel.BResult.060=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="J91" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.TargetSelectionPane.020=选择用于比较的工作簿</v>
+        <f xml:space="preserve"> IF($C91="", "", $C91 &amp; "=" &amp; F91)</f>
+        <v>excel.BResult.060=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="92" spans="2:10">
       <c r="B92" s="1" t="s">
-        <v>743</v>
+        <v>826</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>37</v>
+        <v>200</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>155</v>
+        <v>366</v>
       </c>
       <c r="H92" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.TargetSelectionPane.030=Excel ブック</v>
+        <f xml:space="preserve"> IF($C92="", "", $C92 &amp; "=" &amp; D92)</f>
+        <v>excel.BResult.070=■差分詳細 -----------------------------------------------------</v>
       </c>
       <c r="I92" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.TargetSelectionPane.030=Excel book</v>
+        <f xml:space="preserve"> IF($C92="", "", $C92 &amp; "=" &amp; E92)</f>
+        <v>excel.BResult.070=## DETAIL ------------------------------------------------------</v>
       </c>
       <c r="J92" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.TargetSelectionPane.030=Excel工作簿</v>
+        <f xml:space="preserve"> IF($C92="", "", $C92 &amp; "=" &amp; F92)</f>
+        <v>excel.BResult.070=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="93" spans="2:10">
       <c r="B93" s="1" t="s">
-        <v>744</v>
+        <v>827</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="H93" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.TargetSelectionPane.040=ファイルを読み込めません：</v>
+        <f xml:space="preserve"> IF($C93="", "", $C93 &amp; "=" &amp; D93)</f>
+        <v>excel.DResult.010=(比較相手なし)</v>
       </c>
       <c r="I93" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">gui.component.TargetSelectionPane.040=Failed to open file : </v>
+        <f xml:space="preserve"> IF($C93="", "", $C93 &amp; "=" &amp; E93)</f>
+        <v>excel.DResult.010=(no opponent)</v>
       </c>
       <c r="J93" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.TargetSelectionPane.040=无法读取文件：</v>
+        <f xml:space="preserve"> IF($C93="", "", $C93 &amp; "=" &amp; F93)</f>
+        <v>excel.DResult.010=(没有对比)</v>
       </c>
     </row>
     <row r="94" spans="2:10">
       <c r="B94" s="1" t="s">
-        <v>745</v>
+        <v>828</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>36</v>
+        <v>202</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="H94" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.TargetSelectionPane.050=シートが見つかりません：</v>
+        <f xml:space="preserve"> IF($C94="", "", $C94 &amp; "=" &amp; D94)</f>
+        <v xml:space="preserve">excel.DResult.020=フォルダ%s : </v>
       </c>
       <c r="I94" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">gui.component.TargetSelectionPane.050=No such sheet : </v>
+        <f xml:space="preserve"> IF($C94="", "", $C94 &amp; "=" &amp; E94)</f>
+        <v xml:space="preserve">excel.DResult.020=Folder %s : </v>
       </c>
       <c r="J94" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.TargetSelectionPane.050=没有找到工作表：</v>
+        <f xml:space="preserve"> IF($C94="", "", $C94 &amp; "=" &amp; F94)</f>
+        <v xml:space="preserve">excel.DResult.020=文件夹%s : </v>
       </c>
     </row>
     <row r="95" spans="2:10">
       <c r="B95" s="1" t="s">
-        <v>746</v>
+        <v>829</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>392</v>
+        <v>203</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>394</v>
+        <v>140</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>395</v>
+        <v>157</v>
       </c>
       <c r="H95" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.TargetSelectionPane.060=フォルダを読み込めません：</v>
+        <f xml:space="preserve"> IF($C95="", "", $C95 &amp; "=" &amp; D95)</f>
+        <v>excel.DResult.030=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="I95" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">gui.component.TargetSelectionPane.060=Failed to open folder : </v>
+        <f xml:space="preserve"> IF($C95="", "", $C95 &amp; "=" &amp; E95)</f>
+        <v>excel.DResult.030=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="J95" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.TargetSelectionPane.060=无法读取文件夹：</v>
+        <f xml:space="preserve"> IF($C95="", "", $C95 &amp; "=" &amp; F95)</f>
+        <v>excel.DResult.030=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="96" spans="2:10">
+      <c r="B96" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>366</v>
+      </c>
       <c r="H96" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f xml:space="preserve"> IF($C96="", "", $C96 &amp; "=" &amp; D96)</f>
+        <v>excel.DResult.040=■差分詳細 -----------------------------------------------------</v>
       </c>
       <c r="I96" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f xml:space="preserve"> IF($C96="", "", $C96 &amp; "=" &amp; E96)</f>
+        <v>excel.DResult.040=## DETAIL ------------------------------------------------------</v>
       </c>
       <c r="J96" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f xml:space="preserve"> IF($C96="", "", $C96 &amp; "=" &amp; F96)</f>
+        <v>excel.DResult.040=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="97" spans="2:10">
       <c r="B97" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>466</v>
+        <v>831</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>467</v>
+        <v>194</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>468</v>
+        <v>220</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>470</v>
+        <v>353</v>
       </c>
       <c r="H97" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.010=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
+        <f xml:space="preserve"> IF($C97="", "", $C97 &amp; "=" &amp; D97)</f>
+        <v>excel.DResult.050=★失敗しました</v>
       </c>
       <c r="I97" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.010=Disconnect HoganDiff from Google Drive. Are you sure?</v>
+        <f xml:space="preserve"> IF($C97="", "", $C97 &amp; "=" &amp; E97)</f>
+        <v>excel.DResult.050=★Failed</v>
       </c>
       <c r="J97" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.010=解除方眼Diff与Google Drive的关联。确定吗？</v>
+        <f xml:space="preserve"> IF($C97="", "", $C97 &amp; "=" &amp; F97)</f>
+        <v>excel.DResult.050=★失败</v>
       </c>
     </row>
     <row r="98" spans="2:10">
       <c r="B98" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>473</v>
+        <v>832</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>474</v>
+        <v>139</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>475</v>
+        <v>364</v>
       </c>
       <c r="H98" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.020=資格情報を削除しました。</v>
+        <f xml:space="preserve"> IF($C98="", "", $C98 &amp; "=" &amp; D98)</f>
+        <v>excel.DResult.060=(差分なし)</v>
       </c>
       <c r="I98" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.020=Credentials have been deleted.</v>
+        <f xml:space="preserve"> IF($C98="", "", $C98 &amp; "=" &amp; E98)</f>
+        <v>excel.DResult.060=(no diffs)</v>
       </c>
       <c r="J98" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.020=已删除凭据。</v>
+        <f xml:space="preserve"> IF($C98="", "", $C98 &amp; "=" &amp; F98)</f>
+        <v>excel.DResult.060=(没有区别)</v>
       </c>
     </row>
     <row r="99" spans="2:10">
       <c r="B99" s="1" t="s">
-        <v>717</v>
+        <v>833</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>481</v>
+        <v>254</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>476</v>
+        <v>255</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>477</v>
+        <v>270</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>478</v>
+        <v>368</v>
       </c>
       <c r="H99" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.030=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
+        <f xml:space="preserve"> IF($C99="", "", $C99 &amp; "=" &amp; D99)</f>
+        <v>excel.DResult.070=差異発生%dブック</v>
       </c>
       <c r="I99" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.030=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
+        <f xml:space="preserve"> IF($C99="", "", $C99 &amp; "=" &amp; E99)</f>
+        <v>excel.DResult.070=diff books:%d</v>
       </c>
       <c r="J99" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.030=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
+        <f xml:space="preserve"> IF($C99="", "", $C99 &amp; "=" &amp; F99)</f>
+        <v>excel.DResult.070=差异工作簿%d</v>
       </c>
     </row>
     <row r="100" spans="2:10">
       <c r="B100" s="1" t="s">
-        <v>719</v>
+        <v>834</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>483</v>
+        <v>256</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>482</v>
+        <v>257</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>486</v>
+        <v>271</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>487</v>
+        <v>272</v>
       </c>
       <c r="H100" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.040=資格情報の削除に失敗しました。</v>
+        <f xml:space="preserve"> IF($C100="", "", $C100 &amp; "=" &amp; D100)</f>
+        <v>excel.DResult.080=余剰%dブック</v>
       </c>
       <c r="I100" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.040=Failed to delete credentials.</v>
+        <f xml:space="preserve"> IF($C100="", "", $C100 &amp; "=" &amp; E100)</f>
+        <v>excel.DResult.080=redundant books:%d</v>
       </c>
       <c r="J100" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.040=删除凭据失败。</v>
+        <f xml:space="preserve"> IF($C100="", "", $C100 &amp; "=" &amp; F100)</f>
+        <v>excel.DResult.080=冗余工作簿%d</v>
       </c>
     </row>
     <row r="101" spans="2:10">
       <c r="B101" s="1" t="s">
-        <v>721</v>
+        <v>835</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>485</v>
+        <v>258</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>484</v>
+        <v>259</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>488</v>
+        <v>273</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>489</v>
+        <v>274</v>
       </c>
       <c r="H101" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.050=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f xml:space="preserve"> IF($C101="", "", $C101 &amp; "=" &amp; D101)</f>
+        <v>excel.DResult.090=比較失敗%dブック</v>
       </c>
       <c r="I101" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.050=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
+        <f xml:space="preserve"> IF($C101="", "", $C101 &amp; "=" &amp; E101)</f>
+        <v>excel.DResult.090=failed books:%d</v>
       </c>
       <c r="J101" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.050=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
+        <f xml:space="preserve"> IF($C101="", "", $C101 &amp; "=" &amp; F101)</f>
+        <v>excel.DResult.090=失败工作簿%d</v>
       </c>
     </row>
     <row r="102" spans="2:10">
       <c r="B102" s="1" t="s">
-        <v>723</v>
+        <v>836</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>491</v>
+        <v>260</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>490</v>
+        <v>249</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>492</v>
+        <v>277</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>493</v>
+        <v>278</v>
       </c>
       <c r="H102" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.060=Google連携エラー</v>
+        <f xml:space="preserve"> IF($C102="", "", $C102 &amp; "=" &amp; D102)</f>
+        <v>excel.DResult.100=(比較対象ファイルなし)</v>
       </c>
       <c r="I102" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.060=Google Integration Error</v>
+        <f xml:space="preserve"> IF($C102="", "", $C102 &amp; "=" &amp; E102)</f>
+        <v>excel.DResult.100=(No files to compare)</v>
       </c>
       <c r="J102" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.060=Google关联错误</v>
+        <f xml:space="preserve"> IF($C102="", "", $C102 &amp; "=" &amp; F102)</f>
+        <v>excel.DResult.100=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="103" spans="2:10">
       <c r="B103" s="1" t="s">
-        <v>725</v>
+        <v>837</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>497</v>
+        <v>416</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>494</v>
+        <v>424</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>495</v>
+        <v>438</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>496</v>
+        <v>425</v>
       </c>
       <c r="H103" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.070=Google連携処理中にエラーが発生しました。</v>
+        <f xml:space="preserve"> IF($C103="", "", $C103 &amp; "=" &amp; D103)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.010=比較実行日時：</v>
       </c>
       <c r="I103" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.070=An error occurred during Google integration processing.</v>
+        <f xml:space="preserve"> IF($C103="", "", $C103 &amp; "=" &amp; E103)</f>
+        <v xml:space="preserve">excel.poi.usermodel.BookResultBookCreator.010=Exec datetime : </v>
       </c>
       <c r="J103" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.070=Google关联处理过程中发生错误。</v>
+        <f xml:space="preserve"> IF($C103="", "", $C103 &amp; "=" &amp; F103)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.010=执行日期和时间：</v>
       </c>
     </row>
     <row r="104" spans="2:10">
       <c r="B104" s="1" t="s">
-        <v>727</v>
+        <v>838</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>501</v>
+        <v>417</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>498</v>
+        <v>286</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>499</v>
+        <v>411</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>500</v>
+        <v>294</v>
       </c>
       <c r="H104" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.080=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f xml:space="preserve"> IF($C104="", "", $C104 &amp; "=" &amp; D104)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.020=作業用フォルダ：</v>
       </c>
       <c r="I104" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.080=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
+        <f xml:space="preserve"> IF($C104="", "", $C104 &amp; "=" &amp; E104)</f>
+        <v xml:space="preserve">excel.poi.usermodel.BookResultBookCreator.020=Working dir : </v>
       </c>
       <c r="J104" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.080=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
+        <f xml:space="preserve"> IF($C104="", "", $C104 &amp; "=" &amp; F104)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.020=工作文件夹：</v>
       </c>
     </row>
     <row r="105" spans="2:10">
       <c r="B105" s="1" t="s">
-        <v>729</v>
+        <v>839</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>529</v>
+        <v>423</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>418</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>537</v>
+        <v>224</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>538</v>
+        <v>298</v>
       </c>
       <c r="H105" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.component.GooglePane.090=Googleドライブからファイルをダウンロードしました。</v>
+        <f xml:space="preserve"> IF($C105="", "", $C105 &amp; "=" &amp; D105)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.030=ブック%s：</v>
       </c>
       <c r="I105" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.component.GooglePane.090=File downloaded from Google Drive</v>
+        <f xml:space="preserve"> IF($C105="", "", $C105 &amp; "=" &amp; E105)</f>
+        <v xml:space="preserve">excel.poi.usermodel.BookResultBookCreator.030=Book %s : </v>
       </c>
       <c r="J105" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.component.GooglePane.090=已从Google云端硬盘下载文件</v>
+        <f xml:space="preserve"> IF($C105="", "", $C105 &amp; "=" &amp; F105)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.030=工作簿%s：</v>
       </c>
     </row>
     <row r="106" spans="2:10">
+      <c r="B106" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>434</v>
+      </c>
       <c r="H106" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f xml:space="preserve"> IF($C106="", "", $C106 &amp; "=" &amp; D106)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.040=差分なし</v>
       </c>
       <c r="I106" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f xml:space="preserve"> IF($C106="", "", $C106 &amp; "=" &amp; E106)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.040=No Diffs</v>
       </c>
       <c r="J106" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f xml:space="preserve"> IF($C106="", "", $C106 &amp; "=" &amp; F106)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.040=没有区别</v>
       </c>
     </row>
     <row r="107" spans="2:10">
       <c r="B107" s="1" t="s">
-        <v>748</v>
+        <v>841</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>575</v>
+        <v>427</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>432</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>577</v>
+        <v>436</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>576</v>
+        <v>435</v>
       </c>
       <c r="H107" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>gui.dialogs.SettingDetailsDialogPane.010=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
+        <f xml:space="preserve"> IF($C107="", "", $C107 &amp; "=" &amp; D107)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.050=比較失敗</v>
       </c>
       <c r="I107" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>gui.dialogs.SettingDetailsDialogPane.010=Initialize settings and exit the application.\nAre you sure?</v>
+        <f xml:space="preserve"> IF($C107="", "", $C107 &amp; "=" &amp; E107)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.050=Comparison Failed</v>
       </c>
       <c r="J107" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>gui.dialogs.SettingDetailsDialogPane.010=初始化设置并退出应用程序。\n确定吗？</v>
+        <f xml:space="preserve"> IF($C107="", "", $C107 &amp; "=" &amp; F107)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.050=比较失败</v>
       </c>
     </row>
     <row r="108" spans="2:10">
+      <c r="B108" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>459</v>
+      </c>
       <c r="H108" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f xml:space="preserve"> IF($C108="", "", $C108 &amp; "=" &amp; D108)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.060=余剰行（A: %d, B: %d）</v>
       </c>
       <c r="I108" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f xml:space="preserve"> IF($C108="", "", $C108 &amp; "=" &amp; E108)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.060=Redundant Rows (A: %d, B: %d)</v>
       </c>
       <c r="J108" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f xml:space="preserve"> IF($C108="", "", $C108 &amp; "=" &amp; F108)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.060=冗余行（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="109" spans="2:10">
       <c r="B109" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>59</v>
+        <v>843</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>453</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>124</v>
+        <v>455</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="H109" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppMain.010=方眼Diff</v>
+        <f xml:space="preserve"> IF($C109="", "", $C109 &amp; "=" &amp; D109)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.070=余剰列（A: %d, B: %d）</v>
       </c>
       <c r="I109" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppMain.010=HoganDiff (方眼Diff)</v>
+        <f xml:space="preserve"> IF($C109="", "", $C109 &amp; "=" &amp; E109)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.070=Redundant Columns (A: %d, B: %d)</v>
       </c>
       <c r="J109" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppMain.010=方眼Diff</v>
+        <f xml:space="preserve"> IF($C109="", "", $C109 &amp; "=" &amp; F109)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.070=冗余列（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="110" spans="2:10">
       <c r="B110" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>61</v>
+        <v>844</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>454</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>125</v>
+        <v>456</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>343</v>
+        <v>458</v>
       </c>
       <c r="H110" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppResource.010=設定の保存に失敗しました。</v>
+        <f xml:space="preserve"> IF($C110="", "", $C110 &amp; "=" &amp; D110)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.080=差分セル（%d）</v>
       </c>
       <c r="I110" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppResource.010=Failed to save settings.</v>
+        <f xml:space="preserve"> IF($C110="", "", $C110 &amp; "=" &amp; E110)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.080=Diff Cells (%d)</v>
       </c>
       <c r="J110" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppResource.010=保存设置失败。</v>
+        <f xml:space="preserve"> IF($C110="", "", $C110 &amp; "=" &amp; F110)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.080=差异单元格（%d）</v>
       </c>
     </row>
     <row r="111" spans="2:10">
-      <c r="C111" s="2"/>
-      <c r="D111" s="3"/>
+      <c r="B111" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>363</v>
+      </c>
       <c r="H111" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f xml:space="preserve"> IF($C111="", "", $C111 &amp; "=" &amp; D111)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.090=(比較相手なし)</v>
       </c>
       <c r="I111" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f xml:space="preserve"> IF($C111="", "", $C111 &amp; "=" &amp; E111)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.090=(no opponent)</v>
       </c>
       <c r="J111" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f xml:space="preserve"> IF($C111="", "", $C111 &amp; "=" &amp; F111)</f>
+        <v>excel.poi.usermodel.BookResultBookCreator.090=(没有对比)</v>
       </c>
     </row>
     <row r="112" spans="2:10">
       <c r="B112" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>67</v>
+        <v>846</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="H112" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.030=比較結果テキストを保存しています...</v>
+        <f xml:space="preserve"> IF($C112="", "", $C112 &amp; "=" &amp; D112)</f>
+        <v>excel.poi.usermodel.TreeResultBookCreator.010=比較フォルダ%s：</v>
       </c>
       <c r="I112" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.030=Saving result text...</v>
+        <f xml:space="preserve"> IF($C112="", "", $C112 &amp; "=" &amp; E112)</f>
+        <v xml:space="preserve">excel.poi.usermodel.TreeResultBookCreator.010=Folder %s : </v>
       </c>
       <c r="J112" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.030=存储比较结果文本...</v>
+        <f xml:space="preserve"> IF($C112="", "", $C112 &amp; "=" &amp; F112)</f>
+        <v>excel.poi.usermodel.TreeResultBookCreator.010=文件夹%s：</v>
       </c>
     </row>
     <row r="113" spans="2:10">
       <c r="B113" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>68</v>
+        <v>847</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>286</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>130</v>
+        <v>411</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="H113" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.050=比較結果テキストの保存と表示に失敗しました。</v>
+        <f xml:space="preserve"> IF($C113="", "", $C113 &amp; "=" &amp; D113)</f>
+        <v>excel.poi.usermodel.TreeResultBookCreator.020=作業用フォルダ：</v>
       </c>
       <c r="I113" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.050=Failed to save or open result text.</v>
+        <f xml:space="preserve"> IF($C113="", "", $C113 &amp; "=" &amp; E113)</f>
+        <v xml:space="preserve">excel.poi.usermodel.TreeResultBookCreator.020=Working dir : </v>
       </c>
       <c r="J113" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.050=保存和显示比较结果文本失败。</v>
+        <f xml:space="preserve"> IF($C113="", "", $C113 &amp; "=" &amp; F113)</f>
+        <v>excel.poi.usermodel.TreeResultBookCreator.020=工作文件夹：</v>
       </c>
     </row>
     <row r="114" spans="2:10">
       <c r="B114" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>178</v>
+        <v>848</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>765</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>346</v>
+        <v>158</v>
       </c>
       <c r="H114" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.060=Excelブックに比較結果の色を付けて保存しています...</v>
+        <f xml:space="preserve"> IF($C114="", "", $C114 &amp; "=" &amp; D114)</f>
+        <v>excel.SheetType.010=ワークシート</v>
       </c>
       <c r="I114" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.060=Painting and saving result book(s)...</v>
+        <f xml:space="preserve"> IF($C114="", "", $C114 &amp; "=" &amp; E114)</f>
+        <v>excel.SheetType.010=Worksheet</v>
       </c>
       <c r="J114" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.060=着色和存储在工作簿...</v>
+        <f xml:space="preserve"> IF($C114="", "", $C114 &amp; "=" &amp; F114)</f>
+        <v>excel.SheetType.010=工作表</v>
       </c>
     </row>
     <row r="115" spans="2:10">
       <c r="B115" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>179</v>
+        <v>849</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="H115" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.070=Excelブックの着色・保存に失敗しました。</v>
+        <f xml:space="preserve"> IF($C115="", "", $C115 &amp; "=" &amp; D115)</f>
+        <v>excel.SheetType.020=グラフシート</v>
       </c>
       <c r="I115" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.070=Failed to paint or save result book(s).</v>
+        <f xml:space="preserve"> IF($C115="", "", $C115 &amp; "=" &amp; E115)</f>
+        <v>excel.SheetType.020=Chart</v>
       </c>
       <c r="J115" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.070=着色和保存工作簿失败。</v>
+        <f xml:space="preserve"> IF($C115="", "", $C115 &amp; "=" &amp; F115)</f>
+        <v>excel.SheetType.020=图表表</v>
       </c>
     </row>
     <row r="116" spans="2:10">
       <c r="B116" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>180</v>
+        <v>850</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="H116" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.080=比較結果のExcelブックを表示しています...</v>
+        <f xml:space="preserve"> IF($C116="", "", $C116 &amp; "=" &amp; D116)</f>
+        <v>excel.SheetType.030=MS Excel 5.0 ダイアログシート</v>
       </c>
       <c r="I116" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.080=Opening result book(s)...</v>
+        <f xml:space="preserve"> IF($C116="", "", $C116 &amp; "=" &amp; E116)</f>
+        <v>excel.SheetType.030=MS Excel 5.0 Dialog</v>
       </c>
       <c r="J116" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.080=显示比较结果的工作簿...</v>
+        <f xml:space="preserve"> IF($C116="", "", $C116 &amp; "=" &amp; F116)</f>
+        <v>excel.SheetType.030=MS Excel 5.0 对话表</v>
       </c>
     </row>
     <row r="117" spans="2:10">
       <c r="B117" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>181</v>
+        <v>851</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
       <c r="H117" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.090=Excelブックの表示に失敗しました。</v>
+        <f xml:space="preserve"> IF($C117="", "", $C117 &amp; "=" &amp; D117)</f>
+        <v>excel.SheetType.040=Excel 4.0 マクロシート</v>
       </c>
       <c r="I117" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.090=Failed to open result book(s).</v>
+        <f xml:space="preserve"> IF($C117="", "", $C117 &amp; "=" &amp; E117)</f>
+        <v>excel.SheetType.040=Excel 4.0 Macro</v>
       </c>
       <c r="J117" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.090=显示工作簿失败。</v>
+        <f xml:space="preserve"> IF($C117="", "", $C117 &amp; "=" &amp; F117)</f>
+        <v>excel.SheetType.040=Excel 4.0 宏表</v>
       </c>
     </row>
     <row r="118" spans="2:10">
       <c r="B118" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>182</v>
+        <v>852</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="H118" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.100=ExcelブックAの着色・保存に失敗しました。</v>
+        <f xml:space="preserve"> IF($C118="", "", $C118 &amp; "=" &amp; D118)</f>
+        <v>excel.SResult.010=(差分なし)</v>
       </c>
       <c r="I118" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.100=Failed to paint or save result book A.</v>
+        <f xml:space="preserve"> IF($C118="", "", $C118 &amp; "=" &amp; E118)</f>
+        <v>excel.SResult.010=(no diffs)</v>
       </c>
       <c r="J118" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.100=工作簿A的着色和保存失败。</v>
+        <f xml:space="preserve"> IF($C118="", "", $C118 &amp; "=" &amp; F118)</f>
+        <v>excel.SResult.010=(没有区别)</v>
       </c>
     </row>
     <row r="119" spans="2:10">
       <c r="B119" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>183</v>
+        <v>853</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>351</v>
+        <v>160</v>
       </c>
       <c r="H119" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.110=ExcelブックBの着色・保存に失敗しました。</v>
+        <f xml:space="preserve"> IF($C119="", "", $C119 &amp; "=" &amp; D119)</f>
+        <v>excel.SResult.020=余剰行%d</v>
       </c>
       <c r="I119" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.110=Failed to paint or save result book B.</v>
+        <f xml:space="preserve"> IF($C119="", "", $C119 &amp; "=" &amp; E119)</f>
+        <v>excel.SResult.020=redundant rows:%d</v>
       </c>
       <c r="J119" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.110=工作簿B的着色和保存失败。</v>
+        <f xml:space="preserve"> IF($C119="", "", $C119 &amp; "=" &amp; F119)</f>
+        <v>excel.SResult.020=冗余行%d</v>
       </c>
     </row>
     <row r="120" spans="2:10">
       <c r="B120" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>184</v>
+        <v>854</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>352</v>
+        <v>161</v>
       </c>
       <c r="H120" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.120=処理が完了しました。</v>
+        <f xml:space="preserve"> IF($C120="", "", $C120 &amp; "=" &amp; D120)</f>
+        <v>excel.SResult.030=余剰列%d</v>
       </c>
       <c r="I120" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.120=Process completed.</v>
+        <f xml:space="preserve"> IF($C120="", "", $C120 &amp; "=" &amp; E120)</f>
+        <v>excel.SResult.030=redundant columns:%d</v>
       </c>
       <c r="J120" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.120=过程完成。</v>
+        <f xml:space="preserve"> IF($C120="", "", $C120 &amp; "=" &amp; F120)</f>
+        <v>excel.SResult.030=冗余列%d</v>
       </c>
     </row>
     <row r="121" spans="2:10">
       <c r="B121" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>194</v>
+        <v>855</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="H121" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.150=★失敗しました</v>
+        <f xml:space="preserve"> IF($C121="", "", $C121 &amp; "=" &amp; D121)</f>
+        <v>excel.SResult.040=差分セル%d</v>
       </c>
       <c r="I121" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.150=★Failed</v>
+        <f xml:space="preserve"> IF($C121="", "", $C121 &amp; "=" &amp; E121)</f>
+        <v>excel.SResult.040=diff cells:%d</v>
       </c>
       <c r="J121" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.150=★失败</v>
+        <f xml:space="preserve"> IF($C121="", "", $C121 &amp; "=" &amp; F121)</f>
+        <v>excel.SResult.040=差异单元格%d</v>
       </c>
     </row>
     <row r="122" spans="2:10">
       <c r="B122" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>249</v>
+        <v>856</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="H122" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.160=(比較対象ファイルなし)</v>
+        <f xml:space="preserve"> IF($C122="", "", $C122 &amp; "=" &amp; D122)</f>
+        <v xml:space="preserve">excel.SResult.050=シート%s上の余剰行 : </v>
       </c>
       <c r="I122" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.160=(No files to compare)</v>
+        <f xml:space="preserve"> IF($C122="", "", $C122 &amp; "=" &amp; E122)</f>
+        <v xml:space="preserve">excel.SResult.050=Redundant rows on sheet %s : </v>
       </c>
       <c r="J122" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.160=(没有可比较的文件)</v>
+        <f xml:space="preserve"> IF($C122="", "", $C122 &amp; "=" &amp; F122)</f>
+        <v xml:space="preserve">excel.SResult.050=工作表%s的冗余行 : </v>
       </c>
     </row>
     <row r="123" spans="2:10">
       <c r="B123" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>382</v>
+        <v>857</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
       <c r="H123" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.170=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <f xml:space="preserve"> IF($C123="", "", $C123 &amp; "=" &amp; D123)</f>
+        <v>excel.SResult.060=行%d</v>
       </c>
       <c r="I123" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.170=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <f xml:space="preserve"> IF($C123="", "", $C123 &amp; "=" &amp; E123)</f>
+        <v>excel.SResult.060=Row %d</v>
       </c>
       <c r="J123" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.170=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <f xml:space="preserve"> IF($C123="", "", $C123 &amp; "=" &amp; F123)</f>
+        <v>excel.SResult.060=行%d</v>
       </c>
     </row>
     <row r="124" spans="2:10">
       <c r="B124" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>381</v>
+        <v>858</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>54</v>
+        <v>300</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>156</v>
+        <v>232</v>
       </c>
       <c r="H124" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>AppTaskBase.180=予期せぬ例外が発生しました。</v>
+        <f xml:space="preserve"> IF($C124="", "", $C124 &amp; "=" &amp; D124)</f>
+        <v xml:space="preserve">excel.SResult.070=シート%s上の余剰列 : </v>
       </c>
       <c r="I124" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>AppTaskBase.180=Unexpected exception occurred.</v>
+        <f xml:space="preserve"> IF($C124="", "", $C124 &amp; "=" &amp; E124)</f>
+        <v xml:space="preserve">excel.SResult.070=Redundant columns on sheet %s : </v>
       </c>
       <c r="J124" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>AppTaskBase.180=意外的例外。</v>
+        <f xml:space="preserve"> IF($C124="", "", $C124 &amp; "=" &amp; F124)</f>
+        <v xml:space="preserve">excel.SResult.070=工作表%s的冗余列 : </v>
       </c>
     </row>
     <row r="125" spans="2:10">
       <c r="B125" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>461</v>
+        <v>859</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>438</v>
+        <v>150</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>480</v>
+        <v>104</v>
       </c>
       <c r="H125" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">AppTaskBase.200=比較実行日時 : </v>
+        <f xml:space="preserve"> IF($C125="", "", $C125 &amp; "=" &amp; D125)</f>
+        <v>excel.SResult.080=%s列</v>
       </c>
       <c r="I125" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">AppTaskBase.200=Exec datetime : </v>
+        <f xml:space="preserve"> IF($C125="", "", $C125 &amp; "=" &amp; E125)</f>
+        <v>excel.SResult.080=Column %s</v>
       </c>
       <c r="J125" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">AppTaskBase.200=执行日期和时间 : </v>
+        <f xml:space="preserve"> IF($C125="", "", $C125 &amp; "=" &amp; F125)</f>
+        <v>excel.SResult.080=%s列</v>
       </c>
     </row>
     <row r="126" spans="2:10">
-      <c r="C126" s="2"/>
-      <c r="D126" s="3"/>
+      <c r="B126" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>372</v>
+      </c>
       <c r="H126" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f xml:space="preserve"> IF($C126="", "", $C126 &amp; "=" &amp; D126)</f>
+        <v xml:space="preserve">excel.SResult.090=差分セル : </v>
       </c>
       <c r="I126" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f xml:space="preserve"> IF($C126="", "", $C126 &amp; "=" &amp; E126)</f>
+        <v xml:space="preserve">excel.SResult.090=Diff cells : </v>
       </c>
       <c r="J126" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f xml:space="preserve"> IF($C126="", "", $C126 &amp; "=" &amp; F126)</f>
+        <v xml:space="preserve">excel.SResult.090=差异单元格 : </v>
       </c>
     </row>
     <row r="127" spans="2:10">
       <c r="B127" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>185</v>
+        <v>861</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="H127" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>CompareBooksTask.010=ブック同士の比較を開始します。</v>
+        <f xml:space="preserve"> IF($C127="", "", $C127 &amp; "=" &amp; D127)</f>
+        <v>excel.TreeResult.010=(比較相手なし)</v>
       </c>
       <c r="I127" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>CompareBooksTask.010=Starting comparing books.</v>
+        <f xml:space="preserve"> IF($C127="", "", $C127 &amp; "=" &amp; E127)</f>
+        <v>excel.TreeResult.010=(no opponent)</v>
       </c>
       <c r="J127" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>CompareBooksTask.010=开始互相比较工作簿。</v>
+        <f xml:space="preserve"> IF($C127="", "", $C127 &amp; "=" &amp; F127)</f>
+        <v>excel.TreeResult.010=(没有对比)</v>
       </c>
     </row>
     <row r="128" spans="2:10">
       <c r="B128" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>65</v>
+        <v>862</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>127</v>
+        <v>276</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="H128" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>CompareBooksTask.040=シートを比較しています...</v>
+        <f xml:space="preserve"> IF($C128="", "", $C128 &amp; "=" &amp; D128)</f>
+        <v xml:space="preserve">excel.TreeResult.020=ルートフォルダ%s : </v>
       </c>
       <c r="I128" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>CompareBooksTask.040=Comparing sheets...</v>
+        <f xml:space="preserve"> IF($C128="", "", $C128 &amp; "=" &amp; E128)</f>
+        <v xml:space="preserve">excel.TreeResult.020=Root folder %s : </v>
       </c>
       <c r="J128" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>CompareBooksTask.040=比较工作表...</v>
+        <f xml:space="preserve"> IF($C128="", "", $C128 &amp; "=" &amp; F128)</f>
+        <v xml:space="preserve">excel.TreeResult.020=根文件夹%s : </v>
       </c>
     </row>
     <row r="129" spans="2:10">
       <c r="B129" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>187</v>
+        <v>863</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>356</v>
+        <v>157</v>
       </c>
       <c r="H129" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>CompareBooksTask.050=シートの比較に失敗しました。</v>
+        <f xml:space="preserve"> IF($C129="", "", $C129 &amp; "=" &amp; D129)</f>
+        <v>excel.TreeResult.030=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="I129" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>CompareBooksTask.050=Failed to compare sheets.</v>
+        <f xml:space="preserve"> IF($C129="", "", $C129 &amp; "=" &amp; E129)</f>
+        <v>excel.TreeResult.030=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="J129" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>CompareBooksTask.050=工作表比较失败。</v>
+        <f xml:space="preserve"> IF($C129="", "", $C129 &amp; "=" &amp; F129)</f>
+        <v>excel.TreeResult.030=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="130" spans="2:10">
       <c r="B130" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>419</v>
+        <v>864</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>441</v>
+        <v>366</v>
       </c>
       <c r="H130" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>CompareBooksTask.060=比較結果レポートを保存しています...</v>
+        <f xml:space="preserve"> IF($C130="", "", $C130 &amp; "=" &amp; D130)</f>
+        <v>excel.TreeResult.040=■差分詳細 -----------------------------------------------------</v>
       </c>
       <c r="I130" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>CompareBooksTask.060=Saving result report...</v>
+        <f xml:space="preserve"> IF($C130="", "", $C130 &amp; "=" &amp; E130)</f>
+        <v>excel.TreeResult.040=## DETAIL ------------------------------------------------------</v>
       </c>
       <c r="J130" s="6" t="str">
-        <f t="shared" si="5"/>
-        <v>CompareBooksTask.060=保存比较结果报告...</v>
+        <f xml:space="preserve"> IF($C130="", "", $C130 &amp; "=" &amp; F130)</f>
+        <v>excel.TreeResult.040=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="131" spans="2:10">
       <c r="B131" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>442</v>
+        <v>865</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>443</v>
+        <v>220</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>444</v>
+        <v>353</v>
       </c>
       <c r="H131" s="4" t="str">
-        <f t="shared" ref="H131:H194" si="6" xml:space="preserve"> IF($C131="", "", $C131 &amp; "=" &amp; D131)</f>
-        <v>CompareBooksTask.070=比較結果レポートの保存に失敗しました。</v>
+        <f xml:space="preserve"> IF($C131="", "", $C131 &amp; "=" &amp; D131)</f>
+        <v>excel.TreeResult.050=★失敗しました</v>
       </c>
       <c r="I131" s="5" t="str">
-        <f t="shared" ref="I131:I194" si="7" xml:space="preserve"> IF($C131="", "", $C131 &amp; "=" &amp; E131)</f>
-        <v>CompareBooksTask.070=Failed to save result report.</v>
+        <f xml:space="preserve"> IF($C131="", "", $C131 &amp; "=" &amp; E131)</f>
+        <v>excel.TreeResult.050=★Failed</v>
       </c>
       <c r="J131" s="6" t="str">
-        <f t="shared" ref="J131:J194" si="8" xml:space="preserve"> IF($C131="", "", $C131 &amp; "=" &amp; F131)</f>
-        <v>CompareBooksTask.070=保存比较结果报告失败。</v>
+        <f xml:space="preserve"> IF($C131="", "", $C131 &amp; "=" &amp; F131)</f>
+        <v>excel.TreeResult.050=★失败</v>
       </c>
     </row>
     <row r="132" spans="2:10">
       <c r="B132" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>445</v>
+        <v>866</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>446</v>
+        <v>397</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>447</v>
+        <v>398</v>
       </c>
       <c r="H132" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareBooksTask.080=比較結果レポートを表示しています...</v>
+        <f xml:space="preserve"> IF($C132="", "", $C132 &amp; "=" &amp; D132)</f>
+        <v>fx.EditComparisonPane.010=組み合わせ編集</v>
       </c>
       <c r="I132" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareBooksTask.080=Opening result report...</v>
+        <f xml:space="preserve"> IF($C132="", "", $C132 &amp; "=" &amp; E132)</f>
+        <v>fx.EditComparisonPane.010=Edit Pairing</v>
       </c>
       <c r="J132" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareBooksTask.080=显示比较结果报告...</v>
+        <f xml:space="preserve"> IF($C132="", "", $C132 &amp; "=" &amp; F132)</f>
+        <v>fx.EditComparisonPane.010=组合编辑</v>
       </c>
     </row>
     <row r="133" spans="2:10">
       <c r="B133" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>450</v>
+        <v>867</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>542</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>449</v>
+        <v>544</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
       <c r="H133" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareBooksTask.090=比較結果レポートの表示に失敗しました。</v>
+        <f xml:space="preserve"> IF($C133="", "", $C133 &amp; "=" &amp; D133)</f>
+        <v>fx.GoogleFilePickerDialog.010=方眼Diff  -  Googleドライブ リビジョン選択</v>
       </c>
       <c r="I133" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareBooksTask.090=Failed to open result report.</v>
+        <f xml:space="preserve"> IF($C133="", "", $C133 &amp; "=" &amp; E133)</f>
+        <v>fx.GoogleFilePickerDialog.010=HoganDiff  -  Google Drive Revision Selection</v>
       </c>
       <c r="J133" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareBooksTask.090=显示比较结果报告失败。</v>
+        <f xml:space="preserve"> IF($C133="", "", $C133 &amp; "=" &amp; F133)</f>
+        <v>fx.GoogleFilePickerDialog.010=方眼Diff  -  Google Drive 版本选择</v>
       </c>
     </row>
     <row r="134" spans="2:10">
-      <c r="C134" s="2"/>
-      <c r="D134" s="3"/>
+      <c r="B134" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>547</v>
+      </c>
       <c r="H134" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C134="", "", $C134 &amp; "=" &amp; D134)</f>
+        <v>fx.GoogleFilePickerDialog.020=方眼Diff  -  Googleドライブ ファイル選択</v>
       </c>
       <c r="I134" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C134="", "", $C134 &amp; "=" &amp; E134)</f>
+        <v>fx.GoogleFilePickerDialog.020=HoganDiff  -  Google Drive File Selection</v>
       </c>
       <c r="J134" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f xml:space="preserve"> IF($C134="", "", $C134 &amp; "=" &amp; F134)</f>
+        <v>fx.GoogleFilePickerDialog.020=方眼Diff  -  Google Drive 文件选择</v>
       </c>
     </row>
     <row r="135" spans="2:10">
       <c r="B135" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>188</v>
+        <v>869</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>189</v>
+        <v>551</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>217</v>
+        <v>552</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>357</v>
+        <v>558</v>
       </c>
       <c r="H135" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareDirsTask.010=フォルダ同士の比較を開始します。</v>
+        <f xml:space="preserve"> IF($C135="", "", $C135 &amp; "=" &amp; D135)</f>
+        <v>fx.GoogleFilePickerDialogPane.070=共有ドライブ</v>
       </c>
       <c r="I135" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareDirsTask.010=Starting comparing folders.</v>
+        <f xml:space="preserve"> IF($C135="", "", $C135 &amp; "=" &amp; E135)</f>
+        <v>fx.GoogleFilePickerDialogPane.070=Shared drives</v>
       </c>
       <c r="J135" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareDirsTask.010=开始互相比较文件夹。</v>
+        <f xml:space="preserve"> IF($C135="", "", $C135 &amp; "=" &amp; F135)</f>
+        <v>fx.GoogleFilePickerDialogPane.070=共享云端硬盘</v>
       </c>
     </row>
     <row r="136" spans="2:10">
       <c r="B136" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>190</v>
+        <v>870</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>191</v>
+        <v>555</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>218</v>
+        <v>553</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>221</v>
+        <v>554</v>
       </c>
       <c r="H136" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareDirsTask.020=出力フォルダの作成に失敗しました。</v>
+        <f xml:space="preserve"> IF($C136="", "", $C136 &amp; "=" &amp; D136)</f>
+        <v>fx.GoogleFilePickerDialogPane.080=すべてのファイル</v>
       </c>
       <c r="I136" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareDirsTask.020=Failed to create output directory.</v>
+        <f xml:space="preserve"> IF($C136="", "", $C136 &amp; "=" &amp; E136)</f>
+        <v>fx.GoogleFilePickerDialogPane.080=All files</v>
       </c>
       <c r="J136" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareDirsTask.020=创建输出目的地文件夹失败。</v>
+        <f xml:space="preserve"> IF($C136="", "", $C136 &amp; "=" &amp; F136)</f>
+        <v>fx.GoogleFilePickerDialogPane.080=所有文件</v>
       </c>
     </row>
     <row r="137" spans="2:10">
       <c r="B137" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>192</v>
+        <v>871</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>550</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>193</v>
+        <v>556</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>219</v>
+        <v>557</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>358</v>
+        <v>559</v>
       </c>
       <c r="H137" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareDirsTask.050=Excelブックを比較しています...</v>
+        <f xml:space="preserve"> IF($C137="", "", $C137 &amp; "=" &amp; D137)</f>
+        <v>fx.GoogleFilePickerDialogPane.090=スター付き</v>
       </c>
       <c r="I137" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareDirsTask.050=Comparing books...</v>
+        <f xml:space="preserve"> IF($C137="", "", $C137 &amp; "=" &amp; E137)</f>
+        <v>fx.GoogleFilePickerDialogPane.090=Starred</v>
       </c>
       <c r="J137" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareDirsTask.050=比较工作簿...</v>
+        <f xml:space="preserve"> IF($C137="", "", $C137 &amp; "=" &amp; F137)</f>
+        <v>fx.GoogleFilePickerDialogPane.090=已加星标</v>
       </c>
     </row>
     <row r="138" spans="2:10">
       <c r="B138" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>269</v>
+        <v>872</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>249</v>
+        <v>561</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>277</v>
+        <v>563</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>278</v>
+        <v>562</v>
       </c>
       <c r="H138" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareDirsTask.070=(比較対象ファイルなし)</v>
+        <f xml:space="preserve"> IF($C138="", "", $C138 &amp; "=" &amp; D138)</f>
+        <v>fx.GoogleRevisionSelectorDialog.010=Googleドライブからのファイルダウンロードに失敗しました。</v>
       </c>
       <c r="I138" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareDirsTask.070=(No files to compare)</v>
+        <f xml:space="preserve"> IF($C138="", "", $C138 &amp; "=" &amp; E138)</f>
+        <v>fx.GoogleRevisionSelectorDialog.010=Failed to download the file from Google Drive.</v>
       </c>
       <c r="J138" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareDirsTask.070=(没有可比较的文件)</v>
+        <f xml:space="preserve"> IF($C138="", "", $C138 &amp; "=" &amp; F138)</f>
+        <v>fx.GoogleRevisionSelectorDialog.010=从Google云端硬盘下载文件失败。</v>
       </c>
     </row>
     <row r="139" spans="2:10">
       <c r="B139" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>384</v>
+        <v>873</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>390</v>
+        <v>504</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>385</v>
+        <v>505</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>387</v>
+        <v>504</v>
       </c>
       <c r="H139" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareDirsTask.080=フォルダの比較に失敗しました。</v>
+        <f xml:space="preserve"> IF($C139="", "", $C139 &amp; "=" &amp; D139)</f>
+        <v>google.GoogleFileFetcher.010=更新者不明</v>
       </c>
       <c r="I139" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareDirsTask.080=Failed to compare folders.</v>
+        <f xml:space="preserve"> IF($C139="", "", $C139 &amp; "=" &amp; E139)</f>
+        <v>google.GoogleFileFetcher.010=Unknown</v>
       </c>
       <c r="J139" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareDirsTask.080=文件夹比较失败。</v>
+        <f xml:space="preserve"> IF($C139="", "", $C139 &amp; "=" &amp; F139)</f>
+        <v>google.GoogleFileFetcher.010=更新者不明</v>
       </c>
     </row>
     <row r="140" spans="2:10">
-      <c r="C140" s="2"/>
-      <c r="D140" s="3"/>
+      <c r="B140" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>506</v>
+      </c>
       <c r="H140" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C140="", "", $C140 &amp; "=" &amp; D140)</f>
+        <v>google.GoogleFileFetcher.020=最新版</v>
       </c>
       <c r="I140" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C140="", "", $C140 &amp; "=" &amp; E140)</f>
+        <v>google.GoogleFileFetcher.020=Latest</v>
       </c>
       <c r="J140" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f xml:space="preserve"> IF($C140="", "", $C140 &amp; "=" &amp; F140)</f>
+        <v>google.GoogleFileFetcher.020=最新版</v>
       </c>
     </row>
     <row r="141" spans="2:10">
       <c r="B141" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>63</v>
+        <v>875</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>216</v>
+        <v>468</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="H141" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareSheetsTask.010=シート同士の比較を開始します。</v>
+        <f xml:space="preserve"> IF($C141="", "", $C141 &amp; "=" &amp; D141)</f>
+        <v>gui.component.GooglePane.010=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
       </c>
       <c r="I141" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareSheetsTask.010=Starting comparing sheets.</v>
+        <f xml:space="preserve"> IF($C141="", "", $C141 &amp; "=" &amp; E141)</f>
+        <v>gui.component.GooglePane.010=Disconnect HoganDiff from Google Drive. Are you sure?</v>
       </c>
       <c r="J141" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareSheetsTask.010=开始相互比较工作表。</v>
+        <f xml:space="preserve"> IF($C141="", "", $C141 &amp; "=" &amp; F141)</f>
+        <v>gui.component.GooglePane.010=解除方眼Diff与Google Drive的关联。确定吗？</v>
       </c>
     </row>
     <row r="142" spans="2:10">
       <c r="B142" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>65</v>
+        <v>876</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>127</v>
+        <v>474</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>360</v>
+        <v>475</v>
       </c>
       <c r="H142" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareSheetsTask.020=シートを比較しています...</v>
+        <f xml:space="preserve"> IF($C142="", "", $C142 &amp; "=" &amp; D142)</f>
+        <v>gui.component.GooglePane.020=資格情報を削除しました。</v>
       </c>
       <c r="I142" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareSheetsTask.020=Comparing sheets...</v>
+        <f xml:space="preserve"> IF($C142="", "", $C142 &amp; "=" &amp; E142)</f>
+        <v>gui.component.GooglePane.020=Credentials have been deleted.</v>
       </c>
       <c r="J142" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareSheetsTask.020=比较工作表...</v>
+        <f xml:space="preserve"> IF($C142="", "", $C142 &amp; "=" &amp; F142)</f>
+        <v>gui.component.GooglePane.020=已删除凭据。</v>
       </c>
     </row>
     <row r="143" spans="2:10">
       <c r="B143" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>66</v>
+        <v>877</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>128</v>
+        <v>477</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>386</v>
+        <v>478</v>
       </c>
       <c r="H143" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareSheetsTask.030=シートの比較に失敗しました。</v>
+        <f xml:space="preserve"> IF($C143="", "", $C143 &amp; "=" &amp; D143)</f>
+        <v>gui.component.GooglePane.030=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
       </c>
       <c r="I143" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareSheetsTask.030=Failed to compare sheets.</v>
+        <f xml:space="preserve"> IF($C143="", "", $C143 &amp; "=" &amp; E143)</f>
+        <v>gui.component.GooglePane.030=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
       </c>
       <c r="J143" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareSheetsTask.030=工作表比较失败。</v>
+        <f xml:space="preserve"> IF($C143="", "", $C143 &amp; "=" &amp; F143)</f>
+        <v>gui.component.GooglePane.030=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
     </row>
     <row r="144" spans="2:10">
-      <c r="C144" s="2"/>
-      <c r="D144" s="3"/>
+      <c r="B144" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>487</v>
+      </c>
       <c r="H144" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C144="", "", $C144 &amp; "=" &amp; D144)</f>
+        <v>gui.component.GooglePane.040=資格情報の削除に失敗しました。</v>
       </c>
       <c r="I144" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C144="", "", $C144 &amp; "=" &amp; E144)</f>
+        <v>gui.component.GooglePane.040=Failed to delete credentials.</v>
       </c>
       <c r="J144" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f xml:space="preserve"> IF($C144="", "", $C144 &amp; "=" &amp; F144)</f>
+        <v>gui.component.GooglePane.040=删除凭据失败。</v>
       </c>
     </row>
     <row r="145" spans="2:10">
       <c r="B145" s="1" t="s">
-        <v>639</v>
+        <v>879</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>250</v>
+        <v>485</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>267</v>
+        <v>484</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>266</v>
+        <v>488</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>361</v>
+        <v>489</v>
       </c>
       <c r="H145" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.010=フォルダツリー同士の比較を開始します。</v>
+        <f xml:space="preserve"> IF($C145="", "", $C145 &amp; "=" &amp; D145)</f>
+        <v>gui.component.GooglePane.050=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="I145" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.010=Starting comparing folder trees.</v>
+        <f xml:space="preserve"> IF($C145="", "", $C145 &amp; "=" &amp; E145)</f>
+        <v>gui.component.GooglePane.050=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="J145" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.010=开始互相比较文件夹树。</v>
+        <f xml:space="preserve"> IF($C145="", "", $C145 &amp; "=" &amp; F145)</f>
+        <v>gui.component.GooglePane.050=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="146" spans="2:10">
       <c r="B146" s="1" t="s">
-        <v>640</v>
+        <v>880</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>251</v>
+        <v>491</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>252</v>
+        <v>490</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>268</v>
+        <v>492</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>362</v>
+        <v>493</v>
       </c>
       <c r="H146" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.040=フォルダツリーを比較しています...</v>
+        <f xml:space="preserve"> IF($C146="", "", $C146 &amp; "=" &amp; D146)</f>
+        <v>gui.component.GooglePane.060=Google連携エラー</v>
       </c>
       <c r="I146" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.040=Comparing folders...</v>
+        <f xml:space="preserve"> IF($C146="", "", $C146 &amp; "=" &amp; E146)</f>
+        <v>gui.component.GooglePane.060=Google Integration Error</v>
       </c>
       <c r="J146" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.040=比较文件夹...</v>
+        <f xml:space="preserve"> IF($C146="", "", $C146 &amp; "=" &amp; F146)</f>
+        <v>gui.component.GooglePane.060=Google关联错误</v>
       </c>
     </row>
     <row r="147" spans="2:10">
       <c r="B147" s="1" t="s">
-        <v>641</v>
+        <v>881</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>253</v>
+        <v>497</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>194</v>
+        <v>494</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>220</v>
+        <v>495</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>353</v>
+        <v>496</v>
       </c>
       <c r="H147" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.050=★失敗しました</v>
+        <f xml:space="preserve"> IF($C147="", "", $C147 &amp; "=" &amp; D147)</f>
+        <v>gui.component.GooglePane.070=Google連携処理中にエラーが発生しました。</v>
       </c>
       <c r="I147" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.050=★Failed</v>
+        <f xml:space="preserve"> IF($C147="", "", $C147 &amp; "=" &amp; E147)</f>
+        <v>gui.component.GooglePane.070=An error occurred during Google integration processing.</v>
       </c>
       <c r="J147" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.050=★失败</v>
+        <f xml:space="preserve"> IF($C147="", "", $C147 &amp; "=" &amp; F147)</f>
+        <v>gui.component.GooglePane.070=Google关联处理过程中发生错误。</v>
       </c>
     </row>
     <row r="148" spans="2:10">
       <c r="B148" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>439</v>
+        <v>882</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>498</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>440</v>
+        <v>499</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>441</v>
+        <v>500</v>
       </c>
       <c r="H148" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.070=比較結果レポートを保存しています...</v>
+        <f xml:space="preserve"> IF($C148="", "", $C148 &amp; "=" &amp; D148)</f>
+        <v>gui.component.GooglePane.080=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="I148" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.070=Saving result report...</v>
+        <f xml:space="preserve"> IF($C148="", "", $C148 &amp; "=" &amp; E148)</f>
+        <v>gui.component.GooglePane.080=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="J148" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.070=保存比较结果报告...</v>
+        <f xml:space="preserve"> IF($C148="", "", $C148 &amp; "=" &amp; F148)</f>
+        <v>gui.component.GooglePane.080=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="149" spans="2:10">
       <c r="B149" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>282</v>
+        <v>883</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>442</v>
+        <v>529</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>443</v>
+        <v>537</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>444</v>
+        <v>538</v>
       </c>
       <c r="H149" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.080=比較結果レポートの保存に失敗しました。</v>
+        <f xml:space="preserve"> IF($C149="", "", $C149 &amp; "=" &amp; D149)</f>
+        <v>gui.component.GooglePane.090=Googleドライブからファイルをダウンロードしました。</v>
       </c>
       <c r="I149" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.080=Failed to save result report.</v>
+        <f xml:space="preserve"> IF($C149="", "", $C149 &amp; "=" &amp; E149)</f>
+        <v>gui.component.GooglePane.090=File downloaded from Google Drive</v>
       </c>
       <c r="J149" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.080=保存比较结果报告失败。</v>
+        <f xml:space="preserve"> IF($C149="", "", $C149 &amp; "=" &amp; F149)</f>
+        <v>gui.component.GooglePane.090=已从Google云端硬盘下载文件</v>
       </c>
     </row>
     <row r="150" spans="2:10">
       <c r="B150" s="1" t="s">
-        <v>643</v>
+        <v>884</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>283</v>
+        <v>32</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>445</v>
+        <v>33</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>446</v>
+        <v>114</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>447</v>
+        <v>336</v>
       </c>
       <c r="H150" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.090=比較結果レポートを表示しています...</v>
+        <f xml:space="preserve"> IF($C150="", "", $C150 &amp; "=" &amp; D150)</f>
+        <v>gui.component.LinkPane.010=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
       </c>
       <c r="I150" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.090=Opening result report...</v>
+        <f xml:space="preserve"> IF($C150="", "", $C150 &amp; "=" &amp; E150)</f>
+        <v>gui.component.LinkPane.010=Failed to open the website. Please try using your browser.</v>
       </c>
       <c r="J150" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.090=显示比较结果报告...</v>
+        <f xml:space="preserve"> IF($C150="", "", $C150 &amp; "=" &amp; F150)</f>
+        <v>gui.component.LinkPane.010=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
     </row>
     <row r="151" spans="2:10">
       <c r="B151" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>284</v>
+        <v>885</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>449</v>
+        <v>117</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="H151" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.100=比較結果レポートの表示に失敗しました。</v>
+        <f xml:space="preserve"> IF($C151="", "", $C151 &amp; "=" &amp; D151)</f>
+        <v>gui.component.SettingsPane2.010=作業用フォルダの表示に失敗しました。</v>
       </c>
       <c r="I151" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.100=Failed to open result report.</v>
+        <f xml:space="preserve"> IF($C151="", "", $C151 &amp; "=" &amp; E151)</f>
+        <v>gui.component.SettingsPane2.010=Failed to open working directory.</v>
       </c>
       <c r="J151" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.100=显示比较结果报告失败。</v>
+        <f xml:space="preserve"> IF($C151="", "", $C151 &amp; "=" &amp; F151)</f>
+        <v>gui.component.SettingsPane2.010=显示工作文件夹失败。</v>
       </c>
     </row>
     <row r="152" spans="2:10">
       <c r="B152" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>389</v>
+        <v>886</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>391</v>
+        <v>118</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>387</v>
+        <v>333</v>
       </c>
       <c r="H152" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>CompareTreesTask.110=フォルダツリーの比較に失敗しました。</v>
+        <f xml:space="preserve"> IF($C152="", "", $C152 &amp; "=" &amp; D152)</f>
+        <v>gui.component.SettingsPane2.020=作業用フォルダの変更</v>
       </c>
       <c r="I152" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>CompareTreesTask.110=Failed to compare folder trees.</v>
+        <f xml:space="preserve"> IF($C152="", "", $C152 &amp; "=" &amp; E152)</f>
+        <v>gui.component.SettingsPane2.020=Change working directory</v>
       </c>
       <c r="J152" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>CompareTreesTask.110=文件夹比较失败。</v>
+        <f xml:space="preserve"> IF($C152="", "", $C152 &amp; "=" &amp; F152)</f>
+        <v>gui.component.SettingsPane2.020=改变工作文件夹</v>
       </c>
     </row>
     <row r="153" spans="2:10">
-      <c r="C153" s="2"/>
-      <c r="D153" s="3"/>
+      <c r="B153" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>338</v>
+      </c>
       <c r="H153" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C153="", "", $C153 &amp; "=" &amp; D153)</f>
+        <v>gui.component.SettingsPane2.030=作業用フォルダの変更に失敗しました。</v>
       </c>
       <c r="I153" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C153="", "", $C153 &amp; "=" &amp; E153)</f>
+        <v>gui.component.SettingsPane2.030=Failed to change working directory.</v>
       </c>
       <c r="J153" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f xml:space="preserve"> IF($C153="", "", $C153 &amp; "=" &amp; F153)</f>
+        <v>gui.component.SettingsPane2.030=更改工作文件夹失败。</v>
       </c>
     </row>
     <row r="154" spans="2:10">
       <c r="B154" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>76</v>
+        <v>888</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="H154" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.BResult.010=(比較相手なし)</v>
+        <f xml:space="preserve"> IF($C154="", "", $C154 &amp; "=" &amp; D154)</f>
+        <v>gui.component.SettingsPane2.040=次のフォルダの内容物を全て削除します。よろしいですか？</v>
       </c>
       <c r="I154" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.BResult.010=(no opponent)</v>
+        <f xml:space="preserve"> IF($C154="", "", $C154 &amp; "=" &amp; E154)</f>
+        <v>gui.component.SettingsPane2.040=Delete all contents of the following directory. Are you sure?</v>
       </c>
       <c r="J154" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.010=(没有对比)</v>
+        <f xml:space="preserve"> IF($C154="", "", $C154 &amp; "=" &amp; F154)</f>
+        <v>gui.component.SettingsPane2.040=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
     </row>
     <row r="155" spans="2:10">
       <c r="B155" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>78</v>
+        <v>889</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>364</v>
+        <v>41</v>
       </c>
       <c r="H155" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.BResult.020=(差分なし)</v>
+        <f xml:space="preserve"> IF($C155="", "", $C155 &amp; "=" &amp; D155)</f>
+        <v>gui.component.SettingsPane2.051=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="I155" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.BResult.020=(no diffs)</v>
+        <f xml:space="preserve"> IF($C155="", "", $C155 &amp; "=" &amp; E155)</f>
+        <v>gui.component.SettingsPane2.051=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="J155" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.020=(没有区别)</v>
+        <f xml:space="preserve"> IF($C155="", "", $C155 &amp; "=" &amp; F155)</f>
+        <v>gui.component.SettingsPane2.051=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
     </row>
     <row r="156" spans="2:10">
       <c r="B156" s="1" t="s">
-        <v>666</v>
+        <v>890</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>197</v>
+        <v>172</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>222</v>
+        <v>42</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>365</v>
+        <v>42</v>
       </c>
       <c r="H156" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.BResult.030=差異発生%dシート</v>
+        <f xml:space="preserve"> IF($C156="", "", $C156 &amp; "=" &amp; D156)</f>
+        <v>gui.component.SettingsPane2.052=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="I156" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.BResult.030=diff sheets:%d</v>
+        <f xml:space="preserve"> IF($C156="", "", $C156 &amp; "=" &amp; E156)</f>
+        <v>gui.component.SettingsPane2.052=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="J156" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.030=差异工作表%d</v>
+        <f xml:space="preserve"> IF($C156="", "", $C156 &amp; "=" &amp; F156)</f>
+        <v>gui.component.SettingsPane2.052=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
     </row>
     <row r="157" spans="2:10">
       <c r="B157" s="1" t="s">
-        <v>667</v>
+        <v>891</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>198</v>
+        <v>173</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="H157" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.BResult.040=余剰%dシート</v>
+        <f xml:space="preserve"> IF($C157="", "", $C157 &amp; "=" &amp; D157)</f>
+        <v>gui.component.SettingsPane2.053=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="I157" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.BResult.040=redundant sheets:%d</v>
+        <f xml:space="preserve"> IF($C157="", "", $C157 &amp; "=" &amp; E157)</f>
+        <v>gui.component.SettingsPane2.053=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="J157" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.040=冗余工作表%d</v>
+        <f xml:space="preserve"> IF($C157="", "", $C157 &amp; "=" &amp; F157)</f>
+        <v>gui.component.SettingsPane2.053=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
     </row>
     <row r="158" spans="2:10">
       <c r="B158" s="1" t="s">
-        <v>668</v>
+        <v>892</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>210</v>
+        <v>570</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>571</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>224</v>
+        <v>572</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>298</v>
+        <v>573</v>
       </c>
       <c r="H158" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">excel.BResult.050=ブック%s : </v>
+        <f xml:space="preserve"> IF($C158="", "", $C158 &amp; "=" &amp; D158)</f>
+        <v>gui.component.SettingsPane2.060=方眼Diff  -  詳細設定</v>
       </c>
       <c r="I158" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">excel.BResult.050=Book %s : </v>
+        <f xml:space="preserve"> IF($C158="", "", $C158 &amp; "=" &amp; E158)</f>
+        <v>gui.component.SettingsPane2.060=HoganDiff  -  Advanced Settings</v>
       </c>
       <c r="J158" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.050=工作簿%s：</v>
+        <f xml:space="preserve"> IF($C158="", "", $C158 &amp; "=" &amp; F158)</f>
+        <v>gui.component.SettingsPane2.060=方眼Diff  -  详细设置</v>
       </c>
     </row>
     <row r="159" spans="2:10">
       <c r="B159" s="1" t="s">
-        <v>669</v>
+        <v>893</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>82</v>
+        <v>34</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>157</v>
+        <v>340</v>
       </c>
       <c r="H159" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.BResult.060=■差分サマリ ---------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C159="", "", $C159 &amp; "=" &amp; D159)</f>
+        <v>gui.component.TargetSelectionPane.010=比較対象フォルダの選択</v>
       </c>
       <c r="I159" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.BResult.060=## SUMMARY -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C159="", "", $C159 &amp; "=" &amp; E159)</f>
+        <v>gui.component.TargetSelectionPane.010=Select comparison folder</v>
       </c>
       <c r="J159" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.060=■差异摘要 -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C159="", "", $C159 &amp; "=" &amp; F159)</f>
+        <v>gui.component.TargetSelectionPane.010=选择用于比较的文件夹</v>
       </c>
     </row>
     <row r="160" spans="2:10">
       <c r="B160" s="1" t="s">
-        <v>670</v>
+        <v>894</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="H160" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.BResult.070=■差分詳細 -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C160="", "", $C160 &amp; "=" &amp; D160)</f>
+        <v>gui.component.TargetSelectionPane.020=比較対象ブックの選択</v>
       </c>
       <c r="I160" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.BResult.070=## DETAIL ------------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C160="", "", $C160 &amp; "=" &amp; E160)</f>
+        <v>gui.component.TargetSelectionPane.020=Select comparison book</v>
       </c>
       <c r="J160" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.BResult.070=■差异细节 -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C160="", "", $C160 &amp; "=" &amp; F160)</f>
+        <v>gui.component.TargetSelectionPane.020=选择用于比较的工作簿</v>
       </c>
     </row>
     <row r="161" spans="2:10">
+      <c r="B161" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="H161" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C161="", "", $C161 &amp; "=" &amp; D161)</f>
+        <v>gui.component.TargetSelectionPane.030=Excel ブック</v>
       </c>
       <c r="I161" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C161="", "", $C161 &amp; "=" &amp; E161)</f>
+        <v>gui.component.TargetSelectionPane.030=Excel book</v>
       </c>
       <c r="J161" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f xml:space="preserve"> IF($C161="", "", $C161 &amp; "=" &amp; F161)</f>
+        <v>gui.component.TargetSelectionPane.030=Excel工作簿</v>
       </c>
     </row>
     <row r="162" spans="2:10">
       <c r="B162" s="1" t="s">
-        <v>671</v>
+        <v>896</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>138</v>
+        <v>287</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="H162" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.010=(比較相手なし)</v>
+        <f xml:space="preserve"> IF($C162="", "", $C162 &amp; "=" &amp; D162)</f>
+        <v>gui.component.TargetSelectionPane.040=ファイルを読み込めません：</v>
       </c>
       <c r="I162" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.010=(no opponent)</v>
+        <f xml:space="preserve"> IF($C162="", "", $C162 &amp; "=" &amp; E162)</f>
+        <v xml:space="preserve">gui.component.TargetSelectionPane.040=Failed to open file : </v>
       </c>
       <c r="J162" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.010=(没有对比)</v>
+        <f xml:space="preserve"> IF($C162="", "", $C162 &amp; "=" &amp; F162)</f>
+        <v>gui.component.TargetSelectionPane.040=无法读取文件：</v>
       </c>
     </row>
     <row r="163" spans="2:10">
       <c r="B163" s="1" t="s">
-        <v>672</v>
+        <v>897</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>226</v>
+        <v>175</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="H163" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">excel.DResult.020=フォルダ%s : </v>
+        <f xml:space="preserve"> IF($C163="", "", $C163 &amp; "=" &amp; D163)</f>
+        <v>gui.component.TargetSelectionPane.050=シートが見つかりません：</v>
       </c>
       <c r="I163" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">excel.DResult.020=Folder %s : </v>
+        <f xml:space="preserve"> IF($C163="", "", $C163 &amp; "=" &amp; E163)</f>
+        <v xml:space="preserve">gui.component.TargetSelectionPane.050=No such sheet : </v>
       </c>
       <c r="J163" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">excel.DResult.020=文件夹%s : </v>
+        <f xml:space="preserve"> IF($C163="", "", $C163 &amp; "=" &amp; F163)</f>
+        <v>gui.component.TargetSelectionPane.050=没有找到工作表：</v>
       </c>
     </row>
     <row r="164" spans="2:10">
       <c r="B164" s="1" t="s">
-        <v>673</v>
+        <v>898</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>203</v>
+        <v>392</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>140</v>
+        <v>394</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>157</v>
+        <v>395</v>
       </c>
       <c r="H164" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.030=■差分サマリ ---------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C164="", "", $C164 &amp; "=" &amp; D164)</f>
+        <v>gui.component.TargetSelectionPane.060=フォルダを読み込めません：</v>
       </c>
       <c r="I164" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.030=## SUMMARY -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C164="", "", $C164 &amp; "=" &amp; E164)</f>
+        <v xml:space="preserve">gui.component.TargetSelectionPane.060=Failed to open folder : </v>
       </c>
       <c r="J164" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.030=■差异摘要 -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C164="", "", $C164 &amp; "=" &amp; F164)</f>
+        <v>gui.component.TargetSelectionPane.060=无法读取文件夹：</v>
       </c>
     </row>
     <row r="165" spans="2:10">
       <c r="B165" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="C165" s="7" t="s">
-        <v>204</v>
+        <v>899</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>574</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>141</v>
+        <v>577</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>366</v>
+        <v>576</v>
       </c>
       <c r="H165" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.040=■差分詳細 -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C165="", "", $C165 &amp; "=" &amp; D165)</f>
+        <v>gui.dialogs.SettingDetailsDialogPane.010=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
       </c>
       <c r="I165" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.040=## DETAIL ------------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C165="", "", $C165 &amp; "=" &amp; E165)</f>
+        <v>gui.dialogs.SettingDetailsDialogPane.010=Initialize settings and exit the application.\nAre you sure?</v>
       </c>
       <c r="J165" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.040=■差异细节 -----------------------------------------------------</v>
+        <f xml:space="preserve"> IF($C165="", "", $C165 &amp; "=" &amp; F165)</f>
+        <v>gui.dialogs.SettingDetailsDialogPane.010=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
     </row>
     <row r="166" spans="2:10">
       <c r="B166" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>205</v>
+        <v>900</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="H166" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.050=★失敗しました</v>
+        <f xml:space="preserve"> IF($C166="", "", $C166 &amp; "=" &amp; D166)</f>
+        <v>gui.MainController.010=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
       </c>
       <c r="I166" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.050=★Failed</v>
+        <f xml:space="preserve"> IF($C166="", "", $C166 &amp; "=" &amp; E166)</f>
+        <v>gui.MainController.010=Please specify different folders/books/sheets.</v>
       </c>
       <c r="J166" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.050=★失败</v>
+        <f xml:space="preserve"> IF($C166="", "", $C166 &amp; "=" &amp; F166)</f>
+        <v>gui.MainController.010=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
     </row>
     <row r="167" spans="2:10">
       <c r="B167" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>206</v>
+        <v>901</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="H167" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.060=(差分なし)</v>
+        <f xml:space="preserve"> IF($C167="", "", $C167 &amp; "=" &amp; D167)</f>
+        <v>gui.MainController.020=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
       </c>
       <c r="I167" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.060=(no diffs)</v>
+        <f xml:space="preserve"> IF($C167="", "", $C167 &amp; "=" &amp; E167)</f>
+        <v>gui.MainController.020=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
       </c>
       <c r="J167" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.060=(没有区别)</v>
+        <f xml:space="preserve"> IF($C167="", "", $C167 &amp; "=" &amp; F167)</f>
+        <v>gui.MainController.020=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
     </row>
     <row r="168" spans="2:10">
       <c r="B168" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>255</v>
+        <v>902</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="H168" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.070=差異発生%dブック</v>
+        <f xml:space="preserve"> IF($C168="", "", $C168 &amp; "=" &amp; D168)</f>
+        <v>gui.MainController.030=予期せぬ例外が発生しました。</v>
       </c>
       <c r="I168" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.070=diff books:%d</v>
+        <f xml:space="preserve"> IF($C168="", "", $C168 &amp; "=" &amp; E168)</f>
+        <v>gui.MainController.030=Unexpected exception occurred.</v>
       </c>
       <c r="J168" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.070=差异工作簿%d</v>
+        <f xml:space="preserve"> IF($C168="", "", $C168 &amp; "=" &amp; F168)</f>
+        <v>gui.MainController.030=意外的例外。</v>
       </c>
     </row>
     <row r="169" spans="2:10">
       <c r="B169" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D169" s="4" t="s">
-        <v>257</v>
+        <v>903</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>271</v>
+        <v>126</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="H169" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.080=余剰%dブック</v>
+        <f xml:space="preserve"> IF($C169="", "", $C169 &amp; "=" &amp; D169)</f>
+        <v>gui.MainController.040=作業用フォルダの作成に失敗しました。</v>
       </c>
       <c r="I169" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.080=redundant books:%d</v>
+        <f xml:space="preserve"> IF($C169="", "", $C169 &amp; "=" &amp; E169)</f>
+        <v>gui.MainController.040=Failed to create working directory.</v>
       </c>
       <c r="J169" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.080=冗余工作簿%d</v>
+        <f xml:space="preserve"> IF($C169="", "", $C169 &amp; "=" &amp; F169)</f>
+        <v>gui.MainController.040=创建工作文件夹失败。</v>
       </c>
     </row>
     <row r="170" spans="2:10">
       <c r="B170" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>259</v>
+        <v>904</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="H170" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.090=比較失敗%dブック</v>
+        <f xml:space="preserve"> IF($C170="", "", $C170 &amp; "=" &amp; D170)</f>
+        <v>gui.MainController.050=別の場所を指定してください。</v>
       </c>
       <c r="I170" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.090=failed books:%d</v>
+        <f xml:space="preserve"> IF($C170="", "", $C170 &amp; "=" &amp; E170)</f>
+        <v>gui.MainController.050=Please specify another location.</v>
       </c>
       <c r="J170" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.090=失败工作簿%d</v>
+        <f xml:space="preserve"> IF($C170="", "", $C170 &amp; "=" &amp; F170)</f>
+        <v>gui.MainController.050=请指定其他位置。</v>
       </c>
     </row>
     <row r="171" spans="2:10">
       <c r="B171" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>249</v>
+        <v>905</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>277</v>
+        <v>118</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="H171" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.DResult.100=(比較対象ファイルなし)</v>
+        <f xml:space="preserve"> IF($C171="", "", $C171 &amp; "=" &amp; D171)</f>
+        <v>gui.MainController.060=作業用フォルダの変更</v>
       </c>
       <c r="I171" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.DResult.100=(No files to compare)</v>
+        <f xml:space="preserve"> IF($C171="", "", $C171 &amp; "=" &amp; E171)</f>
+        <v>gui.MainController.060=Change working directory</v>
       </c>
       <c r="J171" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.DResult.100=(没有可比较的文件)</v>
+        <f xml:space="preserve"> IF($C171="", "", $C171 &amp; "=" &amp; F171)</f>
+        <v>gui.MainController.060=改变工作文件夹</v>
       </c>
     </row>
     <row r="172" spans="2:10">
+      <c r="B172" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>311</v>
+      </c>
       <c r="H172" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C172="", "", $C172 &amp; "=" &amp; D172)</f>
+        <v>gui.MainController.070=処理を中止しました。</v>
       </c>
       <c r="I172" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C172="", "", $C172 &amp; "=" &amp; E172)</f>
+        <v>gui.MainController.070=Processing has been canceled.</v>
       </c>
       <c r="J172" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f xml:space="preserve"> IF($C172="", "", $C172 &amp; "=" &amp; F172)</f>
+        <v>gui.MainController.070=处理已被取消。</v>
       </c>
     </row>
     <row r="173" spans="2:10">
       <c r="B173" s="1" t="s">
-        <v>766</v>
+        <v>907</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>765</v>
+        <v>55</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c r="H173" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SheetType.010=ワークシート</v>
+        <f xml:space="preserve"> IF($C173="", "", $C173 &amp; "=" &amp; D173)</f>
+        <v>gui.PasswordDialog.010=パスワード指定</v>
       </c>
       <c r="I173" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SheetType.010=Worksheet</v>
+        <f xml:space="preserve"> IF($C173="", "", $C173 &amp; "=" &amp; E173)</f>
+        <v>gui.PasswordDialog.010=Enter Password</v>
       </c>
       <c r="J173" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SheetType.010=工作表</v>
+        <f xml:space="preserve"> IF($C173="", "", $C173 &amp; "=" &amp; F173)</f>
+        <v>gui.PasswordDialog.010=输入密码</v>
       </c>
     </row>
     <row r="174" spans="2:10">
       <c r="B174" s="1" t="s">
-        <v>767</v>
+        <v>908</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="H174" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SheetType.020=グラフシート</v>
+        <f xml:space="preserve"> IF($C174="", "", $C174 &amp; "=" &amp; D174)</f>
+        <v>gui.PasswordDialogPane.010=%s はパスワードで保護されています。</v>
       </c>
       <c r="I174" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SheetType.020=Chart</v>
+        <f xml:space="preserve"> IF($C174="", "", $C174 &amp; "=" &amp; E174)</f>
+        <v>gui.PasswordDialogPane.010=The book [%s] is password protected.</v>
       </c>
       <c r="J174" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SheetType.020=图表表</v>
+        <f xml:space="preserve"> IF($C174="", "", $C174 &amp; "=" &amp; F174)</f>
+        <v>gui.PasswordDialogPane.010=%s 是受密码保护的。</v>
       </c>
     </row>
     <row r="175" spans="2:10">
       <c r="B175" s="1" t="s">
-        <v>768</v>
+        <v>909</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>89</v>
+        <v>565</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>144</v>
+        <v>568</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>370</v>
+        <v>569</v>
       </c>
       <c r="H175" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SheetType.030=MS Excel 5.0 ダイアログシート</v>
+        <f xml:space="preserve"> IF($C175="", "", $C175 &amp; "=" &amp; D175)</f>
+        <v>gui.UpdateChecker.010=新しいバージョンが利用可能です。</v>
       </c>
       <c r="I175" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SheetType.030=MS Excel 5.0 Dialog</v>
+        <f xml:space="preserve"> IF($C175="", "", $C175 &amp; "=" &amp; E175)</f>
+        <v>gui.UpdateChecker.010=A new version is available.</v>
       </c>
       <c r="J175" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SheetType.030=MS Excel 5.0 对话表</v>
+        <f xml:space="preserve"> IF($C175="", "", $C175 &amp; "=" &amp; F175)</f>
+        <v>gui.UpdateChecker.010=有新版本可用。</v>
       </c>
     </row>
     <row r="176" spans="2:10">
       <c r="B176" s="1" t="s">
-        <v>769</v>
+        <v>910</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>90</v>
+        <v>566</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>91</v>
+        <v>611</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>145</v>
+        <v>606</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>159</v>
+        <v>607</v>
       </c>
       <c r="H176" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SheetType.040=Excel 4.0 マクロシート</v>
+        <f xml:space="preserve"> IF($C176="", "", $C176 &amp; "=" &amp; D176)</f>
+        <v>gui.UpdateChecker.020=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
       </c>
       <c r="I176" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SheetType.040=Excel 4.0 Macro</v>
+        <f xml:space="preserve"> IF($C176="", "", $C176 &amp; "=" &amp; E176)</f>
+        <v>gui.UpdateChecker.020=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
       </c>
       <c r="J176" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SheetType.040=Excel 4.0 宏表</v>
+        <f xml:space="preserve"> IF($C176="", "", $C176 &amp; "=" &amp; F176)</f>
+        <v>gui.UpdateChecker.020=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
       </c>
     </row>
     <row r="177" spans="2:10">
-      <c r="C177" s="2"/>
-      <c r="D177" s="3"/>
+      <c r="B177" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>610</v>
+      </c>
       <c r="H177" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f xml:space="preserve"> IF($C177="", "", $C177 &amp; "=" &amp; D177)</f>
+        <v>gui.UpdateChecker.030=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
       </c>
       <c r="I177" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <f xml:space="preserve"> IF($C177="", "", $C177 &amp; "=" &amp; E177)</f>
+        <v>gui.UpdateChecker.030=Your application is up to date.\n    - Current version : %s</v>
       </c>
       <c r="J177" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="2:10">
-      <c r="B178" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="H178" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SResult.010=(差分なし)</v>
-      </c>
-      <c r="I178" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SResult.010=(no diffs)</v>
-      </c>
-      <c r="J178" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SResult.010=(没有区别)</v>
-      </c>
-    </row>
-    <row r="179" spans="2:10">
-      <c r="B179" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H179" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SResult.020=余剰行%d</v>
-      </c>
-      <c r="I179" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SResult.020=redundant rows:%d</v>
-      </c>
-      <c r="J179" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SResult.020=冗余行%d</v>
-      </c>
-    </row>
-    <row r="180" spans="2:10">
-      <c r="B180" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F180" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="H180" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SResult.030=余剰列%d</v>
-      </c>
-      <c r="I180" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SResult.030=redundant columns:%d</v>
-      </c>
-      <c r="J180" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SResult.030=冗余列%d</v>
-      </c>
-    </row>
-    <row r="181" spans="2:10">
-      <c r="B181" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F181" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="H181" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SResult.040=差分セル%d</v>
-      </c>
-      <c r="I181" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SResult.040=diff cells:%d</v>
-      </c>
-      <c r="J181" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SResult.040=差异单元格%d</v>
-      </c>
-    </row>
-    <row r="182" spans="2:10">
-      <c r="B182" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F182" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="H182" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">excel.SResult.050=シート%s上の余剰行 : </v>
-      </c>
-      <c r="I182" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">excel.SResult.050=Redundant rows on sheet %s : </v>
-      </c>
-      <c r="J182" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">excel.SResult.050=工作表%s的冗余行 : </v>
-      </c>
-    </row>
-    <row r="183" spans="2:10">
-      <c r="B183" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F183" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H183" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SResult.060=行%d</v>
-      </c>
-      <c r="I183" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SResult.060=Row %d</v>
-      </c>
-      <c r="J183" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SResult.060=行%d</v>
-      </c>
-    </row>
-    <row r="184" spans="2:10">
-      <c r="B184" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H184" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">excel.SResult.070=シート%s上の余剰列 : </v>
-      </c>
-      <c r="I184" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">excel.SResult.070=Redundant columns on sheet %s : </v>
-      </c>
-      <c r="J184" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">excel.SResult.070=工作表%s的冗余列 : </v>
-      </c>
-    </row>
-    <row r="185" spans="2:10">
-      <c r="B185" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F185" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H185" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.SResult.080=%s列</v>
-      </c>
-      <c r="I185" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.SResult.080=Column %s</v>
-      </c>
-      <c r="J185" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.SResult.080=%s列</v>
-      </c>
-    </row>
-    <row r="186" spans="2:10">
-      <c r="B186" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="F186" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="H186" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">excel.SResult.090=差分セル : </v>
-      </c>
-      <c r="I186" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">excel.SResult.090=Diff cells : </v>
-      </c>
-      <c r="J186" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">excel.SResult.090=差异单元格 : </v>
-      </c>
-    </row>
-    <row r="187" spans="2:10">
-      <c r="H187" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="I187" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J187" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="2:10">
-      <c r="B188" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="H188" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.TreeResult.010=(比較相手なし)</v>
-      </c>
-      <c r="I188" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.TreeResult.010=(no opponent)</v>
-      </c>
-      <c r="J188" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.TreeResult.010=(没有对比)</v>
-      </c>
-    </row>
-    <row r="189" spans="2:10">
-      <c r="B189" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D189" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F189" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H189" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">excel.TreeResult.020=ルートフォルダ%s : </v>
-      </c>
-      <c r="I189" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">excel.TreeResult.020=Root folder %s : </v>
-      </c>
-      <c r="J189" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">excel.TreeResult.020=根文件夹%s : </v>
-      </c>
-    </row>
-    <row r="190" spans="2:10">
-      <c r="B190" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H190" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.TreeResult.030=■差分サマリ ---------------------------------------------------</v>
-      </c>
-      <c r="I190" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.TreeResult.030=## SUMMARY -----------------------------------------------------</v>
-      </c>
-      <c r="J190" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.TreeResult.030=■差异摘要 -----------------------------------------------------</v>
-      </c>
-    </row>
-    <row r="191" spans="2:10">
-      <c r="B191" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="H191" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.TreeResult.040=■差分詳細 -----------------------------------------------------</v>
-      </c>
-      <c r="I191" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.TreeResult.040=## DETAIL ------------------------------------------------------</v>
-      </c>
-      <c r="J191" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.TreeResult.040=■差异细节 -----------------------------------------------------</v>
-      </c>
-    </row>
-    <row r="192" spans="2:10">
-      <c r="B192" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D192" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E192" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="H192" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>excel.TreeResult.050=★失敗しました</v>
-      </c>
-      <c r="I192" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>excel.TreeResult.050=★Failed</v>
-      </c>
-      <c r="J192" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>excel.TreeResult.050=★失败</v>
-      </c>
-    </row>
-    <row r="193" spans="2:10">
-      <c r="H193" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="I193" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J193" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="2:10">
-      <c r="B194" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="D194" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="F194" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="H194" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>google.GoogleFileFetcher.010=更新者不明</v>
-      </c>
-      <c r="I194" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>google.GoogleFileFetcher.010=Unknown</v>
-      </c>
-      <c r="J194" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>google.GoogleFileFetcher.010=更新者不明</v>
-      </c>
-    </row>
-    <row r="195" spans="2:10">
-      <c r="B195" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="D195" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="E195" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="F195" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="H195" s="4" t="str">
-        <f t="shared" ref="H195:J195" si="9" xml:space="preserve"> IF($C195="", "", $C195 &amp; "=" &amp; D195)</f>
-        <v>google.GoogleFileFetcher.020=最新版</v>
-      </c>
-      <c r="I195" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>google.GoogleFileFetcher.020=Latest</v>
-      </c>
-      <c r="J195" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>google.GoogleFileFetcher.020=最新版</v>
+        <f xml:space="preserve"> IF($C177="", "", $C177 &amp; "=" &amp; F177)</f>
+        <v>gui.UpdateChecker.030=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A47:J177">
+    <sortCondition ref="C47:C177"/>
+  </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namba\OneDrive\workspace_202509\hogandiff4\xyz.hotchpotch.hogandiff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947023AA-F930-4417-9B73-FC6EE684DCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="625">
   <si>
     <t>fx.MenuPane.020</t>
   </si>
@@ -3178,7 +3178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:K177"/>
+  <dimension ref="C1:K177"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -4116,7 +4116,7 @@
         <v>fx.TargetSelectionPane.030=文件夹路径：</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
+    <row r="33" spans="3:11">
       <c r="C33" s="1" t="s">
         <v>484</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>fx.GoogleFilePickerDialogPane.030=文件URL :</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
+    <row r="34" spans="3:11">
       <c r="C34" s="1" t="s">
         <v>484</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>fx.GoogleFilePickerDialogPane.050=文件名 :</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
+    <row r="35" spans="3:11">
       <c r="C35" s="1" t="s">
         <v>484</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>fx.GoogleFilePickerDialogPane.060=版本 :</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
+    <row r="36" spans="3:11">
       <c r="C36" s="1" t="s">
         <v>484</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>fx.GooglePane.010=Google Drive\n关联</v>
       </c>
     </row>
-    <row r="37" spans="2:11">
+    <row r="37" spans="3:11">
       <c r="C37" s="1" t="s">
         <v>484</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>fx.GooglePane.020=Google Drive\n关联解除</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
+    <row r="38" spans="3:11">
       <c r="C38" s="1" t="s">
         <v>484</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>fx.SettingDetailsDialogPane.010=更新确认</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
+    <row r="39" spans="3:11">
       <c r="C39" s="1" t="s">
         <v>484</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>fx.SettingDetailsDialogPane.020=启动时检查是否有新版本</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
+    <row r="40" spans="3:11">
       <c r="C40" s="1" t="s">
         <v>484</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>fx.SettingDetailsDialogPane.030=立即检查是否有新版本</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
+    <row r="41" spans="3:11">
       <c r="C41" s="1" t="s">
         <v>484</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>fx.SettingDetailsDialogPane.040=设置</v>
       </c>
     </row>
-    <row r="42" spans="2:11">
+    <row r="42" spans="3:11">
       <c r="C42" s="1" t="s">
         <v>484</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>fx.SettingDetailsDialogPane.050=显示配置文件</v>
       </c>
     </row>
-    <row r="43" spans="2:11">
+    <row r="43" spans="3:11">
       <c r="C43" s="1" t="s">
         <v>484</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>fx.SettingDetailsDialogPane.060=重置设置…</v>
       </c>
     </row>
-    <row r="44" spans="2:11">
+    <row r="44" spans="3:11">
       <c r="C44" s="1" t="s">
         <v>484</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>gui.component.GooglePane.100=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
+    <row r="45" spans="3:11">
       <c r="C45" s="1" t="s">
         <v>484</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>gui.component.GooglePane.110=不再显示此消息</v>
       </c>
     </row>
-    <row r="46" spans="2:11">
+    <row r="46" spans="3:11">
       <c r="E46" s="3"/>
       <c r="I46" s="4" t="str">
         <f t="shared" si="0"/>
@@ -4508,13 +4508,10 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:11">
-      <c r="B47" s="1" t="str">
-        <f t="shared" ref="B47:B110" si="3" xml:space="preserve"> C47 &amp; "(""" &amp; D47 &amp; """),"</f>
-        <v>APP_0010("APP_0010"),</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>494</v>
+    <row r="47" spans="3:11">
+      <c r="C47" s="1" t="str">
+        <f xml:space="preserve"> "/** " &amp; E47 &amp; " */ " &amp; D47 &amp; ","</f>
+        <v>/** 方眼Diff */ APP_0010,</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>494</v>
@@ -4529,25 +4526,22 @@
         <v>362</v>
       </c>
       <c r="I47" s="4" t="str">
-        <f t="shared" ref="I47:I78" si="4" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; E47)</f>
+        <f t="shared" ref="I47:I78" si="3" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; E47)</f>
         <v>APP_0010=方眼Diff</v>
       </c>
       <c r="J47" s="5" t="str">
-        <f t="shared" ref="J47:J78" si="5" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; F47)</f>
+        <f t="shared" ref="J47:J78" si="4" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; F47)</f>
         <v>APP_0010=HoganDiff (方眼Diff)</v>
       </c>
       <c r="K47" s="6" t="str">
-        <f t="shared" ref="K47:K78" si="6" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; G47)</f>
+        <f t="shared" ref="K47:K78" si="5" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; G47)</f>
         <v>APP_0010=方眼Diff</v>
       </c>
     </row>
-    <row r="48" spans="2:11">
-      <c r="B48" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0020("APP_0020"),</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>495</v>
+    <row r="48" spans="3:11">
+      <c r="C48" s="1" t="str">
+        <f t="shared" ref="C48:C111" si="6" xml:space="preserve"> "/** " &amp; E48 &amp; " */ " &amp; D48 &amp; ","</f>
+        <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>495</v>
@@ -4562,25 +4556,22 @@
         <v>257</v>
       </c>
       <c r="I48" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0020=設定の保存に失敗しました。</v>
+      </c>
+      <c r="J48" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0020=設定の保存に失敗しました。</v>
-      </c>
-      <c r="J48" s="5" t="str">
+        <v>APP_0020=Failed to save settings.</v>
+      </c>
+      <c r="K48" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0020=Failed to save settings.</v>
-      </c>
-      <c r="K48" s="6" t="str">
+        <v>APP_0020=保存设置失败。</v>
+      </c>
+    </row>
+    <row r="49" spans="3:11">
+      <c r="C49" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0020=保存设置失败。</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0030("APP_0030"),</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>496</v>
+        <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>496</v>
@@ -4595,25 +4586,22 @@
         <v>258</v>
       </c>
       <c r="I49" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0030=比較結果テキストを保存しています...</v>
+      </c>
+      <c r="J49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0030=比較結果テキストを保存しています...</v>
-      </c>
-      <c r="J49" s="5" t="str">
+        <v>APP_0030=Saving result text...</v>
+      </c>
+      <c r="K49" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0030=Saving result text...</v>
-      </c>
-      <c r="K49" s="6" t="str">
+        <v>APP_0030=存储比较结果文本...</v>
+      </c>
+    </row>
+    <row r="50" spans="3:11">
+      <c r="C50" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0030=存储比较结果文本...</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0040("APP_0040"),</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>497</v>
+        <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>497</v>
@@ -4628,25 +4616,22 @@
         <v>259</v>
       </c>
       <c r="I50" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
+      </c>
+      <c r="J50" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
-      </c>
-      <c r="J50" s="5" t="str">
+        <v>APP_0040=Failed to save or open result text.</v>
+      </c>
+      <c r="K50" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0040=Failed to save or open result text.</v>
-      </c>
-      <c r="K50" s="6" t="str">
+        <v>APP_0040=保存和显示比较结果文本失败。</v>
+      </c>
+    </row>
+    <row r="51" spans="3:11">
+      <c r="C51" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0040=保存和显示比较结果文本失败。</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0050("APP_0050"),</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>498</v>
+        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>498</v>
@@ -4661,25 +4646,22 @@
         <v>260</v>
       </c>
       <c r="I51" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
+      </c>
+      <c r="J51" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
-      </c>
-      <c r="J51" s="5" t="str">
+        <v>APP_0050=Painting and saving result book(s)...</v>
+      </c>
+      <c r="K51" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0050=Painting and saving result book(s)...</v>
-      </c>
-      <c r="K51" s="6" t="str">
+        <v>APP_0050=着色和存储在工作簿...</v>
+      </c>
+    </row>
+    <row r="52" spans="3:11">
+      <c r="C52" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0050=着色和存储在工作簿...</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0060("APP_0060"),</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>499</v>
+        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>499</v>
@@ -4694,25 +4676,22 @@
         <v>261</v>
       </c>
       <c r="I52" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
+      </c>
+      <c r="J52" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
-      </c>
-      <c r="J52" s="5" t="str">
+        <v>APP_0060=Failed to paint or save result book(s).</v>
+      </c>
+      <c r="K52" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0060=Failed to paint or save result book(s).</v>
-      </c>
-      <c r="K52" s="6" t="str">
+        <v>APP_0060=着色和保存工作簿失败。</v>
+      </c>
+    </row>
+    <row r="53" spans="3:11">
+      <c r="C53" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0060=着色和保存工作簿失败。</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0070("APP_0070"),</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>500</v>
+        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>500</v>
@@ -4727,25 +4706,22 @@
         <v>262</v>
       </c>
       <c r="I53" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
+      </c>
+      <c r="J53" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
-      </c>
-      <c r="J53" s="5" t="str">
+        <v>APP_0070=Opening result book(s)...</v>
+      </c>
+      <c r="K53" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0070=Opening result book(s)...</v>
-      </c>
-      <c r="K53" s="6" t="str">
+        <v>APP_0070=显示比较结果的工作簿...</v>
+      </c>
+    </row>
+    <row r="54" spans="3:11">
+      <c r="C54" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0070=显示比较结果的工作簿...</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="B54" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0080("APP_0080"),</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>501</v>
+        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>501</v>
@@ -4760,25 +4736,22 @@
         <v>263</v>
       </c>
       <c r="I54" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0080=Excelブックの表示に失敗しました。</v>
+      </c>
+      <c r="J54" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0080=Excelブックの表示に失敗しました。</v>
-      </c>
-      <c r="J54" s="5" t="str">
+        <v>APP_0080=Failed to open result book(s).</v>
+      </c>
+      <c r="K54" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0080=Failed to open result book(s).</v>
-      </c>
-      <c r="K54" s="6" t="str">
+        <v>APP_0080=显示工作簿失败。</v>
+      </c>
+    </row>
+    <row r="55" spans="3:11">
+      <c r="C55" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0080=显示工作簿失败。</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0090("APP_0090"),</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>502</v>
+        <v>/** ExcelブックAの着色・保存に失敗しました。 */ APP_0090,</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>502</v>
@@ -4793,25 +4766,22 @@
         <v>264</v>
       </c>
       <c r="I55" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0090=ExcelブックAの着色・保存に失敗しました。</v>
+      </c>
+      <c r="J55" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0090=ExcelブックAの着色・保存に失敗しました。</v>
-      </c>
-      <c r="J55" s="5" t="str">
+        <v>APP_0090=Failed to paint or save result book A.</v>
+      </c>
+      <c r="K55" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0090=Failed to paint or save result book A.</v>
-      </c>
-      <c r="K55" s="6" t="str">
+        <v>APP_0090=工作簿A的着色和保存失败。</v>
+      </c>
+    </row>
+    <row r="56" spans="3:11">
+      <c r="C56" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0090=工作簿A的着色和保存失败。</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0100("APP_0100"),</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>503</v>
+        <v>/** ExcelブックBの着色・保存に失敗しました。 */ APP_0100,</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>503</v>
@@ -4826,25 +4796,22 @@
         <v>265</v>
       </c>
       <c r="I56" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0100=ExcelブックBの着色・保存に失敗しました。</v>
+      </c>
+      <c r="J56" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0100=ExcelブックBの着色・保存に失敗しました。</v>
-      </c>
-      <c r="J56" s="5" t="str">
+        <v>APP_0100=Failed to paint or save result book B.</v>
+      </c>
+      <c r="K56" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0100=Failed to paint or save result book B.</v>
-      </c>
-      <c r="K56" s="6" t="str">
+        <v>APP_0100=工作簿B的着色和保存失败。</v>
+      </c>
+    </row>
+    <row r="57" spans="3:11">
+      <c r="C57" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0100=工作簿B的着色和保存失败。</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0110("APP_0110"),</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>504</v>
+        <v>/** 処理が完了しました。 */ APP_0110,</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>504</v>
@@ -4859,25 +4826,22 @@
         <v>266</v>
       </c>
       <c r="I57" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0110=処理が完了しました。</v>
+      </c>
+      <c r="J57" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0110=処理が完了しました。</v>
-      </c>
-      <c r="J57" s="5" t="str">
+        <v>APP_0110=Process completed.</v>
+      </c>
+      <c r="K57" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0110=Process completed.</v>
-      </c>
-      <c r="K57" s="6" t="str">
+        <v>APP_0110=过程完成。</v>
+      </c>
+    </row>
+    <row r="58" spans="3:11">
+      <c r="C58" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0110=过程完成。</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0120("APP_0120"),</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>505</v>
+        <v>/** ★失敗しました */ APP_0120,</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>505</v>
@@ -4892,25 +4856,22 @@
         <v>267</v>
       </c>
       <c r="I58" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0120=★失敗しました</v>
+      </c>
+      <c r="J58" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0120=★失敗しました</v>
-      </c>
-      <c r="J58" s="5" t="str">
+        <v>APP_0120=★Failed</v>
+      </c>
+      <c r="K58" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0120=★Failed</v>
-      </c>
-      <c r="K58" s="6" t="str">
+        <v>APP_0120=★失败</v>
+      </c>
+    </row>
+    <row r="59" spans="3:11">
+      <c r="C59" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0120=★失败</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0130("APP_0130"),</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>506</v>
+        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>506</v>
@@ -4925,25 +4886,22 @@
         <v>202</v>
       </c>
       <c r="I59" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0130=(比較対象ファイルなし)</v>
+      </c>
+      <c r="J59" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0130=(比較対象ファイルなし)</v>
-      </c>
-      <c r="J59" s="5" t="str">
+        <v>APP_0130=(No files to compare)</v>
+      </c>
+      <c r="K59" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0130=(No files to compare)</v>
-      </c>
-      <c r="K59" s="6" t="str">
+        <v>APP_0130=(没有可比较的文件)</v>
+      </c>
+    </row>
+    <row r="60" spans="3:11">
+      <c r="C60" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0130=(没有可比较的文件)</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0140("APP_0140"),</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>507</v>
+        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>507</v>
@@ -4958,25 +4916,22 @@
         <v>370</v>
       </c>
       <c r="I60" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+      </c>
+      <c r="J60" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
-      </c>
-      <c r="J60" s="5" t="str">
+        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+      </c>
+      <c r="K60" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
-      </c>
-      <c r="K60" s="6" t="str">
+        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:11">
+      <c r="C61" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0150("APP_0150"),</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>508</v>
+        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>508</v>
@@ -4991,25 +4946,22 @@
         <v>125</v>
       </c>
       <c r="I61" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0150=予期せぬ例外が発生しました。</v>
+      </c>
+      <c r="J61" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0150=予期せぬ例外が発生しました。</v>
-      </c>
-      <c r="J61" s="5" t="str">
+        <v>APP_0150=Unexpected exception occurred.</v>
+      </c>
+      <c r="K61" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0150=Unexpected exception occurred.</v>
-      </c>
-      <c r="K61" s="6" t="str">
+        <v>APP_0150=意外的例外。</v>
+      </c>
+    </row>
+    <row r="62" spans="3:11">
+      <c r="C62" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0150=意外的例外。</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0160("APP_0160"),</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>509</v>
+        <v>/** 比較実行日時 :  */ APP_0160,</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>509</v>
@@ -5024,25 +4976,22 @@
         <v>371</v>
       </c>
       <c r="I62" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">APP_0160=比較実行日時 : </v>
+      </c>
+      <c r="J62" s="5" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0160=比較実行日時 : </v>
-      </c>
-      <c r="J62" s="5" t="str">
+        <v xml:space="preserve">APP_0160=Exec datetime : </v>
+      </c>
+      <c r="K62" s="6" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0160=Exec datetime : </v>
-      </c>
-      <c r="K62" s="6" t="str">
+        <v xml:space="preserve">APP_0160=执行日期和时间 : </v>
+      </c>
+    </row>
+    <row r="63" spans="3:11">
+      <c r="C63" s="1" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0160=执行日期和时间 : </v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0170("APP_0170"),</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>510</v>
+        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>510</v>
@@ -5057,25 +5006,22 @@
         <v>268</v>
       </c>
       <c r="I63" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0170=ブック同士の比較を開始します。</v>
+      </c>
+      <c r="J63" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0170=ブック同士の比較を開始します。</v>
-      </c>
-      <c r="J63" s="5" t="str">
+        <v>APP_0170=Starting comparing books.</v>
+      </c>
+      <c r="K63" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0170=Starting comparing books.</v>
-      </c>
-      <c r="K63" s="6" t="str">
+        <v>APP_0170=开始互相比较工作簿。</v>
+      </c>
+    </row>
+    <row r="64" spans="3:11">
+      <c r="C64" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0170=开始互相比较工作簿。</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0180("APP_0180"),</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>511</v>
+        <v>/** シートを比較しています... */ APP_0180,</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>511</v>
@@ -5090,25 +5036,22 @@
         <v>269</v>
       </c>
       <c r="I64" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0180=シートを比較しています...</v>
+      </c>
+      <c r="J64" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0180=シートを比較しています...</v>
-      </c>
-      <c r="J64" s="5" t="str">
+        <v>APP_0180=Comparing sheets...</v>
+      </c>
+      <c r="K64" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0180=Comparing sheets...</v>
-      </c>
-      <c r="K64" s="6" t="str">
+        <v>APP_0180=比较工作表...</v>
+      </c>
+    </row>
+    <row r="65" spans="3:11">
+      <c r="C65" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0180=比较工作表...</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0190("APP_0190"),</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>512</v>
+        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>512</v>
@@ -5123,25 +5066,22 @@
         <v>270</v>
       </c>
       <c r="I65" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0190=シートの比較に失敗しました。</v>
+      </c>
+      <c r="J65" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0190=シートの比較に失敗しました。</v>
-      </c>
-      <c r="J65" s="5" t="str">
+        <v>APP_0190=Failed to compare sheets.</v>
+      </c>
+      <c r="K65" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0190=Failed to compare sheets.</v>
-      </c>
-      <c r="K65" s="6" t="str">
+        <v>APP_0190=工作表比较失败。</v>
+      </c>
+    </row>
+    <row r="66" spans="3:11">
+      <c r="C66" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0190=工作表比较失败。</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0200("APP_0200"),</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>513</v>
+        <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>513</v>
@@ -5156,25 +5096,22 @@
         <v>336</v>
       </c>
       <c r="I66" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0200=比較結果レポートを保存しています...</v>
+      </c>
+      <c r="J66" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0200=比較結果レポートを保存しています...</v>
-      </c>
-      <c r="J66" s="5" t="str">
+        <v>APP_0200=Saving result report...</v>
+      </c>
+      <c r="K66" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0200=Saving result report...</v>
-      </c>
-      <c r="K66" s="6" t="str">
+        <v>APP_0200=保存比较结果报告...</v>
+      </c>
+    </row>
+    <row r="67" spans="3:11">
+      <c r="C67" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0200=保存比较结果报告...</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0210("APP_0210"),</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>514</v>
+        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>514</v>
@@ -5189,25 +5126,22 @@
         <v>339</v>
       </c>
       <c r="I67" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
+      </c>
+      <c r="J67" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
-      </c>
-      <c r="J67" s="5" t="str">
+        <v>APP_0210=Failed to save result report.</v>
+      </c>
+      <c r="K67" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0210=Failed to save result report.</v>
-      </c>
-      <c r="K67" s="6" t="str">
+        <v>APP_0210=保存比较结果报告失败。</v>
+      </c>
+    </row>
+    <row r="68" spans="3:11">
+      <c r="C68" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0210=保存比较结果报告失败。</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0220("APP_0220"),</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>515</v>
+        <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>515</v>
@@ -5222,25 +5156,22 @@
         <v>342</v>
       </c>
       <c r="I68" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0220=比較結果レポートを表示しています...</v>
+      </c>
+      <c r="J68" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0220=比較結果レポートを表示しています...</v>
-      </c>
-      <c r="J68" s="5" t="str">
+        <v>APP_0220=Opening result report...</v>
+      </c>
+      <c r="K68" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0220=Opening result report...</v>
-      </c>
-      <c r="K68" s="6" t="str">
+        <v>APP_0220=显示比较结果报告...</v>
+      </c>
+    </row>
+    <row r="69" spans="3:11">
+      <c r="C69" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0220=显示比较结果报告...</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0230("APP_0230"),</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>516</v>
+        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>516</v>
@@ -5255,25 +5186,22 @@
         <v>343</v>
       </c>
       <c r="I69" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
+      </c>
+      <c r="J69" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
-      </c>
-      <c r="J69" s="5" t="str">
+        <v>APP_0230=Failed to open result report.</v>
+      </c>
+      <c r="K69" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0230=Failed to open result report.</v>
-      </c>
-      <c r="K69" s="6" t="str">
+        <v>APP_0230=显示比较结果报告失败。</v>
+      </c>
+    </row>
+    <row r="70" spans="3:11">
+      <c r="C70" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0230=显示比较结果报告失败。</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="B70" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0240("APP_0240"),</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>517</v>
+        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>517</v>
@@ -5288,25 +5216,22 @@
         <v>271</v>
       </c>
       <c r="I70" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0240=フォルダ同士の比較を開始します。</v>
+      </c>
+      <c r="J70" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0240=フォルダ同士の比較を開始します。</v>
-      </c>
-      <c r="J70" s="5" t="str">
+        <v>APP_0240=Starting comparing folders.</v>
+      </c>
+      <c r="K70" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0240=Starting comparing folders.</v>
-      </c>
-      <c r="K70" s="6" t="str">
+        <v>APP_0240=开始互相比较文件夹。</v>
+      </c>
+    </row>
+    <row r="71" spans="3:11">
+      <c r="C71" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0240=开始互相比较文件夹。</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0250("APP_0250"),</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>518</v>
+        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>518</v>
@@ -5321,25 +5246,22 @@
         <v>160</v>
       </c>
       <c r="I71" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
+      </c>
+      <c r="J71" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
-      </c>
-      <c r="J71" s="5" t="str">
+        <v>APP_0250=Failed to create output directory.</v>
+      </c>
+      <c r="K71" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0250=Failed to create output directory.</v>
-      </c>
-      <c r="K71" s="6" t="str">
+        <v>APP_0250=创建输出目的地文件夹失败。</v>
+      </c>
+    </row>
+    <row r="72" spans="3:11">
+      <c r="C72" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0250=创建输出目的地文件夹失败。</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0260("APP_0260"),</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>519</v>
+        <v>/** Excelブックを比較しています... */ APP_0260,</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>519</v>
@@ -5354,25 +5276,22 @@
         <v>272</v>
       </c>
       <c r="I72" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0260=Excelブックを比較しています...</v>
+      </c>
+      <c r="J72" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0260=Excelブックを比較しています...</v>
-      </c>
-      <c r="J72" s="5" t="str">
+        <v>APP_0260=Comparing books...</v>
+      </c>
+      <c r="K72" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0260=Comparing books...</v>
-      </c>
-      <c r="K72" s="6" t="str">
+        <v>APP_0260=比较工作簿...</v>
+      </c>
+    </row>
+    <row r="73" spans="3:11">
+      <c r="C73" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0260=比较工作簿...</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0270("APP_0270"),</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>520</v>
+        <v>/** (比較対象ファイルなし) */ APP_0270,</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>520</v>
@@ -5387,25 +5306,22 @@
         <v>202</v>
       </c>
       <c r="I73" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0270=(比較対象ファイルなし)</v>
+      </c>
+      <c r="J73" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0270=(比較対象ファイルなし)</v>
-      </c>
-      <c r="J73" s="5" t="str">
+        <v>APP_0270=(No files to compare)</v>
+      </c>
+      <c r="K73" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0270=(No files to compare)</v>
-      </c>
-      <c r="K73" s="6" t="str">
+        <v>APP_0270=(没有可比较的文件)</v>
+      </c>
+    </row>
+    <row r="74" spans="3:11">
+      <c r="C74" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0270=(没有可比较的文件)</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0280("APP_0280"),</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>521</v>
+        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>521</v>
@@ -5420,25 +5336,22 @@
         <v>298</v>
       </c>
       <c r="I74" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0280=フォルダの比較に失敗しました。</v>
+      </c>
+      <c r="J74" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0280=フォルダの比較に失敗しました。</v>
-      </c>
-      <c r="J74" s="5" t="str">
+        <v>APP_0280=Failed to compare folders.</v>
+      </c>
+      <c r="K74" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0280=Failed to compare folders.</v>
-      </c>
-      <c r="K74" s="6" t="str">
+        <v>APP_0280=文件夹比较失败。</v>
+      </c>
+    </row>
+    <row r="75" spans="3:11">
+      <c r="C75" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0280=文件夹比较失败。</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0290("APP_0290"),</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>522</v>
+        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>522</v>
@@ -5453,25 +5366,22 @@
         <v>273</v>
       </c>
       <c r="I75" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0290=シート同士の比較を開始します。</v>
+      </c>
+      <c r="J75" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0290=シート同士の比較を開始します。</v>
-      </c>
-      <c r="J75" s="5" t="str">
+        <v>APP_0290=Starting comparing sheets.</v>
+      </c>
+      <c r="K75" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0290=Starting comparing sheets.</v>
-      </c>
-      <c r="K75" s="6" t="str">
+        <v>APP_0290=开始相互比较工作表。</v>
+      </c>
+    </row>
+    <row r="76" spans="3:11">
+      <c r="C76" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0290=开始相互比较工作表。</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0300("APP_0300"),</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>523</v>
+        <v>/** シートを比較しています... */ APP_0300,</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>523</v>
@@ -5486,25 +5396,22 @@
         <v>274</v>
       </c>
       <c r="I76" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0300=シートを比較しています...</v>
+      </c>
+      <c r="J76" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0300=シートを比較しています...</v>
-      </c>
-      <c r="J76" s="5" t="str">
+        <v>APP_0300=Comparing sheets...</v>
+      </c>
+      <c r="K76" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0300=Comparing sheets...</v>
-      </c>
-      <c r="K76" s="6" t="str">
+        <v>APP_0300=比较工作表...</v>
+      </c>
+    </row>
+    <row r="77" spans="3:11">
+      <c r="C77" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0300=比较工作表...</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0310("APP_0310"),</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>524</v>
+        <v>/** シートの比較に失敗しました。 */ APP_0310,</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>524</v>
@@ -5519,25 +5426,22 @@
         <v>297</v>
       </c>
       <c r="I77" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0310=シートの比較に失敗しました。</v>
+      </c>
+      <c r="J77" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0310=シートの比較に失敗しました。</v>
-      </c>
-      <c r="J77" s="5" t="str">
+        <v>APP_0310=Failed to compare sheets.</v>
+      </c>
+      <c r="K77" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0310=Failed to compare sheets.</v>
-      </c>
-      <c r="K77" s="6" t="str">
+        <v>APP_0310=工作表比较失败。</v>
+      </c>
+    </row>
+    <row r="78" spans="3:11">
+      <c r="C78" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0310=工作表比较失败。</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0320("APP_0320"),</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>525</v>
+        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>525</v>
@@ -5552,25 +5456,22 @@
         <v>275</v>
       </c>
       <c r="I78" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
+      </c>
+      <c r="J78" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
-      </c>
-      <c r="J78" s="5" t="str">
+        <v>APP_0320=Starting comparing folder trees.</v>
+      </c>
+      <c r="K78" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>APP_0320=Starting comparing folder trees.</v>
-      </c>
-      <c r="K78" s="6" t="str">
+        <v>APP_0320=开始互相比较文件夹树。</v>
+      </c>
+    </row>
+    <row r="79" spans="3:11">
+      <c r="C79" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>APP_0320=开始互相比较文件夹树。</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0330("APP_0330"),</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>526</v>
+        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>526</v>
@@ -5597,13 +5498,10 @@
         <v>APP_0330=比较文件夹...</v>
       </c>
     </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0340("APP_0340"),</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>527</v>
+    <row r="80" spans="3:11">
+      <c r="C80" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ★失敗しました */ APP_0340,</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>527</v>
@@ -5630,13 +5528,10 @@
         <v>APP_0340=★失败</v>
       </c>
     </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0350("APP_0350"),</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>528</v>
+    <row r="81" spans="3:11">
+      <c r="C81" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポートを保存しています... */ APP_0350,</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>528</v>
@@ -5663,13 +5558,10 @@
         <v>APP_0350=保存比较结果报告...</v>
       </c>
     </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0360("APP_0360"),</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>529</v>
+    <row r="82" spans="3:11">
+      <c r="C82" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0360,</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>529</v>
@@ -5696,13 +5588,10 @@
         <v>APP_0360=保存比较结果报告失败。</v>
       </c>
     </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0370("APP_0370"),</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>530</v>
+    <row r="83" spans="3:11">
+      <c r="C83" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポートを表示しています... */ APP_0370,</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>530</v>
@@ -5729,13 +5618,10 @@
         <v>APP_0370=显示比较结果报告...</v>
       </c>
     </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0380("APP_0380"),</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>531</v>
+    <row r="84" spans="3:11">
+      <c r="C84" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0380,</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>531</v>
@@ -5762,13 +5648,10 @@
         <v>APP_0380=显示比较结果报告失败。</v>
       </c>
     </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0390("APP_0390"),</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>532</v>
+    <row r="85" spans="3:11">
+      <c r="C85" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>532</v>
@@ -5795,13 +5678,10 @@
         <v>APP_0390=文件夹比较失败。</v>
       </c>
     </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0400("APP_0400"),</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>533</v>
+    <row r="86" spans="3:11">
+      <c r="C86" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** (比較相手なし) */ APP_0400,</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>533</v>
@@ -5828,13 +5708,10 @@
         <v>APP_0400=(没有对比)</v>
       </c>
     </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0410("APP_0410"),</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>534</v>
+    <row r="87" spans="3:11">
+      <c r="C87" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** (差分なし) */ APP_0410,</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>534</v>
@@ -5861,13 +5738,10 @@
         <v>APP_0410=(没有区别)</v>
       </c>
     </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0420("APP_0420"),</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>535</v>
+    <row r="88" spans="3:11">
+      <c r="C88" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 差異発生%dシート */ APP_0420,</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>535</v>
@@ -5894,13 +5768,10 @@
         <v>APP_0420=差异工作表%d</v>
       </c>
     </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0430("APP_0430"),</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>536</v>
+    <row r="89" spans="3:11">
+      <c r="C89" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 余剰%dシート */ APP_0430,</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>536</v>
@@ -5927,13 +5798,10 @@
         <v>APP_0430=冗余工作表%d</v>
       </c>
     </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0440("APP_0440"),</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>537</v>
+    <row r="90" spans="3:11">
+      <c r="C90" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ブック%s :  */ APP_0440,</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>537</v>
@@ -5960,13 +5828,10 @@
         <v>APP_0440=工作簿%s：</v>
       </c>
     </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0450("APP_0450"),</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>538</v>
+    <row r="91" spans="3:11">
+      <c r="C91" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>538</v>
@@ -5993,13 +5858,10 @@
         <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
-    <row r="92" spans="2:11">
-      <c r="B92" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0460("APP_0460"),</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>539</v>
+    <row r="92" spans="3:11">
+      <c r="C92" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>539</v>
@@ -6026,13 +5888,10 @@
         <v>APP_0460=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0470("APP_0470"),</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>540</v>
+    <row r="93" spans="3:11">
+      <c r="C93" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** (比較相手なし) */ APP_0470,</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>540</v>
@@ -6059,13 +5918,10 @@
         <v>APP_0470=(没有对比)</v>
       </c>
     </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0480("APP_0480"),</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>541</v>
+    <row r="94" spans="3:11">
+      <c r="C94" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** フォルダ%s :  */ APP_0480,</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>541</v>
@@ -6092,13 +5948,10 @@
         <v xml:space="preserve">APP_0480=文件夹%s : </v>
       </c>
     </row>
-    <row r="95" spans="2:11">
-      <c r="B95" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0490("APP_0490"),</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>542</v>
+    <row r="95" spans="3:11">
+      <c r="C95" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0490,</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>542</v>
@@ -6125,13 +5978,10 @@
         <v>APP_0490=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0500("APP_0500"),</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>543</v>
+    <row r="96" spans="3:11">
+      <c r="C96" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0500,</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>543</v>
@@ -6158,13 +6008,10 @@
         <v>APP_0500=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
-    <row r="97" spans="2:11">
-      <c r="B97" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0510("APP_0510"),</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>544</v>
+    <row r="97" spans="3:11">
+      <c r="C97" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ★失敗しました */ APP_0510,</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>544</v>
@@ -6191,13 +6038,10 @@
         <v>APP_0510=★失败</v>
       </c>
     </row>
-    <row r="98" spans="2:11">
-      <c r="B98" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0520("APP_0520"),</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>545</v>
+    <row r="98" spans="3:11">
+      <c r="C98" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** (差分なし) */ APP_0520,</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>545</v>
@@ -6224,13 +6068,10 @@
         <v>APP_0520=(没有区别)</v>
       </c>
     </row>
-    <row r="99" spans="2:11">
-      <c r="B99" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0530("APP_0530"),</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>546</v>
+    <row r="99" spans="3:11">
+      <c r="C99" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 差異発生%dブック */ APP_0530,</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>546</v>
@@ -6257,13 +6098,10 @@
         <v>APP_0530=差异工作簿%d</v>
       </c>
     </row>
-    <row r="100" spans="2:11">
-      <c r="B100" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0540("APP_0540"),</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>547</v>
+    <row r="100" spans="3:11">
+      <c r="C100" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 余剰%dブック */ APP_0540,</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>547</v>
@@ -6290,13 +6128,10 @@
         <v>APP_0540=冗余工作簿%d</v>
       </c>
     </row>
-    <row r="101" spans="2:11">
-      <c r="B101" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0550("APP_0550"),</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>548</v>
+    <row r="101" spans="3:11">
+      <c r="C101" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較失敗%dブック */ APP_0550,</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>548</v>
@@ -6323,13 +6158,10 @@
         <v>APP_0550=失败工作簿%d</v>
       </c>
     </row>
-    <row r="102" spans="2:11">
-      <c r="B102" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0560("APP_0560"),</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>549</v>
+    <row r="102" spans="3:11">
+      <c r="C102" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** (比較対象ファイルなし) */ APP_0560,</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>549</v>
@@ -6356,13 +6188,10 @@
         <v>APP_0560=(没有可比较的文件)</v>
       </c>
     </row>
-    <row r="103" spans="2:11">
-      <c r="B103" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0570("APP_0570"),</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>550</v>
+    <row r="103" spans="3:11">
+      <c r="C103" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較実行日時： */ APP_0570,</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>550</v>
@@ -6389,13 +6218,10 @@
         <v>APP_0570=执行日期和时间：</v>
       </c>
     </row>
-    <row r="104" spans="2:11">
-      <c r="B104" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0580("APP_0580"),</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>551</v>
+    <row r="104" spans="3:11">
+      <c r="C104" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 作業用フォルダ： */ APP_0580,</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>551</v>
@@ -6422,13 +6248,10 @@
         <v>APP_0580=工作文件夹：</v>
       </c>
     </row>
-    <row r="105" spans="2:11">
-      <c r="B105" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0590("APP_0590"),</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>552</v>
+    <row r="105" spans="3:11">
+      <c r="C105" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** ブック%s： */ APP_0590,</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>552</v>
@@ -6455,13 +6278,10 @@
         <v>APP_0590=工作簿%s：</v>
       </c>
     </row>
-    <row r="106" spans="2:11">
-      <c r="B106" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0600("APP_0600"),</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>553</v>
+    <row r="106" spans="3:11">
+      <c r="C106" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 差分なし */ APP_0600,</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>553</v>
@@ -6488,13 +6308,10 @@
         <v>APP_0600=没有区别</v>
       </c>
     </row>
-    <row r="107" spans="2:11">
-      <c r="B107" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0610("APP_0610"),</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>554</v>
+    <row r="107" spans="3:11">
+      <c r="C107" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較失敗 */ APP_0610,</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>554</v>
@@ -6521,13 +6338,10 @@
         <v>APP_0610=比较失败</v>
       </c>
     </row>
-    <row r="108" spans="2:11">
-      <c r="B108" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0620("APP_0620"),</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>555</v>
+    <row r="108" spans="3:11">
+      <c r="C108" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>555</v>
@@ -6554,13 +6368,10 @@
         <v>APP_0620=冗余行（A: %d, B: %d）</v>
       </c>
     </row>
-    <row r="109" spans="2:11">
-      <c r="B109" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0630("APP_0630"),</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>556</v>
+    <row r="109" spans="3:11">
+      <c r="C109" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>556</v>
@@ -6587,13 +6398,10 @@
         <v>APP_0630=冗余列（A: %d, B: %d）</v>
       </c>
     </row>
-    <row r="110" spans="2:11">
-      <c r="B110" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0640("APP_0640"),</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>557</v>
+    <row r="110" spans="3:11">
+      <c r="C110" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 差分セル（%d） */ APP_0640,</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>557</v>
@@ -6620,13 +6428,10 @@
         <v>APP_0640=差异单元格（%d）</v>
       </c>
     </row>
-    <row r="111" spans="2:11">
-      <c r="B111" s="1" t="str">
-        <f t="shared" ref="B111:B174" si="10" xml:space="preserve"> C111 &amp; "(""" &amp; D111 &amp; """),"</f>
-        <v>APP_0650("APP_0650"),</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>558</v>
+    <row r="111" spans="3:11">
+      <c r="C111" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** (比較相手なし) */ APP_0650,</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>558</v>
@@ -6641,25 +6446,22 @@
         <v>277</v>
       </c>
       <c r="I111" s="4" t="str">
-        <f t="shared" ref="I111:I142" si="11" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; E111)</f>
+        <f t="shared" ref="I111:I142" si="10" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; E111)</f>
         <v>APP_0650=(比較相手なし)</v>
       </c>
       <c r="J111" s="5" t="str">
-        <f t="shared" ref="J111:J142" si="12" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; F111)</f>
+        <f t="shared" ref="J111:J142" si="11" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; F111)</f>
         <v>APP_0650=(no opponent)</v>
       </c>
       <c r="K111" s="6" t="str">
-        <f t="shared" ref="K111:K142" si="13" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; G111)</f>
+        <f t="shared" ref="K111:K142" si="12" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; G111)</f>
         <v>APP_0650=(没有对比)</v>
       </c>
     </row>
-    <row r="112" spans="2:11">
-      <c r="B112" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0660("APP_0660"),</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>559</v>
+    <row r="112" spans="3:11">
+      <c r="C112" s="1" t="str">
+        <f t="shared" ref="C112:C175" si="13" xml:space="preserve"> "/** " &amp; E112 &amp; " */ " &amp; D112 &amp; ","</f>
+        <v>/** 比較フォルダ%s： */ APP_0660,</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>559</v>
@@ -6674,25 +6476,22 @@
         <v>244</v>
       </c>
       <c r="I112" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0660=比較フォルダ%s：</v>
+      </c>
+      <c r="J112" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0660=比較フォルダ%s：</v>
-      </c>
-      <c r="J112" s="5" t="str">
+        <v xml:space="preserve">APP_0660=Folder %s : </v>
+      </c>
+      <c r="K112" s="6" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0660=Folder %s : </v>
-      </c>
-      <c r="K112" s="6" t="str">
+        <v>APP_0660=文件夹%s：</v>
+      </c>
+    </row>
+    <row r="113" spans="3:11">
+      <c r="C113" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0660=文件夹%s：</v>
-      </c>
-    </row>
-    <row r="113" spans="2:11">
-      <c r="B113" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0670("APP_0670"),</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>560</v>
+        <v>/** 作業用フォルダ： */ APP_0670,</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>560</v>
@@ -6707,25 +6506,22 @@
         <v>212</v>
       </c>
       <c r="I113" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0670=作業用フォルダ：</v>
+      </c>
+      <c r="J113" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0670=作業用フォルダ：</v>
-      </c>
-      <c r="J113" s="5" t="str">
+        <v xml:space="preserve">APP_0670=Working dir : </v>
+      </c>
+      <c r="K113" s="6" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0670=Working dir : </v>
-      </c>
-      <c r="K113" s="6" t="str">
+        <v>APP_0670=工作文件夹：</v>
+      </c>
+    </row>
+    <row r="114" spans="3:11">
+      <c r="C114" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0670=工作文件夹：</v>
-      </c>
-    </row>
-    <row r="114" spans="2:11">
-      <c r="B114" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0680("APP_0680"),</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>561</v>
+        <v>/** ワークシート */ APP_0680,</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>561</v>
@@ -6740,25 +6536,22 @@
         <v>127</v>
       </c>
       <c r="I114" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0680=ワークシート</v>
+      </c>
+      <c r="J114" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0680=ワークシート</v>
-      </c>
-      <c r="J114" s="5" t="str">
+        <v>APP_0680=Worksheet</v>
+      </c>
+      <c r="K114" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0680=Worksheet</v>
-      </c>
-      <c r="K114" s="6" t="str">
+        <v>APP_0680=工作表</v>
+      </c>
+    </row>
+    <row r="115" spans="3:11">
+      <c r="C115" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0680=工作表</v>
-      </c>
-    </row>
-    <row r="115" spans="2:11">
-      <c r="B115" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0690("APP_0690"),</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>562</v>
+        <v>/** グラフシート */ APP_0690,</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>562</v>
@@ -6773,25 +6566,22 @@
         <v>283</v>
       </c>
       <c r="I115" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0690=グラフシート</v>
+      </c>
+      <c r="J115" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0690=グラフシート</v>
-      </c>
-      <c r="J115" s="5" t="str">
+        <v>APP_0690=Chart</v>
+      </c>
+      <c r="K115" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0690=Chart</v>
-      </c>
-      <c r="K115" s="6" t="str">
+        <v>APP_0690=图表表</v>
+      </c>
+    </row>
+    <row r="116" spans="3:11">
+      <c r="C116" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0690=图表表</v>
-      </c>
-    </row>
-    <row r="116" spans="2:11">
-      <c r="B116" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0700("APP_0700"),</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>563</v>
+        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>563</v>
@@ -6806,25 +6596,22 @@
         <v>284</v>
       </c>
       <c r="I116" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
+      </c>
+      <c r="J116" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
-      </c>
-      <c r="J116" s="5" t="str">
+        <v>APP_0700=MS Excel 5.0 Dialog</v>
+      </c>
+      <c r="K116" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0700=MS Excel 5.0 Dialog</v>
-      </c>
-      <c r="K116" s="6" t="str">
+        <v>APP_0700=MS Excel 5.0 对话表</v>
+      </c>
+    </row>
+    <row r="117" spans="3:11">
+      <c r="C117" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0700=MS Excel 5.0 对话表</v>
-      </c>
-    </row>
-    <row r="117" spans="2:11">
-      <c r="B117" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0710("APP_0710"),</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>564</v>
+        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>564</v>
@@ -6839,25 +6626,22 @@
         <v>128</v>
       </c>
       <c r="I117" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0710=Excel 4.0 マクロシート</v>
+      </c>
+      <c r="J117" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0710=Excel 4.0 マクロシート</v>
-      </c>
-      <c r="J117" s="5" t="str">
+        <v>APP_0710=Excel 4.0 Macro</v>
+      </c>
+      <c r="K117" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0710=Excel 4.0 Macro</v>
-      </c>
-      <c r="K117" s="6" t="str">
+        <v>APP_0710=Excel 4.0 宏表</v>
+      </c>
+    </row>
+    <row r="118" spans="3:11">
+      <c r="C118" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0710=Excel 4.0 宏表</v>
-      </c>
-    </row>
-    <row r="118" spans="2:11">
-      <c r="B118" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0720("APP_0720"),</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>565</v>
+        <v>/** (差分なし) */ APP_0720,</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>565</v>
@@ -6872,25 +6656,22 @@
         <v>278</v>
       </c>
       <c r="I118" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0720=(差分なし)</v>
+      </c>
+      <c r="J118" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0720=(差分なし)</v>
-      </c>
-      <c r="J118" s="5" t="str">
+        <v>APP_0720=(no diffs)</v>
+      </c>
+      <c r="K118" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0720=(no diffs)</v>
-      </c>
-      <c r="K118" s="6" t="str">
+        <v>APP_0720=(没有区别)</v>
+      </c>
+    </row>
+    <row r="119" spans="3:11">
+      <c r="C119" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0720=(没有区别)</v>
-      </c>
-    </row>
-    <row r="119" spans="2:11">
-      <c r="B119" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0730("APP_0730"),</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>566</v>
+        <v>/** 余剰行%d */ APP_0730,</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>566</v>
@@ -6905,25 +6686,22 @@
         <v>129</v>
       </c>
       <c r="I119" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0730=余剰行%d</v>
+      </c>
+      <c r="J119" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0730=余剰行%d</v>
-      </c>
-      <c r="J119" s="5" t="str">
+        <v>APP_0730=redundant rows:%d</v>
+      </c>
+      <c r="K119" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0730=redundant rows:%d</v>
-      </c>
-      <c r="K119" s="6" t="str">
+        <v>APP_0730=冗余行%d</v>
+      </c>
+    </row>
+    <row r="120" spans="3:11">
+      <c r="C120" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0730=冗余行%d</v>
-      </c>
-    </row>
-    <row r="120" spans="2:11">
-      <c r="B120" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0740("APP_0740"),</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>567</v>
+        <v>/** 余剰列%d */ APP_0740,</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>567</v>
@@ -6938,25 +6716,22 @@
         <v>130</v>
       </c>
       <c r="I120" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0740=余剰列%d</v>
+      </c>
+      <c r="J120" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0740=余剰列%d</v>
-      </c>
-      <c r="J120" s="5" t="str">
+        <v>APP_0740=redundant columns:%d</v>
+      </c>
+      <c r="K120" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0740=redundant columns:%d</v>
-      </c>
-      <c r="K120" s="6" t="str">
+        <v>APP_0740=冗余列%d</v>
+      </c>
+    </row>
+    <row r="121" spans="3:11">
+      <c r="C121" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0740=冗余列%d</v>
-      </c>
-    </row>
-    <row r="121" spans="2:11">
-      <c r="B121" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0750("APP_0750"),</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>568</v>
+        <v>/** 差分セル%d */ APP_0750,</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>568</v>
@@ -6971,25 +6746,22 @@
         <v>285</v>
       </c>
       <c r="I121" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0750=差分セル%d</v>
+      </c>
+      <c r="J121" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0750=差分セル%d</v>
-      </c>
-      <c r="J121" s="5" t="str">
+        <v>APP_0750=diff cells:%d</v>
+      </c>
+      <c r="K121" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0750=diff cells:%d</v>
-      </c>
-      <c r="K121" s="6" t="str">
+        <v>APP_0750=差异单元格%d</v>
+      </c>
+    </row>
+    <row r="122" spans="3:11">
+      <c r="C122" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0750=差异单元格%d</v>
-      </c>
-    </row>
-    <row r="122" spans="2:11">
-      <c r="B122" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0760("APP_0760"),</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>569</v>
+        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>569</v>
@@ -7004,25 +6776,22 @@
         <v>170</v>
       </c>
       <c r="I122" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
+      </c>
+      <c r="J122" s="5" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
-      </c>
-      <c r="J122" s="5" t="str">
+        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
+      </c>
+      <c r="K122" s="6" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
-      </c>
-      <c r="K122" s="6" t="str">
+        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
+      </c>
+    </row>
+    <row r="123" spans="3:11">
+      <c r="C123" s="1" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
-      </c>
-    </row>
-    <row r="123" spans="2:11">
-      <c r="B123" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0770("APP_0770"),</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>570</v>
+        <v>/** 行%d */ APP_0770,</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>570</v>
@@ -7037,25 +6806,22 @@
         <v>73</v>
       </c>
       <c r="I123" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0770=行%d</v>
+      </c>
+      <c r="J123" s="5" t="str">
         <f t="shared" si="11"/>
+        <v>APP_0770=Row %d</v>
+      </c>
+      <c r="K123" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>APP_0770=行%d</v>
       </c>
-      <c r="J123" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0770=Row %d</v>
-      </c>
-      <c r="K123" s="6" t="str">
+    </row>
+    <row r="124" spans="3:11">
+      <c r="C124" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0770=行%d</v>
-      </c>
-    </row>
-    <row r="124" spans="2:11">
-      <c r="B124" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0780("APP_0780"),</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>571</v>
+        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>571</v>
@@ -7070,25 +6836,22 @@
         <v>171</v>
       </c>
       <c r="I124" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
+      </c>
+      <c r="J124" s="5" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
-      </c>
-      <c r="J124" s="5" t="str">
+        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
+      </c>
+      <c r="K124" s="6" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
-      </c>
-      <c r="K124" s="6" t="str">
+        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
+      </c>
+    </row>
+    <row r="125" spans="3:11">
+      <c r="C125" s="1" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
-      </c>
-    </row>
-    <row r="125" spans="2:11">
-      <c r="B125" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0790("APP_0790"),</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>572</v>
+        <v>/** %s列 */ APP_0790,</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>572</v>
@@ -7103,25 +6866,22 @@
         <v>74</v>
       </c>
       <c r="I125" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0790=%s列</v>
+      </c>
+      <c r="J125" s="5" t="str">
         <f t="shared" si="11"/>
+        <v>APP_0790=Column %s</v>
+      </c>
+      <c r="K125" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>APP_0790=%s列</v>
       </c>
-      <c r="J125" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0790=Column %s</v>
-      </c>
-      <c r="K125" s="6" t="str">
+    </row>
+    <row r="126" spans="3:11">
+      <c r="C126" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0790=%s列</v>
-      </c>
-    </row>
-    <row r="126" spans="2:11">
-      <c r="B126" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0800("APP_0800"),</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>573</v>
+        <v>/** 差分セル :  */ APP_0800,</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>573</v>
@@ -7136,25 +6896,22 @@
         <v>286</v>
       </c>
       <c r="I126" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0800=差分セル : </v>
+      </c>
+      <c r="J126" s="5" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0800=差分セル : </v>
-      </c>
-      <c r="J126" s="5" t="str">
+        <v xml:space="preserve">APP_0800=Diff cells : </v>
+      </c>
+      <c r="K126" s="6" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0800=Diff cells : </v>
-      </c>
-      <c r="K126" s="6" t="str">
+        <v xml:space="preserve">APP_0800=差异单元格 : </v>
+      </c>
+    </row>
+    <row r="127" spans="3:11">
+      <c r="C127" s="1" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">APP_0800=差异单元格 : </v>
-      </c>
-    </row>
-    <row r="127" spans="2:11">
-      <c r="B127" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0810("APP_0810"),</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>574</v>
+        <v>/** (比較相手なし) */ APP_0810,</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>574</v>
@@ -7169,25 +6926,22 @@
         <v>277</v>
       </c>
       <c r="I127" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0810=(比較相手なし)</v>
+      </c>
+      <c r="J127" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0810=(比較相手なし)</v>
-      </c>
-      <c r="J127" s="5" t="str">
+        <v>APP_0810=(no opponent)</v>
+      </c>
+      <c r="K127" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0810=(no opponent)</v>
-      </c>
-      <c r="K127" s="6" t="str">
+        <v>APP_0810=(没有对比)</v>
+      </c>
+    </row>
+    <row r="128" spans="3:11">
+      <c r="C128" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0810=(没有对比)</v>
-      </c>
-    </row>
-    <row r="128" spans="2:11">
-      <c r="B128" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0820("APP_0820"),</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>575</v>
+        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>575</v>
@@ -7202,25 +6956,22 @@
         <v>287</v>
       </c>
       <c r="I128" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
+      </c>
+      <c r="J128" s="5" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
-      </c>
-      <c r="J128" s="5" t="str">
+        <v xml:space="preserve">APP_0820=Root folder %s : </v>
+      </c>
+      <c r="K128" s="6" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0820=Root folder %s : </v>
-      </c>
-      <c r="K128" s="6" t="str">
+        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
+      </c>
+    </row>
+    <row r="129" spans="3:11">
+      <c r="C129" s="1" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
-      </c>
-    </row>
-    <row r="129" spans="2:11">
-      <c r="B129" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0830("APP_0830"),</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>576</v>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0830,</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>576</v>
@@ -7235,25 +6986,22 @@
         <v>126</v>
       </c>
       <c r="I129" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0830=■差分サマリ ---------------------------------------------------</v>
+      </c>
+      <c r="J129" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0830=■差分サマリ ---------------------------------------------------</v>
-      </c>
-      <c r="J129" s="5" t="str">
+        <v>APP_0830=## SUMMARY -----------------------------------------------------</v>
+      </c>
+      <c r="K129" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0830=## SUMMARY -----------------------------------------------------</v>
-      </c>
-      <c r="K129" s="6" t="str">
+        <v>APP_0830=■差异摘要 -----------------------------------------------------</v>
+      </c>
+    </row>
+    <row r="130" spans="3:11">
+      <c r="C130" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0830=■差异摘要 -----------------------------------------------------</v>
-      </c>
-    </row>
-    <row r="130" spans="2:11">
-      <c r="B130" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0840("APP_0840"),</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>577</v>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0840,</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>577</v>
@@ -7268,25 +7016,22 @@
         <v>280</v>
       </c>
       <c r="I130" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0840=■差分詳細 -----------------------------------------------------</v>
+      </c>
+      <c r="J130" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0840=■差分詳細 -----------------------------------------------------</v>
-      </c>
-      <c r="J130" s="5" t="str">
+        <v>APP_0840=## DETAIL ------------------------------------------------------</v>
+      </c>
+      <c r="K130" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0840=## DETAIL ------------------------------------------------------</v>
-      </c>
-      <c r="K130" s="6" t="str">
+        <v>APP_0840=■差异细节 -----------------------------------------------------</v>
+      </c>
+    </row>
+    <row r="131" spans="3:11">
+      <c r="C131" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0840=■差异细节 -----------------------------------------------------</v>
-      </c>
-    </row>
-    <row r="131" spans="2:11">
-      <c r="B131" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0850("APP_0850"),</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>578</v>
+        <v>/** ★失敗しました */ APP_0850,</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>578</v>
@@ -7301,25 +7046,22 @@
         <v>267</v>
       </c>
       <c r="I131" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0850=★失敗しました</v>
+      </c>
+      <c r="J131" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0850=★失敗しました</v>
-      </c>
-      <c r="J131" s="5" t="str">
+        <v>APP_0850=★Failed</v>
+      </c>
+      <c r="K131" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0850=★Failed</v>
-      </c>
-      <c r="K131" s="6" t="str">
+        <v>APP_0850=★失败</v>
+      </c>
+    </row>
+    <row r="132" spans="3:11">
+      <c r="C132" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0850=★失败</v>
-      </c>
-    </row>
-    <row r="132" spans="2:11">
-      <c r="B132" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0860("APP_0860"),</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>579</v>
+        <v>/** 組み合わせ編集 */ APP_0860,</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>579</v>
@@ -7334,25 +7076,22 @@
         <v>307</v>
       </c>
       <c r="I132" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0860=組み合わせ編集</v>
+      </c>
+      <c r="J132" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0860=組み合わせ編集</v>
-      </c>
-      <c r="J132" s="5" t="str">
+        <v>APP_0860=Edit Pairing</v>
+      </c>
+      <c r="K132" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0860=Edit Pairing</v>
-      </c>
-      <c r="K132" s="6" t="str">
+        <v>APP_0860=组合编辑</v>
+      </c>
+    </row>
+    <row r="133" spans="3:11">
+      <c r="C133" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0860=组合编辑</v>
-      </c>
-    </row>
-    <row r="133" spans="2:11">
-      <c r="B133" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0870("APP_0870"),</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>580</v>
+        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>580</v>
@@ -7367,25 +7106,22 @@
         <v>426</v>
       </c>
       <c r="I133" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
+      </c>
+      <c r="J133" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
-      </c>
-      <c r="J133" s="5" t="str">
+        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
+      </c>
+      <c r="K133" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
-      </c>
-      <c r="K133" s="6" t="str">
+        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
+      </c>
+    </row>
+    <row r="134" spans="3:11">
+      <c r="C134" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
-      </c>
-    </row>
-    <row r="134" spans="2:11">
-      <c r="B134" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0880("APP_0880"),</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>581</v>
+        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>581</v>
@@ -7400,25 +7136,22 @@
         <v>427</v>
       </c>
       <c r="I134" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
+      </c>
+      <c r="J134" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
-      </c>
-      <c r="J134" s="5" t="str">
+        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
+      </c>
+      <c r="K134" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
-      </c>
-      <c r="K134" s="6" t="str">
+        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
+      </c>
+    </row>
+    <row r="135" spans="3:11">
+      <c r="C135" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
-      </c>
-    </row>
-    <row r="135" spans="2:11">
-      <c r="B135" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0890("APP_0890"),</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>582</v>
+        <v>/** 共有ドライブ */ APP_0890,</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>582</v>
@@ -7433,25 +7166,22 @@
         <v>435</v>
       </c>
       <c r="I135" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0890=共有ドライブ</v>
+      </c>
+      <c r="J135" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0890=共有ドライブ</v>
-      </c>
-      <c r="J135" s="5" t="str">
+        <v>APP_0890=Shared drives</v>
+      </c>
+      <c r="K135" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0890=Shared drives</v>
-      </c>
-      <c r="K135" s="6" t="str">
+        <v>APP_0890=共享云端硬盘</v>
+      </c>
+    </row>
+    <row r="136" spans="3:11">
+      <c r="C136" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0890=共享云端硬盘</v>
-      </c>
-    </row>
-    <row r="136" spans="2:11">
-      <c r="B136" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0900("APP_0900"),</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>583</v>
+        <v>/** すべてのファイル */ APP_0900,</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>583</v>
@@ -7466,25 +7196,22 @@
         <v>431</v>
       </c>
       <c r="I136" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0900=すべてのファイル</v>
+      </c>
+      <c r="J136" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0900=すべてのファイル</v>
-      </c>
-      <c r="J136" s="5" t="str">
+        <v>APP_0900=All files</v>
+      </c>
+      <c r="K136" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0900=All files</v>
-      </c>
-      <c r="K136" s="6" t="str">
+        <v>APP_0900=所有文件</v>
+      </c>
+    </row>
+    <row r="137" spans="3:11">
+      <c r="C137" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0900=所有文件</v>
-      </c>
-    </row>
-    <row r="137" spans="2:11">
-      <c r="B137" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0910("APP_0910"),</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>584</v>
+        <v>/** スター付き */ APP_0910,</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>584</v>
@@ -7499,25 +7226,22 @@
         <v>436</v>
       </c>
       <c r="I137" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0910=スター付き</v>
+      </c>
+      <c r="J137" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0910=スター付き</v>
-      </c>
-      <c r="J137" s="5" t="str">
+        <v>APP_0910=Starred</v>
+      </c>
+      <c r="K137" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0910=Starred</v>
-      </c>
-      <c r="K137" s="6" t="str">
+        <v>APP_0910=已加星标</v>
+      </c>
+    </row>
+    <row r="138" spans="3:11">
+      <c r="C138" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0910=已加星标</v>
-      </c>
-    </row>
-    <row r="138" spans="2:11">
-      <c r="B138" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0920("APP_0920"),</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>585</v>
+        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>585</v>
@@ -7532,25 +7256,22 @@
         <v>438</v>
       </c>
       <c r="I138" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
+      </c>
+      <c r="J138" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
-      </c>
-      <c r="J138" s="5" t="str">
+        <v>APP_0920=Failed to download the file from Google Drive.</v>
+      </c>
+      <c r="K138" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0920=Failed to download the file from Google Drive.</v>
-      </c>
-      <c r="K138" s="6" t="str">
+        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
+      </c>
+    </row>
+    <row r="139" spans="3:11">
+      <c r="C139" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
-      </c>
-    </row>
-    <row r="139" spans="2:11">
-      <c r="B139" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0930("APP_0930"),</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>586</v>
+        <v>/** 更新者不明 */ APP_0930,</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>586</v>
@@ -7565,25 +7286,22 @@
         <v>387</v>
       </c>
       <c r="I139" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0930=更新者不明</v>
+      </c>
+      <c r="J139" s="5" t="str">
         <f t="shared" si="11"/>
+        <v>APP_0930=Unknown</v>
+      </c>
+      <c r="K139" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>APP_0930=更新者不明</v>
       </c>
-      <c r="J139" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0930=Unknown</v>
-      </c>
-      <c r="K139" s="6" t="str">
+    </row>
+    <row r="140" spans="3:11">
+      <c r="C140" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0930=更新者不明</v>
-      </c>
-    </row>
-    <row r="140" spans="2:11">
-      <c r="B140" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0940("APP_0940"),</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>587</v>
+        <v>/** 最新版 */ APP_0940,</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>587</v>
@@ -7598,25 +7316,22 @@
         <v>389</v>
       </c>
       <c r="I140" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0940=最新版</v>
+      </c>
+      <c r="J140" s="5" t="str">
         <f t="shared" si="11"/>
+        <v>APP_0940=Latest</v>
+      </c>
+      <c r="K140" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>APP_0940=最新版</v>
       </c>
-      <c r="J140" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0940=Latest</v>
-      </c>
-      <c r="K140" s="6" t="str">
+    </row>
+    <row r="141" spans="3:11">
+      <c r="C141" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0940=最新版</v>
-      </c>
-    </row>
-    <row r="141" spans="2:11">
-      <c r="B141" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0950("APP_0950"),</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>588</v>
+        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>588</v>
@@ -7631,25 +7346,22 @@
         <v>363</v>
       </c>
       <c r="I141" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
+      </c>
+      <c r="J141" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
-      </c>
-      <c r="J141" s="5" t="str">
+        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
+      </c>
+      <c r="K141" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
-      </c>
-      <c r="K141" s="6" t="str">
+        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
+      </c>
+    </row>
+    <row r="142" spans="3:11">
+      <c r="C142" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
-      </c>
-    </row>
-    <row r="142" spans="2:11">
-      <c r="B142" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0960("APP_0960"),</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>589</v>
+        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>589</v>
@@ -7664,25 +7376,22 @@
         <v>366</v>
       </c>
       <c r="I142" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0960=資格情報を削除しました。</v>
+      </c>
+      <c r="J142" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>APP_0960=資格情報を削除しました。</v>
-      </c>
-      <c r="J142" s="5" t="str">
+        <v>APP_0960=Credentials have been deleted.</v>
+      </c>
+      <c r="K142" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>APP_0960=Credentials have been deleted.</v>
-      </c>
-      <c r="K142" s="6" t="str">
+        <v>APP_0960=已删除凭据。</v>
+      </c>
+    </row>
+    <row r="143" spans="3:11">
+      <c r="C143" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>APP_0960=已删除凭据。</v>
-      </c>
-    </row>
-    <row r="143" spans="2:11">
-      <c r="B143" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0970("APP_0970"),</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>590</v>
+        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>590</v>
@@ -7709,13 +7418,10 @@
         <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
     </row>
-    <row r="144" spans="2:11">
-      <c r="B144" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0980("APP_0980"),</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>591</v>
+    <row r="144" spans="3:11">
+      <c r="C144" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>591</v>
@@ -7742,13 +7448,10 @@
         <v>APP_0980=删除凭据失败。</v>
       </c>
     </row>
-    <row r="145" spans="2:11">
-      <c r="B145" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0990("APP_0990"),</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>592</v>
+    <row r="145" spans="3:11">
+      <c r="C145" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>592</v>
@@ -7775,13 +7478,10 @@
         <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
-    <row r="146" spans="2:11">
-      <c r="B146" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1000("APP_1000"),</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>593</v>
+    <row r="146" spans="3:11">
+      <c r="C146" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Google連携エラー */ APP_1000,</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>593</v>
@@ -7808,13 +7508,10 @@
         <v>APP_1000=Google关联错误</v>
       </c>
     </row>
-    <row r="147" spans="2:11">
-      <c r="B147" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1010("APP_1010"),</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>594</v>
+    <row r="147" spans="3:11">
+      <c r="C147" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>594</v>
@@ -7841,13 +7538,10 @@
         <v>APP_1010=Google关联处理过程中发生错误。</v>
       </c>
     </row>
-    <row r="148" spans="2:11">
-      <c r="B148" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1020("APP_1020"),</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>595</v>
+    <row r="148" spans="3:11">
+      <c r="C148" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>595</v>
@@ -7874,13 +7568,10 @@
         <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
-    <row r="149" spans="2:11">
-      <c r="B149" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1030("APP_1030"),</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>596</v>
+    <row r="149" spans="3:11">
+      <c r="C149" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>596</v>
@@ -7907,13 +7598,10 @@
         <v>APP_1030=已从Google云端硬盘下载文件</v>
       </c>
     </row>
-    <row r="150" spans="2:11">
-      <c r="B150" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1040("APP_1040"),</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>597</v>
+    <row r="150" spans="3:11">
+      <c r="C150" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>597</v>
@@ -7940,13 +7628,10 @@
         <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
     </row>
-    <row r="151" spans="2:11">
-      <c r="B151" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1050("APP_1050"),</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>598</v>
+    <row r="151" spans="3:11">
+      <c r="C151" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>598</v>
@@ -7973,13 +7658,10 @@
         <v>APP_1050=显示工作文件夹失败。</v>
       </c>
     </row>
-    <row r="152" spans="2:11">
-      <c r="B152" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1060("APP_1060"),</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>599</v>
+    <row r="152" spans="3:11">
+      <c r="C152" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>599</v>
@@ -8006,13 +7688,10 @@
         <v>APP_1060=改变工作文件夹</v>
       </c>
     </row>
-    <row r="153" spans="2:11">
-      <c r="B153" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1070("APP_1070"),</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>600</v>
+    <row r="153" spans="3:11">
+      <c r="C153" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>600</v>
@@ -8039,13 +7718,10 @@
         <v>APP_1070=更改工作文件夹失败。</v>
       </c>
     </row>
-    <row r="154" spans="2:11">
-      <c r="B154" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1080("APP_1080"),</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>601</v>
+    <row r="154" spans="3:11">
+      <c r="C154" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>601</v>
@@ -8072,13 +7748,10 @@
         <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
     </row>
-    <row r="155" spans="2:11">
-      <c r="B155" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1091("APP_1091"),</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>602</v>
+    <row r="155" spans="3:11">
+      <c r="C155" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>602</v>
@@ -8105,13 +7778,10 @@
         <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
     </row>
-    <row r="156" spans="2:11">
-      <c r="B156" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1092("APP_1092"),</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>603</v>
+    <row r="156" spans="3:11">
+      <c r="C156" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>603</v>
@@ -8138,13 +7808,10 @@
         <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
     </row>
-    <row r="157" spans="2:11">
-      <c r="B157" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1093("APP_1093"),</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>604</v>
+    <row r="157" spans="3:11">
+      <c r="C157" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>604</v>
@@ -8171,13 +7838,10 @@
         <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
     </row>
-    <row r="158" spans="2:11">
-      <c r="B158" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1100("APP_1100"),</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>605</v>
+    <row r="158" spans="3:11">
+      <c r="C158" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>605</v>
@@ -8204,13 +7868,10 @@
         <v>APP_1100=方眼Diff  -  详细设置</v>
       </c>
     </row>
-    <row r="159" spans="2:11">
-      <c r="B159" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1110("APP_1110"),</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>606</v>
+    <row r="159" spans="3:11">
+      <c r="C159" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>606</v>
@@ -8237,13 +7898,10 @@
         <v>APP_1110=选择用于比较的文件夹</v>
       </c>
     </row>
-    <row r="160" spans="2:11">
-      <c r="B160" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1120("APP_1120"),</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>607</v>
+    <row r="160" spans="3:11">
+      <c r="C160" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>607</v>
@@ -8270,13 +7928,10 @@
         <v>APP_1120=选择用于比较的工作簿</v>
       </c>
     </row>
-    <row r="161" spans="2:11">
-      <c r="B161" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1130("APP_1130"),</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>608</v>
+    <row r="161" spans="3:11">
+      <c r="C161" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Excel ブック */ APP_1130,</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>608</v>
@@ -8303,13 +7958,10 @@
         <v>APP_1130=Excel工作簿</v>
       </c>
     </row>
-    <row r="162" spans="2:11">
-      <c r="B162" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1140("APP_1140"),</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>609</v>
+    <row r="162" spans="3:11">
+      <c r="C162" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** ファイルを読み込めません： */ APP_1140,</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>609</v>
@@ -8336,13 +7988,10 @@
         <v>APP_1140=无法读取文件：</v>
       </c>
     </row>
-    <row r="163" spans="2:11">
-      <c r="B163" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1150("APP_1150"),</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>610</v>
+    <row r="163" spans="3:11">
+      <c r="C163" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** シートが見つかりません： */ APP_1150,</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>610</v>
@@ -8369,13 +8018,10 @@
         <v>APP_1150=没有找到工作表：</v>
       </c>
     </row>
-    <row r="164" spans="2:11">
-      <c r="B164" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1160("APP_1160"),</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>611</v>
+    <row r="164" spans="3:11">
+      <c r="C164" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** フォルダを読み込めません： */ APP_1160,</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>611</v>
@@ -8402,13 +8048,10 @@
         <v>APP_1160=无法读取文件夹：</v>
       </c>
     </row>
-    <row r="165" spans="2:11">
-      <c r="B165" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1170("APP_1170"),</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>612</v>
+    <row r="165" spans="3:11">
+      <c r="C165" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>612</v>
@@ -8435,13 +8078,10 @@
         <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
     </row>
-    <row r="166" spans="2:11">
-      <c r="B166" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1180("APP_1180"),</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>613</v>
+    <row r="166" spans="3:11">
+      <c r="C166" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>613</v>
@@ -8468,13 +8108,10 @@
         <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
     </row>
-    <row r="167" spans="2:11">
-      <c r="B167" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1190("APP_1190"),</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>614</v>
+    <row r="167" spans="3:11">
+      <c r="C167" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>614</v>
@@ -8501,13 +8138,10 @@
         <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
     </row>
-    <row r="168" spans="2:11">
-      <c r="B168" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1200("APP_1200"),</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>615</v>
+    <row r="168" spans="3:11">
+      <c r="C168" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 予期せぬ例外が発生しました。 */ APP_1200,</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>615</v>
@@ -8534,13 +8168,10 @@
         <v>APP_1200=意外的例外。</v>
       </c>
     </row>
-    <row r="169" spans="2:11">
-      <c r="B169" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1210("APP_1210"),</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>616</v>
+    <row r="169" spans="3:11">
+      <c r="C169" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>616</v>
@@ -8567,13 +8198,10 @@
         <v>APP_1210=创建工作文件夹失败。</v>
       </c>
     </row>
-    <row r="170" spans="2:11">
-      <c r="B170" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1220("APP_1220"),</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>617</v>
+    <row r="170" spans="3:11">
+      <c r="C170" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>617</v>
@@ -8600,13 +8228,10 @@
         <v>APP_1220=请指定其他位置。</v>
       </c>
     </row>
-    <row r="171" spans="2:11">
-      <c r="B171" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1230("APP_1230"),</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>618</v>
+    <row r="171" spans="3:11">
+      <c r="C171" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの変更 */ APP_1230,</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>618</v>
@@ -8633,13 +8258,10 @@
         <v>APP_1230=改变工作文件夹</v>
       </c>
     </row>
-    <row r="172" spans="2:11">
-      <c r="B172" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1240("APP_1240"),</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>619</v>
+    <row r="172" spans="3:11">
+      <c r="C172" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 処理を中止しました。 */ APP_1240,</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>619</v>
@@ -8666,13 +8288,10 @@
         <v>APP_1240=处理已被取消。</v>
       </c>
     </row>
-    <row r="173" spans="2:11">
-      <c r="B173" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1250("APP_1250"),</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>620</v>
+    <row r="173" spans="3:11">
+      <c r="C173" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** パスワード指定 */ APP_1250,</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>620</v>
@@ -8699,13 +8318,10 @@
         <v>APP_1250=输入密码</v>
       </c>
     </row>
-    <row r="174" spans="2:11">
-      <c r="B174" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1260("APP_1260"),</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>621</v>
+    <row r="174" spans="3:11">
+      <c r="C174" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>621</v>
@@ -8732,13 +8348,10 @@
         <v>APP_1260=%s 是受密码保护的。</v>
       </c>
     </row>
-    <row r="175" spans="2:11">
-      <c r="B175" s="1" t="str">
-        <f t="shared" ref="B175:B176" si="17" xml:space="preserve"> C175 &amp; "(""" &amp; D175 &amp; """),"</f>
-        <v>APP_1270("APP_1270"),</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>622</v>
+    <row r="175" spans="3:11">
+      <c r="C175" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>622</v>
@@ -8765,13 +8378,10 @@
         <v>APP_1270=有新版本可用。</v>
       </c>
     </row>
-    <row r="176" spans="2:11">
-      <c r="B176" s="1" t="str">
-        <f t="shared" si="17"/>
-        <v>APP_1280("APP_1280"),</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>623</v>
+    <row r="176" spans="3:11">
+      <c r="C176" s="1" t="str">
+        <f t="shared" ref="C176:C177" si="17" xml:space="preserve"> "/** " &amp; E176 &amp; " */ " &amp; D176 &amp; ","</f>
+        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>623</v>
@@ -8798,13 +8408,10 @@
         <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
       </c>
     </row>
-    <row r="177" spans="2:11">
-      <c r="B177" s="1" t="str">
-        <f xml:space="preserve"> C177 &amp; "(""" &amp; D177 &amp; """),"</f>
-        <v>APP_1290("APP_1290"),</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>624</v>
+    <row r="177" spans="3:11">
+      <c r="C177" s="1" t="str">
+        <f t="shared" si="17"/>
+        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>624</v>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namba\OneDrive\workspace_202509\hogandiff4\xyz.hotchpotch.hogandiff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAC45A9D-4CB8-4E80-9C2F-6FB692BDF6DA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,65 +41,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="625">
-  <si>
-    <t>fx.MenuPane.020</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="624">
   <si>
     <t>website</t>
   </si>
   <si>
-    <t>fx.TargetSelectionPane.020</t>
-  </si>
-  <si>
     <t>シート名：</t>
   </si>
   <si>
     <t>実行</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.010</t>
-  </si>
-  <si>
     <t>比較オプション</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.compare.010</t>
-  </si>
-  <si>
     <t>行の挿入／削除を考慮する</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.compare.020</t>
-  </si>
-  <si>
     <t>列の挿入／削除を考慮する</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.compare.030</t>
-  </si>
-  <si>
     <t>値を比較する</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.compare.040</t>
-  </si>
-  <si>
     <t>数式を比較する</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.020</t>
-  </si>
-  <si>
     <t>レポートオプション</t>
   </si>
   <si>
-    <t>fx.SettingsPane1.report.010</t>
-  </si>
-  <si>
-    <t>fx.SettingsPane1.report.020</t>
-  </si>
-  <si>
     <t>実行オプション</t>
   </si>
   <si>
@@ -109,31 +79,19 @@
     <t>言語</t>
   </si>
   <si>
-    <t>fx.SettingsPane2.020</t>
-  </si>
-  <si>
     <t>作業用\nフォルダ</t>
   </si>
   <si>
     <t>開く</t>
   </si>
   <si>
-    <t>fx.SettingsPane2.workDir.020</t>
-  </si>
-  <si>
     <t>変更...</t>
   </si>
   <si>
-    <t>fx.SettingsPane2.workDir.030</t>
-  </si>
-  <si>
     <t>削除...</t>
   </si>
   <si>
     <t>パスワード：</t>
-  </si>
-  <si>
-    <t>fx.PasswordDialogPane.020</t>
   </si>
   <si>
     <t>パスワードが異なります。</t>
@@ -503,18 +461,6 @@
   </si>
   <si>
     <t>余剰%dシート</t>
-  </si>
-  <si>
-    <t>fx.MenuPane.030</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.MenuPane.040</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.TargetSelectionPane.030</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t xml:space="preserve">ブック%s : </t>
@@ -751,10 +697,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.MenuPane.050</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>比較対象：</t>
     <rPh sb="0" eb="4">
       <t>ヒカクタイショウ</t>
@@ -1170,14 +1112,6 @@
   </si>
   <si>
     <t xml:space="preserve">根文件夹%s : </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingsPane1.execute.030</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingsPane1.execute.040</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1529,10 +1463,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.SettingsPane1.compare.050</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シート名／ブック名の曖昧マッチを有効にする</t>
     <rPh sb="3" eb="4">
       <t>メイ</t>
@@ -1689,10 +1619,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.GoogleFilePickerDialogPane.030</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ファイル名 :</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1701,10 +1627,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.GoogleFilePickerDialogPane.050</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>File Name :</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1721,27 +1643,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.GoogleFilePickerDialogPane.060</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>版本 :</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.GooglePane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Googleドライブ\n連携</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Connect\nGoogle Drive</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.GooglePane.020</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1765,14 +1675,6 @@
   </si>
   <si>
     <t>Googleドライブからファイルをダウンロードしました。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>gui.component.GooglePane.100</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>gui.component.GooglePane.110</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2037,10 +1939,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.SettingsPane2.040</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>詳細設定…</t>
     <rPh sb="0" eb="2">
       <t>ショウサイ</t>
@@ -2055,10 +1953,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.SettingDetailsDialogPane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>更新確認</t>
     <rPh sb="0" eb="2">
       <t>コウシン</t>
@@ -2081,10 +1975,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>fx.SettingDetailsDialogPane.020</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>起動時に新規バージョンの有無を確認する</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2102,14 +1992,6 @@
   </si>
   <si>
     <t>立即检查是否有新版本</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingDetailsDialogPane.030</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingDetailsDialogPane.040</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2145,14 +2027,6 @@
   </si>
   <si>
     <t>設定ファイルを表示する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingDetailsDialogPane.050</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingDetailsDialogPane.060</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2306,49 +2180,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>★fxml利用</t>
-    <rPh sb="5" eb="7">
-      <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.TargetSelectionPane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingsPane2.workDir.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingsPane2.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingsPane1.execute.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.SettingsPane1.030</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.PasswordDialogPane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.MenuPane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.LinkPane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fx.ExecutePane.010</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>APP_0010</t>
   </si>
   <si>
@@ -2762,6 +2593,182 @@
   </si>
   <si>
     <t>APP_1290</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0010</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0350</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0360</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0020</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0070</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0030</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0040</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0050</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0060</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0100</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0110</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0120</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0150</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0130</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0140</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0160</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0170</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0180</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0190</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0200</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0210</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0220</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0240</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0260</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0270</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0280</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0250</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0310</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0290</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0300</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0430</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0440</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0320</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0330</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0340</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0090</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0080</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0370</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0380</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0390</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0400</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0410</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0420</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0230</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2867,12 +2874,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2913,6 +2917,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3183,1327 +3191,1195 @@
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
     <col min="3" max="3" width="9.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="30.58203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="30.58203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="30.58203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="30.58203125" style="6" customWidth="1"/>
     <col min="8" max="8" width="2.58203125" style="1"/>
-    <col min="9" max="9" width="2.58203125" style="4"/>
-    <col min="10" max="10" width="2.58203125" style="5"/>
-    <col min="11" max="11" width="2.58203125" style="6"/>
+    <col min="9" max="9" width="2.58203125" style="3"/>
+    <col min="10" max="10" width="2.58203125" style="4"/>
+    <col min="11" max="11" width="2.58203125" style="5"/>
     <col min="12" max="16384" width="2.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:11">
       <c r="C1" s="1" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="3:11">
+      <c r="D2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I2" s="3" t="str">
+        <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; E2)</f>
+        <v>FXML_0010=実行</v>
+      </c>
+      <c r="J2" s="4" t="str">
+        <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; F2)</f>
+        <v>FXML_0010=Exec</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; G2)</f>
+        <v>FXML_0010=执行</v>
+      </c>
+    </row>
+    <row r="3" spans="3:11">
+      <c r="D3" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I46" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
+        <v>FXML_0020=website</v>
+      </c>
+      <c r="J3" s="4" t="str">
+        <f t="shared" ref="J3:J46" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
+        <v>FXML_0020=website</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <f t="shared" ref="K3:K46" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
+        <v>FXML_0020=website</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11">
+      <c r="D4" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0030=ブック</v>
+      </c>
+      <c r="J4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0030=Books</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0030=工作簿</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11">
+      <c r="D5" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0040=シート</v>
+      </c>
+      <c r="J5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0040=Sheets</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0040=工作表</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11">
+      <c r="D6" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0050=フォルダ</v>
+      </c>
+      <c r="J6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0050=Folders</v>
+      </c>
+      <c r="K6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0050=文件夹</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11">
+      <c r="D7" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0060=子フォルダも含める</v>
+      </c>
+      <c r="J7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0060=Include child folders</v>
+      </c>
+      <c r="K7" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0060=包括子文件夹</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11">
+      <c r="D8" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0070=比較対象：</v>
+      </c>
+      <c r="J8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0070=Compare</v>
+      </c>
+      <c r="K8" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0070=互相比较</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11">
+      <c r="D9" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0080=パスワード：</v>
+      </c>
+      <c r="J9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">FXML_0080=Password : </v>
+      </c>
+      <c r="K9" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0080=密码：</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11">
+      <c r="D10" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0090=パスワードが異なります。</v>
+      </c>
+      <c r="J10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0090=Incorrect password</v>
+      </c>
+      <c r="K10" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0090=密码不正确。</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11">
+      <c r="D11" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0100=比較オプション</v>
+      </c>
+      <c r="J11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0100=Comparison options</v>
+      </c>
+      <c r="K11" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0100=比较选项</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11">
+      <c r="D12" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0110=行の挿入／削除を考慮する</v>
+      </c>
+      <c r="J12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0110=Consider row insertions/deletions</v>
+      </c>
+      <c r="K12" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0110=考虑行的插入／删除</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11">
+      <c r="D13" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0120=列の挿入／削除を考慮する</v>
+      </c>
+      <c r="J13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0120=Consider column insertions/deletions</v>
+      </c>
+      <c r="K13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0120=考虑列的插入／删除</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11">
+      <c r="D14" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0130=値を比較する</v>
+      </c>
+      <c r="J14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0130=Compare values</v>
+      </c>
+      <c r="K14" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0130=比较值</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11">
+      <c r="D15" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0140=数式を比較する</v>
+      </c>
+      <c r="J15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0140=Compare formulas</v>
+      </c>
+      <c r="K15" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0140=比较公式</v>
+      </c>
+    </row>
+    <row r="16" spans="3:11">
+      <c r="D16" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0150=シート名／ブック名の曖昧マッチを有効にする</v>
+      </c>
+      <c r="J16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0150=Enable sheets/books fuzzy matching</v>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0150=启用工作表／工作簿模糊匹配</v>
+      </c>
+    </row>
+    <row r="17" spans="4:11">
+      <c r="D17" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0160=レポートオプション</v>
+      </c>
+      <c r="J17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0160=Reporting options</v>
+      </c>
+      <c r="K17" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0160=报告选项</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11">
+      <c r="D18" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0170=差分箇所に色を着けて表示する</v>
+      </c>
+      <c r="J18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0170=Display differences in colors</v>
+      </c>
+      <c r="K18" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0170=用颜色标记差异</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11">
+      <c r="D19" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0180=比較結果レポートを表示する</v>
+      </c>
+      <c r="J19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0180=Display comparison result report</v>
+      </c>
+      <c r="K19" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0180=显示比较结果报告</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11">
+      <c r="D20" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0190=実行オプション</v>
+      </c>
+      <c r="J20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0190=Execution options</v>
+      </c>
+      <c r="K20" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0190=执行选项</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11">
+      <c r="D21" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0200=比較完了時にこのアプリを終了する</v>
+      </c>
+      <c r="J21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0200=Exit this app upon completion</v>
+      </c>
+      <c r="K21" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0200=比较结束后自动退出此应用程序</v>
+      </c>
+    </row>
+    <row r="22" spans="4:11">
+      <c r="D22" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0210=早さ優先</v>
+      </c>
+      <c r="J22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0210=Prioritize speed</v>
+      </c>
+      <c r="K22" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0210=优先考虑速度</v>
+      </c>
+    </row>
+    <row r="23" spans="4:11">
+      <c r="D23" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="I23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0220=精度優先</v>
+      </c>
+      <c r="J23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0220=Prioritize accuracy</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0220=优先考虑准确性</v>
+      </c>
+    </row>
+    <row r="24" spans="4:11">
+      <c r="D24" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="I24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0230=言語</v>
+      </c>
+      <c r="J24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0230=Language</v>
+      </c>
+      <c r="K24" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0230=语言</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11">
+      <c r="D25" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="3:11">
-      <c r="C2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="I2" s="4" t="str">
-        <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; E2)</f>
-        <v>fx.ExecutePane.010=実行</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; F2)</f>
-        <v>fx.ExecutePane.010=Exec</v>
-      </c>
-      <c r="K2" s="6" t="str">
-        <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; G2)</f>
-        <v>fx.ExecutePane.010=执行</v>
-      </c>
-    </row>
-    <row r="3" spans="3:11">
-      <c r="C3" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="G25" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="I25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0240=作業用\nフォルダ</v>
+      </c>
+      <c r="J25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0240=Working directory</v>
+      </c>
+      <c r="K25" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0240=工作\n文件夹</v>
+      </c>
+    </row>
+    <row r="26" spans="4:11">
+      <c r="D26" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="I26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0250=詳細設定…</v>
+      </c>
+      <c r="J26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0250=Advanced Settings…</v>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0250=详细设置...</v>
+      </c>
+    </row>
+    <row r="27" spans="4:11">
+      <c r="D27" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0260=開く</v>
+      </c>
+      <c r="J27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0260=Open</v>
+      </c>
+      <c r="K27" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0260=打开</v>
+      </c>
+    </row>
+    <row r="28" spans="4:11">
+      <c r="D28" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="I28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0270=変更...</v>
+      </c>
+      <c r="J28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0270=Change...</v>
+      </c>
+      <c r="K28" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0270=改变...</v>
+      </c>
+    </row>
+    <row r="29" spans="4:11">
+      <c r="D29" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0280=削除...</v>
+      </c>
+      <c r="J29" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0280=Delete...</v>
+      </c>
+      <c r="K29" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0280=删除...</v>
+      </c>
+    </row>
+    <row r="30" spans="4:11">
+      <c r="D30" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0290=ブックパス：</v>
+      </c>
+      <c r="J30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">FXML_0290=Book Path : </v>
+      </c>
+      <c r="K30" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0290=工作簿路径：</v>
+      </c>
+    </row>
+    <row r="31" spans="4:11">
+      <c r="D31" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="str">
-        <f t="shared" ref="I3:I46" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
-        <v>fx.LinkPane.010=website</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <f t="shared" ref="J3:J46" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
-        <v>fx.LinkPane.010=website</v>
-      </c>
-      <c r="K3" s="6" t="str">
-        <f t="shared" ref="K3:K46" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
-        <v>fx.LinkPane.010=website</v>
-      </c>
-    </row>
-    <row r="4" spans="3:11">
-      <c r="C4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I4" s="4" t="str">
+      <c r="F31" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.MenuPane.010=ブック</v>
-      </c>
-      <c r="J4" s="5" t="str">
+        <v>FXML_0300=シート名：</v>
+      </c>
+      <c r="J31" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.MenuPane.010=Books</v>
-      </c>
-      <c r="K4" s="6" t="str">
+        <v xml:space="preserve">FXML_0300=Sheet Name : </v>
+      </c>
+      <c r="K31" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.MenuPane.010=工作簿</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11">
-      <c r="C5" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="I5" s="4" t="str">
+        <v>FXML_0300=工作表名称：</v>
+      </c>
+    </row>
+    <row r="32" spans="4:11">
+      <c r="D32" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="I32" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.MenuPane.020=シート</v>
-      </c>
-      <c r="J5" s="5" t="str">
+        <v>FXML_0310=フォルダパス：</v>
+      </c>
+      <c r="J32" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.MenuPane.020=Sheets</v>
-      </c>
-      <c r="K5" s="6" t="str">
+        <v xml:space="preserve">FXML_0310=Folder Path : </v>
+      </c>
+      <c r="K32" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.MenuPane.020=工作表</v>
-      </c>
-    </row>
-    <row r="6" spans="3:11">
-      <c r="C6" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="I6" s="4" t="str">
+        <v>FXML_0310=文件夹路径：</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11">
+      <c r="D33" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I33" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.MenuPane.030=フォルダ</v>
-      </c>
-      <c r="J6" s="5" t="str">
+        <v>FXML_0320=ファイルURL :</v>
+      </c>
+      <c r="J33" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.MenuPane.030=Folders</v>
-      </c>
-      <c r="K6" s="6" t="str">
+        <v>FXML_0320=File URL :</v>
+      </c>
+      <c r="K33" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.MenuPane.030=文件夹</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11">
-      <c r="C7" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I7" s="4" t="str">
+        <v>FXML_0320=文件URL :</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11">
+      <c r="D34" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="I34" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.MenuPane.040=子フォルダも含める</v>
-      </c>
-      <c r="J7" s="5" t="str">
+        <v>FXML_0330=ファイル名 :</v>
+      </c>
+      <c r="J34" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.MenuPane.040=Include child folders</v>
-      </c>
-      <c r="K7" s="6" t="str">
+        <v>FXML_0330=File Name :</v>
+      </c>
+      <c r="K34" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.MenuPane.040=包括子文件夹</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11">
-      <c r="C8" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I8" s="4" t="str">
+        <v>FXML_0330=文件名 :</v>
+      </c>
+    </row>
+    <row r="35" spans="3:11">
+      <c r="D35" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="I35" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.MenuPane.050=比較対象：</v>
-      </c>
-      <c r="J8" s="5" t="str">
+        <v>FXML_0340=リビジョン :</v>
+      </c>
+      <c r="J35" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.MenuPane.050=Compare</v>
-      </c>
-      <c r="K8" s="6" t="str">
+        <v>FXML_0340=Revision :</v>
+      </c>
+      <c r="K35" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.MenuPane.050=互相比较</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11">
-      <c r="C9" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="I9" s="4" t="str">
+        <v>FXML_0340=版本 :</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11">
+      <c r="D36" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="I36" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.PasswordDialogPane.010=パスワード：</v>
-      </c>
-      <c r="J9" s="5" t="str">
+        <v>FXML_0350=Googleドライブ\n連携</v>
+      </c>
+      <c r="J36" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">fx.PasswordDialogPane.010=Password : </v>
-      </c>
-      <c r="K9" s="6" t="str">
+        <v>FXML_0350=Connect\nGoogle Drive</v>
+      </c>
+      <c r="K36" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.PasswordDialogPane.010=密码：</v>
-      </c>
-    </row>
-    <row r="10" spans="3:11">
-      <c r="C10" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I10" s="4" t="str">
+        <v>FXML_0350=Google Drive\n关联</v>
+      </c>
+    </row>
+    <row r="37" spans="3:11">
+      <c r="D37" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="I37" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.PasswordDialogPane.020=パスワードが異なります。</v>
-      </c>
-      <c r="J10" s="5" t="str">
+        <v>FXML_0360=Googleドライブ\n連携解除</v>
+      </c>
+      <c r="J37" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.PasswordDialogPane.020=Incorrect password</v>
-      </c>
-      <c r="K10" s="6" t="str">
+        <v>FXML_0360=Disconnect\nGoogle Drive</v>
+      </c>
+      <c r="K37" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.PasswordDialogPane.020=密码不正确。</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11">
-      <c r="C11" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="I11" s="4" t="str">
+        <v>FXML_0360=Google Drive\n关联解除</v>
+      </c>
+    </row>
+    <row r="38" spans="3:11">
+      <c r="D38" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="I38" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.010=比較オプション</v>
-      </c>
-      <c r="J11" s="5" t="str">
+        <v>FXML_0370=更新確認</v>
+      </c>
+      <c r="J38" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.010=Comparison options</v>
-      </c>
-      <c r="K11" s="6" t="str">
+        <v>FXML_0370=Update Check</v>
+      </c>
+      <c r="K38" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.010=比较选项</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11">
-      <c r="C12" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I12" s="4" t="str">
+        <v>FXML_0370=更新确认</v>
+      </c>
+    </row>
+    <row r="39" spans="3:11">
+      <c r="D39" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="I39" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.compare.010=行の挿入／削除を考慮する</v>
-      </c>
-      <c r="J12" s="5" t="str">
+        <v>FXML_0380=起動時に新規バージョンの有無を確認する</v>
+      </c>
+      <c r="J39" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.compare.010=Consider row insertions/deletions</v>
-      </c>
-      <c r="K12" s="6" t="str">
+        <v>FXML_0380=Check for new versions at startup</v>
+      </c>
+      <c r="K39" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.compare.010=考虑行的插入／删除</v>
-      </c>
-    </row>
-    <row r="13" spans="3:11">
-      <c r="C13" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I13" s="4" t="str">
+        <v>FXML_0380=启动时检查是否有新版本</v>
+      </c>
+    </row>
+    <row r="40" spans="3:11">
+      <c r="D40" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="I40" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.compare.020=列の挿入／削除を考慮する</v>
-      </c>
-      <c r="J13" s="5" t="str">
+        <v>FXML_0390=新規バージョンの有無を今すぐ確認する</v>
+      </c>
+      <c r="J40" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.compare.020=Consider column insertions/deletions</v>
-      </c>
-      <c r="K13" s="6" t="str">
+        <v>FXML_0390=Check for new versions now</v>
+      </c>
+      <c r="K40" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.compare.020=考虑列的插入／删除</v>
-      </c>
-    </row>
-    <row r="14" spans="3:11">
-      <c r="C14" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="I14" s="4" t="str">
+        <v>FXML_0390=立即检查是否有新版本</v>
+      </c>
+    </row>
+    <row r="41" spans="3:11">
+      <c r="D41" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="I41" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.compare.030=値を比較する</v>
-      </c>
-      <c r="J14" s="5" t="str">
+        <v>FXML_0400=設定</v>
+      </c>
+      <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.compare.030=Compare values</v>
-      </c>
-      <c r="K14" s="6" t="str">
+        <v>FXML_0400=Settings</v>
+      </c>
+      <c r="K41" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.compare.030=比较值</v>
-      </c>
-    </row>
-    <row r="15" spans="3:11">
-      <c r="C15" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="I15" s="4" t="str">
+        <v>FXML_0400=设置</v>
+      </c>
+    </row>
+    <row r="42" spans="3:11">
+      <c r="D42" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="I42" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.compare.040=数式を比較する</v>
-      </c>
-      <c r="J15" s="5" t="str">
+        <v>FXML_0410=設定ファイルを表示する</v>
+      </c>
+      <c r="J42" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.compare.040=Compare formulas</v>
-      </c>
-      <c r="K15" s="6" t="str">
+        <v>FXML_0410=Display the configuration file</v>
+      </c>
+      <c r="K42" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.compare.040=比较公式</v>
-      </c>
-    </row>
-    <row r="16" spans="3:11">
-      <c r="C16" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="I16" s="4" t="str">
+        <v>FXML_0410=显示配置文件</v>
+      </c>
+    </row>
+    <row r="43" spans="3:11">
+      <c r="D43" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="I43" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.compare.050=シート名／ブック名の曖昧マッチを有効にする</v>
-      </c>
-      <c r="J16" s="5" t="str">
+        <v>FXML_0420=設定をリセットする…</v>
+      </c>
+      <c r="J43" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.compare.050=Enable sheets/books fuzzy matching</v>
-      </c>
-      <c r="K16" s="6" t="str">
+        <v>FXML_0420=Reset settings…</v>
+      </c>
+      <c r="K43" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.compare.050=启用工作表／工作簿模糊匹配</v>
-      </c>
-    </row>
-    <row r="17" spans="3:11">
-      <c r="C17" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I17" s="4" t="str">
+        <v>FXML_0420=重置设置…</v>
+      </c>
+    </row>
+    <row r="44" spans="3:11">
+      <c r="D44" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I44" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.020=レポートオプション</v>
-      </c>
-      <c r="J17" s="5" t="str">
+        <v>FXML_0430=選択されたファイルをGoogleドライブからダウンロードしてこのPCの下記リンク先フォルダに保存しました。\nPC上に保存された状態が好ましくない場合は、比較処理が終わり次第、ご自身で削除してください。</v>
+      </c>
+      <c r="J44" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.020=Reporting options</v>
-      </c>
-      <c r="K17" s="6" t="str">
+        <v>FXML_0430=The selected file has been downloaded from Google Drive and saved to the folder linked below on this PC.\nIf you prefer not to keep the file stored on your PC, please delete it manually after the comparison process is complete.</v>
+      </c>
+      <c r="K44" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.020=报告选项</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11">
-      <c r="C18" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="I18" s="4" t="str">
+        <v>FXML_0430=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
+      </c>
+    </row>
+    <row r="45" spans="3:11">
+      <c r="D45" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="I45" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.report.010=差分箇所に色を着けて表示する</v>
-      </c>
-      <c r="J18" s="5" t="str">
+        <v>FXML_0440=次回以降、このメッセージを表示しない</v>
+      </c>
+      <c r="J45" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.report.010=Display differences in colors</v>
-      </c>
-      <c r="K18" s="6" t="str">
+        <v>FXML_0440=Don't show this message again</v>
+      </c>
+      <c r="K45" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.report.010=用颜色标记差异</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11">
-      <c r="C19" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="I19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.report.020=比較結果レポートを表示する</v>
-      </c>
-      <c r="J19" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.report.020=Display comparison result report</v>
-      </c>
-      <c r="K19" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.report.020=显示比较结果报告</v>
-      </c>
-    </row>
-    <row r="20" spans="3:11">
-      <c r="C20" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="I20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.030=実行オプション</v>
-      </c>
-      <c r="J20" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.030=Execution options</v>
-      </c>
-      <c r="K20" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.030=执行选项</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11">
-      <c r="C21" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="I21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.execute.010=比較完了時にこのアプリを終了する</v>
-      </c>
-      <c r="J21" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.execute.010=Exit this app upon completion</v>
-      </c>
-      <c r="K21" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.execute.010=比较结束后自动退出此应用程序</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11">
-      <c r="C22" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.execute.030=早さ優先</v>
-      </c>
-      <c r="J22" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.execute.030=Prioritize speed</v>
-      </c>
-      <c r="K22" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.execute.030=优先考虑速度</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11">
-      <c r="C23" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="I23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane1.execute.040=精度優先</v>
-      </c>
-      <c r="J23" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane1.execute.040=Prioritize accuracy</v>
-      </c>
-      <c r="K23" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane1.execute.040=优先考虑准确性</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11">
-      <c r="C24" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane2.010=言語</v>
-      </c>
-      <c r="J24" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane2.010=Language</v>
-      </c>
-      <c r="K24" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane2.010=语言</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11">
-      <c r="C25" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="I25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane2.020=作業用\nフォルダ</v>
-      </c>
-      <c r="J25" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane2.020=Working directory</v>
-      </c>
-      <c r="K25" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane2.020=工作\n文件夹</v>
-      </c>
-    </row>
-    <row r="26" spans="3:11">
-      <c r="C26" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="I26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane2.040=詳細設定…</v>
-      </c>
-      <c r="J26" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane2.040=Advanced Settings…</v>
-      </c>
-      <c r="K26" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane2.040=详细设置...</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11">
-      <c r="C27" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="I27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane2.workDir.010=開く</v>
-      </c>
-      <c r="J27" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane2.workDir.010=Open</v>
-      </c>
-      <c r="K27" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane2.workDir.010=打开</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11">
-      <c r="C28" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane2.workDir.020=変更...</v>
-      </c>
-      <c r="J28" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane2.workDir.020=Change...</v>
-      </c>
-      <c r="K28" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane2.workDir.020=改变...</v>
-      </c>
-    </row>
-    <row r="29" spans="3:11">
-      <c r="C29" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="I29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingsPane2.workDir.030=削除...</v>
-      </c>
-      <c r="J29" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingsPane2.workDir.030=Delete...</v>
-      </c>
-      <c r="K29" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingsPane2.workDir.030=删除...</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11">
-      <c r="C30" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="I30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.TargetSelectionPane.010=ブックパス：</v>
-      </c>
-      <c r="J30" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">fx.TargetSelectionPane.010=Book Path : </v>
-      </c>
-      <c r="K30" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.TargetSelectionPane.010=工作簿路径：</v>
-      </c>
-    </row>
-    <row r="31" spans="3:11">
-      <c r="C31" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.TargetSelectionPane.020=シート名：</v>
-      </c>
-      <c r="J31" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">fx.TargetSelectionPane.020=Sheet Name : </v>
-      </c>
-      <c r="K31" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.TargetSelectionPane.020=工作表名称：</v>
-      </c>
-    </row>
-    <row r="32" spans="3:11">
-      <c r="C32" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="I32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.TargetSelectionPane.030=フォルダパス：</v>
-      </c>
-      <c r="J32" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">fx.TargetSelectionPane.030=Folder Path : </v>
-      </c>
-      <c r="K32" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.TargetSelectionPane.030=文件夹路径：</v>
-      </c>
-    </row>
-    <row r="33" spans="3:11">
-      <c r="C33" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="I33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialogPane.030=ファイルURL :</v>
-      </c>
-      <c r="J33" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialogPane.030=File URL :</v>
-      </c>
-      <c r="K33" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialogPane.030=文件URL :</v>
-      </c>
-    </row>
-    <row r="34" spans="3:11">
-      <c r="C34" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="I34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialogPane.050=ファイル名 :</v>
-      </c>
-      <c r="J34" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialogPane.050=File Name :</v>
-      </c>
-      <c r="K34" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialogPane.050=文件名 :</v>
-      </c>
-    </row>
-    <row r="35" spans="3:11">
-      <c r="C35" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="I35" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GoogleFilePickerDialogPane.060=リビジョン :</v>
-      </c>
-      <c r="J35" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GoogleFilePickerDialogPane.060=Revision :</v>
-      </c>
-      <c r="K35" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GoogleFilePickerDialogPane.060=版本 :</v>
-      </c>
-    </row>
-    <row r="36" spans="3:11">
-      <c r="C36" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="I36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GooglePane.010=Googleドライブ\n連携</v>
-      </c>
-      <c r="J36" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GooglePane.010=Connect\nGoogle Drive</v>
-      </c>
-      <c r="K36" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GooglePane.010=Google Drive\n关联</v>
-      </c>
-    </row>
-    <row r="37" spans="3:11">
-      <c r="C37" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="I37" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.GooglePane.020=Googleドライブ\n連携解除</v>
-      </c>
-      <c r="J37" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.GooglePane.020=Disconnect\nGoogle Drive</v>
-      </c>
-      <c r="K37" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.GooglePane.020=Google Drive\n关联解除</v>
-      </c>
-    </row>
-    <row r="38" spans="3:11">
-      <c r="C38" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="I38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingDetailsDialogPane.010=更新確認</v>
-      </c>
-      <c r="J38" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingDetailsDialogPane.010=Update Check</v>
-      </c>
-      <c r="K38" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingDetailsDialogPane.010=更新确认</v>
-      </c>
-    </row>
-    <row r="39" spans="3:11">
-      <c r="C39" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="I39" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingDetailsDialogPane.020=起動時に新規バージョンの有無を確認する</v>
-      </c>
-      <c r="J39" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingDetailsDialogPane.020=Check for new versions at startup</v>
-      </c>
-      <c r="K39" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingDetailsDialogPane.020=启动时检查是否有新版本</v>
-      </c>
-    </row>
-    <row r="40" spans="3:11">
-      <c r="C40" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="I40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingDetailsDialogPane.030=新規バージョンの有無を今すぐ確認する</v>
-      </c>
-      <c r="J40" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingDetailsDialogPane.030=Check for new versions now</v>
-      </c>
-      <c r="K40" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingDetailsDialogPane.030=立即检查是否有新版本</v>
-      </c>
-    </row>
-    <row r="41" spans="3:11">
-      <c r="C41" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="I41" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingDetailsDialogPane.040=設定</v>
-      </c>
-      <c r="J41" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingDetailsDialogPane.040=Settings</v>
-      </c>
-      <c r="K41" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingDetailsDialogPane.040=设置</v>
-      </c>
-    </row>
-    <row r="42" spans="3:11">
-      <c r="C42" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="I42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingDetailsDialogPane.050=設定ファイルを表示する</v>
-      </c>
-      <c r="J42" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingDetailsDialogPane.050=Display the configuration file</v>
-      </c>
-      <c r="K42" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingDetailsDialogPane.050=显示配置文件</v>
-      </c>
-    </row>
-    <row r="43" spans="3:11">
-      <c r="C43" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="I43" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>fx.SettingDetailsDialogPane.060=設定をリセットする…</v>
-      </c>
-      <c r="J43" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>fx.SettingDetailsDialogPane.060=Reset settings…</v>
-      </c>
-      <c r="K43" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>fx.SettingDetailsDialogPane.060=重置设置…</v>
-      </c>
-    </row>
-    <row r="44" spans="3:11">
-      <c r="C44" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="I44" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>gui.component.GooglePane.100=選択されたファイルをGoogleドライブからダウンロードしてこのPCの下記リンク先フォルダに保存しました。\nPC上に保存された状態が好ましくない場合は、比較処理が終わり次第、ご自身で削除してください。</v>
-      </c>
-      <c r="J44" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>gui.component.GooglePane.100=The selected file has been downloaded from Google Drive and saved to the folder linked below on this PC.\nIf you prefer not to keep the file stored on your PC, please delete it manually after the comparison process is complete.</v>
-      </c>
-      <c r="K44" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>gui.component.GooglePane.100=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
-      </c>
-    </row>
-    <row r="45" spans="3:11">
-      <c r="C45" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="I45" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>gui.component.GooglePane.110=次回以降、このメッセージを表示しない</v>
-      </c>
-      <c r="J45" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>gui.component.GooglePane.110=Don't show this message again</v>
-      </c>
-      <c r="K45" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>gui.component.GooglePane.110=不再显示此消息</v>
+        <v>FXML_0440=不再显示此消息</v>
       </c>
     </row>
     <row r="46" spans="3:11">
-      <c r="E46" s="3"/>
-      <c r="I46" s="4" t="str">
+      <c r="E46" s="2"/>
+      <c r="I46" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J46" s="5" t="str">
+      <c r="J46" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K46" s="6" t="str">
+      <c r="K46" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -4514,26 +4390,26 @@
         <v>/** 方眼Diff */ APP_0010,</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="I47" s="4" t="str">
+        <v>449</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="I47" s="3" t="str">
         <f t="shared" ref="I47:I78" si="3" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; E47)</f>
         <v>APP_0010=方眼Diff</v>
       </c>
-      <c r="J47" s="5" t="str">
+      <c r="J47" s="4" t="str">
         <f t="shared" ref="J47:J78" si="4" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; F47)</f>
         <v>APP_0010=HoganDiff (方眼Diff)</v>
       </c>
-      <c r="K47" s="6" t="str">
+      <c r="K47" s="5" t="str">
         <f t="shared" ref="K47:K78" si="5" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; G47)</f>
         <v>APP_0010=方眼Diff</v>
       </c>
@@ -4544,26 +4420,26 @@
         <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="I48" s="4" t="str">
+        <v>450</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I48" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0020=設定の保存に失敗しました。</v>
       </c>
-      <c r="J48" s="5" t="str">
+      <c r="J48" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0020=Failed to save settings.</v>
       </c>
-      <c r="K48" s="6" t="str">
+      <c r="K48" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0020=保存设置失败。</v>
       </c>
@@ -4574,26 +4450,26 @@
         <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="I49" s="4" t="str">
+        <v>451</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="I49" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0030=比較結果テキストを保存しています...</v>
       </c>
-      <c r="J49" s="5" t="str">
+      <c r="J49" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0030=Saving result text...</v>
       </c>
-      <c r="K49" s="6" t="str">
+      <c r="K49" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0030=存储比较结果文本...</v>
       </c>
@@ -4604,26 +4480,26 @@
         <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="I50" s="4" t="str">
+        <v>452</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="I50" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
       </c>
-      <c r="J50" s="5" t="str">
+      <c r="J50" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0040=Failed to save or open result text.</v>
       </c>
-      <c r="K50" s="6" t="str">
+      <c r="K50" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0040=保存和显示比较结果文本失败。</v>
       </c>
@@ -4634,26 +4510,26 @@
         <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="I51" s="4" t="str">
+        <v>453</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I51" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
       </c>
-      <c r="J51" s="5" t="str">
+      <c r="J51" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0050=Painting and saving result book(s)...</v>
       </c>
-      <c r="K51" s="6" t="str">
+      <c r="K51" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0050=着色和存储在工作簿...</v>
       </c>
@@ -4664,26 +4540,26 @@
         <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I52" s="4" t="str">
+        <v>454</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I52" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
       </c>
-      <c r="J52" s="5" t="str">
+      <c r="J52" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0060=Failed to paint or save result book(s).</v>
       </c>
-      <c r="K52" s="6" t="str">
+      <c r="K52" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0060=着色和保存工作簿失败。</v>
       </c>
@@ -4694,26 +4570,26 @@
         <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="I53" s="4" t="str">
+        <v>455</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I53" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0070=比較結果のExcelブックを表示しています...</v>
       </c>
-      <c r="J53" s="5" t="str">
+      <c r="J53" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0070=Opening result book(s)...</v>
       </c>
-      <c r="K53" s="6" t="str">
+      <c r="K53" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0070=显示比较结果的工作簿...</v>
       </c>
@@ -4724,26 +4600,26 @@
         <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I54" s="4" t="str">
+        <v>456</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I54" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0080=Excelブックの表示に失敗しました。</v>
       </c>
-      <c r="J54" s="5" t="str">
+      <c r="J54" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0080=Failed to open result book(s).</v>
       </c>
-      <c r="K54" s="6" t="str">
+      <c r="K54" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0080=显示工作簿失败。</v>
       </c>
@@ -4754,26 +4630,26 @@
         <v>/** ExcelブックAの着色・保存に失敗しました。 */ APP_0090,</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="I55" s="4" t="str">
+        <v>457</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I55" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0090=ExcelブックAの着色・保存に失敗しました。</v>
       </c>
-      <c r="J55" s="5" t="str">
+      <c r="J55" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0090=Failed to paint or save result book A.</v>
       </c>
-      <c r="K55" s="6" t="str">
+      <c r="K55" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0090=工作簿A的着色和保存失败。</v>
       </c>
@@ -4784,26 +4660,26 @@
         <v>/** ExcelブックBの着色・保存に失敗しました。 */ APP_0100,</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="I56" s="4" t="str">
+        <v>458</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I56" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0100=ExcelブックBの着色・保存に失敗しました。</v>
       </c>
-      <c r="J56" s="5" t="str">
+      <c r="J56" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0100=Failed to paint or save result book B.</v>
       </c>
-      <c r="K56" s="6" t="str">
+      <c r="K56" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0100=工作簿B的着色和保存失败。</v>
       </c>
@@ -4814,26 +4690,26 @@
         <v>/** 処理が完了しました。 */ APP_0110,</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="I57" s="4" t="str">
+        <v>459</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I57" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0110=処理が完了しました。</v>
       </c>
-      <c r="J57" s="5" t="str">
+      <c r="J57" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0110=Process completed.</v>
       </c>
-      <c r="K57" s="6" t="str">
+      <c r="K57" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0110=过程完成。</v>
       </c>
@@ -4844,26 +4720,26 @@
         <v>/** ★失敗しました */ APP_0120,</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I58" s="4" t="str">
+        <v>460</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I58" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0120=★失敗しました</v>
       </c>
-      <c r="J58" s="5" t="str">
+      <c r="J58" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0120=★Failed</v>
       </c>
-      <c r="K58" s="6" t="str">
+      <c r="K58" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0120=★失败</v>
       </c>
@@ -4874,26 +4750,26 @@
         <v>/** (比較対象ファイルなし) */ APP_0130,</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I59" s="4" t="str">
+        <v>461</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I59" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0130=(比較対象ファイルなし)</v>
       </c>
-      <c r="J59" s="5" t="str">
+      <c r="J59" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0130=(No files to compare)</v>
       </c>
-      <c r="K59" s="6" t="str">
+      <c r="K59" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0130=(没有可比较的文件)</v>
       </c>
@@ -4904,26 +4780,26 @@
         <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="I60" s="4" t="str">
+        <v>462</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="I60" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
-      <c r="J60" s="5" t="str">
+      <c r="J60" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
-      <c r="K60" s="6" t="str">
+      <c r="K60" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
@@ -4934,26 +4810,26 @@
         <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I61" s="4" t="str">
+        <v>463</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I61" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0150=予期せぬ例外が発生しました。</v>
       </c>
-      <c r="J61" s="5" t="str">
+      <c r="J61" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0150=Unexpected exception occurred.</v>
       </c>
-      <c r="K61" s="6" t="str">
+      <c r="K61" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0150=意外的例外。</v>
       </c>
@@ -4964,26 +4840,26 @@
         <v>/** 比較実行日時 :  */ APP_0160,</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="I62" s="4" t="str">
+        <v>464</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="I62" s="3" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">APP_0160=比較実行日時 : </v>
       </c>
-      <c r="J62" s="5" t="str">
+      <c r="J62" s="4" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">APP_0160=Exec datetime : </v>
       </c>
-      <c r="K62" s="6" t="str">
+      <c r="K62" s="5" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">APP_0160=执行日期和时间 : </v>
       </c>
@@ -4994,26 +4870,26 @@
         <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="I63" s="4" t="str">
+        <v>465</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="I63" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0170=ブック同士の比較を開始します。</v>
       </c>
-      <c r="J63" s="5" t="str">
+      <c r="J63" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0170=Starting comparing books.</v>
       </c>
-      <c r="K63" s="6" t="str">
+      <c r="K63" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0170=开始互相比较工作簿。</v>
       </c>
@@ -5024,26 +4900,26 @@
         <v>/** シートを比較しています... */ APP_0180,</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="I64" s="4" t="str">
+        <v>466</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I64" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0180=シートを比較しています...</v>
       </c>
-      <c r="J64" s="5" t="str">
+      <c r="J64" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0180=Comparing sheets...</v>
       </c>
-      <c r="K64" s="6" t="str">
+      <c r="K64" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0180=比较工作表...</v>
       </c>
@@ -5054,26 +4930,26 @@
         <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="I65" s="4" t="str">
+        <v>467</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I65" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0190=シートの比較に失敗しました。</v>
       </c>
-      <c r="J65" s="5" t="str">
+      <c r="J65" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0190=Failed to compare sheets.</v>
       </c>
-      <c r="K65" s="6" t="str">
+      <c r="K65" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0190=工作表比较失败。</v>
       </c>
@@ -5084,26 +4960,26 @@
         <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I66" s="4" t="str">
+        <v>468</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I66" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0200=比較結果レポートを保存しています...</v>
       </c>
-      <c r="J66" s="5" t="str">
+      <c r="J66" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0200=Saving result report...</v>
       </c>
-      <c r="K66" s="6" t="str">
+      <c r="K66" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0200=保存比较结果报告...</v>
       </c>
@@ -5114,26 +4990,26 @@
         <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="I67" s="4" t="str">
+        <v>469</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I67" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
       </c>
-      <c r="J67" s="5" t="str">
+      <c r="J67" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0210=Failed to save result report.</v>
       </c>
-      <c r="K67" s="6" t="str">
+      <c r="K67" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0210=保存比较结果报告失败。</v>
       </c>
@@ -5144,26 +5020,26 @@
         <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="I68" s="4" t="str">
+        <v>470</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I68" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0220=比較結果レポートを表示しています...</v>
       </c>
-      <c r="J68" s="5" t="str">
+      <c r="J68" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0220=Opening result report...</v>
       </c>
-      <c r="K68" s="6" t="str">
+      <c r="K68" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0220=显示比较结果报告...</v>
       </c>
@@ -5174,26 +5050,26 @@
         <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="I69" s="4" t="str">
+        <v>471</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I69" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
       </c>
-      <c r="J69" s="5" t="str">
+      <c r="J69" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0230=Failed to open result report.</v>
       </c>
-      <c r="K69" s="6" t="str">
+      <c r="K69" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0230=显示比较结果报告失败。</v>
       </c>
@@ -5204,26 +5080,26 @@
         <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="I70" s="4" t="str">
+        <v>472</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I70" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0240=フォルダ同士の比較を開始します。</v>
       </c>
-      <c r="J70" s="5" t="str">
+      <c r="J70" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0240=Starting comparing folders.</v>
       </c>
-      <c r="K70" s="6" t="str">
+      <c r="K70" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0240=开始互相比较文件夹。</v>
       </c>
@@ -5234,26 +5110,26 @@
         <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="I71" s="4" t="str">
+        <v>473</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I71" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0250=出力フォルダの作成に失敗しました。</v>
       </c>
-      <c r="J71" s="5" t="str">
+      <c r="J71" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0250=Failed to create output directory.</v>
       </c>
-      <c r="K71" s="6" t="str">
+      <c r="K71" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0250=创建输出目的地文件夹失败。</v>
       </c>
@@ -5264,26 +5140,26 @@
         <v>/** Excelブックを比較しています... */ APP_0260,</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="I72" s="4" t="str">
+        <v>474</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I72" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0260=Excelブックを比較しています...</v>
       </c>
-      <c r="J72" s="5" t="str">
+      <c r="J72" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0260=Comparing books...</v>
       </c>
-      <c r="K72" s="6" t="str">
+      <c r="K72" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0260=比较工作簿...</v>
       </c>
@@ -5294,26 +5170,26 @@
         <v>/** (比較対象ファイルなし) */ APP_0270,</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I73" s="4" t="str">
+        <v>475</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I73" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0270=(比較対象ファイルなし)</v>
       </c>
-      <c r="J73" s="5" t="str">
+      <c r="J73" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0270=(No files to compare)</v>
       </c>
-      <c r="K73" s="6" t="str">
+      <c r="K73" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0270=(没有可比较的文件)</v>
       </c>
@@ -5324,26 +5200,26 @@
         <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I74" s="4" t="str">
+        <v>476</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="I74" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0280=フォルダの比較に失敗しました。</v>
       </c>
-      <c r="J74" s="5" t="str">
+      <c r="J74" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0280=Failed to compare folders.</v>
       </c>
-      <c r="K74" s="6" t="str">
+      <c r="K74" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0280=文件夹比较失败。</v>
       </c>
@@ -5354,26 +5230,26 @@
         <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="I75" s="4" t="str">
+        <v>477</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I75" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0290=シート同士の比較を開始します。</v>
       </c>
-      <c r="J75" s="5" t="str">
+      <c r="J75" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0290=Starting comparing sheets.</v>
       </c>
-      <c r="K75" s="6" t="str">
+      <c r="K75" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0290=开始相互比较工作表。</v>
       </c>
@@ -5384,26 +5260,26 @@
         <v>/** シートを比較しています... */ APP_0300,</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I76" s="4" t="str">
+        <v>478</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I76" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0300=シートを比較しています...</v>
       </c>
-      <c r="J76" s="5" t="str">
+      <c r="J76" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0300=Comparing sheets...</v>
       </c>
-      <c r="K76" s="6" t="str">
+      <c r="K76" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0300=比较工作表...</v>
       </c>
@@ -5414,26 +5290,26 @@
         <v>/** シートの比較に失敗しました。 */ APP_0310,</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="I77" s="4" t="str">
+        <v>479</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I77" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0310=シートの比較に失敗しました。</v>
       </c>
-      <c r="J77" s="5" t="str">
+      <c r="J77" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0310=Failed to compare sheets.</v>
       </c>
-      <c r="K77" s="6" t="str">
+      <c r="K77" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0310=工作表比较失败。</v>
       </c>
@@ -5444,26 +5320,26 @@
         <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="I78" s="4" t="str">
+        <v>480</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I78" s="3" t="str">
         <f t="shared" si="3"/>
         <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
       </c>
-      <c r="J78" s="5" t="str">
+      <c r="J78" s="4" t="str">
         <f t="shared" si="4"/>
         <v>APP_0320=Starting comparing folder trees.</v>
       </c>
-      <c r="K78" s="6" t="str">
+      <c r="K78" s="5" t="str">
         <f t="shared" si="5"/>
         <v>APP_0320=开始互相比较文件夹树。</v>
       </c>
@@ -5474,26 +5350,26 @@
         <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="I79" s="4" t="str">
+        <v>481</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="I79" s="3" t="str">
         <f t="shared" ref="I79:I110" si="7" xml:space="preserve"> IF($D79="", "", $D79 &amp; "=" &amp; E79)</f>
         <v>APP_0330=フォルダツリーを比較しています...</v>
       </c>
-      <c r="J79" s="5" t="str">
+      <c r="J79" s="4" t="str">
         <f t="shared" ref="J79:J110" si="8" xml:space="preserve"> IF($D79="", "", $D79 &amp; "=" &amp; F79)</f>
         <v>APP_0330=Comparing folders...</v>
       </c>
-      <c r="K79" s="6" t="str">
+      <c r="K79" s="5" t="str">
         <f t="shared" ref="K79:K110" si="9" xml:space="preserve"> IF($D79="", "", $D79 &amp; "=" &amp; G79)</f>
         <v>APP_0330=比较文件夹...</v>
       </c>
@@ -5504,26 +5380,26 @@
         <v>/** ★失敗しました */ APP_0340,</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I80" s="4" t="str">
+        <v>482</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I80" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0340=★失敗しました</v>
       </c>
-      <c r="J80" s="5" t="str">
+      <c r="J80" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0340=★Failed</v>
       </c>
-      <c r="K80" s="6" t="str">
+      <c r="K80" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0340=★失败</v>
       </c>
@@ -5534,26 +5410,26 @@
         <v>/** 比較結果レポートを保存しています... */ APP_0350,</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I81" s="4" t="str">
+        <v>483</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I81" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0350=比較結果レポートを保存しています...</v>
       </c>
-      <c r="J81" s="5" t="str">
+      <c r="J81" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0350=Saving result report...</v>
       </c>
-      <c r="K81" s="6" t="str">
+      <c r="K81" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0350=保存比较结果报告...</v>
       </c>
@@ -5564,26 +5440,26 @@
         <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0360,</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="I82" s="4" t="str">
+        <v>484</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I82" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0360=比較結果レポートの保存に失敗しました。</v>
       </c>
-      <c r="J82" s="5" t="str">
+      <c r="J82" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0360=Failed to save result report.</v>
       </c>
-      <c r="K82" s="6" t="str">
+      <c r="K82" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0360=保存比较结果报告失败。</v>
       </c>
@@ -5594,26 +5470,26 @@
         <v>/** 比較結果レポートを表示しています... */ APP_0370,</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="I83" s="4" t="str">
+        <v>485</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I83" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0370=比較結果レポートを表示しています...</v>
       </c>
-      <c r="J83" s="5" t="str">
+      <c r="J83" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0370=Opening result report...</v>
       </c>
-      <c r="K83" s="6" t="str">
+      <c r="K83" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0370=显示比较结果报告...</v>
       </c>
@@ -5624,26 +5500,26 @@
         <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0380,</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="I84" s="4" t="str">
+        <v>486</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I84" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0380=比較結果レポートの表示に失敗しました。</v>
       </c>
-      <c r="J84" s="5" t="str">
+      <c r="J84" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0380=Failed to open result report.</v>
       </c>
-      <c r="K84" s="6" t="str">
+      <c r="K84" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0380=显示比较结果报告失败。</v>
       </c>
@@ -5654,26 +5530,26 @@
         <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I85" s="4" t="str">
+        <v>487</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="I85" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
       </c>
-      <c r="J85" s="5" t="str">
+      <c r="J85" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0390=Failed to compare folder trees.</v>
       </c>
-      <c r="K85" s="6" t="str">
+      <c r="K85" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0390=文件夹比较失败。</v>
       </c>
@@ -5684,26 +5560,26 @@
         <v>/** (比較相手なし) */ APP_0400,</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="I86" s="4" t="str">
+        <v>488</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I86" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0400=(比較相手なし)</v>
       </c>
-      <c r="J86" s="5" t="str">
+      <c r="J86" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0400=(no opponent)</v>
       </c>
-      <c r="K86" s="6" t="str">
+      <c r="K86" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0400=(没有对比)</v>
       </c>
@@ -5714,26 +5590,26 @@
         <v>/** (差分なし) */ APP_0410,</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I87" s="4" t="str">
+        <v>489</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I87" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0410=(差分なし)</v>
       </c>
-      <c r="J87" s="5" t="str">
+      <c r="J87" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0410=(no diffs)</v>
       </c>
-      <c r="K87" s="6" t="str">
+      <c r="K87" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0410=(没有区别)</v>
       </c>
@@ -5744,26 +5620,26 @@
         <v>/** 差異発生%dシート */ APP_0420,</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="E88" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F88" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="I88" s="4" t="str">
+      <c r="G88" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I88" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0420=差異発生%dシート</v>
       </c>
-      <c r="J88" s="5" t="str">
+      <c r="J88" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0420=diff sheets:%d</v>
       </c>
-      <c r="K88" s="6" t="str">
+      <c r="K88" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0420=差异工作表%d</v>
       </c>
@@ -5774,26 +5650,26 @@
         <v>/** 余剰%dシート */ APP_0430,</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="E89" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="I89" s="4" t="str">
+      <c r="G89" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I89" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0430=余剰%dシート</v>
       </c>
-      <c r="J89" s="5" t="str">
+      <c r="J89" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0430=redundant sheets:%d</v>
       </c>
-      <c r="K89" s="6" t="str">
+      <c r="K89" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0430=冗余工作表%d</v>
       </c>
@@ -5804,26 +5680,26 @@
         <v>/** ブック%s :  */ APP_0440,</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I90" s="4" t="str">
+        <v>492</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I90" s="3" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">APP_0440=ブック%s : </v>
       </c>
-      <c r="J90" s="5" t="str">
+      <c r="J90" s="4" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">APP_0440=Book %s : </v>
       </c>
-      <c r="K90" s="6" t="str">
+      <c r="K90" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0440=工作簿%s：</v>
       </c>
@@ -5834,26 +5710,26 @@
         <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I91" s="4" t="str">
+        <v>493</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I91" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
       </c>
-      <c r="J91" s="5" t="str">
+      <c r="J91" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
       </c>
-      <c r="K91" s="6" t="str">
+      <c r="K91" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
       </c>
@@ -5864,26 +5740,26 @@
         <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I92" s="4" t="str">
+        <v>494</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I92" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
       </c>
-      <c r="J92" s="5" t="str">
+      <c r="J92" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0460=## DETAIL ------------------------------------------------------</v>
       </c>
-      <c r="K92" s="6" t="str">
+      <c r="K92" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0460=■差异细节 -----------------------------------------------------</v>
       </c>
@@ -5894,26 +5770,26 @@
         <v>/** (比較相手なし) */ APP_0470,</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="I93" s="4" t="str">
+        <v>495</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I93" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0470=(比較相手なし)</v>
       </c>
-      <c r="J93" s="5" t="str">
+      <c r="J93" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0470=(no opponent)</v>
       </c>
-      <c r="K93" s="6" t="str">
+      <c r="K93" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0470=(没有对比)</v>
       </c>
@@ -5924,26 +5800,26 @@
         <v>/** フォルダ%s :  */ APP_0480,</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="I94" s="4" t="str">
+        <v>496</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I94" s="3" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">APP_0480=フォルダ%s : </v>
       </c>
-      <c r="J94" s="5" t="str">
+      <c r="J94" s="4" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">APP_0480=Folder %s : </v>
       </c>
-      <c r="K94" s="6" t="str">
+      <c r="K94" s="5" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">APP_0480=文件夹%s : </v>
       </c>
@@ -5954,26 +5830,26 @@
         <v>/** ■差分サマリ --------------------------------------------------- */ APP_0490,</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I95" s="4" t="str">
+        <v>497</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I95" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0490=■差分サマリ ---------------------------------------------------</v>
       </c>
-      <c r="J95" s="5" t="str">
+      <c r="J95" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0490=## SUMMARY -----------------------------------------------------</v>
       </c>
-      <c r="K95" s="6" t="str">
+      <c r="K95" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0490=■差异摘要 -----------------------------------------------------</v>
       </c>
@@ -5984,26 +5860,26 @@
         <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0500,</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I96" s="4" t="str">
+        <v>498</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I96" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0500=■差分詳細 -----------------------------------------------------</v>
       </c>
-      <c r="J96" s="5" t="str">
+      <c r="J96" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0500=## DETAIL ------------------------------------------------------</v>
       </c>
-      <c r="K96" s="6" t="str">
+      <c r="K96" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0500=■差异细节 -----------------------------------------------------</v>
       </c>
@@ -6014,26 +5890,26 @@
         <v>/** ★失敗しました */ APP_0510,</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I97" s="4" t="str">
+        <v>499</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I97" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0510=★失敗しました</v>
       </c>
-      <c r="J97" s="5" t="str">
+      <c r="J97" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0510=★Failed</v>
       </c>
-      <c r="K97" s="6" t="str">
+      <c r="K97" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0510=★失败</v>
       </c>
@@ -6044,26 +5920,26 @@
         <v>/** (差分なし) */ APP_0520,</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I98" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I98" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0520=(差分なし)</v>
       </c>
-      <c r="J98" s="5" t="str">
+      <c r="J98" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0520=(no diffs)</v>
       </c>
-      <c r="K98" s="6" t="str">
+      <c r="K98" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0520=(没有区别)</v>
       </c>
@@ -6074,26 +5950,26 @@
         <v>/** 差異発生%dブック */ APP_0530,</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="I99" s="4" t="str">
+        <v>501</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I99" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0530=差異発生%dブック</v>
       </c>
-      <c r="J99" s="5" t="str">
+      <c r="J99" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0530=diff books:%d</v>
       </c>
-      <c r="K99" s="6" t="str">
+      <c r="K99" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0530=差异工作簿%d</v>
       </c>
@@ -6104,26 +5980,26 @@
         <v>/** 余剰%dブック */ APP_0540,</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="I100" s="4" t="str">
+        <v>502</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I100" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0540=余剰%dブック</v>
       </c>
-      <c r="J100" s="5" t="str">
+      <c r="J100" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0540=redundant books:%d</v>
       </c>
-      <c r="K100" s="6" t="str">
+      <c r="K100" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0540=冗余工作簿%d</v>
       </c>
@@ -6134,26 +6010,26 @@
         <v>/** 比較失敗%dブック */ APP_0550,</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="I101" s="4" t="str">
+        <v>503</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I101" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0550=比較失敗%dブック</v>
       </c>
-      <c r="J101" s="5" t="str">
+      <c r="J101" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0550=failed books:%d</v>
       </c>
-      <c r="K101" s="6" t="str">
+      <c r="K101" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0550=失败工作簿%d</v>
       </c>
@@ -6164,26 +6040,26 @@
         <v>/** (比較対象ファイルなし) */ APP_0560,</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I102" s="4" t="str">
+        <v>504</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I102" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0560=(比較対象ファイルなし)</v>
       </c>
-      <c r="J102" s="5" t="str">
+      <c r="J102" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0560=(No files to compare)</v>
       </c>
-      <c r="K102" s="6" t="str">
+      <c r="K102" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0560=(没有可比较的文件)</v>
       </c>
@@ -6194,26 +6070,26 @@
         <v>/** 比較実行日時： */ APP_0570,</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="I103" s="4" t="str">
+        <v>505</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I103" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0570=比較実行日時：</v>
       </c>
-      <c r="J103" s="5" t="str">
+      <c r="J103" s="4" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">APP_0570=Exec datetime : </v>
       </c>
-      <c r="K103" s="6" t="str">
+      <c r="K103" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0570=执行日期和时间：</v>
       </c>
@@ -6224,26 +6100,26 @@
         <v>/** 作業用フォルダ： */ APP_0580,</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I104" s="4" t="str">
+        <v>506</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I104" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0580=作業用フォルダ：</v>
       </c>
-      <c r="J104" s="5" t="str">
+      <c r="J104" s="4" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">APP_0580=Working dir : </v>
       </c>
-      <c r="K104" s="6" t="str">
+      <c r="K104" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0580=工作文件夹：</v>
       </c>
@@ -6254,26 +6130,26 @@
         <v>/** ブック%s： */ APP_0590,</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I105" s="4" t="str">
+        <v>507</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I105" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0590=ブック%s：</v>
       </c>
-      <c r="J105" s="5" t="str">
+      <c r="J105" s="4" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">APP_0590=Book %s : </v>
       </c>
-      <c r="K105" s="6" t="str">
+      <c r="K105" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0590=工作簿%s：</v>
       </c>
@@ -6284,26 +6160,26 @@
         <v>/** 差分なし */ APP_0600,</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="I106" s="4" t="str">
+        <v>508</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="I106" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0600=差分なし</v>
       </c>
-      <c r="J106" s="5" t="str">
+      <c r="J106" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0600=No Diffs</v>
       </c>
-      <c r="K106" s="6" t="str">
+      <c r="K106" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0600=没有区别</v>
       </c>
@@ -6314,26 +6190,26 @@
         <v>/** 比較失敗 */ APP_0610,</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="I107" s="4" t="str">
+        <v>509</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="I107" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0610=比較失敗</v>
       </c>
-      <c r="J107" s="5" t="str">
+      <c r="J107" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0610=Comparison Failed</v>
       </c>
-      <c r="K107" s="6" t="str">
+      <c r="K107" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0610=比较失败</v>
       </c>
@@ -6344,26 +6220,26 @@
         <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="I108" s="4" t="str">
+        <v>510</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I108" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0620=余剰行（A: %d, B: %d）</v>
       </c>
-      <c r="J108" s="5" t="str">
+      <c r="J108" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
       </c>
-      <c r="K108" s="6" t="str">
+      <c r="K108" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0620=冗余行（A: %d, B: %d）</v>
       </c>
@@ -6374,26 +6250,26 @@
         <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="I109" s="4" t="str">
+        <v>511</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I109" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0630=余剰列（A: %d, B: %d）</v>
       </c>
-      <c r="J109" s="5" t="str">
+      <c r="J109" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
       </c>
-      <c r="K109" s="6" t="str">
+      <c r="K109" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0630=冗余列（A: %d, B: %d）</v>
       </c>
@@ -6404,26 +6280,26 @@
         <v>/** 差分セル（%d） */ APP_0640,</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="I110" s="4" t="str">
+        <v>512</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I110" s="3" t="str">
         <f t="shared" si="7"/>
         <v>APP_0640=差分セル（%d）</v>
       </c>
-      <c r="J110" s="5" t="str">
+      <c r="J110" s="4" t="str">
         <f t="shared" si="8"/>
         <v>APP_0640=Diff Cells (%d)</v>
       </c>
-      <c r="K110" s="6" t="str">
+      <c r="K110" s="5" t="str">
         <f t="shared" si="9"/>
         <v>APP_0640=差异单元格（%d）</v>
       </c>
@@ -6434,26 +6310,26 @@
         <v>/** (比較相手なし) */ APP_0650,</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="I111" s="4" t="str">
+        <v>513</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I111" s="3" t="str">
         <f t="shared" ref="I111:I142" si="10" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; E111)</f>
         <v>APP_0650=(比較相手なし)</v>
       </c>
-      <c r="J111" s="5" t="str">
+      <c r="J111" s="4" t="str">
         <f t="shared" ref="J111:J142" si="11" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; F111)</f>
         <v>APP_0650=(no opponent)</v>
       </c>
-      <c r="K111" s="6" t="str">
+      <c r="K111" s="5" t="str">
         <f t="shared" ref="K111:K142" si="12" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; G111)</f>
         <v>APP_0650=(没有对比)</v>
       </c>
@@ -6464,26 +6340,26 @@
         <v>/** 比較フォルダ%s： */ APP_0660,</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I112" s="4" t="str">
+        <v>514</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I112" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0660=比較フォルダ%s：</v>
       </c>
-      <c r="J112" s="5" t="str">
+      <c r="J112" s="4" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">APP_0660=Folder %s : </v>
       </c>
-      <c r="K112" s="6" t="str">
+      <c r="K112" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0660=文件夹%s：</v>
       </c>
@@ -6494,26 +6370,26 @@
         <v>/** 作業用フォルダ： */ APP_0670,</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I113" s="4" t="str">
+        <v>515</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I113" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0670=作業用フォルダ：</v>
       </c>
-      <c r="J113" s="5" t="str">
+      <c r="J113" s="4" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">APP_0670=Working dir : </v>
       </c>
-      <c r="K113" s="6" t="str">
+      <c r="K113" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0670=工作文件夹：</v>
       </c>
@@ -6524,26 +6400,26 @@
         <v>/** ワークシート */ APP_0680,</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="I114" s="4" t="str">
+        <v>516</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I114" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0680=ワークシート</v>
       </c>
-      <c r="J114" s="5" t="str">
+      <c r="J114" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0680=Worksheet</v>
       </c>
-      <c r="K114" s="6" t="str">
+      <c r="K114" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0680=工作表</v>
       </c>
@@ -6554,26 +6430,26 @@
         <v>/** グラフシート */ APP_0690,</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G115" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="I115" s="4" t="str">
+        <v>517</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I115" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0690=グラフシート</v>
       </c>
-      <c r="J115" s="5" t="str">
+      <c r="J115" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0690=Chart</v>
       </c>
-      <c r="K115" s="6" t="str">
+      <c r="K115" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0690=图表表</v>
       </c>
@@ -6584,26 +6460,26 @@
         <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="I116" s="4" t="str">
+        <v>518</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I116" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
       </c>
-      <c r="J116" s="5" t="str">
+      <c r="J116" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0700=MS Excel 5.0 Dialog</v>
       </c>
-      <c r="K116" s="6" t="str">
+      <c r="K116" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0700=MS Excel 5.0 对话表</v>
       </c>
@@ -6614,26 +6490,26 @@
         <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F117" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G117" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G117" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="I117" s="4" t="str">
+      <c r="I117" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0710=Excel 4.0 マクロシート</v>
       </c>
-      <c r="J117" s="5" t="str">
+      <c r="J117" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0710=Excel 4.0 Macro</v>
       </c>
-      <c r="K117" s="6" t="str">
+      <c r="K117" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0710=Excel 4.0 宏表</v>
       </c>
@@ -6644,26 +6520,26 @@
         <v>/** (差分なし) */ APP_0720,</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I118" s="4" t="str">
+        <v>520</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I118" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0720=(差分なし)</v>
       </c>
-      <c r="J118" s="5" t="str">
+      <c r="J118" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0720=(no diffs)</v>
       </c>
-      <c r="K118" s="6" t="str">
+      <c r="K118" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0720=(没有区别)</v>
       </c>
@@ -6674,26 +6550,26 @@
         <v>/** 余剰行%d */ APP_0730,</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F119" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G119" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G119" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="I119" s="4" t="str">
+      <c r="I119" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0730=余剰行%d</v>
       </c>
-      <c r="J119" s="5" t="str">
+      <c r="J119" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0730=redundant rows:%d</v>
       </c>
-      <c r="K119" s="6" t="str">
+      <c r="K119" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0730=冗余行%d</v>
       </c>
@@ -6704,26 +6580,26 @@
         <v>/** 余剰列%d */ APP_0740,</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F120" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G120" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G120" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I120" s="4" t="str">
+      <c r="I120" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0740=余剰列%d</v>
       </c>
-      <c r="J120" s="5" t="str">
+      <c r="J120" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0740=redundant columns:%d</v>
       </c>
-      <c r="K120" s="6" t="str">
+      <c r="K120" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0740=冗余列%d</v>
       </c>
@@ -6734,26 +6610,26 @@
         <v>/** 差分セル%d */ APP_0750,</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I121" s="4" t="str">
+        <v>523</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="I121" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0750=差分セル%d</v>
       </c>
-      <c r="J121" s="5" t="str">
+      <c r="J121" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0750=diff cells:%d</v>
       </c>
-      <c r="K121" s="6" t="str">
+      <c r="K121" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0750=差异单元格%d</v>
       </c>
@@ -6764,26 +6640,26 @@
         <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I122" s="4" t="str">
+        <v>524</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I122" s="3" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
       </c>
-      <c r="J122" s="5" t="str">
+      <c r="J122" s="4" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
       </c>
-      <c r="K122" s="6" t="str">
+      <c r="K122" s="5" t="str">
         <f t="shared" si="12"/>
         <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
       </c>
@@ -6794,26 +6670,26 @@
         <v>/** 行%d */ APP_0770,</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I123" s="4" t="str">
+        <v>525</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I123" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0770=行%d</v>
       </c>
-      <c r="J123" s="5" t="str">
+      <c r="J123" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0770=Row %d</v>
       </c>
-      <c r="K123" s="6" t="str">
+      <c r="K123" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0770=行%d</v>
       </c>
@@ -6824,26 +6700,26 @@
         <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G124" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="I124" s="4" t="str">
+        <v>526</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I124" s="3" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
       </c>
-      <c r="J124" s="5" t="str">
+      <c r="J124" s="4" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
       </c>
-      <c r="K124" s="6" t="str">
+      <c r="K124" s="5" t="str">
         <f t="shared" si="12"/>
         <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
       </c>
@@ -6854,26 +6730,26 @@
         <v>/** %s列 */ APP_0790,</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I125" s="4" t="str">
+        <v>527</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I125" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0790=%s列</v>
       </c>
-      <c r="J125" s="5" t="str">
+      <c r="J125" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0790=Column %s</v>
       </c>
-      <c r="K125" s="6" t="str">
+      <c r="K125" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0790=%s列</v>
       </c>
@@ -6884,26 +6760,26 @@
         <v>/** 差分セル :  */ APP_0800,</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I126" s="4" t="str">
+        <v>528</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="I126" s="3" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">APP_0800=差分セル : </v>
       </c>
-      <c r="J126" s="5" t="str">
+      <c r="J126" s="4" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">APP_0800=Diff cells : </v>
       </c>
-      <c r="K126" s="6" t="str">
+      <c r="K126" s="5" t="str">
         <f t="shared" si="12"/>
         <v xml:space="preserve">APP_0800=差异单元格 : </v>
       </c>
@@ -6914,26 +6790,26 @@
         <v>/** (比較相手なし) */ APP_0810,</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="I127" s="4" t="str">
+        <v>529</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I127" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0810=(比較相手なし)</v>
       </c>
-      <c r="J127" s="5" t="str">
+      <c r="J127" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0810=(no opponent)</v>
       </c>
-      <c r="K127" s="6" t="str">
+      <c r="K127" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0810=(没有对比)</v>
       </c>
@@ -6944,26 +6820,26 @@
         <v>/** ルートフォルダ%s :  */ APP_0820,</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="I128" s="4" t="str">
+        <v>530</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I128" s="3" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
       </c>
-      <c r="J128" s="5" t="str">
+      <c r="J128" s="4" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">APP_0820=Root folder %s : </v>
       </c>
-      <c r="K128" s="6" t="str">
+      <c r="K128" s="5" t="str">
         <f t="shared" si="12"/>
         <v xml:space="preserve">APP_0820=根文件夹%s : </v>
       </c>
@@ -6974,26 +6850,26 @@
         <v>/** ■差分サマリ --------------------------------------------------- */ APP_0830,</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I129" s="4" t="str">
+        <v>531</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I129" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0830=■差分サマリ ---------------------------------------------------</v>
       </c>
-      <c r="J129" s="5" t="str">
+      <c r="J129" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0830=## SUMMARY -----------------------------------------------------</v>
       </c>
-      <c r="K129" s="6" t="str">
+      <c r="K129" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0830=■差异摘要 -----------------------------------------------------</v>
       </c>
@@ -7004,26 +6880,26 @@
         <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0840,</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I130" s="4" t="str">
+        <v>532</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I130" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0840=■差分詳細 -----------------------------------------------------</v>
       </c>
-      <c r="J130" s="5" t="str">
+      <c r="J130" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0840=## DETAIL ------------------------------------------------------</v>
       </c>
-      <c r="K130" s="6" t="str">
+      <c r="K130" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0840=■差异细节 -----------------------------------------------------</v>
       </c>
@@ -7034,26 +6910,26 @@
         <v>/** ★失敗しました */ APP_0850,</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I131" s="4" t="str">
+        <v>533</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I131" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0850=★失敗しました</v>
       </c>
-      <c r="J131" s="5" t="str">
+      <c r="J131" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0850=★Failed</v>
       </c>
-      <c r="K131" s="6" t="str">
+      <c r="K131" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0850=★失败</v>
       </c>
@@ -7064,26 +6940,26 @@
         <v>/** 組み合わせ編集 */ APP_0860,</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="I132" s="4" t="str">
+        <v>534</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I132" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0860=組み合わせ編集</v>
       </c>
-      <c r="J132" s="5" t="str">
+      <c r="J132" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0860=Edit Pairing</v>
       </c>
-      <c r="K132" s="6" t="str">
+      <c r="K132" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0860=组合编辑</v>
       </c>
@@ -7094,26 +6970,26 @@
         <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="I133" s="4" t="str">
+        <v>535</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="I133" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
       </c>
-      <c r="J133" s="5" t="str">
+      <c r="J133" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
       </c>
-      <c r="K133" s="6" t="str">
+      <c r="K133" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
       </c>
@@ -7124,26 +7000,26 @@
         <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="G134" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="I134" s="4" t="str">
+        <v>536</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="I134" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
       </c>
-      <c r="J134" s="5" t="str">
+      <c r="J134" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
       </c>
-      <c r="K134" s="6" t="str">
+      <c r="K134" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
       </c>
@@ -7154,26 +7030,26 @@
         <v>/** 共有ドライブ */ APP_0890,</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="G135" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="I135" s="4" t="str">
+        <v>537</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="I135" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0890=共有ドライブ</v>
       </c>
-      <c r="J135" s="5" t="str">
+      <c r="J135" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0890=Shared drives</v>
       </c>
-      <c r="K135" s="6" t="str">
+      <c r="K135" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0890=共享云端硬盘</v>
       </c>
@@ -7184,26 +7060,26 @@
         <v>/** すべてのファイル */ APP_0900,</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="G136" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="I136" s="4" t="str">
+        <v>538</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I136" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0900=すべてのファイル</v>
       </c>
-      <c r="J136" s="5" t="str">
+      <c r="J136" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0900=All files</v>
       </c>
-      <c r="K136" s="6" t="str">
+      <c r="K136" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0900=所有文件</v>
       </c>
@@ -7214,26 +7090,26 @@
         <v>/** スター付き */ APP_0910,</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G137" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="I137" s="4" t="str">
+        <v>539</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="I137" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0910=スター付き</v>
       </c>
-      <c r="J137" s="5" t="str">
+      <c r="J137" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0910=Starred</v>
       </c>
-      <c r="K137" s="6" t="str">
+      <c r="K137" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0910=已加星标</v>
       </c>
@@ -7244,26 +7120,26 @@
         <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="I138" s="4" t="str">
+        <v>540</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="I138" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
       </c>
-      <c r="J138" s="5" t="str">
+      <c r="J138" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0920=Failed to download the file from Google Drive.</v>
       </c>
-      <c r="K138" s="6" t="str">
+      <c r="K138" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0920=从Google云端硬盘下载文件失败。</v>
       </c>
@@ -7274,26 +7150,26 @@
         <v>/** 更新者不明 */ APP_0930,</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="I139" s="4" t="str">
+        <v>541</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="I139" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0930=更新者不明</v>
       </c>
-      <c r="J139" s="5" t="str">
+      <c r="J139" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0930=Unknown</v>
       </c>
-      <c r="K139" s="6" t="str">
+      <c r="K139" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0930=更新者不明</v>
       </c>
@@ -7304,26 +7180,26 @@
         <v>/** 最新版 */ APP_0940,</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="I140" s="4" t="str">
+        <v>542</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="I140" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0940=最新版</v>
       </c>
-      <c r="J140" s="5" t="str">
+      <c r="J140" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0940=Latest</v>
       </c>
-      <c r="K140" s="6" t="str">
+      <c r="K140" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0940=最新版</v>
       </c>
@@ -7334,26 +7210,26 @@
         <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="I141" s="4" t="str">
+        <v>543</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="I141" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
       </c>
-      <c r="J141" s="5" t="str">
+      <c r="J141" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
       </c>
-      <c r="K141" s="6" t="str">
+      <c r="K141" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
       </c>
@@ -7364,26 +7240,26 @@
         <v>/** 資格情報を削除しました。 */ APP_0960,</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="I142" s="4" t="str">
+        <v>544</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I142" s="3" t="str">
         <f t="shared" si="10"/>
         <v>APP_0960=資格情報を削除しました。</v>
       </c>
-      <c r="J142" s="5" t="str">
+      <c r="J142" s="4" t="str">
         <f t="shared" si="11"/>
         <v>APP_0960=Credentials have been deleted.</v>
       </c>
-      <c r="K142" s="6" t="str">
+      <c r="K142" s="5" t="str">
         <f t="shared" si="12"/>
         <v>APP_0960=已删除凭据。</v>
       </c>
@@ -7394,26 +7270,26 @@
         <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="I143" s="4" t="str">
+        <v>545</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I143" s="3" t="str">
         <f t="shared" ref="I143:I177" si="14" xml:space="preserve"> IF($D143="", "", $D143 &amp; "=" &amp; E143)</f>
         <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
       </c>
-      <c r="J143" s="5" t="str">
+      <c r="J143" s="4" t="str">
         <f t="shared" ref="J143:J177" si="15" xml:space="preserve"> IF($D143="", "", $D143 &amp; "=" &amp; F143)</f>
         <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
       </c>
-      <c r="K143" s="6" t="str">
+      <c r="K143" s="5" t="str">
         <f t="shared" ref="K143:K177" si="16" xml:space="preserve"> IF($D143="", "", $D143 &amp; "=" &amp; G143)</f>
         <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
@@ -7424,26 +7300,26 @@
         <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="I144" s="4" t="str">
+        <v>546</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="I144" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_0980=資格情報の削除に失敗しました。</v>
       </c>
-      <c r="J144" s="5" t="str">
+      <c r="J144" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_0980=Failed to delete credentials.</v>
       </c>
-      <c r="K144" s="6" t="str">
+      <c r="K144" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_0980=删除凭据失败。</v>
       </c>
@@ -7454,26 +7330,26 @@
         <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="I145" s="4" t="str">
+        <v>547</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="I145" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
-      <c r="J145" s="5" t="str">
+      <c r="J145" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
       </c>
-      <c r="K145" s="6" t="str">
+      <c r="K145" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
@@ -7484,26 +7360,26 @@
         <v>/** Google連携エラー */ APP_1000,</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="I146" s="4" t="str">
+        <v>548</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="I146" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1000=Google連携エラー</v>
       </c>
-      <c r="J146" s="5" t="str">
+      <c r="J146" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1000=Google Integration Error</v>
       </c>
-      <c r="K146" s="6" t="str">
+      <c r="K146" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1000=Google关联错误</v>
       </c>
@@ -7514,26 +7390,26 @@
         <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="I147" s="4" t="str">
+        <v>549</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="I147" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
       </c>
-      <c r="J147" s="5" t="str">
+      <c r="J147" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1010=An error occurred during Google integration processing.</v>
       </c>
-      <c r="K147" s="6" t="str">
+      <c r="K147" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1010=Google关联处理过程中发生错误。</v>
       </c>
@@ -7544,26 +7420,26 @@
         <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="I148" s="4" t="str">
+        <v>550</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="I148" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
-      <c r="J148" s="5" t="str">
+      <c r="J148" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
       </c>
-      <c r="K148" s="6" t="str">
+      <c r="K148" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
@@ -7574,26 +7450,26 @@
         <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I149" s="4" t="str">
+        <v>551</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="I149" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
       </c>
-      <c r="J149" s="5" t="str">
+      <c r="J149" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1030=File downloaded from Google Drive</v>
       </c>
-      <c r="K149" s="6" t="str">
+      <c r="K149" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1030=已从Google云端硬盘下载文件</v>
       </c>
@@ -7604,26 +7480,26 @@
         <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="I150" s="4" t="str">
+        <v>552</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I150" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
       </c>
-      <c r="J150" s="5" t="str">
+      <c r="J150" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1040=Failed to open the website. Please try using your browser.</v>
       </c>
-      <c r="K150" s="6" t="str">
+      <c r="K150" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
@@ -7634,26 +7510,26 @@
         <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="I151" s="4" t="str">
+        <v>553</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I151" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
       </c>
-      <c r="J151" s="5" t="str">
+      <c r="J151" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1050=Failed to open working directory.</v>
       </c>
-      <c r="K151" s="6" t="str">
+      <c r="K151" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1050=显示工作文件夹失败。</v>
       </c>
@@ -7664,26 +7540,26 @@
         <v>/** 作業用フォルダの変更 */ APP_1060,</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I152" s="4" t="str">
+        <v>554</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I152" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1060=作業用フォルダの変更</v>
       </c>
-      <c r="J152" s="5" t="str">
+      <c r="J152" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1060=Change working directory</v>
       </c>
-      <c r="K152" s="6" t="str">
+      <c r="K152" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1060=改变工作文件夹</v>
       </c>
@@ -7694,26 +7570,26 @@
         <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I153" s="4" t="str">
+        <v>555</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="I153" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
       </c>
-      <c r="J153" s="5" t="str">
+      <c r="J153" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1070=Failed to change working directory.</v>
       </c>
-      <c r="K153" s="6" t="str">
+      <c r="K153" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1070=更改工作文件夹失败。</v>
       </c>
@@ -7724,26 +7600,26 @@
         <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G154" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="I154" s="4" t="str">
+        <v>556</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I154" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
       </c>
-      <c r="J154" s="5" t="str">
+      <c r="J154" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
       </c>
-      <c r="K154" s="6" t="str">
+      <c r="K154" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
@@ -7754,26 +7630,26 @@
         <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I155" s="4" t="str">
+        <v>557</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I155" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
-      <c r="J155" s="5" t="str">
+      <c r="J155" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
-      <c r="K155" s="6" t="str">
+      <c r="K155" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
@@ -7784,26 +7660,26 @@
         <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I156" s="4" t="str">
+        <v>558</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I156" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
-      <c r="J156" s="5" t="str">
+      <c r="J156" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
-      <c r="K156" s="6" t="str">
+      <c r="K156" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
@@ -7814,26 +7690,26 @@
         <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I157" s="4" t="str">
+        <v>559</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I157" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
-      <c r="J157" s="5" t="str">
+      <c r="J157" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
-      <c r="K157" s="6" t="str">
+      <c r="K157" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
@@ -7844,26 +7720,26 @@
         <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="I158" s="4" t="str">
+        <v>560</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="I158" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1100=方眼Diff  -  詳細設定</v>
       </c>
-      <c r="J158" s="5" t="str">
+      <c r="J158" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1100=HoganDiff  -  Advanced Settings</v>
       </c>
-      <c r="K158" s="6" t="str">
+      <c r="K158" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1100=方眼Diff  -  详细设置</v>
       </c>
@@ -7874,26 +7750,26 @@
         <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="I159" s="4" t="str">
+        <v>561</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I159" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1110=比較対象フォルダの選択</v>
       </c>
-      <c r="J159" s="5" t="str">
+      <c r="J159" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1110=Select comparison folder</v>
       </c>
-      <c r="K159" s="6" t="str">
+      <c r="K159" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1110=选择用于比较的文件夹</v>
       </c>
@@ -7904,26 +7780,26 @@
         <v>/** 比較対象ブックの選択 */ APP_1120,</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="I160" s="4" t="str">
+        <v>562</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I160" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1120=比較対象ブックの選択</v>
       </c>
-      <c r="J160" s="5" t="str">
+      <c r="J160" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1120=Select comparison book</v>
       </c>
-      <c r="K160" s="6" t="str">
+      <c r="K160" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1120=选择用于比较的工作簿</v>
       </c>
@@ -7934,26 +7810,26 @@
         <v>/** Excel ブック */ APP_1130,</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I161" s="4" t="str">
+        <v>563</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I161" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1130=Excel ブック</v>
       </c>
-      <c r="J161" s="5" t="str">
+      <c r="J161" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1130=Excel book</v>
       </c>
-      <c r="K161" s="6" t="str">
+      <c r="K161" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1130=Excel工作簿</v>
       </c>
@@ -7964,26 +7840,26 @@
         <v>/** ファイルを読み込めません： */ APP_1140,</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G162" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I162" s="4" t="str">
+        <v>564</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I162" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1140=ファイルを読み込めません：</v>
       </c>
-      <c r="J162" s="5" t="str">
+      <c r="J162" s="4" t="str">
         <f t="shared" si="15"/>
         <v xml:space="preserve">APP_1140=Failed to open file : </v>
       </c>
-      <c r="K162" s="6" t="str">
+      <c r="K162" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1140=无法读取文件：</v>
       </c>
@@ -7994,26 +7870,26 @@
         <v>/** シートが見つかりません： */ APP_1150,</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G163" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I163" s="4" t="str">
+        <v>565</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I163" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1150=シートが見つかりません：</v>
       </c>
-      <c r="J163" s="5" t="str">
+      <c r="J163" s="4" t="str">
         <f t="shared" si="15"/>
         <v xml:space="preserve">APP_1150=No such sheet : </v>
       </c>
-      <c r="K163" s="6" t="str">
+      <c r="K163" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1150=没有找到工作表：</v>
       </c>
@@ -8024,26 +7900,26 @@
         <v>/** フォルダを読み込めません： */ APP_1160,</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G164" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="I164" s="4" t="str">
+        <v>566</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="I164" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1160=フォルダを読み込めません：</v>
       </c>
-      <c r="J164" s="5" t="str">
+      <c r="J164" s="4" t="str">
         <f t="shared" si="15"/>
         <v xml:space="preserve">APP_1160=Failed to open folder : </v>
       </c>
-      <c r="K164" s="6" t="str">
+      <c r="K164" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1160=无法读取文件夹：</v>
       </c>
@@ -8054,26 +7930,26 @@
         <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="G165" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="I165" s="4" t="str">
+        <v>567</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="I165" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
       </c>
-      <c r="J165" s="5" t="str">
+      <c r="J165" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
       </c>
-      <c r="K165" s="6" t="str">
+      <c r="K165" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
@@ -8084,26 +7960,26 @@
         <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G166" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I166" s="4" t="str">
+        <v>568</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I166" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
       </c>
-      <c r="J166" s="5" t="str">
+      <c r="J166" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1180=Please specify different folders/books/sheets.</v>
       </c>
-      <c r="K166" s="6" t="str">
+      <c r="K166" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
@@ -8114,26 +7990,26 @@
         <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G167" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="I167" s="4" t="str">
+        <v>569</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="I167" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
       </c>
-      <c r="J167" s="5" t="str">
+      <c r="J167" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
       </c>
-      <c r="K167" s="6" t="str">
+      <c r="K167" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
@@ -8144,26 +8020,26 @@
         <v>/** 予期せぬ例外が発生しました。 */ APP_1200,</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G168" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I168" s="4" t="str">
+        <v>570</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G168" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I168" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1200=予期せぬ例外が発生しました。</v>
       </c>
-      <c r="J168" s="5" t="str">
+      <c r="J168" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1200=Unexpected exception occurred.</v>
       </c>
-      <c r="K168" s="6" t="str">
+      <c r="K168" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1200=意外的例外。</v>
       </c>
@@ -8174,26 +8050,26 @@
         <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G169" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="I169" s="4" t="str">
+        <v>571</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G169" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I169" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
       </c>
-      <c r="J169" s="5" t="str">
+      <c r="J169" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1210=Failed to create working directory.</v>
       </c>
-      <c r="K169" s="6" t="str">
+      <c r="K169" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1210=创建工作文件夹失败。</v>
       </c>
@@ -8204,26 +8080,26 @@
         <v>/** 別の場所を指定してください。 */ APP_1220,</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="I170" s="4" t="str">
+        <v>572</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G170" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I170" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1220=別の場所を指定してください。</v>
       </c>
-      <c r="J170" s="5" t="str">
+      <c r="J170" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1220=Please specify another location.</v>
       </c>
-      <c r="K170" s="6" t="str">
+      <c r="K170" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1220=请指定其他位置。</v>
       </c>
@@ -8234,26 +8110,26 @@
         <v>/** 作業用フォルダの変更 */ APP_1230,</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G171" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I171" s="4" t="str">
+        <v>573</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I171" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1230=作業用フォルダの変更</v>
       </c>
-      <c r="J171" s="5" t="str">
+      <c r="J171" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1230=Change working directory</v>
       </c>
-      <c r="K171" s="6" t="str">
+      <c r="K171" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1230=改变工作文件夹</v>
       </c>
@@ -8264,26 +8140,26 @@
         <v>/** 処理を中止しました。 */ APP_1240,</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="I172" s="4" t="str">
+        <v>574</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I172" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1240=処理を中止しました。</v>
       </c>
-      <c r="J172" s="5" t="str">
+      <c r="J172" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1240=Processing has been canceled.</v>
       </c>
-      <c r="K172" s="6" t="str">
+      <c r="K172" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1240=处理已被取消。</v>
       </c>
@@ -8294,26 +8170,26 @@
         <v>/** パスワード指定 */ APP_1250,</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="I173" s="4" t="str">
+        <v>575</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I173" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1250=パスワード指定</v>
       </c>
-      <c r="J173" s="5" t="str">
+      <c r="J173" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1250=Enter Password</v>
       </c>
-      <c r="K173" s="6" t="str">
+      <c r="K173" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1250=输入密码</v>
       </c>
@@ -8324,26 +8200,26 @@
         <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I174" s="4" t="str">
+        <v>576</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I174" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1260=%s はパスワードで保護されています。</v>
       </c>
-      <c r="J174" s="5" t="str">
+      <c r="J174" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1260=The book [%s] is password protected.</v>
       </c>
-      <c r="K174" s="6" t="str">
+      <c r="K174" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1260=%s 是受密码保护的。</v>
       </c>
@@ -8354,26 +8230,26 @@
         <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="G175" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="I175" s="4" t="str">
+        <v>577</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="I175" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1270=新しいバージョンが利用可能です。</v>
       </c>
-      <c r="J175" s="5" t="str">
+      <c r="J175" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1270=A new version is available.</v>
       </c>
-      <c r="K175" s="6" t="str">
+      <c r="K175" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1270=有新版本可用。</v>
       </c>
@@ -8384,26 +8260,26 @@
         <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="I176" s="4" t="str">
+        <v>578</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="I176" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
       </c>
-      <c r="J176" s="5" t="str">
+      <c r="J176" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
       </c>
-      <c r="K176" s="6" t="str">
+      <c r="K176" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
       </c>
@@ -8414,26 +8290,26 @@
         <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E177" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="I177" s="4" t="str">
+        <v>579</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="I177" s="3" t="str">
         <f t="shared" si="14"/>
         <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
       </c>
-      <c r="J177" s="5" t="str">
+      <c r="J177" s="4" t="str">
         <f t="shared" si="15"/>
         <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
       </c>
-      <c r="K177" s="6" t="str">
+      <c r="K177" s="5" t="str">
         <f t="shared" si="16"/>
         <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
       </c>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAC45A9D-4CB8-4E80-9C2F-6FB692BDF6DA}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646F8428-5611-4494-81EA-95EC4933D09B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="(3)" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$179</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="632">
   <si>
     <t>website</t>
   </si>
@@ -1995,17 +1995,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>設定</t>
-    <rPh sb="0" eb="2">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Settings</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <t>详细设置</t>
     </r>
@@ -2019,10 +2008,6 @@
       </rPr>
       <t>...</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>设置</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2769,6 +2754,71 @@
   </si>
   <si>
     <t>FXML_0230</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定管理</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Settings Management</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>设置管理</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0450</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0460</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他設定</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>其他设置</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Other settings</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー情報を自動でサーバに送信する</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Automatically send error information to the server</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自动发送错误信息到服务器</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3186,7 +3236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:K177"/>
+  <dimension ref="C1:K179"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -3204,7 +3254,7 @@
   <sheetData>
     <row r="1" spans="3:11">
       <c r="C1" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>108</v>
@@ -3227,7 +3277,7 @@
     </row>
     <row r="2" spans="3:11">
       <c r="D2" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -3253,7 +3303,7 @@
     </row>
     <row r="3" spans="3:11">
       <c r="D3" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -3265,21 +3315,21 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I46" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
+        <f t="shared" ref="I3:I66" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="J3" s="4" t="str">
-        <f t="shared" ref="J3:J46" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
+        <f t="shared" ref="J3:J66" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="K3" s="5" t="str">
-        <f t="shared" ref="K3:K46" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
+        <f t="shared" ref="K3:K66" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
         <v>FXML_0020=website</v>
       </c>
     </row>
     <row r="4" spans="3:11">
       <c r="D4" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>157</v>
@@ -3305,7 +3355,7 @@
     </row>
     <row r="5" spans="3:11">
       <c r="D5" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>158</v>
@@ -3331,7 +3381,7 @@
     </row>
     <row r="6" spans="3:11">
       <c r="D6" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>159</v>
@@ -3357,7 +3407,7 @@
     </row>
     <row r="7" spans="3:11">
       <c r="D7" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>123</v>
@@ -3383,7 +3433,7 @@
     </row>
     <row r="8" spans="3:11">
       <c r="D8" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>156</v>
@@ -3409,7 +3459,7 @@
     </row>
     <row r="9" spans="3:11">
       <c r="D9" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>16</v>
@@ -3435,7 +3485,7 @@
     </row>
     <row r="10" spans="3:11">
       <c r="D10" s="1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
@@ -3461,7 +3511,7 @@
     </row>
     <row r="11" spans="3:11">
       <c r="D11" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -3487,7 +3537,7 @@
     </row>
     <row r="12" spans="3:11">
       <c r="D12" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>4</v>
@@ -3513,7 +3563,7 @@
     </row>
     <row r="13" spans="3:11">
       <c r="D13" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -3539,7 +3589,7 @@
     </row>
     <row r="14" spans="3:11">
       <c r="D14" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -3565,7 +3615,7 @@
     </row>
     <row r="15" spans="3:11">
       <c r="D15" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -3591,7 +3641,7 @@
     </row>
     <row r="16" spans="3:11">
       <c r="D16" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>336</v>
@@ -3617,7 +3667,7 @@
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>8</v>
@@ -3643,7 +3693,7 @@
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>288</v>
@@ -3669,7 +3719,7 @@
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>300</v>
@@ -3695,7 +3745,7 @@
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>9</v>
@@ -3721,7 +3771,7 @@
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -3747,7 +3797,7 @@
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>270</v>
@@ -3773,7 +3823,7 @@
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>271</v>
@@ -3799,7 +3849,7 @@
     </row>
     <row r="24" spans="4:11">
       <c r="D24" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
@@ -3825,7 +3875,7 @@
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -3851,7 +3901,7 @@
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>421</v>
@@ -3860,7 +3910,7 @@
         <v>422</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3877,7 +3927,7 @@
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>13</v>
@@ -3903,7 +3953,7 @@
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>14</v>
@@ -3929,7 +3979,7 @@
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
@@ -3955,7 +4005,7 @@
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>192</v>
@@ -3981,7 +4031,7 @@
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>1</v>
@@ -4007,7 +4057,7 @@
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>155</v>
@@ -4031,9 +4081,9 @@
         <v>FXML_0310=文件夹路径：</v>
       </c>
     </row>
-    <row r="33" spans="3:11">
+    <row r="33" spans="4:11">
       <c r="D33" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>370</v>
@@ -4057,9 +4107,9 @@
         <v>FXML_0320=文件URL :</v>
       </c>
     </row>
-    <row r="34" spans="3:11">
+    <row r="34" spans="4:11">
       <c r="D34" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>372</v>
@@ -4083,9 +4133,9 @@
         <v>FXML_0330=文件名 :</v>
       </c>
     </row>
-    <row r="35" spans="3:11">
+    <row r="35" spans="4:11">
       <c r="D35" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>376</v>
@@ -4109,9 +4159,9 @@
         <v>FXML_0340=版本 :</v>
       </c>
     </row>
-    <row r="36" spans="3:11">
+    <row r="36" spans="4:11">
       <c r="D36" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>379</v>
@@ -4135,9 +4185,9 @@
         <v>FXML_0350=Google Drive\n关联</v>
       </c>
     </row>
-    <row r="37" spans="3:11">
+    <row r="37" spans="4:11">
       <c r="D37" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>381</v>
@@ -4161,9 +4211,9 @@
         <v>FXML_0360=Google Drive\n关联解除</v>
       </c>
     </row>
-    <row r="38" spans="3:11">
+    <row r="38" spans="4:11">
       <c r="D38" s="1" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>423</v>
@@ -4187,9 +4237,9 @@
         <v>FXML_0370=更新确认</v>
       </c>
     </row>
-    <row r="39" spans="3:11">
+    <row r="39" spans="4:11">
       <c r="D39" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>427</v>
@@ -4213,9 +4263,9 @@
         <v>FXML_0380=启动时检查是否有新版本</v>
       </c>
     </row>
-    <row r="40" spans="3:11">
+    <row r="40" spans="4:11">
       <c r="D40" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>429</v>
@@ -4239,44 +4289,44 @@
         <v>FXML_0390=立即检查是否有新版本</v>
       </c>
     </row>
-    <row r="41" spans="3:11">
+    <row r="41" spans="4:11">
       <c r="D41" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>432</v>
+        <v>621</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>433</v>
+        <v>622</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>435</v>
+        <v>623</v>
       </c>
       <c r="I41" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0400=設定</v>
+        <v>FXML_0400=設定管理</v>
       </c>
       <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0400=Settings</v>
+        <v>FXML_0400=Settings Management</v>
       </c>
       <c r="K41" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0400=设置</v>
-      </c>
-    </row>
-    <row r="42" spans="3:11">
+        <v>FXML_0400=设置管理</v>
+      </c>
+    </row>
+    <row r="42" spans="4:11">
       <c r="D42" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4291,18 +4341,18 @@
         <v>FXML_0410=显示配置文件</v>
       </c>
     </row>
-    <row r="43" spans="3:11">
+    <row r="43" spans="4:11">
       <c r="D43" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4317,9 +4367,9 @@
         <v>FXML_0420=重置设置…</v>
       </c>
     </row>
-    <row r="44" spans="3:11">
+    <row r="44" spans="4:11">
       <c r="D44" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>393</v>
@@ -4343,9 +4393,9 @@
         <v>FXML_0430=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
       </c>
     </row>
-    <row r="45" spans="3:11">
+    <row r="45" spans="4:11">
       <c r="D45" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>386</v>
@@ -4369,3954 +4419,4006 @@
         <v>FXML_0440=不再显示此消息</v>
       </c>
     </row>
-    <row r="46" spans="3:11">
-      <c r="E46" s="2"/>
+    <row r="46" spans="4:11">
+      <c r="D46" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>627</v>
+      </c>
       <c r="I46" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>FXML_0450=その他設定</v>
       </c>
       <c r="J46" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>FXML_0450=Other settings</v>
       </c>
       <c r="K46" s="5" t="str">
         <f t="shared" si="2"/>
+        <v>FXML_0450=其他设置</v>
+      </c>
+    </row>
+    <row r="47" spans="4:11">
+      <c r="D47" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="I47" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>FXML_0460=エラー情報を自動でサーバに送信する</v>
+      </c>
+      <c r="J47" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>FXML_0460=Automatically send error information to the server</v>
+      </c>
+      <c r="K47" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>FXML_0460=自动发送错误信息到服务器</v>
+      </c>
+    </row>
+    <row r="48" spans="4:11">
+      <c r="E48" s="2"/>
+      <c r="I48" s="3" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="47" spans="3:11">
-      <c r="C47" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E47 &amp; " */ " &amp; D47 &amp; ","</f>
-        <v>/** 方眼Diff */ APP_0010,</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="I47" s="3" t="str">
-        <f t="shared" ref="I47:I78" si="3" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; E47)</f>
-        <v>APP_0010=方眼Diff</v>
-      </c>
-      <c r="J47" s="4" t="str">
-        <f t="shared" ref="J47:J78" si="4" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; F47)</f>
-        <v>APP_0010=HoganDiff (方眼Diff)</v>
-      </c>
-      <c r="K47" s="5" t="str">
-        <f t="shared" ref="K47:K78" si="5" xml:space="preserve"> IF($D47="", "", $D47 &amp; "=" &amp; G47)</f>
-        <v>APP_0010=方眼Diff</v>
-      </c>
-    </row>
-    <row r="48" spans="3:11">
-      <c r="C48" s="1" t="str">
-        <f t="shared" ref="C48:C111" si="6" xml:space="preserve"> "/** " &amp; E48 &amp; " */ " &amp; D48 &amp; ","</f>
-        <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="I48" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0020=設定の保存に失敗しました。</v>
-      </c>
       <c r="J48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0020=Failed to save settings.</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="K48" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0020=保存设置失败。</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
     <row r="49" spans="3:11">
       <c r="C49" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
+        <f xml:space="preserve"> "/** " &amp; E49 &amp; " */ " &amp; D49 &amp; ","</f>
+        <v>/** 方眼Diff */ APP_0010,</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="I49" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0030=比較結果テキストを保存しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0010=方眼Diff</v>
       </c>
       <c r="J49" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0030=Saving result text...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0010=HoganDiff (方眼Diff)</v>
       </c>
       <c r="K49" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0030=存储比较结果文本...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0010=方眼Diff</v>
       </c>
     </row>
     <row r="50" spans="3:11">
       <c r="C50" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
+        <f t="shared" ref="C50:C113" si="3" xml:space="preserve"> "/** " &amp; E50 &amp; " */ " &amp; D50 &amp; ","</f>
+        <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I50" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0020=設定の保存に失敗しました。</v>
       </c>
       <c r="J50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0040=Failed to save or open result text.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0020=Failed to save settings.</v>
       </c>
       <c r="K50" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0040=保存和显示比较结果文本失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0020=保存设置失败。</v>
       </c>
     </row>
     <row r="51" spans="3:11">
       <c r="C51" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I51" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0030=比較結果テキストを保存しています...</v>
       </c>
       <c r="J51" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0050=Painting and saving result book(s)...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0030=Saving result text...</v>
       </c>
       <c r="K51" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0050=着色和存储在工作簿...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0030=存储比较结果文本...</v>
       </c>
     </row>
     <row r="52" spans="3:11">
       <c r="C52" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I52" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
       </c>
       <c r="J52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0060=Failed to paint or save result book(s).</v>
+        <f t="shared" si="1"/>
+        <v>APP_0040=Failed to save or open result text.</v>
       </c>
       <c r="K52" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0060=着色和保存工作簿失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0040=保存和显示比较结果文本失败。</v>
       </c>
     </row>
     <row r="53" spans="3:11">
       <c r="C53" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I53" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
       </c>
       <c r="J53" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0070=Opening result book(s)...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0050=Painting and saving result book(s)...</v>
       </c>
       <c r="K53" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0070=显示比较结果的工作簿...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0050=着色和存储在工作簿...</v>
       </c>
     </row>
     <row r="54" spans="3:11">
       <c r="C54" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I54" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0080=Excelブックの表示に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
       </c>
       <c r="J54" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0080=Failed to open result book(s).</v>
+        <f t="shared" si="1"/>
+        <v>APP_0060=Failed to paint or save result book(s).</v>
       </c>
       <c r="K54" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0080=显示工作簿失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0060=着色和保存工作簿失败。</v>
       </c>
     </row>
     <row r="55" spans="3:11">
       <c r="C55" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** ExcelブックAの着色・保存に失敗しました。 */ APP_0090,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I55" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0090=ExcelブックAの着色・保存に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
       </c>
       <c r="J55" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0090=Failed to paint or save result book A.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0070=Opening result book(s)...</v>
       </c>
       <c r="K55" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0090=工作簿A的着色和保存失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0070=显示比较结果的工作簿...</v>
       </c>
     </row>
     <row r="56" spans="3:11">
       <c r="C56" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** ExcelブックBの着色・保存に失敗しました。 */ APP_0100,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0100=ExcelブックBの着色・保存に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0080=Excelブックの表示に失敗しました。</v>
       </c>
       <c r="J56" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0100=Failed to paint or save result book B.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0080=Failed to open result book(s).</v>
       </c>
       <c r="K56" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0100=工作簿B的着色和保存失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0080=显示工作簿失败。</v>
       </c>
     </row>
     <row r="57" spans="3:11">
       <c r="C57" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 処理が完了しました。 */ APP_0110,</v>
+        <f t="shared" si="3"/>
+        <v>/** ExcelブックAの着色・保存に失敗しました。 */ APP_0090,</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I57" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0110=処理が完了しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0090=ExcelブックAの着色・保存に失敗しました。</v>
       </c>
       <c r="J57" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0110=Process completed.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0090=Failed to paint or save result book A.</v>
       </c>
       <c r="K57" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0110=过程完成。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0090=工作簿A的着色和保存失败。</v>
       </c>
     </row>
     <row r="58" spans="3:11">
       <c r="C58" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** ★失敗しました */ APP_0120,</v>
+        <f t="shared" si="3"/>
+        <v>/** ExcelブックBの着色・保存に失敗しました。 */ APP_0100,</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>129</v>
+        <v>455</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0120=★失敗しました</v>
+        <f t="shared" si="0"/>
+        <v>APP_0100=ExcelブックBの着色・保存に失敗しました。</v>
       </c>
       <c r="J58" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0120=★Failed</v>
+        <f t="shared" si="1"/>
+        <v>APP_0100=Failed to paint or save result book B.</v>
       </c>
       <c r="K58" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0120=★失败</v>
+        <f t="shared" si="2"/>
+        <v>APP_0100=工作簿B的着色和保存失败。</v>
       </c>
     </row>
     <row r="59" spans="3:11">
       <c r="C59" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
+        <f t="shared" si="3"/>
+        <v>/** 処理が完了しました。 */ APP_0110,</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>168</v>
+        <v>456</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0130=(比較対象ファイルなし)</v>
+        <f t="shared" si="0"/>
+        <v>APP_0110=処理が完了しました。</v>
       </c>
       <c r="J59" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0130=(No files to compare)</v>
+        <f t="shared" si="1"/>
+        <v>APP_0110=Process completed.</v>
       </c>
       <c r="K59" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0130=(没有可比较的文件)</v>
+        <f t="shared" si="2"/>
+        <v>APP_0110=过程完成。</v>
       </c>
     </row>
     <row r="60" spans="3:11">
       <c r="C60" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
+        <f t="shared" si="3"/>
+        <v>/** ★失敗しました */ APP_0120,</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>274</v>
+        <v>129</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>275</v>
+        <v>142</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>349</v>
+        <v>249</v>
       </c>
       <c r="I60" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <f t="shared" si="0"/>
+        <v>APP_0120=★失敗しました</v>
       </c>
       <c r="J60" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <f t="shared" si="1"/>
+        <v>APP_0120=★Failed</v>
       </c>
       <c r="K60" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <f t="shared" si="2"/>
+        <v>APP_0120=★失败</v>
       </c>
     </row>
     <row r="61" spans="3:11">
       <c r="C61" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
+        <f t="shared" si="3"/>
+        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>29</v>
+        <v>458</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="I61" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0150=予期せぬ例外が発生しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0130=(比較対象ファイルなし)</v>
       </c>
       <c r="J61" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0150=Unexpected exception occurred.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0130=(No files to compare)</v>
       </c>
       <c r="K61" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0150=意外的例外。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0130=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="62" spans="3:11">
       <c r="C62" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 比較実行日時 :  */ APP_0160,</v>
+        <f t="shared" si="3"/>
+        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>313</v>
+        <v>275</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I62" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0160=比較実行日時 : </v>
+        <f t="shared" si="0"/>
+        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="J62" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0160=Exec datetime : </v>
+        <f t="shared" si="1"/>
+        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="K62" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0160=执行日期和时间 : </v>
+        <f t="shared" si="2"/>
+        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
     </row>
     <row r="63" spans="3:11">
       <c r="C63" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
+        <f t="shared" si="3"/>
+        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="I63" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0170=ブック同士の比較を開始します。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0150=予期せぬ例外が発生しました。</v>
       </c>
       <c r="J63" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0170=Starting comparing books.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0150=Unexpected exception occurred.</v>
       </c>
       <c r="K63" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0170=开始互相比较工作簿。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0150=意外的例外。</v>
       </c>
     </row>
     <row r="64" spans="3:11">
       <c r="C64" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** シートを比較しています... */ APP_0180,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較実行日時 :  */ APP_0160,</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>37</v>
+        <v>461</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>251</v>
+        <v>350</v>
       </c>
       <c r="I64" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0180=シートを比較しています...</v>
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">APP_0160=比較実行日時 : </v>
       </c>
       <c r="J64" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0180=Comparing sheets...</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">APP_0160=Exec datetime : </v>
       </c>
       <c r="K64" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0180=比较工作表...</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">APP_0160=执行日期和时间 : </v>
       </c>
     </row>
     <row r="65" spans="3:11">
       <c r="C65" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
+        <f t="shared" si="3"/>
+        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I65" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0190=シートの比較に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0170=ブック同士の比較を開始します。</v>
       </c>
       <c r="J65" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0190=Failed to compare sheets.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0170=Starting comparing books.</v>
       </c>
       <c r="K65" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0190=工作表比较失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0170=开始互相比较工作簿。</v>
       </c>
     </row>
     <row r="66" spans="3:11">
       <c r="C66" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
+        <f t="shared" si="3"/>
+        <v>/** シートを比較しています... */ APP_0180,</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>314</v>
+        <v>37</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>316</v>
+        <v>251</v>
       </c>
       <c r="I66" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0200=比較結果レポートを保存しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0180=シートを比較しています...</v>
       </c>
       <c r="J66" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0200=Saving result report...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0180=Comparing sheets...</v>
       </c>
       <c r="K66" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0200=保存比较结果报告...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0180=比较工作表...</v>
       </c>
     </row>
     <row r="67" spans="3:11">
       <c r="C67" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
+        <f t="shared" si="3"/>
+        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="I67" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
+        <f t="shared" ref="I67:I130" si="4" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; E67)</f>
+        <v>APP_0190=シートの比較に失敗しました。</v>
       </c>
       <c r="J67" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0210=Failed to save result report.</v>
+        <f t="shared" ref="J67:J130" si="5" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; F67)</f>
+        <v>APP_0190=Failed to compare sheets.</v>
       </c>
       <c r="K67" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0210=保存比较结果报告失败。</v>
+        <f t="shared" ref="K67:K130" si="6" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; G67)</f>
+        <v>APP_0190=工作表比较失败。</v>
       </c>
     </row>
     <row r="68" spans="3:11">
       <c r="C68" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I68" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0200=比較結果レポートを保存しています...</v>
+      </c>
+      <c r="J68" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0200=Saving result report...</v>
+      </c>
+      <c r="K68" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="I68" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0220=比較結果レポートを表示しています...</v>
-      </c>
-      <c r="J68" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0220=Opening result report...</v>
-      </c>
-      <c r="K68" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0220=显示比较结果报告...</v>
+        <v>APP_0200=保存比较结果报告...</v>
       </c>
     </row>
     <row r="69" spans="3:11">
       <c r="C69" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I69" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
+      </c>
+      <c r="J69" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0210=Failed to save result report.</v>
+      </c>
+      <c r="K69" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I69" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
-      </c>
-      <c r="J69" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0230=Failed to open result report.</v>
-      </c>
-      <c r="K69" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0230=显示比较结果报告失败。</v>
+        <v>APP_0210=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="70" spans="3:11">
       <c r="C70" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I70" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0220=比較結果レポートを表示しています...</v>
+      </c>
+      <c r="J70" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0220=Opening result report...</v>
+      </c>
+      <c r="K70" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="I70" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0240=フォルダ同士の比較を開始します。</v>
-      </c>
-      <c r="J70" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0240=Starting comparing folders.</v>
-      </c>
-      <c r="K70" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0240=开始互相比较文件夹。</v>
+        <v>APP_0220=显示比较结果报告...</v>
       </c>
     </row>
     <row r="71" spans="3:11">
       <c r="C71" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I71" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
+      </c>
+      <c r="J71" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0230=Failed to open result report.</v>
+      </c>
+      <c r="K71" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I71" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
-      </c>
-      <c r="J71" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0250=Failed to create output directory.</v>
-      </c>
-      <c r="K71" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0250=创建输出目的地文件夹失败。</v>
+        <v>APP_0230=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="72" spans="3:11">
       <c r="C72" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I72" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0240=フォルダ同士の比較を開始します。</v>
+      </c>
+      <c r="J72" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0240=Starting comparing folders.</v>
+      </c>
+      <c r="K72" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** Excelブックを比較しています... */ APP_0260,</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="I72" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0260=Excelブックを比較しています...</v>
-      </c>
-      <c r="J72" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0260=Comparing books...</v>
-      </c>
-      <c r="K72" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0260=比较工作簿...</v>
+        <v>APP_0240=开始互相比较文件夹。</v>
       </c>
     </row>
     <row r="73" spans="3:11">
       <c r="C73" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I73" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
+      </c>
+      <c r="J73" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0250=Failed to create output directory.</v>
+      </c>
+      <c r="K73" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (比較対象ファイルなし) */ APP_0270,</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="I73" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0270=(比較対象ファイルなし)</v>
-      </c>
-      <c r="J73" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0270=(No files to compare)</v>
-      </c>
-      <c r="K73" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0270=(没有可比较的文件)</v>
+        <v>APP_0250=创建输出目的地文件夹失败。</v>
       </c>
     </row>
     <row r="74" spans="3:11">
       <c r="C74" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** Excelブックを比較しています... */ APP_0260,</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I74" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0260=Excelブックを比較しています...</v>
+      </c>
+      <c r="J74" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0260=Comparing books...</v>
+      </c>
+      <c r="K74" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="I74" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0280=フォルダの比較に失敗しました。</v>
-      </c>
-      <c r="J74" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0280=Failed to compare folders.</v>
-      </c>
-      <c r="K74" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0280=文件夹比较失败。</v>
+        <v>APP_0260=比较工作簿...</v>
       </c>
     </row>
     <row r="75" spans="3:11">
       <c r="C75" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** (比較対象ファイルなし) */ APP_0270,</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I75" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0270=(比較対象ファイルなし)</v>
+      </c>
+      <c r="J75" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0270=(No files to compare)</v>
+      </c>
+      <c r="K75" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="I75" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0290=シート同士の比較を開始します。</v>
-      </c>
-      <c r="J75" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0290=Starting comparing sheets.</v>
-      </c>
-      <c r="K75" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0290=开始相互比较工作表。</v>
+        <v>APP_0270=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="76" spans="3:11">
       <c r="C76" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="I76" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0280=フォルダの比較に失敗しました。</v>
+      </c>
+      <c r="J76" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0280=Failed to compare folders.</v>
+      </c>
+      <c r="K76" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** シートを比較しています... */ APP_0300,</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="I76" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0300=シートを比較しています...</v>
-      </c>
-      <c r="J76" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0300=Comparing sheets...</v>
-      </c>
-      <c r="K76" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0300=比较工作表...</v>
+        <v>APP_0280=文件夹比较失败。</v>
       </c>
     </row>
     <row r="77" spans="3:11">
       <c r="C77" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I77" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0290=シート同士の比較を開始します。</v>
+      </c>
+      <c r="J77" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0290=Starting comparing sheets.</v>
+      </c>
+      <c r="K77" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** シートの比較に失敗しました。 */ APP_0310,</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="I77" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0310=シートの比較に失敗しました。</v>
-      </c>
-      <c r="J77" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0310=Failed to compare sheets.</v>
-      </c>
-      <c r="K77" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0310=工作表比较失败。</v>
+        <v>APP_0290=开始相互比较工作表。</v>
       </c>
     </row>
     <row r="78" spans="3:11">
       <c r="C78" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** シートを比較しています... */ APP_0300,</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I78" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0300=シートを比較しています...</v>
+      </c>
+      <c r="J78" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0300=Comparing sheets...</v>
+      </c>
+      <c r="K78" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="I78" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
-      </c>
-      <c r="J78" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0320=Starting comparing folder trees.</v>
-      </c>
-      <c r="K78" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0320=开始互相比较文件夹树。</v>
+        <v>APP_0300=比较工作表...</v>
       </c>
     </row>
     <row r="79" spans="3:11">
       <c r="C79" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** シートの比較に失敗しました。 */ APP_0310,</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I79" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0310=シートの比較に失敗しました。</v>
+      </c>
+      <c r="J79" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0310=Failed to compare sheets.</v>
+      </c>
+      <c r="K79" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I79" s="3" t="str">
-        <f t="shared" ref="I79:I110" si="7" xml:space="preserve"> IF($D79="", "", $D79 &amp; "=" &amp; E79)</f>
-        <v>APP_0330=フォルダツリーを比較しています...</v>
-      </c>
-      <c r="J79" s="4" t="str">
-        <f t="shared" ref="J79:J110" si="8" xml:space="preserve"> IF($D79="", "", $D79 &amp; "=" &amp; F79)</f>
-        <v>APP_0330=Comparing folders...</v>
-      </c>
-      <c r="K79" s="5" t="str">
-        <f t="shared" ref="K79:K110" si="9" xml:space="preserve"> IF($D79="", "", $D79 &amp; "=" &amp; G79)</f>
-        <v>APP_0330=比较文件夹...</v>
+        <v>APP_0310=工作表比较失败。</v>
       </c>
     </row>
     <row r="80" spans="3:11">
       <c r="C80" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I80" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
+      </c>
+      <c r="J80" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0320=Starting comparing folder trees.</v>
+      </c>
+      <c r="K80" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ★失敗しました */ APP_0340,</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="I80" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0340=★失敗しました</v>
-      </c>
-      <c r="J80" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0340=★Failed</v>
-      </c>
-      <c r="K80" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0340=★失败</v>
+        <v>APP_0320=开始互相比较文件夹树。</v>
       </c>
     </row>
     <row r="81" spans="3:11">
       <c r="C81" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="I81" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0330=フォルダツリーを比較しています...</v>
+      </c>
+      <c r="J81" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0330=Comparing folders...</v>
+      </c>
+      <c r="K81" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較結果レポートを保存しています... */ APP_0350,</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="I81" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0350=比較結果レポートを保存しています...</v>
-      </c>
-      <c r="J81" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0350=Saving result report...</v>
-      </c>
-      <c r="K81" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0350=保存比较结果报告...</v>
+        <v>APP_0330=比较文件夹...</v>
       </c>
     </row>
     <row r="82" spans="3:11">
       <c r="C82" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ★失敗しました */ APP_0340,</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I82" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0340=★失敗しました</v>
+      </c>
+      <c r="J82" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0340=★Failed</v>
+      </c>
+      <c r="K82" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0360,</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="I82" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0360=比較結果レポートの保存に失敗しました。</v>
-      </c>
-      <c r="J82" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0360=Failed to save result report.</v>
-      </c>
-      <c r="K82" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0360=保存比较结果报告失败。</v>
+        <v>APP_0340=★失败</v>
       </c>
     </row>
     <row r="83" spans="3:11">
       <c r="C83" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートを保存しています... */ APP_0350,</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I83" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0350=比較結果レポートを保存しています...</v>
+      </c>
+      <c r="J83" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0350=Saving result report...</v>
+      </c>
+      <c r="K83" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較結果レポートを表示しています... */ APP_0370,</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="I83" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0370=比較結果レポートを表示しています...</v>
-      </c>
-      <c r="J83" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0370=Opening result report...</v>
-      </c>
-      <c r="K83" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0370=显示比较结果报告...</v>
+        <v>APP_0350=保存比较结果报告...</v>
       </c>
     </row>
     <row r="84" spans="3:11">
       <c r="C84" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0360,</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I84" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0360=比較結果レポートの保存に失敗しました。</v>
+      </c>
+      <c r="J84" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0360=Failed to save result report.</v>
+      </c>
+      <c r="K84" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0380,</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I84" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0380=比較結果レポートの表示に失敗しました。</v>
-      </c>
-      <c r="J84" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0380=Failed to open result report.</v>
-      </c>
-      <c r="K84" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0380=显示比较结果报告失败。</v>
+        <v>APP_0360=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="85" spans="3:11">
       <c r="C85" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートを表示しています... */ APP_0370,</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I85" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0370=比較結果レポートを表示しています...</v>
+      </c>
+      <c r="J85" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0370=Opening result report...</v>
+      </c>
+      <c r="K85" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="I85" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
-      </c>
-      <c r="J85" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0390=Failed to compare folder trees.</v>
-      </c>
-      <c r="K85" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0390=文件夹比较失败。</v>
+        <v>APP_0370=显示比较结果报告...</v>
       </c>
     </row>
     <row r="86" spans="3:11">
       <c r="C86" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0380,</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I86" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0380=比較結果レポートの表示に失敗しました。</v>
+      </c>
+      <c r="J86" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0380=Failed to open result report.</v>
+      </c>
+      <c r="K86" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (比較相手なし) */ APP_0400,</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="I86" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0400=(比較相手なし)</v>
-      </c>
-      <c r="J86" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0400=(no opponent)</v>
-      </c>
-      <c r="K86" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0400=(没有对比)</v>
+        <v>APP_0380=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="87" spans="3:11">
       <c r="C87" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="I87" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
+      </c>
+      <c r="J87" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0390=Failed to compare folder trees.</v>
+      </c>
+      <c r="K87" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (差分なし) */ APP_0410,</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="I87" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0410=(差分なし)</v>
-      </c>
-      <c r="J87" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0410=(no diffs)</v>
-      </c>
-      <c r="K87" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0410=(没有区别)</v>
+        <v>APP_0390=文件夹比较失败。</v>
       </c>
     </row>
     <row r="88" spans="3:11">
       <c r="C88" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** (比較相手なし) */ APP_0400,</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I88" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0400=(比較相手なし)</v>
+      </c>
+      <c r="J88" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0400=(no opponent)</v>
+      </c>
+      <c r="K88" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 差異発生%dシート */ APP_0420,</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I88" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0420=差異発生%dシート</v>
-      </c>
-      <c r="J88" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0420=diff sheets:%d</v>
-      </c>
-      <c r="K88" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0420=差异工作表%d</v>
+        <v>APP_0400=(没有对比)</v>
       </c>
     </row>
     <row r="89" spans="3:11">
       <c r="C89" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** (差分なし) */ APP_0410,</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I89" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0410=(差分なし)</v>
+      </c>
+      <c r="J89" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0410=(no diffs)</v>
+      </c>
+      <c r="K89" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 余剰%dシート */ APP_0430,</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="I89" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0430=余剰%dシート</v>
-      </c>
-      <c r="J89" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0430=redundant sheets:%d</v>
-      </c>
-      <c r="K89" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0430=冗余工作表%d</v>
+        <v>APP_0410=(没有区别)</v>
       </c>
     </row>
     <row r="90" spans="3:11">
       <c r="C90" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 差異発生%dシート */ APP_0420,</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I90" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0420=差異発生%dシート</v>
+      </c>
+      <c r="J90" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0420=diff sheets:%d</v>
+      </c>
+      <c r="K90" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ブック%s :  */ APP_0440,</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I90" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0440=ブック%s : </v>
-      </c>
-      <c r="J90" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">APP_0440=Book %s : </v>
-      </c>
-      <c r="K90" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0440=工作簿%s：</v>
+        <v>APP_0420=差异工作表%d</v>
       </c>
     </row>
     <row r="91" spans="3:11">
       <c r="C91" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 余剰%dシート */ APP_0430,</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I91" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0430=余剰%dシート</v>
+      </c>
+      <c r="J91" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0430=redundant sheets:%d</v>
+      </c>
+      <c r="K91" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I91" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
-      </c>
-      <c r="J91" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
-      </c>
-      <c r="K91" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
+        <v>APP_0430=冗余工作表%d</v>
       </c>
     </row>
     <row r="92" spans="3:11">
       <c r="C92" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ブック%s :  */ APP_0440,</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I92" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0440=ブック%s : </v>
+      </c>
+      <c r="J92" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0440=Book %s : </v>
+      </c>
+      <c r="K92" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="I92" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
-      </c>
-      <c r="J92" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
-      </c>
-      <c r="K92" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
+        <v>APP_0440=工作簿%s：</v>
       </c>
     </row>
     <row r="93" spans="3:11">
       <c r="C93" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I93" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
+      </c>
+      <c r="J93" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
+      </c>
+      <c r="K93" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (比較相手なし) */ APP_0470,</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="I93" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0470=(比較相手なし)</v>
-      </c>
-      <c r="J93" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0470=(no opponent)</v>
-      </c>
-      <c r="K93" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0470=(没有对比)</v>
+        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="94" spans="3:11">
       <c r="C94" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I94" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
+      </c>
+      <c r="J94" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
+      </c>
+      <c r="K94" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** フォルダ%s :  */ APP_0480,</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="I94" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
-      </c>
-      <c r="J94" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">APP_0480=Folder %s : </v>
-      </c>
-      <c r="K94" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">APP_0480=文件夹%s : </v>
+        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="95" spans="3:11">
       <c r="C95" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** (比較相手なし) */ APP_0470,</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I95" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0470=(比較相手なし)</v>
+      </c>
+      <c r="J95" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0470=(no opponent)</v>
+      </c>
+      <c r="K95" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0490,</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I95" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0490=■差分サマリ ---------------------------------------------------</v>
-      </c>
-      <c r="J95" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0490=## SUMMARY -----------------------------------------------------</v>
-      </c>
-      <c r="K95" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0490=■差异摘要 -----------------------------------------------------</v>
+        <v>APP_0470=(没有对比)</v>
       </c>
     </row>
     <row r="96" spans="3:11">
       <c r="C96" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** フォルダ%s :  */ APP_0480,</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I96" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
+      </c>
+      <c r="J96" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0480=Folder %s : </v>
+      </c>
+      <c r="K96" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0500,</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="I96" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0500=■差分詳細 -----------------------------------------------------</v>
-      </c>
-      <c r="J96" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0500=## DETAIL ------------------------------------------------------</v>
-      </c>
-      <c r="K96" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0500=■差异细节 -----------------------------------------------------</v>
+        <v xml:space="preserve">APP_0480=文件夹%s : </v>
       </c>
     </row>
     <row r="97" spans="3:11">
       <c r="C97" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0490,</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I97" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0490=■差分サマリ ---------------------------------------------------</v>
+      </c>
+      <c r="J97" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0490=## SUMMARY -----------------------------------------------------</v>
+      </c>
+      <c r="K97" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ★失敗しました */ APP_0510,</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="I97" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0510=★失敗しました</v>
-      </c>
-      <c r="J97" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0510=★Failed</v>
-      </c>
-      <c r="K97" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0510=★失败</v>
+        <v>APP_0490=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="98" spans="3:11">
       <c r="C98" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0500,</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I98" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0500=■差分詳細 -----------------------------------------------------</v>
+      </c>
+      <c r="J98" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0500=## DETAIL ------------------------------------------------------</v>
+      </c>
+      <c r="K98" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (差分なし) */ APP_0520,</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="I98" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0520=(差分なし)</v>
-      </c>
-      <c r="J98" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0520=(no diffs)</v>
-      </c>
-      <c r="K98" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0520=(没有区别)</v>
+        <v>APP_0500=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="99" spans="3:11">
       <c r="C99" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ★失敗しました */ APP_0510,</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I99" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0510=★失敗しました</v>
+      </c>
+      <c r="J99" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0510=★Failed</v>
+      </c>
+      <c r="K99" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 差異発生%dブック */ APP_0530,</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="I99" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0530=差異発生%dブック</v>
-      </c>
-      <c r="J99" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0530=diff books:%d</v>
-      </c>
-      <c r="K99" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0530=差异工作簿%d</v>
+        <v>APP_0510=★失败</v>
       </c>
     </row>
     <row r="100" spans="3:11">
       <c r="C100" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** (差分なし) */ APP_0520,</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I100" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0520=(差分なし)</v>
+      </c>
+      <c r="J100" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0520=(no diffs)</v>
+      </c>
+      <c r="K100" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 余剰%dブック */ APP_0540,</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I100" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0540=余剰%dブック</v>
-      </c>
-      <c r="J100" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0540=redundant books:%d</v>
-      </c>
-      <c r="K100" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0540=冗余工作簿%d</v>
+        <v>APP_0520=(没有区别)</v>
       </c>
     </row>
     <row r="101" spans="3:11">
       <c r="C101" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 差異発生%dブック */ APP_0530,</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I101" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0530=差異発生%dブック</v>
+      </c>
+      <c r="J101" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0530=diff books:%d</v>
+      </c>
+      <c r="K101" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較失敗%dブック */ APP_0550,</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="I101" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0550=比較失敗%dブック</v>
-      </c>
-      <c r="J101" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0550=failed books:%d</v>
-      </c>
-      <c r="K101" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0550=失败工作簿%d</v>
+        <v>APP_0530=差异工作簿%d</v>
       </c>
     </row>
     <row r="102" spans="3:11">
       <c r="C102" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 余剰%dブック */ APP_0540,</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I102" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0540=余剰%dブック</v>
+      </c>
+      <c r="J102" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0540=redundant books:%d</v>
+      </c>
+      <c r="K102" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (比較対象ファイルなし) */ APP_0560,</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="I102" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0560=(比較対象ファイルなし)</v>
-      </c>
-      <c r="J102" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0560=(No files to compare)</v>
-      </c>
-      <c r="K102" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0560=(没有可比较的文件)</v>
+        <v>APP_0540=冗余工作簿%d</v>
       </c>
     </row>
     <row r="103" spans="3:11">
       <c r="C103" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較失敗%dブック */ APP_0550,</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I103" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0550=比較失敗%dブック</v>
+      </c>
+      <c r="J103" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0550=failed books:%d</v>
+      </c>
+      <c r="K103" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較実行日時： */ APP_0570,</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="I103" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0570=比較実行日時：</v>
-      </c>
-      <c r="J103" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">APP_0570=Exec datetime : </v>
-      </c>
-      <c r="K103" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0570=执行日期和时间：</v>
+        <v>APP_0550=失败工作簿%d</v>
       </c>
     </row>
     <row r="104" spans="3:11">
       <c r="C104" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** (比較対象ファイルなし) */ APP_0560,</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I104" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0560=(比較対象ファイルなし)</v>
+      </c>
+      <c r="J104" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0560=(No files to compare)</v>
+      </c>
+      <c r="K104" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 作業用フォルダ： */ APP_0580,</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I104" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0580=作業用フォルダ：</v>
-      </c>
-      <c r="J104" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">APP_0580=Working dir : </v>
-      </c>
-      <c r="K104" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0580=工作文件夹：</v>
+        <v>APP_0560=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="105" spans="3:11">
       <c r="C105" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較実行日時： */ APP_0570,</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I105" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0570=比較実行日時：</v>
+      </c>
+      <c r="J105" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0570=Exec datetime : </v>
+      </c>
+      <c r="K105" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** ブック%s： */ APP_0590,</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I105" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0590=ブック%s：</v>
-      </c>
-      <c r="J105" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">APP_0590=Book %s : </v>
-      </c>
-      <c r="K105" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0590=工作簿%s：</v>
+        <v>APP_0570=执行日期和时间：</v>
       </c>
     </row>
     <row r="106" spans="3:11">
       <c r="C106" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 作業用フォルダ： */ APP_0580,</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I106" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0580=作業用フォルダ：</v>
+      </c>
+      <c r="J106" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0580=Working dir : </v>
+      </c>
+      <c r="K106" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 差分なし */ APP_0600,</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="I106" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0600=差分なし</v>
-      </c>
-      <c r="J106" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0600=No Diffs</v>
-      </c>
-      <c r="K106" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0600=没有区别</v>
+        <v>APP_0580=工作文件夹：</v>
       </c>
     </row>
     <row r="107" spans="3:11">
       <c r="C107" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** ブック%s： */ APP_0590,</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I107" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0590=ブック%s：</v>
+      </c>
+      <c r="J107" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0590=Book %s : </v>
+      </c>
+      <c r="K107" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 比較失敗 */ APP_0610,</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="I107" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0610=比較失敗</v>
-      </c>
-      <c r="J107" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0610=Comparison Failed</v>
-      </c>
-      <c r="K107" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0610=比较失败</v>
+        <v>APP_0590=工作簿%s：</v>
       </c>
     </row>
     <row r="108" spans="3:11">
       <c r="C108" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 差分なし */ APP_0600,</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="I108" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0600=差分なし</v>
+      </c>
+      <c r="J108" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0600=No Diffs</v>
+      </c>
+      <c r="K108" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I108" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0620=余剰行（A: %d, B: %d）</v>
-      </c>
-      <c r="J108" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
-      </c>
-      <c r="K108" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0620=冗余行（A: %d, B: %d）</v>
+        <v>APP_0600=没有区别</v>
       </c>
     </row>
     <row r="109" spans="3:11">
       <c r="C109" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 比較失敗 */ APP_0610,</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="I109" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0610=比較失敗</v>
+      </c>
+      <c r="J109" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0610=Comparison Failed</v>
+      </c>
+      <c r="K109" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="I109" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0630=余剰列（A: %d, B: %d）</v>
-      </c>
-      <c r="J109" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
-      </c>
-      <c r="K109" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0630=冗余列（A: %d, B: %d）</v>
+        <v>APP_0610=比较失败</v>
       </c>
     </row>
     <row r="110" spans="3:11">
       <c r="C110" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I110" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0620=余剰行（A: %d, B: %d）</v>
+      </c>
+      <c r="J110" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
+      </c>
+      <c r="K110" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** 差分セル（%d） */ APP_0640,</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="I110" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0640=差分セル（%d）</v>
-      </c>
-      <c r="J110" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_0640=Diff Cells (%d)</v>
-      </c>
-      <c r="K110" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>APP_0640=差异单元格（%d）</v>
+        <v>APP_0620=冗余行（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="111" spans="3:11">
       <c r="C111" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I111" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>APP_0630=余剰列（A: %d, B: %d）</v>
+      </c>
+      <c r="J111" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
+      </c>
+      <c r="K111" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>/** (比較相手なし) */ APP_0650,</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="I111" s="3" t="str">
-        <f t="shared" ref="I111:I142" si="10" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; E111)</f>
-        <v>APP_0650=(比較相手なし)</v>
-      </c>
-      <c r="J111" s="4" t="str">
-        <f t="shared" ref="J111:J142" si="11" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; F111)</f>
-        <v>APP_0650=(no opponent)</v>
-      </c>
-      <c r="K111" s="5" t="str">
-        <f t="shared" ref="K111:K142" si="12" xml:space="preserve"> IF($D111="", "", $D111 &amp; "=" &amp; G111)</f>
-        <v>APP_0650=(没有对比)</v>
+        <v>APP_0630=冗余列（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="112" spans="3:11">
       <c r="C112" s="1" t="str">
-        <f t="shared" ref="C112:C175" si="13" xml:space="preserve"> "/** " &amp; E112 &amp; " */ " &amp; D112 &amp; ","</f>
-        <v>/** 比較フォルダ%s： */ APP_0660,</v>
+        <f t="shared" si="3"/>
+        <v>/** 差分セル（%d） */ APP_0640,</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>185</v>
+        <v>329</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>149</v>
+        <v>331</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>226</v>
+        <v>333</v>
       </c>
       <c r="I112" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0660=比較フォルダ%s：</v>
+        <f t="shared" si="4"/>
+        <v>APP_0640=差分セル（%d）</v>
       </c>
       <c r="J112" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0660=Folder %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0640=Diff Cells (%d)</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0660=文件夹%s：</v>
+        <f t="shared" si="6"/>
+        <v>APP_0640=差异单元格（%d）</v>
       </c>
     </row>
     <row r="113" spans="3:11">
       <c r="C113" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダ： */ APP_0670,</v>
+        <f t="shared" si="3"/>
+        <v>/** (比較相手なし) */ APP_0650,</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>186</v>
+        <v>510</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>299</v>
+        <v>93</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="I113" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0670=作業用フォルダ：</v>
+        <f t="shared" si="4"/>
+        <v>APP_0650=(比較相手なし)</v>
       </c>
       <c r="J113" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0670=Working dir : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0650=(no opponent)</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0670=工作文件夹：</v>
+        <f t="shared" si="6"/>
+        <v>APP_0650=(没有对比)</v>
       </c>
     </row>
     <row r="114" spans="3:11">
       <c r="C114" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** ワークシート */ APP_0680,</v>
+        <f t="shared" ref="C114:C177" si="7" xml:space="preserve"> "/** " &amp; E114 &amp; " */ " &amp; D114 &amp; ","</f>
+        <v>/** 比較フォルダ%s： */ APP_0660,</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>52</v>
+        <v>511</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>113</v>
+        <v>226</v>
       </c>
       <c r="I114" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0680=ワークシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0660=比較フォルダ%s：</v>
       </c>
       <c r="J114" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0680=Worksheet</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0660=Folder %s : </v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0680=工作表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0660=文件夹%s：</v>
       </c>
     </row>
     <row r="115" spans="3:11">
       <c r="C115" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** グラフシート */ APP_0690,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダ： */ APP_0670,</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>53</v>
+        <v>512</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>98</v>
+        <v>299</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="I115" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0690=グラフシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0670=作業用フォルダ：</v>
       </c>
       <c r="J115" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0690=Chart</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0670=Working dir : </v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0690=图表表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0670=工作文件夹：</v>
       </c>
     </row>
     <row r="116" spans="3:11">
       <c r="C116" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
+        <f t="shared" si="7"/>
+        <v>/** ワークシート */ APP_0680,</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="I116" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0680=ワークシート</v>
       </c>
       <c r="J116" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0700=MS Excel 5.0 Dialog</v>
+        <f t="shared" si="5"/>
+        <v>APP_0680=Worksheet</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0700=MS Excel 5.0 对话表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0680=工作表</v>
       </c>
     </row>
     <row r="117" spans="3:11">
       <c r="C117" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
+        <f t="shared" si="7"/>
+        <v>/** グラフシート */ APP_0690,</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>114</v>
+        <v>265</v>
       </c>
       <c r="I117" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0710=Excel 4.0 マクロシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0690=グラフシート</v>
       </c>
       <c r="J117" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0710=Excel 4.0 Macro</v>
+        <f t="shared" si="5"/>
+        <v>APP_0690=Chart</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0710=Excel 4.0 宏表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0690=图表表</v>
       </c>
     </row>
     <row r="118" spans="3:11">
       <c r="C118" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** (差分なし) */ APP_0720,</v>
+        <f t="shared" si="7"/>
+        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I118" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0720=(差分なし)</v>
+        <f t="shared" si="4"/>
+        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
       </c>
       <c r="J118" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0720=(no diffs)</v>
+        <f t="shared" si="5"/>
+        <v>APP_0700=MS Excel 5.0 Dialog</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0720=(没有区别)</v>
+        <f t="shared" si="6"/>
+        <v>APP_0700=MS Excel 5.0 对话表</v>
       </c>
     </row>
     <row r="119" spans="3:11">
       <c r="C119" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 余剰行%d */ APP_0730,</v>
+        <f t="shared" si="7"/>
+        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I119" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0730=余剰行%d</v>
+        <f t="shared" si="4"/>
+        <v>APP_0710=Excel 4.0 マクロシート</v>
       </c>
       <c r="J119" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0730=redundant rows:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0710=Excel 4.0 Macro</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0730=冗余行%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0710=Excel 4.0 宏表</v>
       </c>
     </row>
     <row r="120" spans="3:11">
       <c r="C120" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 余剰列%d */ APP_0740,</v>
+        <f t="shared" si="7"/>
+        <v>/** (差分なし) */ APP_0720,</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>116</v>
+        <v>260</v>
       </c>
       <c r="I120" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0740=余剰列%d</v>
+        <f t="shared" si="4"/>
+        <v>APP_0720=(差分なし)</v>
       </c>
       <c r="J120" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0740=redundant columns:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0720=(no diffs)</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0740=冗余列%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0720=(没有区别)</v>
       </c>
     </row>
     <row r="121" spans="3:11">
       <c r="C121" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 差分セル%d */ APP_0750,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰行%d */ APP_0730,</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c r="I121" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0750=差分セル%d</v>
+        <f t="shared" si="4"/>
+        <v>APP_0730=余剰行%d</v>
       </c>
       <c r="J121" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0750=diff cells:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0730=redundant rows:%d</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0750=差异单元格%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0730=冗余行%d</v>
       </c>
     </row>
     <row r="122" spans="3:11">
       <c r="C122" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰列%d */ APP_0740,</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="I122" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
+        <f t="shared" si="4"/>
+        <v>APP_0740=余剰列%d</v>
       </c>
       <c r="J122" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0740=redundant columns:%d</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
+        <f t="shared" si="6"/>
+        <v>APP_0740=冗余列%d</v>
       </c>
     </row>
     <row r="123" spans="3:11">
       <c r="C123" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 行%d */ APP_0770,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差分セル%d */ APP_0750,</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>59</v>
+        <v>267</v>
       </c>
       <c r="I123" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="4"/>
+        <v>APP_0750=差分セル%d</v>
       </c>
       <c r="J123" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0770=Row %d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0750=diff cells:%d</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0750=差异单元格%d</v>
       </c>
     </row>
     <row r="124" spans="3:11">
       <c r="C124" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
+        <f t="shared" si="7"/>
+        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I124" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
       </c>
       <c r="J124" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
       </c>
       <c r="K124" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
       </c>
     </row>
     <row r="125" spans="3:11">
       <c r="C125" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** %s列 */ APP_0790,</v>
+        <f t="shared" si="7"/>
+        <v>/** 行%d */ APP_0770,</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I125" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="4"/>
+        <v>APP_0770=行%d</v>
       </c>
       <c r="J125" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0790=Column %s</v>
+        <f t="shared" si="5"/>
+        <v>APP_0770=Row %d</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="6"/>
+        <v>APP_0770=行%d</v>
       </c>
     </row>
     <row r="126" spans="3:11">
       <c r="C126" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 差分セル :  */ APP_0800,</v>
+        <f t="shared" si="7"/>
+        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="I126" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">APP_0800=差分セル : </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
       </c>
       <c r="J126" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0800=Diff cells : </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
       </c>
       <c r="K126" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0800=差异单元格 : </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
       </c>
     </row>
     <row r="127" spans="3:11">
       <c r="C127" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** (比較相手なし) */ APP_0810,</v>
+        <f t="shared" si="7"/>
+        <v>/** %s列 */ APP_0790,</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>259</v>
+        <v>60</v>
       </c>
       <c r="I127" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0810=(比較相手なし)</v>
+        <f t="shared" si="4"/>
+        <v>APP_0790=%s列</v>
       </c>
       <c r="J127" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0810=(no opponent)</v>
+        <f t="shared" si="5"/>
+        <v>APP_0790=Column %s</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0810=(没有对比)</v>
+        <f t="shared" si="6"/>
+        <v>APP_0790=%s列</v>
       </c>
     </row>
     <row r="128" spans="3:11">
       <c r="C128" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差分セル :  */ APP_0800,</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>181</v>
+        <v>525</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I128" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0800=差分セル : </v>
       </c>
       <c r="J128" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_0820=Root folder %s : </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0800=Diff cells : </v>
       </c>
       <c r="K128" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0800=差异单元格 : </v>
       </c>
     </row>
     <row r="129" spans="3:11">
       <c r="C129" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0830,</v>
+        <f t="shared" si="7"/>
+        <v>/** (比較相手なし) */ APP_0810,</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>112</v>
+        <v>259</v>
       </c>
       <c r="I129" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0830=■差分サマリ ---------------------------------------------------</v>
+        <f t="shared" si="4"/>
+        <v>APP_0810=(比較相手なし)</v>
       </c>
       <c r="J129" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0830=## SUMMARY -----------------------------------------------------</v>
+        <f t="shared" si="5"/>
+        <v>APP_0810=(no opponent)</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0830=■差异摘要 -----------------------------------------------------</v>
+        <f t="shared" si="6"/>
+        <v>APP_0810=(没有对比)</v>
       </c>
     </row>
     <row r="130" spans="3:11">
       <c r="C130" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0840,</v>
+        <f t="shared" si="7"/>
+        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>51</v>
+        <v>527</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I130" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0840=■差分詳細 -----------------------------------------------------</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
       </c>
       <c r="J130" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0840=## DETAIL ------------------------------------------------------</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0820=Root folder %s : </v>
       </c>
       <c r="K130" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0840=■差异细节 -----------------------------------------------------</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
       </c>
     </row>
     <row r="131" spans="3:11">
       <c r="C131" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** ★失敗しました */ APP_0850,</v>
+        <f t="shared" si="7"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0830,</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>129</v>
+        <v>528</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>249</v>
+        <v>112</v>
       </c>
       <c r="I131" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0850=★失敗しました</v>
+        <f t="shared" ref="I131:I179" si="8" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; E131)</f>
+        <v>APP_0830=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="J131" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0850=★Failed</v>
+        <f t="shared" ref="J131:J179" si="9" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; F131)</f>
+        <v>APP_0830=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0850=★失败</v>
+        <f t="shared" ref="K131:K179" si="10" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; G131)</f>
+        <v>APP_0830=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="132" spans="3:11">
       <c r="C132" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 組み合わせ編集 */ APP_0860,</v>
+        <f t="shared" si="7"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0840,</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>285</v>
+        <v>529</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>286</v>
+        <v>96</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="I132" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0840=■差分詳細 -----------------------------------------------------</v>
+      </c>
+      <c r="J132" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0840=## DETAIL ------------------------------------------------------</v>
+      </c>
+      <c r="K132" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0860=組み合わせ編集</v>
-      </c>
-      <c r="J132" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0860=Edit Pairing</v>
-      </c>
-      <c r="K132" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0860=组合编辑</v>
+        <v>APP_0840=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="133" spans="3:11">
       <c r="C133" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
+        <f t="shared" si="7"/>
+        <v>/** ★失敗しました */ APP_0850,</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>394</v>
+        <v>129</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>396</v>
+        <v>142</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>398</v>
+        <v>249</v>
       </c>
       <c r="I133" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0850=★失敗しました</v>
+      </c>
+      <c r="J133" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0850=★Failed</v>
+      </c>
+      <c r="K133" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
-      </c>
-      <c r="J133" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
-      </c>
-      <c r="K133" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
+        <v>APP_0850=★失败</v>
       </c>
     </row>
     <row r="134" spans="3:11">
       <c r="C134" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
+        <f t="shared" si="7"/>
+        <v>/** 組み合わせ編集 */ APP_0860,</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>395</v>
+        <v>285</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>397</v>
+        <v>286</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>399</v>
+        <v>287</v>
       </c>
       <c r="I134" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0860=組み合わせ編集</v>
+      </c>
+      <c r="J134" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0860=Edit Pairing</v>
+      </c>
+      <c r="K134" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
-      </c>
-      <c r="J134" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
-      </c>
-      <c r="K134" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
+        <v>APP_0860=组合编辑</v>
       </c>
     </row>
     <row r="135" spans="3:11">
       <c r="C135" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 共有ドライブ */ APP_0890,</v>
+        <f t="shared" si="7"/>
+        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="I135" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
+      </c>
+      <c r="J135" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
+      </c>
+      <c r="K135" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0890=共有ドライブ</v>
-      </c>
-      <c r="J135" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0890=Shared drives</v>
-      </c>
-      <c r="K135" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0890=共享云端硬盘</v>
+        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
       </c>
     </row>
     <row r="136" spans="3:11">
       <c r="C136" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** すべてのファイル */ APP_0900,</v>
+        <f t="shared" si="7"/>
+        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I136" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
+      </c>
+      <c r="J136" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
+      </c>
+      <c r="K136" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0900=すべてのファイル</v>
-      </c>
-      <c r="J136" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0900=All files</v>
-      </c>
-      <c r="K136" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0900=所有文件</v>
+        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
       </c>
     </row>
     <row r="137" spans="3:11">
       <c r="C137" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** スター付き */ APP_0910,</v>
+        <f t="shared" si="7"/>
+        <v>/** 共有ドライブ */ APP_0890,</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I137" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0890=共有ドライブ</v>
+      </c>
+      <c r="J137" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0890=Shared drives</v>
+      </c>
+      <c r="K137" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0910=スター付き</v>
-      </c>
-      <c r="J137" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0910=Starred</v>
-      </c>
-      <c r="K137" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0910=已加星标</v>
+        <v>APP_0890=共享云端硬盘</v>
       </c>
     </row>
     <row r="138" spans="3:11">
       <c r="C138" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
+        <f t="shared" si="7"/>
+        <v>/** すべてのファイル */ APP_0900,</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="I138" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0900=すべてのファイル</v>
+      </c>
+      <c r="J138" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0900=All files</v>
+      </c>
+      <c r="K138" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
-      </c>
-      <c r="J138" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0920=Failed to download the file from Google Drive.</v>
-      </c>
-      <c r="K138" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
+        <v>APP_0900=所有文件</v>
       </c>
     </row>
     <row r="139" spans="3:11">
       <c r="C139" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
+        <v>/** スター付き */ APP_0910,</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="I139" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0910=スター付き</v>
+      </c>
+      <c r="J139" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0910=Starred</v>
+      </c>
+      <c r="K139" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0910=已加星标</v>
+      </c>
+    </row>
+    <row r="140" spans="3:11">
+      <c r="C140" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="I140" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
+      </c>
+      <c r="J140" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0920=Failed to download the file from Google Drive.</v>
+      </c>
+      <c r="K140" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
+      </c>
+    </row>
+    <row r="141" spans="3:11">
+      <c r="C141" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>/** 更新者不明 */ APP_0930,</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="E139" s="3" t="s">
+      <c r="D141" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="F139" s="4" t="s">
+      <c r="F141" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="G139" s="6" t="s">
+      <c r="G141" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="I139" s="3" t="str">
+      <c r="I141" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0930=更新者不明</v>
+      </c>
+      <c r="J141" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0930=Unknown</v>
+      </c>
+      <c r="K141" s="5" t="str">
         <f t="shared" si="10"/>
         <v>APP_0930=更新者不明</v>
       </c>
-      <c r="J139" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0930=Unknown</v>
-      </c>
-      <c r="K139" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0930=更新者不明</v>
-      </c>
-    </row>
-    <row r="140" spans="3:11">
-      <c r="C140" s="1" t="str">
-        <f t="shared" si="13"/>
+    </row>
+    <row r="142" spans="3:11">
+      <c r="C142" s="1" t="str">
+        <f t="shared" si="7"/>
         <v>/** 最新版 */ APP_0940,</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="E140" s="3" t="s">
+      <c r="D142" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E142" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F142" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="G140" s="6" t="s">
+      <c r="G142" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I140" s="3" t="str">
+      <c r="I142" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_0940=最新版</v>
+      </c>
+      <c r="J142" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_0940=Latest</v>
+      </c>
+      <c r="K142" s="5" t="str">
         <f t="shared" si="10"/>
         <v>APP_0940=最新版</v>
       </c>
-      <c r="J140" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0940=Latest</v>
-      </c>
-      <c r="K140" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0940=最新版</v>
-      </c>
-    </row>
-    <row r="141" spans="3:11">
-      <c r="C141" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="I141" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
-      </c>
-      <c r="J141" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
-      </c>
-      <c r="K141" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
-      </c>
-    </row>
-    <row r="142" spans="3:11">
-      <c r="C142" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="I142" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_0960=資格情報を削除しました。</v>
-      </c>
-      <c r="J142" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_0960=Credentials have been deleted.</v>
-      </c>
-      <c r="K142" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_0960=已删除凭据。</v>
-      </c>
     </row>
     <row r="143" spans="3:11">
       <c r="C143" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
+        <f t="shared" si="7"/>
+        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="I143" s="3" t="str">
-        <f t="shared" ref="I143:I177" si="14" xml:space="preserve"> IF($D143="", "", $D143 &amp; "=" &amp; E143)</f>
-        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
       </c>
       <c r="J143" s="4" t="str">
-        <f t="shared" ref="J143:J177" si="15" xml:space="preserve"> IF($D143="", "", $D143 &amp; "=" &amp; F143)</f>
-        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" ref="K143:K177" si="16" xml:space="preserve"> IF($D143="", "", $D143 &amp; "=" &amp; G143)</f>
-        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
       </c>
     </row>
     <row r="144" spans="3:11">
       <c r="C144" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
+        <f t="shared" si="7"/>
+        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="I144" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_0980=資格情報の削除に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0960=資格情報を削除しました。</v>
       </c>
       <c r="J144" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_0980=Failed to delete credentials.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0960=Credentials have been deleted.</v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_0980=删除凭据失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0960=已删除凭据。</v>
       </c>
     </row>
     <row r="145" spans="3:11">
       <c r="C145" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
+        <f t="shared" si="7"/>
+        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I145" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
       </c>
       <c r="J145" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
     </row>
     <row r="146" spans="3:11">
       <c r="C146" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Google連携エラー */ APP_1000,</v>
+        <f t="shared" si="7"/>
+        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="I146" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1000=Google連携エラー</v>
+        <f t="shared" si="8"/>
+        <v>APP_0980=資格情報の削除に失敗しました。</v>
       </c>
       <c r="J146" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1000=Google Integration Error</v>
+        <f t="shared" si="9"/>
+        <v>APP_0980=Failed to delete credentials.</v>
       </c>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1000=Google关联错误</v>
+        <f t="shared" si="10"/>
+        <v>APP_0980=删除凭据失败。</v>
       </c>
     </row>
     <row r="147" spans="3:11">
       <c r="C147" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
+        <f t="shared" si="7"/>
+        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="I147" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J147" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1010=An error occurred during Google integration processing.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1010=Google关联处理过程中发生错误。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="148" spans="3:11">
       <c r="C148" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
+        <f t="shared" si="7"/>
+        <v>/** Google連携エラー */ APP_1000,</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="I148" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1000=Google連携エラー</v>
       </c>
       <c r="J148" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1000=Google Integration Error</v>
       </c>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1000=Google关联错误</v>
       </c>
     </row>
     <row r="149" spans="3:11">
       <c r="C149" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
+        <f t="shared" si="7"/>
+        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>385</v>
+        <v>546</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>360</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="I149" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
       </c>
       <c r="J149" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1030=File downloaded from Google Drive</v>
+        <f t="shared" si="9"/>
+        <v>APP_1010=An error occurred during Google integration processing.</v>
       </c>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1030=已从Google云端硬盘下载文件</v>
+        <f t="shared" si="10"/>
+        <v>APP_1010=Google关联处理过程中发生错误。</v>
       </c>
     </row>
     <row r="150" spans="3:11">
       <c r="C150" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
+        <f t="shared" si="7"/>
+        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>18</v>
+        <v>547</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>363</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>232</v>
+        <v>365</v>
       </c>
       <c r="I150" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J150" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="151" spans="3:11">
       <c r="C151" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
+        <f t="shared" si="7"/>
+        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>25</v>
+        <v>385</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>72</v>
+        <v>390</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>233</v>
+        <v>391</v>
       </c>
       <c r="I151" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
       </c>
       <c r="J151" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1050=Failed to open working directory.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1030=File downloaded from Google Drive</v>
       </c>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1050=显示工作文件夹失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1030=已从Google云端硬盘下载文件</v>
       </c>
     </row>
     <row r="152" spans="3:11">
       <c r="C152" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
+        <f t="shared" si="7"/>
+        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I152" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1060=作業用フォルダの変更</v>
+        <f t="shared" si="8"/>
+        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
       </c>
       <c r="J152" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1060=Change working directory</v>
+        <f t="shared" si="9"/>
+        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
       </c>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1060=改变工作文件夹</v>
+        <f t="shared" si="10"/>
+        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
     </row>
     <row r="153" spans="3:11">
       <c r="C153" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I153" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
       </c>
       <c r="J153" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1070=Failed to change working directory.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1050=Failed to open working directory.</v>
       </c>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1070=更改工作文件夹失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1050=显示工作文件夹失败。</v>
       </c>
     </row>
     <row r="154" spans="3:11">
       <c r="C154" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="I154" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
+        <f t="shared" si="8"/>
+        <v>APP_1060=作業用フォルダの変更</v>
       </c>
       <c r="J154" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
+        <f t="shared" si="9"/>
+        <v>APP_1060=Change working directory</v>
       </c>
       <c r="K154" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
+        <f t="shared" si="10"/>
+        <v>APP_1060=改变工作文件夹</v>
       </c>
     </row>
     <row r="155" spans="3:11">
       <c r="C155" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="I155" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
       </c>
       <c r="J155" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1070=Failed to change working directory.</v>
       </c>
       <c r="K155" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1070=更改工作文件夹失败。</v>
       </c>
     </row>
     <row r="156" spans="3:11">
       <c r="C156" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
+        <f t="shared" si="7"/>
+        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>23</v>
+        <v>235</v>
       </c>
       <c r="I156" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="8"/>
+        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
       </c>
       <c r="J156" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
       </c>
       <c r="K156" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
     </row>
     <row r="157" spans="3:11">
       <c r="C157" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
+        <f t="shared" si="7"/>
+        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I157" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="J157" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="K157" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
     </row>
     <row r="158" spans="3:11">
       <c r="C158" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
+        <f t="shared" si="7"/>
+        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>415</v>
+        <v>555</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>416</v>
+        <v>23</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>417</v>
+        <v>23</v>
       </c>
       <c r="I158" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1100=方眼Diff  -  詳細設定</v>
+        <f t="shared" si="8"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="J158" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
+        <f t="shared" si="9"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="K158" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1100=方眼Diff  -  详细设置</v>
+        <f t="shared" si="10"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
     </row>
     <row r="159" spans="3:11">
       <c r="C159" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
+        <f t="shared" si="7"/>
+        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>125</v>
+        <v>556</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>236</v>
+        <v>24</v>
       </c>
       <c r="I159" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1110=比較対象フォルダの選択</v>
+        <f t="shared" si="8"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="J159" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1110=Select comparison folder</v>
+        <f t="shared" si="9"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="K159" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1110=选择用于比较的文件夹</v>
+        <f t="shared" si="10"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
     </row>
     <row r="160" spans="3:11">
       <c r="C160" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
+        <f t="shared" si="7"/>
+        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>20</v>
+        <v>557</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>415</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>70</v>
+        <v>416</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>237</v>
+        <v>417</v>
       </c>
       <c r="I160" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1120=比較対象ブックの選択</v>
+        <f t="shared" si="8"/>
+        <v>APP_1100=方眼Diff  -  詳細設定</v>
       </c>
       <c r="J160" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1120=Select comparison book</v>
+        <f t="shared" si="9"/>
+        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
       </c>
       <c r="K160" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1120=选择用于比较的工作簿</v>
+        <f t="shared" si="10"/>
+        <v>APP_1100=方眼Diff  -  详细设置</v>
       </c>
     </row>
     <row r="161" spans="3:11">
       <c r="C161" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** Excel ブック */ APP_1130,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>21</v>
+        <v>558</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="I161" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1130=Excel ブック</v>
+        <f t="shared" si="8"/>
+        <v>APP_1110=比較対象フォルダの選択</v>
       </c>
       <c r="J161" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1130=Excel book</v>
+        <f t="shared" si="9"/>
+        <v>APP_1110=Select comparison folder</v>
       </c>
       <c r="K161" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1130=Excel工作簿</v>
+        <f t="shared" si="10"/>
+        <v>APP_1110=选择用于比较的文件夹</v>
       </c>
     </row>
     <row r="162" spans="3:11">
       <c r="C162" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** ファイルを読み込めません： */ APP_1140,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I162" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1140=ファイルを読み込めません：</v>
+        <f t="shared" si="8"/>
+        <v>APP_1120=比較対象ブックの選択</v>
       </c>
       <c r="J162" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">APP_1140=Failed to open file : </v>
+        <f t="shared" si="9"/>
+        <v>APP_1120=Select comparison book</v>
       </c>
       <c r="K162" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1140=无法读取文件：</v>
+        <f t="shared" si="10"/>
+        <v>APP_1120=选择用于比较的工作簿</v>
       </c>
     </row>
     <row r="163" spans="3:11">
       <c r="C163" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** シートが見つかりません： */ APP_1150,</v>
+        <f t="shared" si="7"/>
+        <v>/** Excel ブック */ APP_1130,</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="I163" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1150=シートが見つかりません：</v>
+        <f t="shared" si="8"/>
+        <v>APP_1130=Excel ブック</v>
       </c>
       <c r="J163" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">APP_1150=No such sheet : </v>
+        <f t="shared" si="9"/>
+        <v>APP_1130=Excel book</v>
       </c>
       <c r="K163" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1150=没有找到工作表：</v>
+        <f t="shared" si="10"/>
+        <v>APP_1130=Excel工作簿</v>
       </c>
     </row>
     <row r="164" spans="3:11">
       <c r="C164" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** フォルダを読み込めません： */ APP_1160,</v>
+        <f t="shared" si="7"/>
+        <v>/** ファイルを読み込めません： */ APP_1140,</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="I164" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1160=フォルダを読み込めません：</v>
+        <f t="shared" si="8"/>
+        <v>APP_1140=ファイルを読み込めません：</v>
       </c>
       <c r="J164" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_1140=Failed to open file : </v>
       </c>
       <c r="K164" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1160=无法读取文件夹：</v>
+        <f t="shared" si="10"/>
+        <v>APP_1140=无法读取文件：</v>
       </c>
     </row>
     <row r="165" spans="3:11">
       <c r="C165" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
+        <f t="shared" si="7"/>
+        <v>/** シートが見つかりません： */ APP_1150,</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>420</v>
+        <v>196</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>419</v>
+        <v>197</v>
       </c>
       <c r="I165" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
+        <f t="shared" si="8"/>
+        <v>APP_1150=シートが見つかりません：</v>
       </c>
       <c r="J165" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_1150=No such sheet : </v>
       </c>
       <c r="K165" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
+        <f t="shared" si="10"/>
+        <v>APP_1150=没有找到工作表：</v>
       </c>
     </row>
     <row r="166" spans="3:11">
       <c r="C166" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
+        <f t="shared" si="7"/>
+        <v>/** フォルダを読み込めません： */ APP_1160,</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>124</v>
+        <v>563</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>133</v>
+        <v>283</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="I166" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1160=フォルダを読み込めません：</v>
       </c>
       <c r="J166" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1180=Please specify different folders/books/sheets.</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
       </c>
       <c r="K166" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1160=无法读取文件夹：</v>
       </c>
     </row>
     <row r="167" spans="3:11">
       <c r="C167" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
+        <f t="shared" si="7"/>
+        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>121</v>
+        <v>418</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>122</v>
+        <v>420</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>228</v>
+        <v>419</v>
       </c>
       <c r="I167" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
       </c>
       <c r="J167" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
       </c>
       <c r="K167" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
     </row>
     <row r="168" spans="3:11">
       <c r="C168" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 予期せぬ例外が発生しました。 */ APP_1200,</v>
+        <f t="shared" si="7"/>
+        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>29</v>
+        <v>565</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>111</v>
+        <v>227</v>
       </c>
       <c r="I168" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1200=予期せぬ例外が発生しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
       </c>
       <c r="J168" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1200=Unexpected exception occurred.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1180=Please specify different folders/books/sheets.</v>
       </c>
       <c r="K168" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1200=意外的例外。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
     </row>
     <row r="169" spans="3:11">
       <c r="C169" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="I169" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
       </c>
       <c r="J169" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1210=Failed to create working directory.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
       </c>
       <c r="K169" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1210=创建工作文件夹失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
     </row>
     <row r="170" spans="3:11">
       <c r="C170" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
+        <f t="shared" si="7"/>
+        <v>/** 予期せぬ例外が発生しました。 */ APP_1200,</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>202</v>
+        <v>29</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>203</v>
+        <v>76</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="I170" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1220=別の場所を指定してください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1200=予期せぬ例外が発生しました。</v>
       </c>
       <c r="J170" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1220=Please specify another location.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1200=Unexpected exception occurred.</v>
       </c>
       <c r="K170" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1220=请指定其他位置。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1200=意外的例外。</v>
       </c>
     </row>
     <row r="171" spans="3:11">
       <c r="C171" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダの変更 */ APP_1230,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="I171" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1230=作業用フォルダの変更</v>
+        <f t="shared" si="8"/>
+        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
       </c>
       <c r="J171" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1230=Change working directory</v>
+        <f t="shared" si="9"/>
+        <v>APP_1210=Failed to create working directory.</v>
       </c>
       <c r="K171" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1230=改变工作文件夹</v>
+        <f t="shared" si="10"/>
+        <v>APP_1210=创建工作文件夹失败。</v>
       </c>
     </row>
     <row r="172" spans="3:11">
       <c r="C172" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 処理を中止しました。 */ APP_1240,</v>
+        <f t="shared" si="7"/>
+        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I172" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1240=処理を中止しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1220=別の場所を指定してください。</v>
       </c>
       <c r="J172" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1240=Processing has been canceled.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1220=Please specify another location.</v>
       </c>
       <c r="K172" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1240=处理已被取消。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1220=请指定其他位置。</v>
       </c>
     </row>
     <row r="173" spans="3:11">
       <c r="C173" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** パスワード指定 */ APP_1250,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダの変更 */ APP_1230,</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I173" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1250=パスワード指定</v>
+        <f t="shared" si="8"/>
+        <v>APP_1230=作業用フォルダの変更</v>
       </c>
       <c r="J173" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1250=Enter Password</v>
+        <f t="shared" si="9"/>
+        <v>APP_1230=Change working directory</v>
       </c>
       <c r="K173" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1250=输入密码</v>
+        <f t="shared" si="10"/>
+        <v>APP_1230=改变工作文件夹</v>
       </c>
     </row>
     <row r="174" spans="3:11">
       <c r="C174" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
+        <f t="shared" si="7"/>
+        <v>/** 処理を中止しました。 */ APP_1240,</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="I174" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1260=%s はパスワードで保護されています。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1240=処理を中止しました。</v>
       </c>
       <c r="J174" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1260=The book [%s] is password protected.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1240=Processing has been canceled.</v>
       </c>
       <c r="K174" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1260=%s 是受密码保护的。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1240=处理已被取消。</v>
       </c>
     </row>
     <row r="175" spans="3:11">
       <c r="C175" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
+        <f t="shared" si="7"/>
+        <v>/** パスワード指定 */ APP_1250,</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>412</v>
+        <v>30</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>414</v>
+        <v>230</v>
       </c>
       <c r="I175" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1270=新しいバージョンが利用可能です。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1250=パスワード指定</v>
       </c>
       <c r="J175" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1270=A new version is available.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1250=Enter Password</v>
       </c>
       <c r="K175" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1270=有新版本可用。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1250=输入密码</v>
       </c>
     </row>
     <row r="176" spans="3:11">
       <c r="C176" s="1" t="str">
-        <f t="shared" ref="C176:C177" si="17" xml:space="preserve"> "/** " &amp; E176 &amp; " */ " &amp; D176 &amp; ","</f>
-        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
+        <f t="shared" si="7"/>
+        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>447</v>
+        <v>31</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>443</v>
+        <v>231</v>
       </c>
       <c r="I176" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1260=%s はパスワードで保護されています。</v>
       </c>
       <c r="J176" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+        <f t="shared" si="9"/>
+        <v>APP_1260=The book [%s] is password protected.</v>
       </c>
       <c r="K176" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+        <f t="shared" si="10"/>
+        <v>APP_1260=%s 是受密码保护的。</v>
       </c>
     </row>
     <row r="177" spans="3:11">
       <c r="C177" s="1" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
+        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="I177" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_1270=新しいバージョンが利用可能です。</v>
+      </c>
+      <c r="J177" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_1270=A new version is available.</v>
+      </c>
+      <c r="K177" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_1270=有新版本可用。</v>
+      </c>
+    </row>
+    <row r="178" spans="3:11">
+      <c r="C178" s="1" t="str">
+        <f t="shared" ref="C178:C179" si="11" xml:space="preserve"> "/** " &amp; E178 &amp; " */ " &amp; D178 &amp; ","</f>
+        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="I178" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+      </c>
+      <c r="J178" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+      </c>
+      <c r="K178" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+      </c>
+    </row>
+    <row r="179" spans="3:11">
+      <c r="C179" s="1" t="str">
+        <f t="shared" si="11"/>
         <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F177" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="G177" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="I177" s="3" t="str">
-        <f t="shared" si="14"/>
+      <c r="D179" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="I179" s="3" t="str">
+        <f t="shared" si="8"/>
         <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
       </c>
-      <c r="J177" s="4" t="str">
-        <f t="shared" si="15"/>
+      <c r="J179" s="4" t="str">
+        <f t="shared" si="9"/>
         <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
       </c>
-      <c r="K177" s="5" t="str">
-        <f t="shared" si="16"/>
+      <c r="K179" s="5" t="str">
+        <f t="shared" si="10"/>
         <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A47:K177">
-    <sortCondition ref="D47:D177"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:K179">
+    <sortCondition ref="D49:D179"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646F8428-5611-4494-81EA-95EC4933D09B}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{B5932D3B-6BC2-4ECA-B654-E40995BA4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67BE7024-0DD8-475E-8694-78712A41FB0F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2767,10 +2767,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Settings Management</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>设置管理</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2819,6 +2815,10 @@
   </si>
   <si>
     <t>自动发送错误信息到服务器</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Settings\nManagement</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4297,10 +4297,10 @@
         <v>621</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>622</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>623</v>
       </c>
       <c r="I41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0400=Settings Management</v>
+        <v>FXML_0400=Settings\nManagement</v>
       </c>
       <c r="K41" s="5" t="str">
         <f t="shared" si="2"/>
@@ -4421,16 +4421,16 @@
     </row>
     <row r="46" spans="4:11">
       <c r="D46" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E46" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>626</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>627</v>
       </c>
       <c r="I46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4447,16 +4447,16 @@
     </row>
     <row r="47" spans="4:11">
       <c r="D47" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>630</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>631</v>
       </c>
       <c r="I47" s="3" t="str">
         <f t="shared" si="0"/>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namba\OneDrive\workspace_202509\hogandiff4\xyz.hotchpotch.hogandiff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B521CB60-0517-423C-A006-2C76B01E93F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{837EF89F-D38D-40BC-8B80-6986C3B731F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="(3)" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="598">
   <si>
     <t>website</t>
   </si>
@@ -681,13 +681,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>比較対象：</t>
-    <rPh sb="0" eb="4">
-      <t>ヒカクタイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ブック</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -700,10 +693,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Compare</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Books</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -713,10 +702,6 @@
   </si>
   <si>
     <t>Folders</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>互相比较</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2285,10 +2270,6 @@
   </si>
   <si>
     <t>FXML_0020</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FXML_0070</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2964,7 +2945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:K154"/>
+  <dimension ref="C1:K153"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -2982,7 +2963,7 @@
   <sheetData>
     <row r="1" spans="3:11">
       <c r="C1" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>104</v>
@@ -3005,7 +2986,7 @@
     </row>
     <row r="2" spans="3:11">
       <c r="D2" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -3014,7 +2995,7 @@
         <v>59</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I2" s="3" t="str">
         <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; E2)</f>
@@ -3031,7 +3012,7 @@
     </row>
     <row r="3" spans="3:11">
       <c r="D3" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -3043,30 +3024,30 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I66" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
+        <f t="shared" ref="I3:I65" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="J3" s="4" t="str">
-        <f t="shared" ref="J3:J66" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
+        <f t="shared" ref="J3:J65" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="K3" s="5" t="str">
-        <f t="shared" ref="K3:K66" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
+        <f t="shared" ref="K3:K65" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
         <v>FXML_0020=website</v>
       </c>
     </row>
     <row r="4" spans="3:11">
       <c r="D4" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3083,16 +3064,16 @@
     </row>
     <row r="5" spans="3:11">
       <c r="D5" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3109,16 +3090,16 @@
     </row>
     <row r="6" spans="3:11">
       <c r="D6" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3135,7 +3116,7 @@
     </row>
     <row r="7" spans="3:11">
       <c r="D7" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>119</v>
@@ -3144,7 +3125,7 @@
         <v>129</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3161,686 +3142,686 @@
     </row>
     <row r="8" spans="3:11">
       <c r="D8" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>151</v>
+        <v>566</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>155</v>
+        <v>286</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="I8" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0070=比較対象：</v>
+        <v>FXML_0080=パスワード：</v>
       </c>
       <c r="J8" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0070=Compare</v>
+        <v xml:space="preserve">FXML_0080=Password : </v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0070=互相比较</v>
+        <v>FXML_0080=密码：</v>
       </c>
     </row>
     <row r="9" spans="3:11">
       <c r="D9" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I9" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0080=パスワード：</v>
+        <v>FXML_0090=パスワードが異なります。</v>
       </c>
       <c r="J9" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">FXML_0080=Password : </v>
+        <v>FXML_0090=Incorrect password</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0080=密码：</v>
+        <v>FXML_0090=密码不正确。</v>
       </c>
     </row>
     <row r="10" spans="3:11">
       <c r="D10" s="1" t="s">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0090=パスワードが異なります。</v>
+        <v>FXML_0100=比較オプション</v>
       </c>
       <c r="J10" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0090=Incorrect password</v>
+        <v>FXML_0100=Comparison options</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0090=密码不正确。</v>
+        <v>FXML_0100=比较选项</v>
       </c>
     </row>
     <row r="11" spans="3:11">
       <c r="D11" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>60</v>
+        <v>278</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I11" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0100=比較オプション</v>
+        <v>FXML_0110=行の挿入／削除を考慮する</v>
       </c>
       <c r="J11" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0100=Comparison options</v>
+        <v>FXML_0110=Consider row insertions/deletions</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0100=比较选项</v>
+        <v>FXML_0110=考虑行的插入／删除</v>
       </c>
     </row>
     <row r="12" spans="3:11">
       <c r="D12" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I12" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0110=行の挿入／削除を考慮する</v>
+        <v>FXML_0120=列の挿入／削除を考慮する</v>
       </c>
       <c r="J12" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0110=Consider row insertions/deletions</v>
+        <v>FXML_0120=Consider column insertions/deletions</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0110=考虑行的插入／删除</v>
+        <v>FXML_0120=考虑列的插入／删除</v>
       </c>
     </row>
     <row r="13" spans="3:11">
       <c r="D13" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I13" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0120=列の挿入／削除を考慮する</v>
+        <v>FXML_0130=値を比較する</v>
       </c>
       <c r="J13" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0120=Consider column insertions/deletions</v>
+        <v>FXML_0130=Compare values</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0120=考虑列的插入／删除</v>
+        <v>FXML_0130=比较值</v>
       </c>
     </row>
     <row r="14" spans="3:11">
       <c r="D14" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I14" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0130=値を比較する</v>
+        <v>FXML_0140=数式を比較する</v>
       </c>
       <c r="J14" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0130=Compare values</v>
+        <v>FXML_0140=Compare formulas</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0130=比较值</v>
+        <v>FXML_0140=比较公式</v>
       </c>
     </row>
     <row r="15" spans="3:11">
       <c r="D15" s="1" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="I15" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0140=数式を比較する</v>
+        <v>FXML_0150=シート名／ブック名の曖昧マッチを有効にする</v>
       </c>
       <c r="J15" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0140=Compare formulas</v>
+        <v>FXML_0150=Enable sheets/books fuzzy matching</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0140=比较公式</v>
+        <v>FXML_0150=启用工作表／工作簿模糊匹配</v>
       </c>
     </row>
     <row r="16" spans="3:11">
       <c r="D16" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>326</v>
+        <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>328</v>
+        <v>61</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>327</v>
+        <v>210</v>
       </c>
       <c r="I16" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0150=シート名／ブック名の曖昧マッチを有効にする</v>
+        <v>FXML_0160=レポートオプション</v>
       </c>
       <c r="J16" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0150=Enable sheets/books fuzzy matching</v>
+        <v>FXML_0160=Reporting options</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0150=启用工作表／工作簿模糊匹配</v>
+        <v>FXML_0160=报告选项</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="I17" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0160=レポートオプション</v>
+        <v>FXML_0170=差分箇所に色を着けて表示する</v>
       </c>
       <c r="J17" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0160=Reporting options</v>
+        <v>FXML_0170=Display differences in colors</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0160=报告选项</v>
+        <v>FXML_0170=用颜色标记差异</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="I18" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0170=差分箇所に色を着けて表示する</v>
+        <v>FXML_0180=比較結果レポートを表示する</v>
       </c>
       <c r="J18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0170=Display differences in colors</v>
+        <v>FXML_0180=Display comparison result report</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0170=用颜色标记差异</v>
+        <v>FXML_0180=显示比较结果报告</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>292</v>
+        <v>62</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>294</v>
+        <v>211</v>
       </c>
       <c r="I19" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0180=比較結果レポートを表示する</v>
+        <v>FXML_0190=実行オプション</v>
       </c>
       <c r="J19" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0180=Display comparison result report</v>
+        <v>FXML_0190=Execution options</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0180=显示比较结果报告</v>
+        <v>FXML_0190=执行选项</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I20" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0190=実行オプション</v>
+        <v>FXML_0200=比較完了時にこのアプリを終了する</v>
       </c>
       <c r="J20" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0190=Execution options</v>
+        <v>FXML_0200=Exit this app upon completion</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0190=执行选项</v>
+        <v>FXML_0200=比较结束后自动退出此应用程序</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>10</v>
+        <v>259</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="I21" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0200=比較完了時にこのアプリを終了する</v>
+        <v>FXML_0210=早さ優先</v>
       </c>
       <c r="J21" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0200=Exit this app upon completion</v>
+        <v>FXML_0210=Prioritize speed</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0200=比较结束后自动退出此应用程序</v>
+        <v>FXML_0210=优先考虑速度</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="I22" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0210=早さ優先</v>
+        <v>FXML_0220=精度優先</v>
       </c>
       <c r="J22" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0210=Prioritize speed</v>
+        <v>FXML_0220=Prioritize accuracy</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0210=优先考虑速度</v>
+        <v>FXML_0220=优先考虑准确性</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>263</v>
+        <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>287</v>
+        <v>63</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="I23" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0220=精度優先</v>
+        <v>FXML_0230=言語</v>
       </c>
       <c r="J23" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0220=Prioritize accuracy</v>
+        <v>FXML_0230=Language</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0220=优先考虑准确性</v>
+        <v>FXML_0230=语言</v>
       </c>
     </row>
     <row r="24" spans="4:11">
       <c r="D24" s="1" t="s">
-        <v>577</v>
+        <v>552</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I24" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0230=言語</v>
+        <v>FXML_0240=作業用\nフォルダ</v>
       </c>
       <c r="J24" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0230=Language</v>
+        <v>FXML_0240=Working directory</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0230=语言</v>
+        <v>FXML_0240=工作\n文件夹</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
+      <c r="E25" s="7" t="s">
+        <v>405</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>116</v>
+        <v>406</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>217</v>
+        <v>591</v>
       </c>
       <c r="I25" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0240=作業用\nフォルダ</v>
+        <v>FXML_0250=詳細設定…</v>
       </c>
       <c r="J25" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0240=Working directory</v>
+        <v>FXML_0250=Advanced Settings…</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0240=工作\n文件夹</v>
+        <v>FXML_0250=详细设置...</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>408</v>
+        <v>553</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>409</v>
+        <v>64</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>595</v>
+        <v>105</v>
       </c>
       <c r="I26" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0250=詳細設定…</v>
+        <v>FXML_0260=開く</v>
       </c>
       <c r="J26" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0250=Advanced Settings…</v>
+        <v>FXML_0260=Open</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0250=详细设置...</v>
+        <v>FXML_0260=打开</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="I27" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0260=開く</v>
+        <v>FXML_0270=変更...</v>
       </c>
       <c r="J27" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0260=Open</v>
+        <v>FXML_0270=Change...</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0260=打开</v>
+        <v>FXML_0270=改变...</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I28" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0270=変更...</v>
+        <v>FXML_0280=削除...</v>
       </c>
       <c r="J28" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0270=Change...</v>
+        <v>FXML_0280=Delete...</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0270=改变...</v>
+        <v>FXML_0280=删除...</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>66</v>
+        <v>180</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="I29" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0280=削除...</v>
+        <v>FXML_0290=ブックパス：</v>
       </c>
       <c r="J29" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0280=Delete...</v>
+        <v xml:space="preserve">FXML_0290=Book Path : </v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0280=删除...</v>
+        <v>FXML_0290=工作簿路径：</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I30" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0290=ブックパス：</v>
+        <v>FXML_0300=シート名：</v>
       </c>
       <c r="J30" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">FXML_0290=Book Path : </v>
+        <v xml:space="preserve">FXML_0300=Sheet Name : </v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0290=工作簿路径：</v>
+        <v>FXML_0300=工作表名称：</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>1</v>
+        <v>557</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="I31" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0300=シート名：</v>
+        <v>FXML_0310=フォルダパス：</v>
       </c>
       <c r="J31" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">FXML_0300=Sheet Name : </v>
+        <v xml:space="preserve">FXML_0310=Folder Path : </v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0300=工作表名称：</v>
+        <v>FXML_0310=文件夹路径：</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>150</v>
+        <v>356</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>185</v>
+        <v>357</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>220</v>
+        <v>359</v>
       </c>
       <c r="I32" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0310=フォルダパス：</v>
+        <v>FXML_0320=ファイルURL :</v>
       </c>
       <c r="J32" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">FXML_0310=Folder Path : </v>
+        <v>FXML_0320=File URL :</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0310=文件夹路径：</v>
-      </c>
-    </row>
-    <row r="33" spans="4:11">
+        <v>FXML_0320=文件URL :</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11">
       <c r="D33" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>360</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I33" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0320=ファイルURL :</v>
+        <v>FXML_0330=ファイル名 :</v>
       </c>
       <c r="J33" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0320=File URL :</v>
+        <v>FXML_0330=File Name :</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0320=文件URL :</v>
-      </c>
-    </row>
-    <row r="34" spans="4:11">
+        <v>FXML_0330=文件名 :</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11">
       <c r="D34" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>363</v>
@@ -3850,20 +3831,20 @@
       </c>
       <c r="I34" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0330=ファイル名 :</v>
+        <v>FXML_0340=リビジョン :</v>
       </c>
       <c r="J34" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0330=File Name :</v>
+        <v>FXML_0340=Revision :</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0330=文件名 :</v>
-      </c>
-    </row>
-    <row r="35" spans="4:11">
+        <v>FXML_0340=版本 :</v>
+      </c>
+    </row>
+    <row r="35" spans="3:11">
       <c r="D35" s="1" t="s">
-        <v>568</v>
+        <v>532</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>365</v>
@@ -3872,895 +3853,899 @@
         <v>366</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I35" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0340=リビジョン :</v>
+        <v>FXML_0350=Googleドライブ\n連携</v>
       </c>
       <c r="J35" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0340=Revision :</v>
+        <v>FXML_0350=Connect\nGoogle Drive</v>
       </c>
       <c r="K35" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0340=版本 :</v>
-      </c>
-    </row>
-    <row r="36" spans="4:11">
+        <v>FXML_0350=Google Drive\n关联</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11">
       <c r="D36" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>369</v>
-      </c>
       <c r="G36" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I36" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0350=Googleドライブ\n連携</v>
+        <v>FXML_0360=Googleドライブ\n連携解除</v>
       </c>
       <c r="J36" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0350=Connect\nGoogle Drive</v>
+        <v>FXML_0360=Disconnect\nGoogle Drive</v>
       </c>
       <c r="K36" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0350=Google Drive\n关联</v>
-      </c>
-    </row>
-    <row r="37" spans="4:11">
+        <v>FXML_0360=Google Drive\n关联解除</v>
+      </c>
+    </row>
+    <row r="37" spans="3:11">
       <c r="D37" s="1" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="I37" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0360=Googleドライブ\n連携解除</v>
+        <v>FXML_0370=更新確認</v>
       </c>
       <c r="J37" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0360=Disconnect\nGoogle Drive</v>
+        <v>FXML_0370=Update Check</v>
       </c>
       <c r="K37" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0360=Google Drive\n关联解除</v>
-      </c>
-    </row>
-    <row r="38" spans="4:11">
+        <v>FXML_0370=更新确认</v>
+      </c>
+    </row>
+    <row r="38" spans="3:11">
       <c r="D38" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>410</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>412</v>
       </c>
       <c r="I38" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0370=更新確認</v>
+        <v>FXML_0380=起動時に新規バージョンの有無を確認する</v>
       </c>
       <c r="J38" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0370=Update Check</v>
+        <v>FXML_0380=Check for new versions at startup</v>
       </c>
       <c r="K38" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0370=更新确认</v>
-      </c>
-    </row>
-    <row r="39" spans="4:11">
+        <v>FXML_0380=启动时检查是否有新版本</v>
+      </c>
+    </row>
+    <row r="39" spans="3:11">
       <c r="D39" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>415</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>413</v>
       </c>
       <c r="I39" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0380=起動時に新規バージョンの有無を確認する</v>
+        <v>FXML_0390=新規バージョンの有無を今すぐ確認する</v>
       </c>
       <c r="J39" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0380=Check for new versions at startup</v>
+        <v>FXML_0390=Check for new versions now</v>
       </c>
       <c r="K39" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0380=启动时检查是否有新版本</v>
-      </c>
-    </row>
-    <row r="40" spans="4:11">
+        <v>FXML_0390=立即检查是否有新版本</v>
+      </c>
+    </row>
+    <row r="40" spans="3:11">
       <c r="D40" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>416</v>
+        <v>574</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>417</v>
+        <v>584</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>418</v>
+        <v>575</v>
       </c>
       <c r="I40" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0390=新規バージョンの有無を今すぐ確認する</v>
+        <v>FXML_0400=設定管理</v>
       </c>
       <c r="J40" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0390=Check for new versions now</v>
+        <v>FXML_0400=Settings\nManagement</v>
       </c>
       <c r="K40" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0390=立即检查是否有新版本</v>
-      </c>
-    </row>
-    <row r="41" spans="4:11">
+        <v>FXML_0400=设置管理</v>
+      </c>
+    </row>
+    <row r="41" spans="3:11">
       <c r="D41" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>578</v>
+        <v>416</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>588</v>
+        <v>418</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>579</v>
+        <v>417</v>
       </c>
       <c r="I41" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0400=設定管理</v>
+        <v>FXML_0410=設定ファイルを表示する</v>
       </c>
       <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0400=Settings\nManagement</v>
+        <v>FXML_0410=Display the configuration file</v>
       </c>
       <c r="K41" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0400=设置管理</v>
-      </c>
-    </row>
-    <row r="42" spans="4:11">
+        <v>FXML_0410=显示配置文件</v>
+      </c>
+    </row>
+    <row r="42" spans="3:11">
       <c r="D42" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>419</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>420</v>
+        <v>592</v>
       </c>
       <c r="I42" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0410=設定ファイルを表示する</v>
+        <v>FXML_0420=設定をリセットする…</v>
       </c>
       <c r="J42" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0410=Display the configuration file</v>
+        <v>FXML_0420=Reset settings…</v>
       </c>
       <c r="K42" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0410=显示配置文件</v>
-      </c>
-    </row>
-    <row r="43" spans="4:11">
+        <v>FXML_0420=重置设置…</v>
+      </c>
+    </row>
+    <row r="43" spans="3:11">
       <c r="D43" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>422</v>
+        <v>560</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>423</v>
+        <v>373</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>596</v>
+        <v>378</v>
       </c>
       <c r="I43" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0420=設定をリセットする…</v>
+        <v>FXML_0430=選択されたファイルをGoogleドライブからダウンロードしてこのPCの下記リンク先フォルダに保存しました。\nPC上に保存された状態が好ましくない場合は、比較処理が終わり次第、ご自身で削除してください。</v>
       </c>
       <c r="J43" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0420=Reset settings…</v>
+        <v>FXML_0430=The selected file has been downloaded from Google Drive and saved to the folder linked below on this PC.\nIf you prefer not to keep the file stored on your PC, please delete it manually after the comparison process is complete.</v>
       </c>
       <c r="K43" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0420=重置设置…</v>
-      </c>
-    </row>
-    <row r="44" spans="4:11">
+        <v>FXML_0430=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
+      </c>
+    </row>
+    <row r="44" spans="3:11">
       <c r="D44" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="I44" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0430=選択されたファイルをGoogleドライブからダウンロードしてこのPCの下記リンク先フォルダに保存しました。\nPC上に保存された状態が好ましくない場合は、比較処理が終わり次第、ご自身で削除してください。</v>
+        <v>FXML_0440=次回以降、このメッセージを表示しない</v>
       </c>
       <c r="J44" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0430=The selected file has been downloaded from Google Drive and saved to the folder linked below on this PC.\nIf you prefer not to keep the file stored on your PC, please delete it manually after the comparison process is complete.</v>
+        <v>FXML_0440=Don't show this message again</v>
       </c>
       <c r="K44" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0430=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
-      </c>
-    </row>
-    <row r="45" spans="4:11">
+        <v>FXML_0440=不再显示此消息</v>
+      </c>
+    </row>
+    <row r="45" spans="3:11">
       <c r="D45" s="1" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>375</v>
+        <v>578</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>377</v>
+        <v>580</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>378</v>
+        <v>579</v>
       </c>
       <c r="I45" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0440=次回以降、このメッセージを表示しない</v>
+        <v>FXML_0450=その他設定</v>
       </c>
       <c r="J45" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0440=Don't show this message again</v>
+        <v>FXML_0450=Other settings</v>
       </c>
       <c r="K45" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0440=不再显示此消息</v>
-      </c>
-    </row>
-    <row r="46" spans="4:11">
+        <v>FXML_0450=其他设置</v>
+      </c>
+    </row>
+    <row r="46" spans="3:11">
       <c r="D46" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E46" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>582</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>584</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>583</v>
       </c>
       <c r="I46" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0450=その他設定</v>
+        <v>FXML_0460=エラー情報を自動でサーバに送信する</v>
       </c>
       <c r="J46" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0450=Other settings</v>
+        <v>FXML_0460=Automatically send error information to the server</v>
       </c>
       <c r="K46" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0450=其他设置</v>
-      </c>
-    </row>
-    <row r="47" spans="4:11">
-      <c r="D47" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>587</v>
-      </c>
+        <v>FXML_0460=自动发送错误信息到服务器</v>
+      </c>
+    </row>
+    <row r="47" spans="3:11">
+      <c r="E47" s="2"/>
       <c r="I47" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0460=エラー情報を自動でサーバに送信する</v>
+        <v/>
       </c>
       <c r="J47" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0460=Automatically send error information to the server</v>
+        <v/>
       </c>
       <c r="K47" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0460=自动发送错误信息到服务器</v>
-      </c>
-    </row>
-    <row r="48" spans="4:11">
-      <c r="E48" s="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="3:11">
+      <c r="C48" s="1" t="str">
+        <f t="shared" ref="C48:C79" si="3" xml:space="preserve"> "/** " &amp; E48 &amp; " */ " &amp; D48 &amp; ","</f>
+        <v>/** 方眼Diff */ APP_0010,</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>328</v>
+      </c>
       <c r="I48" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>APP_0010=方眼Diff</v>
       </c>
       <c r="J48" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>APP_0010=HoganDiff (方眼Diff)</v>
       </c>
       <c r="K48" s="5" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>APP_0010=方眼Diff</v>
       </c>
     </row>
     <row r="49" spans="3:11">
       <c r="C49" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E49 &amp; " */ " &amp; D49 &amp; ","</f>
-        <v>/** 方眼Diff */ APP_0010,</v>
+        <f t="shared" si="3"/>
+        <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>331</v>
+        <v>231</v>
       </c>
       <c r="I49" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0010=方眼Diff</v>
+        <v>APP_0020=設定の保存に失敗しました。</v>
       </c>
       <c r="J49" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0010=HoganDiff (方眼Diff)</v>
+        <v>APP_0020=Failed to save settings.</v>
       </c>
       <c r="K49" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0010=方眼Diff</v>
+        <v>APP_0020=保存设置失败。</v>
       </c>
     </row>
     <row r="50" spans="3:11">
       <c r="C50" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E50 &amp; " */ " &amp; D50 &amp; ","</f>
-        <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I50" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0020=設定の保存に失敗しました。</v>
+        <v>APP_0030=比較結果テキストを保存しています...</v>
       </c>
       <c r="J50" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0020=Failed to save settings.</v>
+        <v>APP_0030=Saving result text...</v>
       </c>
       <c r="K50" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0020=保存设置失败。</v>
+        <v>APP_0030=存储比较结果文本...</v>
       </c>
     </row>
     <row r="51" spans="3:11">
       <c r="C51" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E51 &amp; " */ " &amp; D51 &amp; ","</f>
-        <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I51" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0030=比較結果テキストを保存しています...</v>
+        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
       </c>
       <c r="J51" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0030=Saving result text...</v>
+        <v>APP_0040=Failed to save or open result text.</v>
       </c>
       <c r="K51" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0030=存储比较结果文本...</v>
+        <v>APP_0040=保存和显示比较结果文本失败。</v>
       </c>
     </row>
     <row r="52" spans="3:11">
       <c r="C52" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E52 &amp; " */ " &amp; D52 &amp; ","</f>
-        <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
+        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
       </c>
       <c r="J52" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0040=Failed to save or open result text.</v>
+        <v>APP_0050=Painting and saving result book(s)...</v>
       </c>
       <c r="K52" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0040=保存和显示比较结果文本失败。</v>
+        <v>APP_0050=着色和存储在工作簿...</v>
       </c>
     </row>
     <row r="53" spans="3:11">
       <c r="C53" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E53 &amp; " */ " &amp; D53 &amp; ","</f>
-        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
+        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
       </c>
       <c r="J53" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0050=Painting and saving result book(s)...</v>
+        <v>APP_0060=Failed to paint or save result book(s).</v>
       </c>
       <c r="K53" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0050=着色和存储在工作簿...</v>
+        <v>APP_0060=着色和保存工作簿失败。</v>
       </c>
     </row>
     <row r="54" spans="3:11">
       <c r="C54" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E54 &amp; " */ " &amp; D54 &amp; ","</f>
-        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
+        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
       </c>
       <c r="J54" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0060=Failed to paint or save result book(s).</v>
+        <v>APP_0070=Opening result book(s)...</v>
       </c>
       <c r="K54" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0060=着色和保存工作簿失败。</v>
+        <v>APP_0070=显示比较结果的工作簿...</v>
       </c>
     </row>
     <row r="55" spans="3:11">
       <c r="C55" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E55 &amp; " */ " &amp; D55 &amp; ","</f>
-        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
+        <v>APP_0080=Excelブックの表示に失敗しました。</v>
       </c>
       <c r="J55" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0070=Opening result book(s)...</v>
+        <v>APP_0080=Failed to open result book(s).</v>
       </c>
       <c r="K55" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0070=显示比较结果的工作簿...</v>
+        <v>APP_0080=显示工作簿失败。</v>
       </c>
     </row>
     <row r="56" spans="3:11">
       <c r="C56" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E56 &amp; " */ " &amp; D56 &amp; ","</f>
-        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブック%sの着色・保存に失敗しました。 */ APP_0090,</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>44</v>
+        <v>589</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>87</v>
+        <v>590</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>240</v>
+        <v>593</v>
       </c>
       <c r="I56" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0080=Excelブックの表示に失敗しました。</v>
+        <v>APP_0090=Excelブック%sの着色・保存に失敗しました。</v>
       </c>
       <c r="J56" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0080=Failed to open result book(s).</v>
+        <v>APP_0090=Failed to paint or save result book %s.</v>
       </c>
       <c r="K56" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0080=显示工作簿失败。</v>
+        <v>APP_0090=工作簿%s的着色和保存失败。</v>
       </c>
     </row>
     <row r="57" spans="3:11">
       <c r="C57" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E57 &amp; " */ " &amp; D57 &amp; ","</f>
-        <v>/** Excelブック%sの着色・保存に失敗しました。 */ APP_0090,</v>
+        <f t="shared" si="3"/>
+        <v>/** 処理が完了しました。 */ APP_0110,</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>593</v>
+        <v>45</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>594</v>
+        <v>88</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>597</v>
+        <v>238</v>
       </c>
       <c r="I57" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0090=Excelブック%sの着色・保存に失敗しました。</v>
+        <v>APP_0110=処理が完了しました。</v>
       </c>
       <c r="J57" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0090=Failed to paint or save result book %s.</v>
+        <v>APP_0110=Process completed.</v>
       </c>
       <c r="K57" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0090=工作簿%s的着色和保存失败。</v>
+        <v>APP_0110=过程完成。</v>
       </c>
     </row>
     <row r="58" spans="3:11">
       <c r="C58" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E58 &amp; " */ " &amp; D58 &amp; ","</f>
-        <v>/** 処理が完了しました。 */ APP_0110,</v>
+        <f t="shared" si="3"/>
+        <v>/** ★失敗しました */ APP_0120,</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>45</v>
+        <v>436</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I58" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0110=処理が完了しました。</v>
+        <v>APP_0120=★失敗しました</v>
       </c>
       <c r="J58" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0110=Process completed.</v>
+        <v>APP_0120=★Failed</v>
       </c>
       <c r="K58" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0110=过程完成。</v>
+        <v>APP_0120=★失败</v>
       </c>
     </row>
     <row r="59" spans="3:11">
       <c r="C59" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E59 &amp; " */ " &amp; D59 &amp; ","</f>
-        <v>/** ★失敗しました */ APP_0120,</v>
+        <f t="shared" si="3"/>
+        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="I59" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0120=★失敗しました</v>
+        <v>APP_0130=(比較対象ファイルなし)</v>
       </c>
       <c r="J59" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0120=★Failed</v>
+        <v>APP_0130=(No files to compare)</v>
       </c>
       <c r="K59" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0120=★失败</v>
+        <v>APP_0130=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="60" spans="3:11">
       <c r="C60" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E60 &amp; " */ " &amp; D60 &amp; ","</f>
-        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
+        <f t="shared" si="3"/>
+        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>178</v>
+        <v>264</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>179</v>
+        <v>336</v>
       </c>
       <c r="I60" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0130=(比較対象ファイルなし)</v>
+        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="J60" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0130=(No files to compare)</v>
+        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="K60" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0130=(没有可比较的文件)</v>
+        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
     </row>
     <row r="61" spans="3:11">
       <c r="C61" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E61 &amp; " */ " &amp; D61 &amp; ","</f>
-        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
+        <f t="shared" si="3"/>
+        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>266</v>
+        <v>439</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>267</v>
+        <v>74</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>339</v>
+        <v>107</v>
       </c>
       <c r="I61" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <v>APP_0150=予期せぬ例外が発生しました。</v>
       </c>
       <c r="J61" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <v>APP_0150=Unexpected exception occurred.</v>
       </c>
       <c r="K61" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <v>APP_0150=意外的例外。</v>
       </c>
     </row>
     <row r="62" spans="3:11">
       <c r="C62" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E62 &amp; " */ " &amp; D62 &amp; ","</f>
-        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較実行日時： */ APP_0160,</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>29</v>
+        <v>440</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>74</v>
+        <v>301</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>107</v>
+        <v>294</v>
       </c>
       <c r="I62" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0150=予期せぬ例外が発生しました。</v>
+        <v>APP_0160=比較実行日時：</v>
       </c>
       <c r="J62" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0150=Unexpected exception occurred.</v>
+        <v xml:space="preserve">APP_0160=Exec datetime : </v>
       </c>
       <c r="K62" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0150=意外的例外。</v>
+        <v>APP_0160=执行日期和时间：</v>
       </c>
     </row>
     <row r="63" spans="3:11">
       <c r="C63" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E63 &amp; " */ " &amp; D63 &amp; ","</f>
-        <v>/** 比較実行日時： */ APP_0160,</v>
+        <f t="shared" si="3"/>
+        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>296</v>
+        <v>441</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>304</v>
+        <v>132</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="I63" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0160=比較実行日時：</v>
+        <v>APP_0170=ブック同士の比較を開始します。</v>
       </c>
       <c r="J63" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">APP_0160=Exec datetime : </v>
+        <v>APP_0170=Starting comparing books.</v>
       </c>
       <c r="K63" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0160=执行日期和时间：</v>
+        <v>APP_0170=开始互相比较工作簿。</v>
       </c>
     </row>
     <row r="64" spans="3:11">
       <c r="C64" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E64 &amp; " */ " &amp; D64 &amp; ","</f>
-        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
+        <f t="shared" si="3"/>
+        <v>/** シートを比較しています... */ APP_0180,</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I64" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0170=ブック同士の比較を開始します。</v>
+        <v>APP_0180=シートを比較しています...</v>
       </c>
       <c r="J64" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0170=Starting comparing books.</v>
+        <v>APP_0180=Comparing sheets...</v>
       </c>
       <c r="K64" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0170=开始互相比较工作簿。</v>
+        <v>APP_0180=比较工作表...</v>
       </c>
     </row>
     <row r="65" spans="3:11">
       <c r="C65" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E65 &amp; " */ " &amp; D65 &amp; ","</f>
-        <v>/** シートを比較しています... */ APP_0180,</v>
+        <f t="shared" si="3"/>
+        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I65" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0180=シートを比較しています...</v>
+        <v>APP_0190=シートの比較に失敗しました。</v>
       </c>
       <c r="J65" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0180=Comparing sheets...</v>
+        <v>APP_0190=Failed to compare sheets.</v>
       </c>
       <c r="K65" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0180=比较工作表...</v>
+        <v>APP_0190=工作表比较失败。</v>
       </c>
     </row>
     <row r="66" spans="3:11">
       <c r="C66" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E66 &amp; " */ " &amp; D66 &amp; ","</f>
-        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>38</v>
+        <v>302</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="I66" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>APP_0190=シートの比較に失敗しました。</v>
+        <f t="shared" ref="I66:I129" si="4" xml:space="preserve"> IF($D66="", "", $D66 &amp; "=" &amp; E66)</f>
+        <v>APP_0200=比較結果レポートを保存しています...</v>
       </c>
       <c r="J66" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>APP_0190=Failed to compare sheets.</v>
+        <f t="shared" ref="J66:J129" si="5" xml:space="preserve"> IF($D66="", "", $D66 &amp; "=" &amp; F66)</f>
+        <v>APP_0200=Saving result report...</v>
       </c>
       <c r="K66" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>APP_0190=工作表比较失败。</v>
+        <f t="shared" ref="K66:K129" si="6" xml:space="preserve"> IF($D66="", "", $D66 &amp; "=" &amp; G66)</f>
+        <v>APP_0200=保存比较结果报告...</v>
       </c>
     </row>
     <row r="67" spans="3:11">
       <c r="C67" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E67 &amp; " */ " &amp; D67 &amp; ","</f>
-        <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>305</v>
@@ -4772,25 +4757,25 @@
         <v>307</v>
       </c>
       <c r="I67" s="3" t="str">
-        <f t="shared" ref="I67:I130" si="3" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; E67)</f>
-        <v>APP_0200=比較結果レポートを保存しています...</v>
+        <f t="shared" si="4"/>
+        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
       </c>
       <c r="J67" s="4" t="str">
-        <f t="shared" ref="J67:J130" si="4" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; F67)</f>
-        <v>APP_0200=Saving result report...</v>
+        <f t="shared" si="5"/>
+        <v>APP_0210=Failed to save result report.</v>
       </c>
       <c r="K67" s="5" t="str">
-        <f t="shared" ref="K67:K130" si="5" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; G67)</f>
-        <v>APP_0200=保存比较结果报告...</v>
+        <f t="shared" si="6"/>
+        <v>APP_0210=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="68" spans="3:11">
       <c r="C68" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E68 &amp; " */ " &amp; D68 &amp; ","</f>
-        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>308</v>
@@ -4802,1555 +4787,1555 @@
         <v>310</v>
       </c>
       <c r="I68" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0220=比較結果レポートを表示しています...</v>
       </c>
       <c r="J68" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0210=Failed to save result report.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0220=Opening result report...</v>
       </c>
       <c r="K68" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0210=保存比较结果报告失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0220=显示比较结果报告...</v>
       </c>
     </row>
     <row r="69" spans="3:11">
       <c r="C69" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E69 &amp; " */ " &amp; D69 &amp; ","</f>
-        <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
+        <f t="shared" si="3"/>
+        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>312</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I69" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0220=比較結果レポートを表示しています...</v>
+        <f t="shared" si="4"/>
+        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
       </c>
       <c r="J69" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0220=Opening result report...</v>
+        <f t="shared" si="5"/>
+        <v>APP_0230=Failed to open result report.</v>
       </c>
       <c r="K69" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0220=显示比较结果报告...</v>
+        <f t="shared" si="6"/>
+        <v>APP_0230=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="70" spans="3:11">
       <c r="C70" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E70 &amp; " */ " &amp; D70 &amp; ","</f>
-        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
+        <f t="shared" si="3"/>
+        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>316</v>
+        <v>448</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>315</v>
+        <v>134</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="I70" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0240=フォルダ同士の比較を開始します。</v>
       </c>
       <c r="J70" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0230=Failed to open result report.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0240=Starting comparing folders.</v>
       </c>
       <c r="K70" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0230=显示比较结果报告失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0240=开始互相比较文件夹。</v>
       </c>
     </row>
     <row r="71" spans="3:11">
       <c r="C71" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E71 &amp; " */ " &amp; D71 &amp; ","</f>
-        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
+        <f t="shared" si="3"/>
+        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="I71" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0240=フォルダ同士の比較を開始します。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
       </c>
       <c r="J71" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0240=Starting comparing folders.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0250=Failed to create output directory.</v>
       </c>
       <c r="K71" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0240=开始互相比较文件夹。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0250=创建输出目的地文件夹失败。</v>
       </c>
     </row>
     <row r="72" spans="3:11">
       <c r="C72" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E72 &amp; " */ " &amp; D72 &amp; ","</f>
-        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
+        <f t="shared" si="3"/>
+        <v>/** Excelブックを比較しています... */ APP_0260,</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="I72" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0260=Excelブックを比較しています...</v>
       </c>
       <c r="J72" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0250=Failed to create output directory.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0260=Comparing books...</v>
       </c>
       <c r="K72" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0250=创建输出目的地文件夹失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0260=比较工作簿...</v>
       </c>
     </row>
     <row r="73" spans="3:11">
       <c r="C73" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E73 &amp; " */ " &amp; D73 &amp; ","</f>
-        <v>/** Excelブックを比較しています... */ APP_0260,</v>
+        <f t="shared" si="3"/>
+        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>124</v>
+        <v>268</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>136</v>
+        <v>265</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="I73" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0260=Excelブックを比較しています...</v>
+        <f t="shared" si="4"/>
+        <v>APP_0280=フォルダの比較に失敗しました。</v>
       </c>
       <c r="J73" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0260=Comparing books...</v>
+        <f t="shared" si="5"/>
+        <v>APP_0280=Failed to compare folders.</v>
       </c>
       <c r="K73" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0260=比较工作簿...</v>
+        <f t="shared" si="6"/>
+        <v>APP_0280=文件夹比较失败。</v>
       </c>
     </row>
     <row r="74" spans="3:11">
       <c r="C74" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E74 &amp; " */ " &amp; D74 &amp; ","</f>
-        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
+        <f t="shared" si="3"/>
+        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>271</v>
+        <v>452</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="I74" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0280=フォルダの比較に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0290=シート同士の比較を開始します。</v>
       </c>
       <c r="J74" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0280=Failed to compare folders.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0290=Starting comparing sheets.</v>
       </c>
       <c r="K74" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0280=文件夹比较失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0290=开始相互比较工作表。</v>
       </c>
     </row>
     <row r="75" spans="3:11">
       <c r="C75" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E75 &amp; " */ " &amp; D75 &amp; ","</f>
-        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
+        <f t="shared" si="3"/>
+        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>35</v>
+        <v>453</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I75" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0290=シート同士の比較を開始します。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
       </c>
       <c r="J75" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0290=Starting comparing sheets.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0320=Starting comparing folder trees.</v>
       </c>
       <c r="K75" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0290=开始相互比较工作表。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0320=开始互相比较文件夹树。</v>
       </c>
     </row>
     <row r="76" spans="3:11">
       <c r="C76" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E76 &amp; " */ " &amp; D76 &amp; ","</f>
-        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
+        <f t="shared" si="3"/>
+        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I76" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0330=フォルダツリーを比較しています...</v>
       </c>
       <c r="J76" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0320=Starting comparing folder trees.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0330=Comparing folders...</v>
       </c>
       <c r="K76" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0320=开始互相比较文件夹树。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0330=比较文件夹...</v>
       </c>
     </row>
     <row r="77" spans="3:11">
       <c r="C77" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E77 &amp; " */ " &amp; D77 &amp; ","</f>
-        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
+        <f t="shared" si="3"/>
+        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>164</v>
+        <v>267</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>170</v>
+        <v>269</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="I77" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0330=フォルダツリーを比較しています...</v>
+        <f t="shared" si="4"/>
+        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
       </c>
       <c r="J77" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0330=Comparing folders...</v>
+        <f t="shared" si="5"/>
+        <v>APP_0390=Failed to compare folder trees.</v>
       </c>
       <c r="K77" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0330=比较文件夹...</v>
+        <f t="shared" si="6"/>
+        <v>APP_0390=文件夹比较失败。</v>
       </c>
     </row>
     <row r="78" spans="3:11">
       <c r="C78" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E78 &amp; " */ " &amp; D78 &amp; ","</f>
-        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
+        <f t="shared" si="3"/>
+        <v>/** (比較相手なし) */ APP_0400,</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>270</v>
+        <v>456</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>272</v>
+        <v>89</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="I78" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0400=(比較相手なし)</v>
       </c>
       <c r="J78" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0390=Failed to compare folder trees.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0400=(no opponent)</v>
       </c>
       <c r="K78" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0390=文件夹比较失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0400=(没有对比)</v>
       </c>
     </row>
     <row r="79" spans="3:11">
       <c r="C79" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E79 &amp; " */ " &amp; D79 &amp; ","</f>
-        <v>/** (比較相手なし) */ APP_0400,</v>
+        <f t="shared" si="3"/>
+        <v>/** (差分なし) */ APP_0410,</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I79" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0400=(比較相手なし)</v>
+        <f t="shared" si="4"/>
+        <v>APP_0410=(差分なし)</v>
       </c>
       <c r="J79" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0400=(no opponent)</v>
+        <f t="shared" si="5"/>
+        <v>APP_0410=(no diffs)</v>
       </c>
       <c r="K79" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0400=(没有对比)</v>
+        <f t="shared" si="6"/>
+        <v>APP_0410=(没有区别)</v>
       </c>
     </row>
     <row r="80" spans="3:11">
       <c r="C80" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E80 &amp; " */ " &amp; D80 &amp; ","</f>
-        <v>/** (差分なし) */ APP_0410,</v>
+        <f t="shared" ref="C80:C111" si="7" xml:space="preserve"> "/** " &amp; E80 &amp; " */ " &amp; D80 &amp; ","</f>
+        <v>/** 差異発生%dシート */ APP_0420,</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>47</v>
+        <v>458</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I80" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0410=(差分なし)</v>
+        <f t="shared" si="4"/>
+        <v>APP_0420=差異発生%dシート</v>
       </c>
       <c r="J80" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0410=(no diffs)</v>
+        <f t="shared" si="5"/>
+        <v>APP_0420=diff sheets:%d</v>
       </c>
       <c r="K80" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0410=(没有区别)</v>
+        <f t="shared" si="6"/>
+        <v>APP_0420=差异工作表%d</v>
       </c>
     </row>
     <row r="81" spans="3:11">
       <c r="C81" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E81 &amp; " */ " &amp; D81 &amp; ","</f>
-        <v>/** 差異発生%dシート */ APP_0420,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰%dシート */ APP_0430,</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>253</v>
+        <v>142</v>
       </c>
       <c r="I81" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0420=差異発生%dシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0430=余剰%dシート</v>
       </c>
       <c r="J81" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0420=diff sheets:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0430=redundant sheets:%d</v>
       </c>
       <c r="K81" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0420=差异工作表%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0430=冗余工作表%d</v>
       </c>
     </row>
     <row r="82" spans="3:11">
       <c r="C82" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E82 &amp; " */ " &amp; D82 &amp; ","</f>
-        <v>/** 余剰%dシート */ APP_0430,</v>
+        <f t="shared" si="7"/>
+        <v>/** ブック%s： */ APP_0440,</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>127</v>
+        <v>292</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="I82" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0430=余剰%dシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0440=ブック%s：</v>
       </c>
       <c r="J82" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0430=redundant sheets:%d</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0440=Book %s : </v>
       </c>
       <c r="K82" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0430=冗余工作表%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0440=工作簿%s：</v>
       </c>
     </row>
     <row r="83" spans="3:11">
       <c r="C83" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E83 &amp; " */ " &amp; D83 &amp; ","</f>
-        <v>/** ブック%s： */ APP_0440,</v>
+        <f t="shared" si="7"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>295</v>
+        <v>461</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="I83" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0440=ブック%s：</v>
+        <f t="shared" si="4"/>
+        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="J83" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0440=Book %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="K83" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0440=工作簿%s：</v>
+        <f t="shared" si="6"/>
+        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="84" spans="3:11">
       <c r="C84" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E84 &amp; " */ " &amp; D84 &amp; ","</f>
-        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
+        <f t="shared" si="7"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="I84" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
+        <f t="shared" si="4"/>
+        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
       </c>
       <c r="J84" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
+        <f t="shared" si="5"/>
+        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
       </c>
       <c r="K84" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
+        <f t="shared" si="6"/>
+        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="85" spans="3:11">
       <c r="C85" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E85 &amp; " */ " &amp; D85 &amp; ","</f>
-        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
+        <f t="shared" si="7"/>
+        <v>/** フォルダ%s :  */ APP_0480,</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>49</v>
+        <v>463</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I85" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
       </c>
       <c r="J85" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0480=Folder %s : </v>
       </c>
       <c r="K85" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0480=文件夹%s : </v>
       </c>
     </row>
     <row r="86" spans="3:11">
       <c r="C86" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E86 &amp; " */ " &amp; D86 &amp; ","</f>
-        <v>/** フォルダ%s :  */ APP_0480,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差異発生%dブック */ APP_0530,</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I86" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
+        <f t="shared" si="4"/>
+        <v>APP_0530=差異発生%dブック</v>
       </c>
       <c r="J86" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0480=Folder %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0530=diff books:%d</v>
       </c>
       <c r="K86" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0480=文件夹%s : </v>
+        <f t="shared" si="6"/>
+        <v>APP_0530=差异工作簿%d</v>
       </c>
     </row>
     <row r="87" spans="3:11">
       <c r="C87" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E87 &amp; " */ " &amp; D87 &amp; ","</f>
-        <v>/** 差異発生%dブック */ APP_0530,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰%dブック */ APP_0540,</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>256</v>
+        <v>170</v>
       </c>
       <c r="I87" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0530=差異発生%dブック</v>
+        <f t="shared" si="4"/>
+        <v>APP_0540=余剰%dブック</v>
       </c>
       <c r="J87" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0530=diff books:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0540=redundant books:%d</v>
       </c>
       <c r="K87" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0530=差异工作簿%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0540=冗余工作簿%d</v>
       </c>
     </row>
     <row r="88" spans="3:11">
       <c r="C88" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E88 &amp; " */ " &amp; D88 &amp; ","</f>
-        <v>/** 余剰%dブック */ APP_0540,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較失敗%dブック */ APP_0550,</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F88" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="G88" s="6" t="s">
-        <v>173</v>
-      </c>
       <c r="I88" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0540=余剰%dブック</v>
+        <f t="shared" si="4"/>
+        <v>APP_0550=比較失敗%dブック</v>
       </c>
       <c r="J88" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0540=redundant books:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0550=failed books:%d</v>
       </c>
       <c r="K88" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0540=冗余工作簿%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0550=失败工作簿%d</v>
       </c>
     </row>
     <row r="89" spans="3:11">
       <c r="C89" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E89 &amp; " */ " &amp; D89 &amp; ","</f>
-        <v>/** 比較失敗%dブック */ APP_0550,</v>
+        <f t="shared" si="7"/>
+        <v>/** 作業用フォルダ： */ APP_0580,</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="I89" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0550=比較失敗%dブック</v>
+        <f t="shared" si="4"/>
+        <v>APP_0580=作業用フォルダ：</v>
       </c>
       <c r="J89" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0550=failed books:%d</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0580=Working dir : </v>
       </c>
       <c r="K89" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0550=失败工作簿%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0580=工作文件夹：</v>
       </c>
     </row>
     <row r="90" spans="3:11">
       <c r="C90" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E90 &amp; " */ " &amp; D90 &amp; ","</f>
-        <v>/** 作業用フォルダ： */ APP_0580,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差分なし */ APP_0600,</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>181</v>
+        <v>295</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="I90" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0580=作業用フォルダ：</v>
+        <f t="shared" si="4"/>
+        <v>APP_0600=差分なし</v>
       </c>
       <c r="J90" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0580=Working dir : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0600=No Diffs</v>
       </c>
       <c r="K90" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0580=工作文件夹：</v>
+        <f t="shared" si="6"/>
+        <v>APP_0600=没有区别</v>
       </c>
     </row>
     <row r="91" spans="3:11">
       <c r="C91" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E91 &amp; " */ " &amp; D91 &amp; ","</f>
-        <v>/** 差分なし */ APP_0600,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較失敗 */ APP_0610,</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>300</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I91" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0600=差分なし</v>
+        <f t="shared" si="4"/>
+        <v>APP_0610=比較失敗</v>
       </c>
       <c r="J91" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0600=No Diffs</v>
+        <f t="shared" si="5"/>
+        <v>APP_0610=Comparison Failed</v>
       </c>
       <c r="K91" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0600=没有区别</v>
+        <f t="shared" si="6"/>
+        <v>APP_0610=比较失败</v>
       </c>
     </row>
     <row r="92" spans="3:11">
       <c r="C92" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E92 &amp; " */ " &amp; D92 &amp; ","</f>
-        <v>/** 比較失敗 */ APP_0610,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="I92" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0610=比較失敗</v>
+        <f t="shared" si="4"/>
+        <v>APP_0620=余剰行（A: %d, B: %d）</v>
       </c>
       <c r="J92" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0610=Comparison Failed</v>
+        <f t="shared" si="5"/>
+        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
       </c>
       <c r="K92" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0610=比较失败</v>
+        <f t="shared" si="6"/>
+        <v>APP_0620=冗余行（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="93" spans="3:11">
       <c r="C93" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E93 &amp; " */ " &amp; D93 &amp; ","</f>
-        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>318</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I93" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0620=余剰行（A: %d, B: %d）</v>
+        <f t="shared" si="4"/>
+        <v>APP_0630=余剰列（A: %d, B: %d）</v>
       </c>
       <c r="J93" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
+        <f t="shared" si="5"/>
+        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
       </c>
       <c r="K93" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0620=冗余行（A: %d, B: %d）</v>
+        <f t="shared" si="6"/>
+        <v>APP_0630=冗余列（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="94" spans="3:11">
       <c r="C94" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E94 &amp; " */ " &amp; D94 &amp; ","</f>
-        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差分セル（%d） */ APP_0640,</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E94" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F94" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="G94" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="I94" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0630=余剰列（A: %d, B: %d）</v>
+        <f t="shared" si="4"/>
+        <v>APP_0640=差分セル（%d）</v>
       </c>
       <c r="J94" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
+        <f t="shared" si="5"/>
+        <v>APP_0640=Diff Cells (%d)</v>
       </c>
       <c r="K94" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0630=冗余列（A: %d, B: %d）</v>
+        <f t="shared" si="6"/>
+        <v>APP_0640=差异单元格（%d）</v>
       </c>
     </row>
     <row r="95" spans="3:11">
       <c r="C95" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E95 &amp; " */ " &amp; D95 &amp; ","</f>
-        <v>/** 差分セル（%d） */ APP_0640,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較フォルダ%s： */ APP_0660,</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>320</v>
+        <v>177</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="I95" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0640=差分セル（%d）</v>
+        <f t="shared" si="4"/>
+        <v>APP_0660=比較フォルダ%s：</v>
       </c>
       <c r="J95" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0640=Diff Cells (%d)</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0660=Folder %s : </v>
       </c>
       <c r="K95" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0640=差异单元格（%d）</v>
+        <f t="shared" si="6"/>
+        <v>APP_0660=文件夹%s：</v>
       </c>
     </row>
     <row r="96" spans="3:11">
       <c r="C96" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E96 &amp; " */ " &amp; D96 &amp; ","</f>
-        <v>/** 比較フォルダ%s： */ APP_0660,</v>
+        <f t="shared" si="7"/>
+        <v>/** ワークシート */ APP_0680,</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>180</v>
+        <v>474</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="I96" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0660=比較フォルダ%s：</v>
+        <f t="shared" si="4"/>
+        <v>APP_0680=ワークシート</v>
       </c>
       <c r="J96" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0660=Folder %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0680=Worksheet</v>
       </c>
       <c r="K96" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0660=文件夹%s：</v>
+        <f t="shared" si="6"/>
+        <v>APP_0680=工作表</v>
       </c>
     </row>
     <row r="97" spans="3:11">
       <c r="C97" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E97 &amp; " */ " &amp; D97 &amp; ","</f>
-        <v>/** ワークシート */ APP_0680,</v>
+        <f t="shared" si="7"/>
+        <v>/** グラフシート */ APP_0690,</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>109</v>
+        <v>254</v>
       </c>
       <c r="I97" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0680=ワークシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0690=グラフシート</v>
       </c>
       <c r="J97" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0680=Worksheet</v>
+        <f t="shared" si="5"/>
+        <v>APP_0690=Chart</v>
       </c>
       <c r="K97" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0680=工作表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0690=图表表</v>
       </c>
     </row>
     <row r="98" spans="3:11">
       <c r="C98" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E98 &amp; " */ " &amp; D98 &amp; ","</f>
-        <v>/** グラフシート */ APP_0690,</v>
+        <f t="shared" si="7"/>
+        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I98" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0690=グラフシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
       </c>
       <c r="J98" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0690=Chart</v>
+        <f t="shared" si="5"/>
+        <v>APP_0700=MS Excel 5.0 Dialog</v>
       </c>
       <c r="K98" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0690=图表表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0700=MS Excel 5.0 对话表</v>
       </c>
     </row>
     <row r="99" spans="3:11">
       <c r="C99" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E99 &amp; " */ " &amp; D99 &amp; ","</f>
-        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
+        <f t="shared" si="7"/>
+        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>258</v>
+        <v>110</v>
       </c>
       <c r="I99" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0710=Excel 4.0 マクロシート</v>
       </c>
       <c r="J99" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0700=MS Excel 5.0 Dialog</v>
+        <f t="shared" si="5"/>
+        <v>APP_0710=Excel 4.0 Macro</v>
       </c>
       <c r="K99" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0700=MS Excel 5.0 对话表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0710=Excel 4.0 宏表</v>
       </c>
     </row>
     <row r="100" spans="3:11">
       <c r="C100" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E100 &amp; " */ " &amp; D100 &amp; ","</f>
-        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰行%d */ APP_0730,</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I100" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0710=Excel 4.0 マクロシート</v>
+        <f t="shared" si="4"/>
+        <v>APP_0730=余剰行%d</v>
       </c>
       <c r="J100" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0710=Excel 4.0 Macro</v>
+        <f t="shared" si="5"/>
+        <v>APP_0730=redundant rows:%d</v>
       </c>
       <c r="K100" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0710=Excel 4.0 宏表</v>
+        <f t="shared" si="6"/>
+        <v>APP_0730=冗余行%d</v>
       </c>
     </row>
     <row r="101" spans="3:11">
       <c r="C101" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E101 &amp; " */ " &amp; D101 &amp; ","</f>
-        <v>/** 余剰行%d */ APP_0730,</v>
+        <f t="shared" si="7"/>
+        <v>/** 余剰列%d */ APP_0740,</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I101" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0730=余剰行%d</v>
+        <f t="shared" si="4"/>
+        <v>APP_0740=余剰列%d</v>
       </c>
       <c r="J101" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0730=redundant rows:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0740=redundant columns:%d</v>
       </c>
       <c r="K101" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0730=冗余行%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0740=冗余列%d</v>
       </c>
     </row>
     <row r="102" spans="3:11">
       <c r="C102" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E102 &amp; " */ " &amp; D102 &amp; ","</f>
-        <v>/** 余剰列%d */ APP_0740,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差分セル%d */ APP_0750,</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="I102" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0740=余剰列%d</v>
+        <f t="shared" si="4"/>
+        <v>APP_0750=差分セル%d</v>
       </c>
       <c r="J102" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0740=redundant columns:%d</v>
+        <f t="shared" si="5"/>
+        <v>APP_0750=diff cells:%d</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0740=冗余列%d</v>
+        <f t="shared" si="6"/>
+        <v>APP_0750=差异单元格%d</v>
       </c>
     </row>
     <row r="103" spans="3:11">
       <c r="C103" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E103 &amp; " */ " &amp; D103 &amp; ","</f>
-        <v>/** 差分セル%d */ APP_0750,</v>
+        <f t="shared" si="7"/>
+        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>259</v>
+        <v>148</v>
       </c>
       <c r="I103" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0750=差分セル%d</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
       </c>
       <c r="J103" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0750=diff cells:%d</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
       </c>
       <c r="K103" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0750=差异单元格%d</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
       </c>
     </row>
     <row r="104" spans="3:11">
       <c r="C104" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E104 &amp; " */ " &amp; D104 &amp; ","</f>
-        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
+        <f t="shared" si="7"/>
+        <v>/** 行%d */ APP_0770,</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>148</v>
+        <v>57</v>
       </c>
       <c r="I104" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
+        <f t="shared" si="4"/>
+        <v>APP_0770=行%d</v>
       </c>
       <c r="J104" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0770=Row %d</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
+        <f t="shared" si="6"/>
+        <v>APP_0770=行%d</v>
       </c>
     </row>
     <row r="105" spans="3:11">
       <c r="C105" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E105 &amp; " */ " &amp; D105 &amp; ","</f>
-        <v>/** 行%d */ APP_0770,</v>
+        <f t="shared" si="7"/>
+        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="I105" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
       </c>
       <c r="J105" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0770=Row %d</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
       </c>
       <c r="K105" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
       </c>
     </row>
     <row r="106" spans="3:11">
       <c r="C106" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E106 &amp; " */ " &amp; D106 &amp; ","</f>
-        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
+        <f t="shared" si="7"/>
+        <v>/** %s列 */ APP_0790,</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>195</v>
+        <v>58</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="I106" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
+        <f t="shared" si="4"/>
+        <v>APP_0790=%s列</v>
       </c>
       <c r="J106" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0790=Column %s</v>
       </c>
       <c r="K106" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
+        <f t="shared" si="6"/>
+        <v>APP_0790=%s列</v>
       </c>
     </row>
     <row r="107" spans="3:11">
       <c r="C107" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E107 &amp; " */ " &amp; D107 &amp; ","</f>
-        <v>/** %s列 */ APP_0790,</v>
+        <f t="shared" si="7"/>
+        <v>/** 差分セル :  */ APP_0800,</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>58</v>
+        <v>257</v>
       </c>
       <c r="I107" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0800=差分セル : </v>
       </c>
       <c r="J107" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0790=Column %s</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0800=Diff cells : </v>
       </c>
       <c r="K107" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0800=差异单元格 : </v>
       </c>
     </row>
     <row r="108" spans="3:11">
       <c r="C108" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E108 &amp; " */ " &amp; D108 &amp; ","</f>
-        <v>/** 差分セル :  */ APP_0800,</v>
+        <f t="shared" si="7"/>
+        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>196</v>
+        <v>486</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I108" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0800=差分セル : </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
       </c>
       <c r="J108" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0800=Diff cells : </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">APP_0820=Root folder %s : </v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0800=差异单元格 : </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
       </c>
     </row>
     <row r="109" spans="3:11">
       <c r="C109" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E109 &amp; " */ " &amp; D109 &amp; ","</f>
-        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
+        <f t="shared" si="7"/>
+        <v>/** 組み合わせ編集 */ APP_0860,</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>176</v>
+        <v>273</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="I109" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
+        <f t="shared" si="4"/>
+        <v>APP_0860=組み合わせ編集</v>
       </c>
       <c r="J109" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0820=Root folder %s : </v>
+        <f t="shared" si="5"/>
+        <v>APP_0860=Edit Pairing</v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
+        <f t="shared" si="6"/>
+        <v>APP_0860=组合编辑</v>
       </c>
     </row>
     <row r="110" spans="3:11">
       <c r="C110" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E110 &amp; " */ " &amp; D110 &amp; ","</f>
-        <v>/** 組み合わせ編集 */ APP_0860,</v>
+        <f t="shared" si="7"/>
+        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>276</v>
+        <v>380</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>277</v>
+        <v>382</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>278</v>
+        <v>384</v>
       </c>
       <c r="I110" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0860=組み合わせ編集</v>
+        <f t="shared" si="4"/>
+        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
       </c>
       <c r="J110" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0860=Edit Pairing</v>
+        <f t="shared" si="5"/>
+        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0860=组合编辑</v>
+        <f t="shared" si="6"/>
+        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
       </c>
     </row>
     <row r="111" spans="3:11">
       <c r="C111" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E111 &amp; " */ " &amp; D111 &amp; ","</f>
-        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
+        <f t="shared" si="7"/>
+        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E111" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="G111" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G111" s="6" t="s">
-        <v>387</v>
-      </c>
       <c r="I111" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
+        <f t="shared" si="4"/>
+        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
       </c>
       <c r="J111" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
+        <f t="shared" si="5"/>
+        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
+        <f t="shared" si="6"/>
+        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
       </c>
     </row>
     <row r="112" spans="3:11">
       <c r="C112" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E112 &amp; " */ " &amp; D112 &amp; ","</f>
-        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
+        <f t="shared" ref="C112:C143" si="8" xml:space="preserve"> "/** " &amp; E112 &amp; " */ " &amp; D112 &amp; ","</f>
+        <v>/** 共有ドライブ */ APP_0890,</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I112" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
+        <f t="shared" si="4"/>
+        <v>APP_0890=共有ドライブ</v>
       </c>
       <c r="J112" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
+        <f t="shared" si="5"/>
+        <v>APP_0890=Shared drives</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
+        <f t="shared" si="6"/>
+        <v>APP_0890=共享云端硬盘</v>
       </c>
     </row>
     <row r="113" spans="3:11">
       <c r="C113" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E113 &amp; " */ " &amp; D113 &amp; ","</f>
-        <v>/** 共有ドライブ */ APP_0890,</v>
+        <f t="shared" si="8"/>
+        <v>/** すべてのファイル */ APP_0900,</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E113" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G113" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G113" s="6" t="s">
-        <v>396</v>
-      </c>
       <c r="I113" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0890=共有ドライブ</v>
+        <f t="shared" si="4"/>
+        <v>APP_0900=すべてのファイル</v>
       </c>
       <c r="J113" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0890=Shared drives</v>
+        <f t="shared" si="5"/>
+        <v>APP_0900=All files</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0890=共享云端硬盘</v>
+        <f t="shared" si="6"/>
+        <v>APP_0900=所有文件</v>
       </c>
     </row>
     <row r="114" spans="3:11">
       <c r="C114" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E114 &amp; " */ " &amp; D114 &amp; ","</f>
-        <v>/** すべてのファイル */ APP_0900,</v>
+        <f t="shared" si="8"/>
+        <v>/** スター付き */ APP_0910,</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I114" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0900=すべてのファイル</v>
+        <f t="shared" si="4"/>
+        <v>APP_0910=スター付き</v>
       </c>
       <c r="J114" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0900=All files</v>
+        <f t="shared" si="5"/>
+        <v>APP_0910=Starred</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0900=所有文件</v>
+        <f t="shared" si="6"/>
+        <v>APP_0910=已加星标</v>
       </c>
     </row>
     <row r="115" spans="3:11">
       <c r="C115" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E115 &amp; " */ " &amp; D115 &amp; ","</f>
-        <v>/** スター付き */ APP_0910,</v>
+        <f t="shared" si="8"/>
+        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I115" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0910=スター付き</v>
+        <f t="shared" si="4"/>
+        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
       </c>
       <c r="J115" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0910=Starred</v>
+        <f t="shared" si="5"/>
+        <v>APP_0920=Failed to download the file from Google Drive.</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0910=已加星标</v>
+        <f t="shared" si="6"/>
+        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
       </c>
     </row>
     <row r="116" spans="3:11">
       <c r="C116" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E116 &amp; " */ " &amp; D116 &amp; ","</f>
-        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
+        <f t="shared" si="8"/>
+        <v>/** 更新者不明 */ APP_0930,</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>398</v>
+        <v>352</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="I116" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0930=更新者不明</v>
       </c>
       <c r="J116" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0920=Failed to download the file from Google Drive.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0930=Unknown</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0930=更新者不明</v>
       </c>
     </row>
     <row r="117" spans="3:11">
       <c r="C117" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E117 &amp; " */ " &amp; D117 &amp; ","</f>
-        <v>/** 更新者不明 */ APP_0930,</v>
+        <f t="shared" si="8"/>
+        <v>/** 最新版 */ APP_0940,</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E117" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F117" s="4" t="s">
-        <v>356</v>
-      </c>
       <c r="G117" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I117" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0930=更新者不明</v>
+        <f t="shared" si="4"/>
+        <v>APP_0940=最新版</v>
       </c>
       <c r="J117" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0930=Unknown</v>
+        <f t="shared" si="5"/>
+        <v>APP_0940=Latest</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0930=更新者不明</v>
+        <f t="shared" si="6"/>
+        <v>APP_0940=最新版</v>
       </c>
     </row>
     <row r="118" spans="3:11">
       <c r="C118" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E118 &amp; " */ " &amp; D118 &amp; ","</f>
-        <v>/** 最新版 */ APP_0940,</v>
+        <f t="shared" si="8"/>
+        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="I118" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0940=最新版</v>
+        <f t="shared" si="4"/>
+        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
       </c>
       <c r="J118" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0940=Latest</v>
+        <f t="shared" si="5"/>
+        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0940=最新版</v>
+        <f t="shared" si="6"/>
+        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
       </c>
     </row>
     <row r="119" spans="3:11">
       <c r="C119" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E119 &amp; " */ " &amp; D119 &amp; ","</f>
-        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
+        <f t="shared" si="8"/>
+        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>332</v>
       </c>
       <c r="I119" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
+        <f t="shared" si="4"/>
+        <v>APP_0960=資格情報を削除しました。</v>
       </c>
       <c r="J119" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
+        <f t="shared" si="5"/>
+        <v>APP_0960=Credentials have been deleted.</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
+        <f t="shared" si="6"/>
+        <v>APP_0960=已删除凭据。</v>
       </c>
     </row>
     <row r="120" spans="3:11">
       <c r="C120" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E120 &amp; " */ " &amp; D120 &amp; ","</f>
-        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
+        <f t="shared" si="8"/>
+        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>333</v>
@@ -6362,88 +6347,88 @@
         <v>335</v>
       </c>
       <c r="I120" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0960=資格情報を削除しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
       </c>
       <c r="J120" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0960=Credentials have been deleted.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0960=已删除凭据。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
     </row>
     <row r="121" spans="3:11">
       <c r="C121" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E121 &amp; " */ " &amp; D121 &amp; ","</f>
-        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
+        <f t="shared" si="8"/>
+        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I121" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0980=資格情報の削除に失敗しました。</v>
       </c>
       <c r="J121" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0980=Failed to delete credentials.</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0980=删除凭据失败。</v>
       </c>
     </row>
     <row r="122" spans="3:11">
       <c r="C122" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E122 &amp; " */ " &amp; D122 &amp; ","</f>
-        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
+        <f t="shared" si="8"/>
+        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F122" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="G122" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="G122" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="I122" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0980=資格情報の削除に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J122" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0980=Failed to delete credentials.</v>
+        <f t="shared" si="5"/>
+        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0980=删除凭据失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="123" spans="3:11">
       <c r="C123" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E123 &amp; " */ " &amp; D123 &amp; ","</f>
-        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
+        <f t="shared" si="8"/>
+        <v>/** Google連携エラー */ APP_1000,</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>344</v>
@@ -6452,25 +6437,25 @@
         <v>345</v>
       </c>
       <c r="I123" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f t="shared" si="4"/>
+        <v>APP_1000=Google連携エラー</v>
       </c>
       <c r="J123" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="5"/>
+        <v>APP_1000=Google Integration Error</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="6"/>
+        <v>APP_1000=Google关联错误</v>
       </c>
     </row>
     <row r="124" spans="3:11">
       <c r="C124" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E124 &amp; " */ " &amp; D124 &amp; ","</f>
-        <v>/** Google連携エラー */ APP_1000,</v>
+        <f t="shared" si="8"/>
+        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>346</v>
@@ -6482,25 +6467,25 @@
         <v>348</v>
       </c>
       <c r="I124" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1000=Google連携エラー</v>
+        <f t="shared" si="4"/>
+        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
       </c>
       <c r="J124" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1000=Google Integration Error</v>
+        <f t="shared" si="5"/>
+        <v>APP_1010=An error occurred during Google integration processing.</v>
       </c>
       <c r="K124" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1000=Google关联错误</v>
+        <f t="shared" si="6"/>
+        <v>APP_1010=Google关联处理过程中发生错误。</v>
       </c>
     </row>
     <row r="125" spans="3:11">
       <c r="C125" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E125 &amp; " */ " &amp; D125 &amp; ","</f>
-        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
+        <f t="shared" si="8"/>
+        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>349</v>
@@ -6512,891 +6497,861 @@
         <v>351</v>
       </c>
       <c r="I125" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J125" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1010=An error occurred during Google integration processing.</v>
+        <f t="shared" si="5"/>
+        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1010=Google关联处理过程中发生错误。</v>
+        <f t="shared" si="6"/>
+        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="126" spans="3:11">
       <c r="C126" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E126 &amp; " */ " &amp; D126 &amp; ","</f>
-        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
+        <f t="shared" si="8"/>
+        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>352</v>
+        <v>504</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="I126" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f t="shared" si="4"/>
+        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
       </c>
       <c r="J126" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="5"/>
+        <v>APP_1030=File downloaded from Google Drive</v>
       </c>
       <c r="K126" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="6"/>
+        <v>APP_1030=已从Google云端硬盘下载文件</v>
       </c>
     </row>
     <row r="127" spans="3:11">
       <c r="C127" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E127 &amp; " */ " &amp; D127 &amp; ","</f>
-        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
+        <f t="shared" si="8"/>
+        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>374</v>
+        <v>18</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>379</v>
+        <v>67</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>380</v>
+        <v>224</v>
       </c>
       <c r="I127" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
       </c>
       <c r="J127" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1030=File downloaded from Google Drive</v>
+        <f t="shared" si="5"/>
+        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1030=已从Google云端硬盘下载文件</v>
+        <f t="shared" si="6"/>
+        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
     </row>
     <row r="128" spans="3:11">
       <c r="C128" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E128 &amp; " */ " &amp; D128 &amp; ","</f>
-        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
+        <f t="shared" si="8"/>
+        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I128" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
+        <f t="shared" si="4"/>
+        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
       </c>
       <c r="J128" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
+        <f t="shared" si="5"/>
+        <v>APP_1050=Failed to open working directory.</v>
       </c>
       <c r="K128" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
+        <f t="shared" si="6"/>
+        <v>APP_1050=显示工作文件夹失败。</v>
       </c>
     </row>
     <row r="129" spans="3:11">
       <c r="C129" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E129 &amp; " */ " &amp; D129 &amp; ","</f>
-        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
+        <f t="shared" si="8"/>
+        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I129" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
+        <f t="shared" si="4"/>
+        <v>APP_1060=作業用フォルダの変更</v>
       </c>
       <c r="J129" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1050=Failed to open working directory.</v>
+        <f t="shared" si="5"/>
+        <v>APP_1060=Change working directory</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1050=显示工作文件夹失败。</v>
+        <f t="shared" si="6"/>
+        <v>APP_1060=改变工作文件夹</v>
       </c>
     </row>
     <row r="130" spans="3:11">
       <c r="C130" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E130 &amp; " */ " &amp; D130 &amp; ","</f>
-        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
+        <f t="shared" si="8"/>
+        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I130" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1060=作業用フォルダの変更</v>
+        <f t="shared" ref="I130:I153" si="9" xml:space="preserve"> IF($D130="", "", $D130 &amp; "=" &amp; E130)</f>
+        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
       </c>
       <c r="J130" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1060=Change working directory</v>
+        <f t="shared" ref="J130:J153" si="10" xml:space="preserve"> IF($D130="", "", $D130 &amp; "=" &amp; F130)</f>
+        <v>APP_1070=Failed to change working directory.</v>
       </c>
       <c r="K130" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1060=改变工作文件夹</v>
+        <f t="shared" ref="K130:K153" si="11" xml:space="preserve"> IF($D130="", "", $D130 &amp; "=" &amp; G130)</f>
+        <v>APP_1070=更改工作文件夹失败。</v>
       </c>
     </row>
     <row r="131" spans="3:11">
       <c r="C131" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E131 &amp; " */ " &amp; D131 &amp; ","</f>
-        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
+        <f t="shared" si="8"/>
+        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I131" s="3" t="str">
-        <f t="shared" ref="I131:I154" si="6" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; E131)</f>
-        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
       </c>
       <c r="J131" s="4" t="str">
-        <f t="shared" ref="J131:J154" si="7" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; F131)</f>
-        <v>APP_1070=Failed to change working directory.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f t="shared" ref="K131:K154" si="8" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; G131)</f>
-        <v>APP_1070=更改工作文件夹失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
     </row>
     <row r="132" spans="3:11">
       <c r="C132" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E132 &amp; " */ " &amp; D132 &amp; ","</f>
-        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
+        <f t="shared" si="8"/>
+        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="I132" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
+        <f t="shared" si="9"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="J132" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
+        <f t="shared" si="10"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="K132" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
+        <f t="shared" si="11"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
     </row>
     <row r="133" spans="3:11">
       <c r="C133" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E133 &amp; " */ " &amp; D133 &amp; ","</f>
-        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
+        <f t="shared" si="8"/>
+        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I133" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="J133" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="K133" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
     </row>
     <row r="134" spans="3:11">
       <c r="C134" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E134 &amp; " */ " &amp; D134 &amp; ","</f>
-        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
+        <f t="shared" si="8"/>
+        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I134" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="J134" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="K134" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="11"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
     </row>
     <row r="135" spans="3:11">
       <c r="C135" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E135 &amp; " */ " &amp; D135 &amp; ","</f>
-        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
+        <f t="shared" si="8"/>
+        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>24</v>
+        <v>513</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>131</v>
+        <v>402</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>24</v>
+        <v>595</v>
       </c>
       <c r="I135" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1100=方眼Diff  -  詳細設定</v>
       </c>
       <c r="J135" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
       </c>
       <c r="K135" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1100=方眼Diff  -  详细设置</v>
       </c>
     </row>
     <row r="136" spans="3:11">
       <c r="C136" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E136 &amp; " */ " &amp; D136 &amp; ","</f>
-        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
+        <f t="shared" si="8"/>
+        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>404</v>
+        <v>514</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>405</v>
+        <v>130</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>599</v>
+        <v>228</v>
       </c>
       <c r="I136" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1100=方眼Diff  -  詳細設定</v>
+        <f t="shared" si="9"/>
+        <v>APP_1110=比較対象フォルダの選択</v>
       </c>
       <c r="J136" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
+        <f t="shared" si="10"/>
+        <v>APP_1110=Select comparison folder</v>
       </c>
       <c r="K136" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1100=方眼Diff  -  详细设置</v>
+        <f t="shared" si="11"/>
+        <v>APP_1110=选择用于比较的文件夹</v>
       </c>
     </row>
     <row r="137" spans="3:11">
       <c r="C137" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E137 &amp; " */ " &amp; D137 &amp; ","</f>
-        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
+        <f t="shared" si="8"/>
+        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>121</v>
+        <v>515</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I137" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1110=比較対象フォルダの選択</v>
+        <f t="shared" si="9"/>
+        <v>APP_1120=比較対象ブックの選択</v>
       </c>
       <c r="J137" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1110=Select comparison folder</v>
+        <f t="shared" si="10"/>
+        <v>APP_1120=Select comparison book</v>
       </c>
       <c r="K137" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1110=选择用于比较的文件夹</v>
+        <f t="shared" si="11"/>
+        <v>APP_1120=选择用于比较的工作簿</v>
       </c>
     </row>
     <row r="138" spans="3:11">
       <c r="C138" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E138 &amp; " */ " &amp; D138 &amp; ","</f>
-        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
+        <f t="shared" si="8"/>
+        <v>/** Excel ブック */ APP_1130,</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="I138" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1120=比較対象ブックの選択</v>
+        <f t="shared" si="9"/>
+        <v>APP_1130=Excel ブック</v>
       </c>
       <c r="J138" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1120=Select comparison book</v>
+        <f t="shared" si="10"/>
+        <v>APP_1130=Excel book</v>
       </c>
       <c r="K138" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1120=选择用于比较的工作簿</v>
+        <f t="shared" si="11"/>
+        <v>APP_1130=Excel工作簿</v>
       </c>
     </row>
     <row r="139" spans="3:11">
       <c r="C139" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E139 &amp; " */ " &amp; D139 &amp; ","</f>
-        <v>/** Excel ブック */ APP_1130,</v>
+        <f t="shared" si="8"/>
+        <v>/** ファイルを読み込めません： */ APP_1140,</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="I139" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1130=Excel ブック</v>
+        <f t="shared" si="9"/>
+        <v>APP_1140=ファイルを読み込めません：</v>
       </c>
       <c r="J139" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1130=Excel book</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_1140=Failed to open file : </v>
       </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1130=Excel工作簿</v>
+        <f t="shared" si="11"/>
+        <v>APP_1140=无法读取文件：</v>
       </c>
     </row>
     <row r="140" spans="3:11">
       <c r="C140" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E140 &amp; " */ " &amp; D140 &amp; ","</f>
-        <v>/** ファイルを読み込めません： */ APP_1140,</v>
+        <f t="shared" si="8"/>
+        <v>/** シートが見つかりません： */ APP_1150,</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="I140" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1140=ファイルを読み込めません：</v>
+        <f t="shared" si="9"/>
+        <v>APP_1150=シートが見つかりません：</v>
       </c>
       <c r="J140" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_1140=Failed to open file : </v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_1150=No such sheet : </v>
       </c>
       <c r="K140" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1140=无法读取文件：</v>
+        <f t="shared" si="11"/>
+        <v>APP_1150=没有找到工作表：</v>
       </c>
     </row>
     <row r="141" spans="3:11">
       <c r="C141" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E141 &amp; " */ " &amp; D141 &amp; ","</f>
-        <v>/** シートが見つかりません： */ APP_1150,</v>
+        <f t="shared" si="8"/>
+        <v>/** フォルダを読み込めません： */ APP_1160,</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="I141" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1150=シートが見つかりません：</v>
+        <f t="shared" si="9"/>
+        <v>APP_1160=フォルダを読み込めません：</v>
       </c>
       <c r="J141" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_1150=No such sheet : </v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1150=没有找到工作表：</v>
+        <f t="shared" si="11"/>
+        <v>APP_1160=无法读取文件夹：</v>
       </c>
     </row>
     <row r="142" spans="3:11">
       <c r="C142" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E142 &amp; " */ " &amp; D142 &amp; ","</f>
-        <v>/** フォルダを読み込めません： */ APP_1160,</v>
+        <f t="shared" si="8"/>
+        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>273</v>
+        <v>403</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>274</v>
+        <v>404</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>275</v>
+        <v>597</v>
       </c>
       <c r="I142" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1160=フォルダを読み込めません：</v>
+        <f t="shared" si="9"/>
+        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
       </c>
       <c r="J142" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
+        <f t="shared" si="10"/>
+        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
       </c>
       <c r="K142" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1160=无法读取文件夹：</v>
+        <f t="shared" si="11"/>
+        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
     </row>
     <row r="143" spans="3:11">
       <c r="C143" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E143 &amp; " */ " &amp; D143 &amp; ","</f>
-        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
+        <f t="shared" si="8"/>
+        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>406</v>
+        <v>521</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>407</v>
+        <v>128</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>601</v>
+        <v>219</v>
       </c>
       <c r="I143" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
+        <f t="shared" si="9"/>
+        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
       </c>
       <c r="J143" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
+        <f t="shared" si="10"/>
+        <v>APP_1180=Please specify different folders/books/sheets.</v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
+        <f t="shared" si="11"/>
+        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
     </row>
     <row r="144" spans="3:11">
       <c r="C144" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E144 &amp; " */ " &amp; D144 &amp; ","</f>
-        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
+        <f t="shared" ref="C144:C175" si="12" xml:space="preserve"> "/** " &amp; E144 &amp; " */ " &amp; D144 &amp; ","</f>
+        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>120</v>
+        <v>522</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I144" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
       </c>
       <c r="J144" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1180=Please specify different folders/books/sheets.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
     </row>
     <row r="145" spans="3:11">
       <c r="C145" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E145 &amp; " */ " &amp; D145 &amp; ","</f>
-        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
+        <f t="shared" si="12"/>
+        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="I145" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
       </c>
       <c r="J145" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1210=Failed to create working directory.</v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1210=创建工作文件夹失败。</v>
       </c>
     </row>
     <row r="146" spans="3:11">
       <c r="C146" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E146 &amp; " */ " &amp; D146 &amp; ","</f>
-        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
+        <f t="shared" si="12"/>
+        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I146" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1220=別の場所を指定してください。</v>
       </c>
       <c r="J146" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1210=Failed to create working directory.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1220=Please specify another location.</v>
       </c>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1210=创建工作文件夹失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1220=请指定其他位置。</v>
       </c>
     </row>
     <row r="147" spans="3:11">
       <c r="C147" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E147 &amp; " */ " &amp; D147 &amp; ","</f>
-        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
+        <f t="shared" si="12"/>
+        <v>/** 処理を中止しました。 */ APP_1240,</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G147" s="6" t="s">
         <v>199</v>
       </c>
       <c r="I147" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1220=別の場所を指定してください。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1240=処理を中止しました。</v>
       </c>
       <c r="J147" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1220=Please specify another location.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1240=Processing has been canceled.</v>
       </c>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1220=请指定其他位置。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1240=处理已被取消。</v>
       </c>
     </row>
     <row r="148" spans="3:11">
       <c r="C148" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E148 &amp; " */ " &amp; D148 &amp; ","</f>
-        <v>/** 処理を中止しました。 */ APP_1240,</v>
+        <f t="shared" si="12"/>
+        <v>/** パスワード指定 */ APP_1250,</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="I148" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1240=処理を中止しました。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1250=パスワード指定</v>
       </c>
       <c r="J148" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1240=Processing has been canceled.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1250=Enter Password</v>
       </c>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1240=处理已被取消。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1250=输入密码</v>
       </c>
     </row>
     <row r="149" spans="3:11">
       <c r="C149" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E149 &amp; " */ " &amp; D149 &amp; ","</f>
-        <v>/** パスワード指定 */ APP_1250,</v>
+        <f t="shared" si="12"/>
+        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I149" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1250=パスワード指定</v>
+        <f t="shared" si="9"/>
+        <v>APP_1260=%s はパスワードで保護されています。</v>
       </c>
       <c r="J149" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1250=Enter Password</v>
+        <f t="shared" si="10"/>
+        <v>APP_1260=The book [%s] is password protected.</v>
       </c>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1250=输入密码</v>
+        <f t="shared" si="11"/>
+        <v>APP_1260=%s 是受密码保护的。</v>
       </c>
     </row>
     <row r="150" spans="3:11">
       <c r="C150" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E150 &amp; " */ " &amp; D150 &amp; ","</f>
-        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
+        <f t="shared" si="12"/>
+        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>31</v>
+        <v>398</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>76</v>
+        <v>399</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>226</v>
+        <v>400</v>
       </c>
       <c r="I150" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1260=%s はパスワードで保護されています。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1270=新しいバージョンが利用可能です。</v>
       </c>
       <c r="J150" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1260=The book [%s] is password protected.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1270=A new version is available.</v>
       </c>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1260=%s 是受密码保护的。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1270=有新版本可用。</v>
       </c>
     </row>
     <row r="151" spans="3:11">
       <c r="C151" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E151 &amp; " */ " &amp; D151 &amp; ","</f>
-        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
+        <f t="shared" si="12"/>
+        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>403</v>
+        <v>596</v>
       </c>
       <c r="I151" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1270=新しいバージョンが利用可能です。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
       </c>
       <c r="J151" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1270=A new version is available.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
       </c>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1270=有新版本可用。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
       </c>
     </row>
     <row r="152" spans="3:11">
       <c r="C152" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E152 &amp; " */ " &amp; D152 &amp; ","</f>
-        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
+        <f t="shared" si="12"/>
+        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>427</v>
+        <v>530</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="I152" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
       </c>
       <c r="J152" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+        <f t="shared" si="10"/>
+        <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
       </c>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+        <f t="shared" si="11"/>
+        <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
       </c>
     </row>
     <row r="153" spans="3:11">
       <c r="C153" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E153 &amp; " */ " &amp; D153 &amp; ","</f>
-        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
+        <f t="shared" si="12"/>
+        <v>/** ★パスワード不明のためスキップ */ APP_1300,</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>533</v>
+        <v>586</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>425</v>
+        <v>585</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>426</v>
+        <v>587</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="I153" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
+        <f t="shared" si="9"/>
+        <v>APP_1300=★パスワード不明のためスキップ</v>
       </c>
       <c r="J153" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
+        <f t="shared" si="10"/>
+        <v>APP_1300=★Skipped due to unknown password</v>
       </c>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
-      </c>
-    </row>
-    <row r="154" spans="3:11">
-      <c r="C154" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E154 &amp; " */ " &amp; D154 &amp; ","</f>
-        <v>/** ★パスワード不明のためスキップ */ APP_1300,</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="I154" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1300=★パスワード不明のためスキップ</v>
-      </c>
-      <c r="J154" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1300=★Skipped due to unknown password</v>
-      </c>
-      <c r="K154" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>APP_1300=★因密码未知而跳过</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:K154">
-    <sortCondition ref="D49:D154"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A48:K153">
+    <sortCondition ref="D48:D153"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namba\OneDrive\workspace_202509\hogandiff4\xyz.hotchpotch.hogandiff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B521CB60-0517-423C-A006-2C76B01E93F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{B521CB60-0517-423C-A006-2C76B01E93F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{296A5ED9-70A9-40BC-BC1B-3675DA976D7A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="(3)" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$156</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="614">
   <si>
     <t>website</t>
   </si>
@@ -160,12 +160,6 @@
     <t>シートの比較に失敗しました。</t>
   </si>
   <si>
-    <t>比較結果テキストを保存しています...</t>
-  </si>
-  <si>
-    <t>比較結果テキストの保存と表示に失敗しました。</t>
-  </si>
-  <si>
     <t>Excelブックに比較結果の色を付けて保存しています...</t>
   </si>
   <si>
@@ -290,9 +284,6 @@
   </si>
   <si>
     <t>Saving result text...</t>
-  </si>
-  <si>
-    <t>Failed to save or open result text.</t>
   </si>
   <si>
     <t>Painting and saving result book(s)...</t>
@@ -999,9 +990,6 @@
     <t>存储比较结果文本...</t>
   </si>
   <si>
-    <t>保存和显示比较结果文本失败。</t>
-  </si>
-  <si>
     <t>着色和存储在工作簿...</t>
   </si>
   <si>
@@ -1246,22 +1234,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>比較結果レポートを表示する</t>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Display comparison result report</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Display differences in colors</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>显示比较结果报告</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1323,10 +1296,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>比較結果レポートを保存しています...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Saving result report...</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1335,10 +1304,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>比較結果レポートの保存に失敗しました。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Failed to save result report.</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1347,10 +1312,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>比較結果レポートを表示しています...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Opening result report...</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1364,10 +1325,6 @@
   </si>
   <si>
     <t>Failed to open result report.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポートの表示に失敗しました。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2565,6 +2522,115 @@
   </si>
   <si>
     <t>初始化设置并退出应用程序。\n确定吗？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）を保存しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）の保存に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）を表示しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）の表示に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）を保存しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）の保存に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Failed to save result text.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>对比结果文本保存失败。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_0042</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_0041</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）を表示しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）の表示に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Opening result text...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Failed to open result text.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示比较结果文本...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示比较结果文本失败。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Excelレポートを表示</t>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Display excel report</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示文本报告</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストレポートを表示</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Display text report</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B050"/>
+        <rFont val="NSimSun"/>
+        <family val="3"/>
+      </rPr>
+      <t>Excel报告</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FXML_0181</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2656,7 +2722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2671,9 +2737,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2699,6 +2762,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2964,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:K154"/>
+  <dimension ref="C1:K157"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -2972,7 +3039,7 @@
     <col min="4" max="4" width="8.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="30.58203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="30.58203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.58203125" style="5" customWidth="1"/>
     <col min="8" max="8" width="2.58203125" style="1"/>
     <col min="9" max="9" width="2.58203125" style="3"/>
     <col min="10" max="10" width="2.58203125" style="4"/>
@@ -2982,39 +3049,39 @@
   <sheetData>
     <row r="1" spans="3:11">
       <c r="C1" s="1" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="3:11">
       <c r="D2" s="1" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>204</v>
+        <v>57</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="I2" s="3" t="str">
         <f xml:space="preserve"> IF($D2="", "", $D2 &amp; "=" &amp; E2)</f>
@@ -3031,7 +3098,7 @@
     </row>
     <row r="3" spans="3:11">
       <c r="D3" s="1" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -3039,34 +3106,34 @@
       <c r="F3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I66" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
+        <f t="shared" ref="I3:I69" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="J3" s="4" t="str">
-        <f t="shared" ref="J3:J66" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
+        <f t="shared" ref="J3:J69" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="K3" s="5" t="str">
-        <f t="shared" ref="K3:K66" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
+        <f t="shared" ref="K3:K69" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
         <v>FXML_0020=website</v>
       </c>
     </row>
     <row r="4" spans="3:11">
       <c r="D4" s="1" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>160</v>
+        <v>153</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3083,16 +3150,16 @@
     </row>
     <row r="5" spans="3:11">
       <c r="D5" s="1" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3109,16 +3176,16 @@
     </row>
     <row r="6" spans="3:11">
       <c r="D6" s="1" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>162</v>
+        <v>155</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="I6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3135,16 +3202,16 @@
     </row>
     <row r="7" spans="3:11">
       <c r="D7" s="1" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>205</v>
+        <v>126</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="I7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3161,16 +3228,16 @@
     </row>
     <row r="8" spans="3:11">
       <c r="D8" s="1" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>159</v>
+        <v>152</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="I8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3187,16 +3254,16 @@
     </row>
     <row r="9" spans="3:11">
       <c r="D9" s="1" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>206</v>
+        <v>285</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="I9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3213,16 +3280,16 @@
     </row>
     <row r="10" spans="3:11">
       <c r="D10" s="1" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>207</v>
+        <v>284</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>204</v>
       </c>
       <c r="I10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3239,16 +3306,16 @@
     </row>
     <row r="11" spans="3:11">
       <c r="D11" s="1" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>208</v>
+        <v>58</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="I11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3265,16 +3332,16 @@
     </row>
     <row r="12" spans="3:11">
       <c r="D12" s="1" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>209</v>
+        <v>277</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="I12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3291,16 +3358,16 @@
     </row>
     <row r="13" spans="3:11">
       <c r="D13" s="1" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>210</v>
+        <v>278</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="I13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3317,16 +3384,16 @@
     </row>
     <row r="14" spans="3:11">
       <c r="D14" s="1" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>211</v>
+        <v>279</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="I14" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3343,16 +3410,16 @@
     </row>
     <row r="15" spans="3:11">
       <c r="D15" s="1" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>212</v>
+        <v>280</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="I15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3369,16 +3436,16 @@
     </row>
     <row r="16" spans="3:11">
       <c r="D16" s="1" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>327</v>
+        <v>317</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>316</v>
       </c>
       <c r="I16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3395,16 +3462,16 @@
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>213</v>
+        <v>59</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="I17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3421,16 +3488,16 @@
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>280</v>
+        <v>287</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="I18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3447,3956 +3514,4042 @@
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>607</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>294</v>
+        <v>608</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>612</v>
       </c>
       <c r="I19" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>FXML_0180=比較結果レポートを表示する</v>
+        <v>FXML_0180=Excelレポートを表示</v>
       </c>
       <c r="J19" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>FXML_0180=Display comparison result report</v>
+        <v>FXML_0180=Display excel report</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>FXML_0180=显示比较结果报告</v>
+        <v>FXML_0180=显示Excel报告</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>552</v>
+        <v>613</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" ref="I20" si="3" xml:space="preserve"> IF($D20="", "", $D20 &amp; "=" &amp; E20)</f>
+        <v>FXML_0181=テキストレポートを表示</v>
+      </c>
+      <c r="J20" s="4" t="str">
+        <f t="shared" ref="J20" si="4" xml:space="preserve"> IF($D20="", "", $D20 &amp; "=" &amp; F20)</f>
+        <v>FXML_0181=Display text report</v>
+      </c>
+      <c r="K20" s="5" t="str">
+        <f t="shared" ref="K20" si="5" xml:space="preserve"> IF($D20="", "", $D20 &amp; "=" &amp; G20)</f>
+        <v>FXML_0181=显示文本报告</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11">
+      <c r="D21" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I20" s="3" t="str">
+      <c r="F21" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0190=実行オプション</v>
       </c>
-      <c r="J20" s="4" t="str">
+      <c r="J21" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0190=Execution options</v>
       </c>
-      <c r="K20" s="5" t="str">
+      <c r="K21" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0190=执行选项</v>
       </c>
     </row>
-    <row r="21" spans="4:11">
-      <c r="D21" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="E21" s="2" t="s">
+    <row r="22" spans="4:11">
+      <c r="D22" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I21" s="3" t="str">
+      <c r="F22" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0200=比較完了時にこのアプリを終了する</v>
       </c>
-      <c r="J21" s="4" t="str">
+      <c r="J22" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0200=Exit this app upon completion</v>
       </c>
-      <c r="K21" s="5" t="str">
+      <c r="K22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0200=比较结束后自动退出此应用程序</v>
       </c>
     </row>
-    <row r="22" spans="4:11">
-      <c r="D22" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="I22" s="3" t="str">
+    <row r="23" spans="4:11">
+      <c r="D23" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0210=早さ優先</v>
       </c>
-      <c r="J22" s="4" t="str">
+      <c r="J23" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0210=Prioritize speed</v>
       </c>
-      <c r="K22" s="5" t="str">
+      <c r="K23" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0210=优先考虑速度</v>
       </c>
     </row>
-    <row r="23" spans="4:11">
-      <c r="D23" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="3" t="str">
+    <row r="24" spans="4:11">
+      <c r="D24" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="I24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0220=精度優先</v>
       </c>
-      <c r="J23" s="4" t="str">
+      <c r="J24" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0220=Prioritize accuracy</v>
       </c>
-      <c r="K23" s="5" t="str">
+      <c r="K24" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0220=优先考虑准确性</v>
       </c>
     </row>
-    <row r="24" spans="4:11">
-      <c r="D24" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="E24" s="2" t="s">
+    <row r="25" spans="4:11">
+      <c r="D25" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="I24" s="3" t="str">
+      <c r="F25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0230=言語</v>
       </c>
-      <c r="J24" s="4" t="str">
+      <c r="J25" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0230=Language</v>
       </c>
-      <c r="K24" s="5" t="str">
+      <c r="K25" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0230=语言</v>
       </c>
     </row>
-    <row r="25" spans="4:11">
-      <c r="D25" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="E25" s="2" t="s">
+    <row r="26" spans="4:11">
+      <c r="D26" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="I25" s="3" t="str">
+      <c r="F26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0240=作業用\nフォルダ</v>
       </c>
-      <c r="J25" s="4" t="str">
+      <c r="J26" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0240=Working directory</v>
       </c>
-      <c r="K25" s="5" t="str">
+      <c r="K26" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0240=工作\n文件夹</v>
       </c>
     </row>
-    <row r="26" spans="4:11">
-      <c r="D26" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="I26" s="3" t="str">
+    <row r="27" spans="4:11">
+      <c r="D27" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="I27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0250=詳細設定…</v>
       </c>
-      <c r="J26" s="4" t="str">
+      <c r="J27" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0250=Advanced Settings…</v>
       </c>
-      <c r="K26" s="5" t="str">
+      <c r="K27" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0250=详细设置...</v>
       </c>
     </row>
-    <row r="27" spans="4:11">
-      <c r="D27" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="E27" s="2" t="s">
+    <row r="28" spans="4:11">
+      <c r="D28" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I27" s="3" t="str">
+      <c r="F28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0260=開く</v>
       </c>
-      <c r="J27" s="4" t="str">
+      <c r="J28" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0260=Open</v>
       </c>
-      <c r="K27" s="5" t="str">
+      <c r="K28" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0260=打开</v>
       </c>
     </row>
-    <row r="28" spans="4:11">
-      <c r="D28" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="E28" s="2" t="s">
+    <row r="29" spans="4:11">
+      <c r="D29" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="I28" s="3" t="str">
+      <c r="F29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0270=変更...</v>
       </c>
-      <c r="J28" s="4" t="str">
+      <c r="J29" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0270=Change...</v>
       </c>
-      <c r="K28" s="5" t="str">
+      <c r="K29" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0270=改变...</v>
       </c>
     </row>
-    <row r="29" spans="4:11">
-      <c r="D29" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="E29" s="2" t="s">
+    <row r="30" spans="4:11">
+      <c r="D30" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I29" s="3" t="str">
+      <c r="F30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0280=削除...</v>
       </c>
-      <c r="J29" s="4" t="str">
+      <c r="J30" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0280=Delete...</v>
       </c>
-      <c r="K29" s="5" t="str">
+      <c r="K30" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0280=删除...</v>
       </c>
     </row>
-    <row r="30" spans="4:11">
-      <c r="D30" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F30" s="4" t="s">
+    <row r="31" spans="4:11">
+      <c r="D31" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="I30" s="3" t="str">
+      <c r="I31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0290=ブックパス：</v>
       </c>
-      <c r="J30" s="4" t="str">
+      <c r="J31" s="4" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">FXML_0290=Book Path : </v>
       </c>
-      <c r="K30" s="5" t="str">
+      <c r="K31" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0290=工作簿路径：</v>
       </c>
     </row>
-    <row r="31" spans="4:11">
-      <c r="D31" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E31" s="2" t="s">
+    <row r="32" spans="4:11">
+      <c r="D32" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="I31" s="3" t="str">
+      <c r="F32" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0300=シート名：</v>
       </c>
-      <c r="J31" s="4" t="str">
+      <c r="J32" s="4" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">FXML_0300=Sheet Name : </v>
       </c>
-      <c r="K31" s="5" t="str">
+      <c r="K32" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0300=工作表名称：</v>
       </c>
     </row>
-    <row r="32" spans="4:11">
-      <c r="D32" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="I32" s="3" t="str">
+    <row r="33" spans="4:11">
+      <c r="D33" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0310=フォルダパス：</v>
       </c>
-      <c r="J32" s="4" t="str">
+      <c r="J33" s="4" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">FXML_0310=Folder Path : </v>
       </c>
-      <c r="K32" s="5" t="str">
+      <c r="K33" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0310=文件夹路径：</v>
       </c>
     </row>
-    <row r="33" spans="4:11">
-      <c r="D33" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="I33" s="3" t="str">
+    <row r="34" spans="4:11">
+      <c r="D34" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="I34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0320=ファイルURL :</v>
       </c>
-      <c r="J33" s="4" t="str">
+      <c r="J34" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0320=File URL :</v>
       </c>
-      <c r="K33" s="5" t="str">
+      <c r="K34" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0320=文件URL :</v>
       </c>
     </row>
-    <row r="34" spans="4:11">
-      <c r="D34" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="I34" s="3" t="str">
+    <row r="35" spans="4:11">
+      <c r="D35" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I35" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0330=ファイル名 :</v>
       </c>
-      <c r="J34" s="4" t="str">
+      <c r="J35" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0330=File Name :</v>
       </c>
-      <c r="K34" s="5" t="str">
+      <c r="K35" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0330=文件名 :</v>
       </c>
     </row>
-    <row r="35" spans="4:11">
-      <c r="D35" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="I35" s="3" t="str">
+    <row r="36" spans="4:11">
+      <c r="D36" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="I36" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0340=リビジョン :</v>
       </c>
-      <c r="J35" s="4" t="str">
+      <c r="J36" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0340=Revision :</v>
       </c>
-      <c r="K35" s="5" t="str">
+      <c r="K36" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0340=版本 :</v>
       </c>
     </row>
-    <row r="36" spans="4:11">
-      <c r="D36" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="I36" s="3" t="str">
+    <row r="37" spans="4:11">
+      <c r="D37" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I37" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0350=Googleドライブ\n連携</v>
       </c>
-      <c r="J36" s="4" t="str">
+      <c r="J37" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0350=Connect\nGoogle Drive</v>
       </c>
-      <c r="K36" s="5" t="str">
+      <c r="K37" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0350=Google Drive\n关联</v>
       </c>
     </row>
-    <row r="37" spans="4:11">
-      <c r="D37" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="I37" s="3" t="str">
+    <row r="38" spans="4:11">
+      <c r="D38" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="I38" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0360=Googleドライブ\n連携解除</v>
       </c>
-      <c r="J37" s="4" t="str">
+      <c r="J38" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0360=Disconnect\nGoogle Drive</v>
       </c>
-      <c r="K37" s="5" t="str">
+      <c r="K38" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0360=Google Drive\n关联解除</v>
       </c>
     </row>
-    <row r="38" spans="4:11">
-      <c r="D38" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="I38" s="3" t="str">
+    <row r="39" spans="4:11">
+      <c r="D39" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="I39" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0370=更新確認</v>
       </c>
-      <c r="J38" s="4" t="str">
+      <c r="J39" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0370=Update Check</v>
       </c>
-      <c r="K38" s="5" t="str">
+      <c r="K39" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0370=更新确认</v>
       </c>
     </row>
-    <row r="39" spans="4:11">
-      <c r="D39" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="I39" s="3" t="str">
+    <row r="40" spans="4:11">
+      <c r="D40" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="I40" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0380=起動時に新規バージョンの有無を確認する</v>
       </c>
-      <c r="J39" s="4" t="str">
+      <c r="J40" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0380=Check for new versions at startup</v>
       </c>
-      <c r="K39" s="5" t="str">
+      <c r="K40" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0380=启动时检查是否有新版本</v>
       </c>
     </row>
-    <row r="40" spans="4:11">
-      <c r="D40" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="I40" s="3" t="str">
+    <row r="41" spans="4:11">
+      <c r="D41" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="I41" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0390=新規バージョンの有無を今すぐ確認する</v>
       </c>
-      <c r="J40" s="4" t="str">
+      <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0390=Check for new versions now</v>
       </c>
-      <c r="K40" s="5" t="str">
+      <c r="K41" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0390=立即检查是否有新版本</v>
       </c>
     </row>
-    <row r="41" spans="4:11">
-      <c r="D41" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="I41" s="3" t="str">
+    <row r="42" spans="4:11">
+      <c r="D42" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="I42" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0400=設定管理</v>
       </c>
-      <c r="J41" s="4" t="str">
+      <c r="J42" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0400=Settings\nManagement</v>
       </c>
-      <c r="K41" s="5" t="str">
+      <c r="K42" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0400=设置管理</v>
       </c>
     </row>
-    <row r="42" spans="4:11">
-      <c r="D42" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="I42" s="3" t="str">
+    <row r="43" spans="4:11">
+      <c r="D43" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="I43" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0410=設定ファイルを表示する</v>
       </c>
-      <c r="J42" s="4" t="str">
+      <c r="J43" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0410=Display the configuration file</v>
       </c>
-      <c r="K42" s="5" t="str">
+      <c r="K43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0410=显示配置文件</v>
       </c>
     </row>
-    <row r="43" spans="4:11">
-      <c r="D43" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="I43" s="3" t="str">
+    <row r="44" spans="4:11">
+      <c r="D44" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="I44" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0420=設定をリセットする…</v>
       </c>
-      <c r="J43" s="4" t="str">
+      <c r="J44" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0420=Reset settings…</v>
       </c>
-      <c r="K43" s="5" t="str">
+      <c r="K44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0420=重置设置…</v>
       </c>
     </row>
-    <row r="44" spans="4:11">
-      <c r="D44" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="I44" s="3" t="str">
+    <row r="45" spans="4:11">
+      <c r="D45" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="I45" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0430=選択されたファイルをGoogleドライブからダウンロードしてこのPCの下記リンク先フォルダに保存しました。\nPC上に保存された状態が好ましくない場合は、比較処理が終わり次第、ご自身で削除してください。</v>
       </c>
-      <c r="J44" s="4" t="str">
+      <c r="J45" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0430=The selected file has been downloaded from Google Drive and saved to the folder linked below on this PC.\nIf you prefer not to keep the file stored on your PC, please delete it manually after the comparison process is complete.</v>
       </c>
-      <c r="K44" s="5" t="str">
+      <c r="K45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0430=已从Google云端硬盘下载所选文件，并保存到本机下方链接的文件夹中。\n如果您不希望文件保存在电脑上，请在比较处理完成后自行删除。</v>
       </c>
     </row>
-    <row r="45" spans="4:11">
-      <c r="D45" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="I45" s="3" t="str">
+    <row r="46" spans="4:11">
+      <c r="D46" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="I46" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0440=次回以降、このメッセージを表示しない</v>
       </c>
-      <c r="J45" s="4" t="str">
+      <c r="J46" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0440=Don't show this message again</v>
       </c>
-      <c r="K45" s="5" t="str">
+      <c r="K46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0440=不再显示此消息</v>
       </c>
     </row>
-    <row r="46" spans="4:11">
-      <c r="D46" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="I46" s="3" t="str">
+    <row r="47" spans="4:11">
+      <c r="D47" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="I47" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0450=その他設定</v>
       </c>
-      <c r="J46" s="4" t="str">
+      <c r="J47" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0450=Other settings</v>
       </c>
-      <c r="K46" s="5" t="str">
+      <c r="K47" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0450=其他设置</v>
       </c>
     </row>
-    <row r="47" spans="4:11">
-      <c r="D47" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="I47" s="3" t="str">
+    <row r="48" spans="4:11">
+      <c r="D48" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="I48" s="3" t="str">
         <f t="shared" si="0"/>
         <v>FXML_0460=エラー情報を自動でサーバに送信する</v>
       </c>
-      <c r="J47" s="4" t="str">
+      <c r="J48" s="4" t="str">
         <f t="shared" si="1"/>
         <v>FXML_0460=Automatically send error information to the server</v>
       </c>
-      <c r="K47" s="5" t="str">
+      <c r="K48" s="5" t="str">
         <f t="shared" si="2"/>
         <v>FXML_0460=自动发送错误信息到服务器</v>
       </c>
     </row>
-    <row r="48" spans="4:11">
-      <c r="E48" s="2"/>
-      <c r="I48" s="3" t="str">
+    <row r="49" spans="3:11">
+      <c r="E49" s="2"/>
+      <c r="I49" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J48" s="4" t="str">
+      <c r="J49" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K48" s="5" t="str">
+      <c r="K49" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:11">
-      <c r="C49" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E49 &amp; " */ " &amp; D49 &amp; ","</f>
+    <row r="50" spans="3:11">
+      <c r="C50" s="1" t="str">
+        <f t="shared" ref="C50:C83" si="6" xml:space="preserve"> "/** " &amp; E50 &amp; " */ " &amp; D50 &amp; ","</f>
         <v>/** 方眼Diff */ APP_0010,</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D50" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="I49" s="3" t="str">
+      <c r="F50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I50" s="3" t="str">
         <f t="shared" si="0"/>
         <v>APP_0010=方眼Diff</v>
       </c>
-      <c r="J49" s="4" t="str">
+      <c r="J50" s="4" t="str">
         <f t="shared" si="1"/>
         <v>APP_0010=HoganDiff (方眼Diff)</v>
       </c>
-      <c r="K49" s="5" t="str">
+      <c r="K50" s="5" t="str">
         <f t="shared" si="2"/>
         <v>APP_0010=方眼Diff</v>
       </c>
     </row>
-    <row r="50" spans="3:11">
-      <c r="C50" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E50 &amp; " */ " &amp; D50 &amp; ","</f>
+    <row r="51" spans="3:11">
+      <c r="C51" s="1" t="str">
+        <f t="shared" si="6"/>
         <v>/** 設定の保存に失敗しました。 */ APP_0020,</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="D51" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="I50" s="3" t="str">
+      <c r="F51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I51" s="3" t="str">
         <f t="shared" si="0"/>
         <v>APP_0020=設定の保存に失敗しました。</v>
       </c>
-      <c r="J50" s="4" t="str">
+      <c r="J51" s="4" t="str">
         <f t="shared" si="1"/>
         <v>APP_0020=Failed to save settings.</v>
       </c>
-      <c r="K50" s="5" t="str">
+      <c r="K51" s="5" t="str">
         <f t="shared" si="2"/>
         <v>APP_0020=保存设置失败。</v>
       </c>
     </row>
-    <row r="51" spans="3:11">
-      <c r="C51" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E51 &amp; " */ " &amp; D51 &amp; ","</f>
-        <v>/** 比較結果テキストを保存しています... */ APP_0030,</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="I51" s="3" t="str">
+    <row r="52" spans="3:11">
+      <c r="C52" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポート（テキスト）を保存しています... */ APP_0030,</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I52" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0030=比較結果テキストを保存しています...</v>
-      </c>
-      <c r="J51" s="4" t="str">
+        <v>APP_0030=比較結果レポート（テキスト）を保存しています...</v>
+      </c>
+      <c r="J52" s="4" t="str">
         <f t="shared" si="1"/>
         <v>APP_0030=Saving result text...</v>
       </c>
-      <c r="K51" s="5" t="str">
+      <c r="K52" s="5" t="str">
         <f t="shared" si="2"/>
         <v>APP_0030=存储比较结果文本...</v>
       </c>
     </row>
-    <row r="52" spans="3:11">
-      <c r="C52" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E52 &amp; " */ " &amp; D52 &amp; ","</f>
-        <v>/** 比較結果テキストの保存と表示に失敗しました。 */ APP_0040,</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="I52" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>APP_0040=比較結果テキストの保存と表示に失敗しました。</v>
-      </c>
-      <c r="J52" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>APP_0040=Failed to save or open result text.</v>
-      </c>
-      <c r="K52" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>APP_0040=保存和显示比较结果文本失败。</v>
-      </c>
-    </row>
     <row r="53" spans="3:11">
       <c r="C53" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E53 &amp; " */ " &amp; D53 &amp; ","</f>
-        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポート（テキスト）の保存に失敗しました。 */ APP_0040,</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>41</v>
+        <v>596</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>237</v>
+        <v>597</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>598</v>
       </c>
       <c r="I53" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
+        <v>APP_0040=比較結果レポート（テキスト）の保存に失敗しました。</v>
       </c>
       <c r="J53" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0050=Painting and saving result book(s)...</v>
+        <v>APP_0040=Failed to save result text.</v>
       </c>
       <c r="K53" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0050=着色和存储在工作簿...</v>
+        <v>APP_0040=对比结果文本保存失败。</v>
       </c>
     </row>
     <row r="54" spans="3:11">
       <c r="C54" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E54 &amp; " */ " &amp; D54 &amp; ","</f>
-        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
+        <f t="shared" ref="C54:C55" si="7" xml:space="preserve"> "/** " &amp; E54 &amp; " */ " &amp; D54 &amp; ","</f>
+        <v>/** 比較結果レポート（テキスト）を表示しています... */ APP_0041,</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>434</v>
+        <v>600</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>42</v>
+        <v>601</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>238</v>
+        <v>603</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>605</v>
       </c>
       <c r="I54" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
+        <v>APP_0041=比較結果レポート（テキスト）を表示しています...</v>
       </c>
       <c r="J54" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0060=Failed to paint or save result book(s).</v>
+        <v>APP_0041=Opening result text...</v>
       </c>
       <c r="K54" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0060=着色和保存工作簿失败。</v>
+        <v>APP_0041=显示比较结果文本...</v>
       </c>
     </row>
     <row r="55" spans="3:11">
       <c r="C55" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E55 &amp; " */ " &amp; D55 &amp; ","</f>
-        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
+        <f t="shared" si="7"/>
+        <v>/** 比較結果レポート（テキスト）の表示に失敗しました。 */ APP_0042,</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>435</v>
+        <v>599</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>43</v>
+        <v>602</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>239</v>
+        <v>604</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>606</v>
       </c>
       <c r="I55" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
+        <v>APP_0042=比較結果レポート（テキスト）の表示に失敗しました。</v>
       </c>
       <c r="J55" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0070=Opening result book(s)...</v>
+        <v>APP_0042=Failed to open result text.</v>
       </c>
       <c r="K55" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0070=显示比较结果的工作簿...</v>
+        <v>APP_0042=显示比较结果文本失败。</v>
       </c>
     </row>
     <row r="56" spans="3:11">
       <c r="C56" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E56 &amp; " */ " &amp; D56 &amp; ","</f>
-        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
+        <f t="shared" si="6"/>
+        <v>/** Excelブックに比較結果の色を付けて保存しています... */ APP_0050,</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>240</v>
+        <v>81</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="I56" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0080=Excelブックの表示に失敗しました。</v>
+        <v>APP_0050=Excelブックに比較結果の色を付けて保存しています...</v>
       </c>
       <c r="J56" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0080=Failed to open result book(s).</v>
+        <v>APP_0050=Painting and saving result book(s)...</v>
       </c>
       <c r="K56" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0080=显示工作簿失败。</v>
+        <v>APP_0050=着色和存储在工作簿...</v>
       </c>
     </row>
     <row r="57" spans="3:11">
       <c r="C57" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E57 &amp; " */ " &amp; D57 &amp; ","</f>
-        <v>/** Excelブック%sの着色・保存に失敗しました。 */ APP_0090,</v>
+        <f t="shared" si="6"/>
+        <v>/** Excelブックの着色・保存に失敗しました。 */ APP_0060,</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>593</v>
+        <v>40</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>597</v>
+        <v>82</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="I57" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0090=Excelブック%sの着色・保存に失敗しました。</v>
+        <v>APP_0060=Excelブックの着色・保存に失敗しました。</v>
       </c>
       <c r="J57" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0090=Failed to paint or save result book %s.</v>
+        <v>APP_0060=Failed to paint or save result book(s).</v>
       </c>
       <c r="K57" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0090=工作簿%s的着色和保存失败。</v>
+        <v>APP_0060=着色和保存工作簿失败。</v>
       </c>
     </row>
     <row r="58" spans="3:11">
       <c r="C58" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E58 &amp; " */ " &amp; D58 &amp; ","</f>
-        <v>/** 処理が完了しました。 */ APP_0110,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較結果のExcelブックを表示しています... */ APP_0070,</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>241</v>
+        <v>83</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="I58" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0110=処理が完了しました。</v>
+        <v>APP_0070=比較結果のExcelブックを表示しています...</v>
       </c>
       <c r="J58" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0110=Process completed.</v>
+        <v>APP_0070=Opening result book(s)...</v>
       </c>
       <c r="K58" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0110=过程完成。</v>
+        <v>APP_0070=显示比较结果的工作簿...</v>
       </c>
     </row>
     <row r="59" spans="3:11">
       <c r="C59" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E59 &amp; " */ " &amp; D59 &amp; ","</f>
-        <v>/** ★失敗しました */ APP_0120,</v>
+        <f t="shared" si="6"/>
+        <v>/** Excelブックの表示に失敗しました。 */ APP_0080,</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>125</v>
+        <v>425</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>242</v>
+        <v>84</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="I59" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0120=★失敗しました</v>
+        <v>APP_0080=Excelブックの表示に失敗しました。</v>
       </c>
       <c r="J59" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0120=★Failed</v>
+        <v>APP_0080=Failed to open result book(s).</v>
       </c>
       <c r="K59" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0120=★失败</v>
+        <v>APP_0080=显示工作簿失败。</v>
       </c>
     </row>
     <row r="60" spans="3:11">
       <c r="C60" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E60 &amp; " */ " &amp; D60 &amp; ","</f>
-        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
+        <f t="shared" si="6"/>
+        <v>/** Excelブック%sの着色・保存に失敗しました。 */ APP_0090,</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>163</v>
+        <v>426</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>582</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>179</v>
+        <v>583</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>586</v>
       </c>
       <c r="I60" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0130=(比較対象ファイルなし)</v>
+        <v>APP_0090=Excelブック%sの着色・保存に失敗しました。</v>
       </c>
       <c r="J60" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0130=(No files to compare)</v>
+        <v>APP_0090=Failed to paint or save result book %s.</v>
       </c>
       <c r="K60" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0130=(没有可比较的文件)</v>
+        <v>APP_0090=工作簿%s的着色和保存失败。</v>
       </c>
     </row>
     <row r="61" spans="3:11">
       <c r="C61" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E61 &amp; " */ " &amp; D61 &amp; ","</f>
-        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
+        <f t="shared" si="6"/>
+        <v>/** 処理が完了しました。 */ APP_0110,</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>266</v>
+        <v>427</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>339</v>
+        <v>85</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="I61" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <v>APP_0110=処理が完了しました。</v>
       </c>
       <c r="J61" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <v>APP_0110=Process completed.</v>
       </c>
       <c r="K61" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
+        <v>APP_0110=过程完成。</v>
       </c>
     </row>
     <row r="62" spans="3:11">
       <c r="C62" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E62 &amp; " */ " &amp; D62 &amp; ","</f>
-        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
+        <f t="shared" si="6"/>
+        <v>/** ★失敗しました */ APP_0120,</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>29</v>
+        <v>428</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>107</v>
+        <v>134</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="I62" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0150=予期せぬ例外が発生しました。</v>
+        <v>APP_0120=★失敗しました</v>
       </c>
       <c r="J62" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0150=Unexpected exception occurred.</v>
+        <v>APP_0120=★Failed</v>
       </c>
       <c r="K62" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0150=意外的例外。</v>
+        <v>APP_0120=★失败</v>
       </c>
     </row>
     <row r="63" spans="3:11">
       <c r="C63" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E63 &amp; " */ " &amp; D63 &amp; ","</f>
-        <v>/** 比較実行日時： */ APP_0160,</v>
+        <f t="shared" si="6"/>
+        <v>/** (比較対象ファイルなし) */ APP_0130,</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>296</v>
+        <v>160</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>297</v>
+        <v>175</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="I63" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0160=比較実行日時：</v>
+        <v>APP_0130=(比較対象ファイルなし)</v>
       </c>
       <c r="J63" s="4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">APP_0160=Exec datetime : </v>
+        <v>APP_0130=(No files to compare)</v>
       </c>
       <c r="K63" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0160=执行日期和时间：</v>
+        <v>APP_0130=(没有可比较的文件)</v>
       </c>
     </row>
     <row r="64" spans="3:11">
       <c r="C64" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E64 &amp; " */ " &amp; D64 &amp; ","</f>
-        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
+        <f t="shared" si="6"/>
+        <v>/** メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3 */ APP_0140,</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>34</v>
+        <v>430</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>243</v>
+        <v>263</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>328</v>
       </c>
       <c r="I64" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0170=ブック同士の比較を開始します。</v>
+        <v>APP_0140=メモリ不足のため処理が失敗しました。\n割り当てメモリ量を増やして再度お試しください。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="J64" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0170=Starting comparing books.</v>
+        <v>APP_0140=Processing failed due to insufficient memory.\nPlease increase the amount of allocated memory and try again.\nSee: https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
       <c r="K64" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0170=开始互相比较工作簿。</v>
+        <v>APP_0140=由于内存不足，处理失败。\n请增加分配的内存量，然后重试。\n参考：https://hogandiff.hotchpotch.xyz/faq/#toc3</v>
       </c>
     </row>
     <row r="65" spans="3:11">
       <c r="C65" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E65 &amp; " */ " &amp; D65 &amp; ","</f>
-        <v>/** シートを比較しています... */ APP_0180,</v>
+        <f t="shared" si="6"/>
+        <v>/** 予期せぬ例外が発生しました。 */ APP_0150,</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>244</v>
+        <v>72</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="I65" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0180=シートを比較しています...</v>
+        <v>APP_0150=予期せぬ例外が発生しました。</v>
       </c>
       <c r="J65" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0180=Comparing sheets...</v>
+        <v>APP_0150=Unexpected exception occurred.</v>
       </c>
       <c r="K65" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0180=比较工作表...</v>
+        <v>APP_0150=意外的例外。</v>
       </c>
     </row>
     <row r="66" spans="3:11">
       <c r="C66" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E66 &amp; " */ " &amp; D66 &amp; ","</f>
-        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較実行日時： */ APP_0160,</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>38</v>
+        <v>432</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>245</v>
+        <v>297</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>290</v>
       </c>
       <c r="I66" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>APP_0190=シートの比較に失敗しました。</v>
+        <v>APP_0160=比較実行日時：</v>
       </c>
       <c r="J66" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>APP_0190=Failed to compare sheets.</v>
+        <v xml:space="preserve">APP_0160=Exec datetime : </v>
       </c>
       <c r="K66" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>APP_0190=工作表比较失败。</v>
+        <v>APP_0160=执行日期和时间：</v>
       </c>
     </row>
     <row r="67" spans="3:11">
       <c r="C67" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E67 &amp; " */ " &amp; D67 &amp; ","</f>
-        <v>/** 比較結果レポートを保存しています... */ APP_0200,</v>
+        <f t="shared" si="6"/>
+        <v>/** ブック同士の比較を開始します。 */ APP_0170,</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>307</v>
+        <v>129</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="I67" s="3" t="str">
-        <f t="shared" ref="I67:I130" si="3" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; E67)</f>
-        <v>APP_0200=比較結果レポートを保存しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0170=ブック同士の比較を開始します。</v>
       </c>
       <c r="J67" s="4" t="str">
-        <f t="shared" ref="J67:J130" si="4" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; F67)</f>
-        <v>APP_0200=Saving result report...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0170=Starting comparing books.</v>
       </c>
       <c r="K67" s="5" t="str">
-        <f t="shared" ref="K67:K130" si="5" xml:space="preserve"> IF($D67="", "", $D67 &amp; "=" &amp; G67)</f>
-        <v>APP_0200=保存比较结果报告...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0170=开始互相比较工作簿。</v>
       </c>
     </row>
     <row r="68" spans="3:11">
       <c r="C68" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E68 &amp; " */ " &amp; D68 &amp; ","</f>
-        <v>/** 比較結果レポートの保存に失敗しました。 */ APP_0210,</v>
+        <f t="shared" si="6"/>
+        <v>/** シートを比較しています... */ APP_0180,</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>308</v>
+        <v>37</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>310</v>
+        <v>78</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="I68" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0210=比較結果レポートの保存に失敗しました。</v>
+        <f t="shared" si="0"/>
+        <v>APP_0180=シートを比較しています...</v>
       </c>
       <c r="J68" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0210=Failed to save result report.</v>
+        <f t="shared" si="1"/>
+        <v>APP_0180=Comparing sheets...</v>
       </c>
       <c r="K68" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0210=保存比较结果报告失败。</v>
+        <f t="shared" si="2"/>
+        <v>APP_0180=比较工作表...</v>
       </c>
     </row>
     <row r="69" spans="3:11">
       <c r="C69" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E69 &amp; " */ " &amp; D69 &amp; ","</f>
-        <v>/** 比較結果レポートを表示しています... */ APP_0220,</v>
+        <f t="shared" si="6"/>
+        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>311</v>
+        <v>38</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>313</v>
+        <v>79</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="I69" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0220=比較結果レポートを表示しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0190=シートの比較に失敗しました。</v>
       </c>
       <c r="J69" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0220=Opening result report...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0190=Failed to compare sheets.</v>
       </c>
       <c r="K69" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0220=显示比较结果报告...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0190=工作表比较失败。</v>
       </c>
     </row>
     <row r="70" spans="3:11">
       <c r="C70" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E70 &amp; " */ " &amp; D70 &amp; ","</f>
-        <v>/** 比較結果レポートの表示に失敗しました。 */ APP_0230,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポート（Excel）を保存しています... */ APP_0200,</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>316</v>
+        <v>591</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>314</v>
+        <v>298</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>299</v>
       </c>
       <c r="I70" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0230=比較結果レポートの表示に失敗しました。</v>
+        <f t="shared" ref="I70:I133" si="8" xml:space="preserve"> IF($D70="", "", $D70 &amp; "=" &amp; E70)</f>
+        <v>APP_0200=比較結果レポート（Excel）を保存しています...</v>
       </c>
       <c r="J70" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0230=Failed to open result report.</v>
+        <f t="shared" ref="J70:J133" si="9" xml:space="preserve"> IF($D70="", "", $D70 &amp; "=" &amp; F70)</f>
+        <v>APP_0200=Saving result report...</v>
       </c>
       <c r="K70" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0230=显示比较结果报告失败。</v>
+        <f t="shared" ref="K70:K133" si="10" xml:space="preserve"> IF($D70="", "", $D70 &amp; "=" &amp; G70)</f>
+        <v>APP_0200=保存比较结果报告...</v>
       </c>
     </row>
     <row r="71" spans="3:11">
       <c r="C71" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E71 &amp; " */ " &amp; D71 &amp; ","</f>
-        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポート（Excel）の保存に失敗しました。 */ APP_0210,</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>122</v>
+        <v>437</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>246</v>
+        <v>300</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>301</v>
       </c>
       <c r="I71" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0240=フォルダ同士の比較を開始します。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0210=比較結果レポート（Excel）の保存に失敗しました。</v>
       </c>
       <c r="J71" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0240=Starting comparing folders.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0210=Failed to save result report.</v>
       </c>
       <c r="K71" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0240=开始互相比较文件夹。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0210=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="72" spans="3:11">
       <c r="C72" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E72 &amp; " */ " &amp; D72 &amp; ","</f>
-        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポート（Excel）を表示しています... */ APP_0220,</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>123</v>
+        <v>438</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>138</v>
+        <v>302</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="I72" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0220=比較結果レポート（Excel）を表示しています...</v>
       </c>
       <c r="J72" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0250=Failed to create output directory.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0220=Opening result report...</v>
       </c>
       <c r="K72" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0250=创建输出目的地文件夹失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0220=显示比较结果报告...</v>
       </c>
     </row>
     <row r="73" spans="3:11">
       <c r="C73" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E73 &amp; " */ " &amp; D73 &amp; ","</f>
-        <v>/** Excelブックを比較しています... */ APP_0260,</v>
+        <f t="shared" si="6"/>
+        <v>/** 比較結果レポート（Excel）の表示に失敗しました。 */ APP_0230,</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>124</v>
+        <v>439</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>594</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>247</v>
+        <v>305</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="I73" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0260=Excelブックを比較しています...</v>
+        <f t="shared" si="8"/>
+        <v>APP_0230=比較結果レポート（Excel）の表示に失敗しました。</v>
       </c>
       <c r="J73" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0260=Comparing books...</v>
+        <f t="shared" si="9"/>
+        <v>APP_0230=Failed to open result report.</v>
       </c>
       <c r="K73" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0260=比较工作簿...</v>
+        <f t="shared" si="10"/>
+        <v>APP_0230=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="74" spans="3:11">
       <c r="C74" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E74 &amp; " */ " &amp; D74 &amp; ","</f>
-        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
+        <f t="shared" si="6"/>
+        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>271</v>
+        <v>119</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>269</v>
+        <v>131</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="I74" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0280=フォルダの比較に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0240=フォルダ同士の比較を開始します。</v>
       </c>
       <c r="J74" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0280=Failed to compare folders.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0240=Starting comparing folders.</v>
       </c>
       <c r="K74" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0280=文件夹比较失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0240=开始互相比较文件夹。</v>
       </c>
     </row>
     <row r="75" spans="3:11">
       <c r="C75" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E75 &amp; " */ " &amp; D75 &amp; ","</f>
-        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
+        <f t="shared" si="6"/>
+        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>35</v>
+        <v>441</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>248</v>
+        <v>132</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="I75" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0290=シート同士の比較を開始します。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
       </c>
       <c r="J75" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0290=Starting comparing sheets.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0250=Failed to create output directory.</v>
       </c>
       <c r="K75" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0290=开始相互比较工作表。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0250=创建输出目的地文件夹失败。</v>
       </c>
     </row>
     <row r="76" spans="3:11">
       <c r="C76" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E76 &amp; " */ " &amp; D76 &amp; ","</f>
-        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
+        <f t="shared" si="6"/>
+        <v>/** Excelブックを比較しています... */ APP_0260,</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>249</v>
+        <v>133</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="I76" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0260=Excelブックを比較しています...</v>
       </c>
       <c r="J76" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0320=Starting comparing folder trees.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0260=Comparing books...</v>
       </c>
       <c r="K76" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0320=开始互相比较文件夹树。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0260=比较工作簿...</v>
       </c>
     </row>
     <row r="77" spans="3:11">
       <c r="C77" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E77 &amp; " */ " &amp; D77 &amp; ","</f>
-        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
+        <f t="shared" si="6"/>
+        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>164</v>
+        <v>267</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>250</v>
+        <v>264</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="I77" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0330=フォルダツリーを比較しています...</v>
+        <f t="shared" si="8"/>
+        <v>APP_0280=フォルダの比較に失敗しました。</v>
       </c>
       <c r="J77" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0330=Comparing folders...</v>
+        <f t="shared" si="9"/>
+        <v>APP_0280=Failed to compare folders.</v>
       </c>
       <c r="K77" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0330=比较文件夹...</v>
+        <f t="shared" si="10"/>
+        <v>APP_0280=文件夹比较失败。</v>
       </c>
     </row>
     <row r="78" spans="3:11">
       <c r="C78" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E78 &amp; " */ " &amp; D78 &amp; ","</f>
-        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
+        <f t="shared" si="6"/>
+        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>270</v>
+        <v>444</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>269</v>
+        <v>130</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="I78" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0290=シート同士の比較を開始します。</v>
       </c>
       <c r="J78" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0390=Failed to compare folder trees.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0290=Starting comparing sheets.</v>
       </c>
       <c r="K78" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0390=文件夹比较失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0290=开始相互比较工作表。</v>
       </c>
     </row>
     <row r="79" spans="3:11">
       <c r="C79" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E79 &amp; " */ " &amp; D79 &amp; ","</f>
-        <v>/** (比較相手なし) */ APP_0400,</v>
+        <f t="shared" si="6"/>
+        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>46</v>
+        <v>445</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>251</v>
+        <v>165</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="I79" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0400=(比較相手なし)</v>
+        <f t="shared" si="8"/>
+        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
       </c>
       <c r="J79" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0400=(no opponent)</v>
+        <f t="shared" si="9"/>
+        <v>APP_0320=Starting comparing folder trees.</v>
       </c>
       <c r="K79" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0400=(没有对比)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0320=开始互相比较文件夹树。</v>
       </c>
     </row>
     <row r="80" spans="3:11">
       <c r="C80" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E80 &amp; " */ " &amp; D80 &amp; ","</f>
-        <v>/** (差分なし) */ APP_0410,</v>
+        <f t="shared" si="6"/>
+        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>47</v>
+        <v>446</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>252</v>
+        <v>167</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="I80" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0410=(差分なし)</v>
+        <f t="shared" si="8"/>
+        <v>APP_0330=フォルダツリーを比較しています...</v>
       </c>
       <c r="J80" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0410=(no diffs)</v>
+        <f t="shared" si="9"/>
+        <v>APP_0330=Comparing folders...</v>
       </c>
       <c r="K80" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0410=(没有区别)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0330=比较文件夹...</v>
       </c>
     </row>
     <row r="81" spans="3:11">
       <c r="C81" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E81 &amp; " */ " &amp; D81 &amp; ","</f>
-        <v>/** 差異発生%dシート */ APP_0420,</v>
+        <f t="shared" si="6"/>
+        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>253</v>
+        <v>268</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="I81" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0420=差異発生%dシート</v>
+        <f t="shared" si="8"/>
+        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
       </c>
       <c r="J81" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0420=diff sheets:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0390=Failed to compare folder trees.</v>
       </c>
       <c r="K81" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0420=差异工作表%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0390=文件夹比较失败。</v>
       </c>
     </row>
     <row r="82" spans="3:11">
       <c r="C82" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E82 &amp; " */ " &amp; D82 &amp; ","</f>
-        <v>/** 余剰%dシート */ APP_0430,</v>
+        <f t="shared" si="6"/>
+        <v>/** (比較相手なし) */ APP_0400,</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>127</v>
+        <v>448</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>142</v>
+        <v>86</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="I82" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0430=余剰%dシート</v>
+        <f t="shared" si="8"/>
+        <v>APP_0400=(比較相手なし)</v>
       </c>
       <c r="J82" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0430=redundant sheets:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0400=(no opponent)</v>
       </c>
       <c r="K82" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0430=冗余工作表%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0400=(没有对比)</v>
       </c>
     </row>
     <row r="83" spans="3:11">
       <c r="C83" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E83 &amp; " */ " &amp; D83 &amp; ","</f>
-        <v>/** ブック%s： */ APP_0440,</v>
+        <f t="shared" si="6"/>
+        <v>/** (差分なし) */ APP_0410,</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>295</v>
+        <v>449</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>193</v>
+        <v>87</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="I83" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0440=ブック%s：</v>
+        <f t="shared" si="8"/>
+        <v>APP_0410=(差分なし)</v>
       </c>
       <c r="J83" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0440=Book %s : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0410=(no diffs)</v>
       </c>
       <c r="K83" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0440=工作簿%s：</v>
+        <f t="shared" si="10"/>
+        <v>APP_0410=(没有区别)</v>
       </c>
     </row>
     <row r="84" spans="3:11">
       <c r="C84" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E84 &amp; " */ " &amp; D84 &amp; ","</f>
-        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
+        <f t="shared" ref="C84:C115" si="11" xml:space="preserve"> "/** " &amp; E84 &amp; " */ " &amp; D84 &amp; ","</f>
+        <v>/** 差異発生%dシート */ APP_0420,</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>48</v>
+        <v>450</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>108</v>
+        <v>136</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="I84" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
+        <f t="shared" si="8"/>
+        <v>APP_0420=差異発生%dシート</v>
       </c>
       <c r="J84" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
+        <f t="shared" si="9"/>
+        <v>APP_0420=diff sheets:%d</v>
       </c>
       <c r="K84" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
+        <f t="shared" si="10"/>
+        <v>APP_0420=差异工作表%d</v>
       </c>
     </row>
     <row r="85" spans="3:11">
       <c r="C85" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E85 &amp; " */ " &amp; D85 &amp; ","</f>
-        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
+        <f t="shared" si="11"/>
+        <v>/** 余剰%dシート */ APP_0430,</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>49</v>
+        <v>451</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>254</v>
+        <v>137</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="I85" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
+        <f t="shared" si="8"/>
+        <v>APP_0430=余剰%dシート</v>
       </c>
       <c r="J85" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
+        <f t="shared" si="9"/>
+        <v>APP_0430=redundant sheets:%d</v>
       </c>
       <c r="K85" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
+        <f t="shared" si="10"/>
+        <v>APP_0430=冗余工作表%d</v>
       </c>
     </row>
     <row r="86" spans="3:11">
       <c r="C86" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E86 &amp; " */ " &amp; D86 &amp; ","</f>
-        <v>/** フォルダ%s :  */ APP_0480,</v>
+        <f t="shared" si="11"/>
+        <v>/** ブック%s： */ APP_0440,</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>143</v>
+        <v>288</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>138</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="I86" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
+        <f t="shared" si="8"/>
+        <v>APP_0440=ブック%s：</v>
       </c>
       <c r="J86" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0480=Folder %s : </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0440=Book %s : </v>
       </c>
       <c r="K86" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0480=文件夹%s : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0440=工作簿%s：</v>
       </c>
     </row>
     <row r="87" spans="3:11">
       <c r="C87" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E87 &amp; " */ " &amp; D87 &amp; ","</f>
-        <v>/** 差異発生%dブック */ APP_0530,</v>
+        <f t="shared" si="11"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>165</v>
+        <v>453</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>256</v>
+        <v>88</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="I87" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0530=差異発生%dブック</v>
+        <f t="shared" si="8"/>
+        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="J87" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0530=diff books:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="K87" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0530=差异工作簿%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="88" spans="3:11">
       <c r="C88" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E88 &amp; " */ " &amp; D88 &amp; ","</f>
-        <v>/** 余剰%dブック */ APP_0540,</v>
+        <f t="shared" si="11"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>166</v>
+        <v>454</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>173</v>
+        <v>89</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="I88" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0540=余剰%dブック</v>
+        <f t="shared" si="8"/>
+        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
       </c>
       <c r="J88" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0540=redundant books:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
       </c>
       <c r="K88" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0540=冗余工作簿%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="89" spans="3:11">
       <c r="C89" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E89 &amp; " */ " &amp; D89 &amp; ","</f>
-        <v>/** 比較失敗%dブック */ APP_0550,</v>
+        <f t="shared" si="11"/>
+        <v>/** フォルダ%s :  */ APP_0480,</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>175</v>
+        <v>141</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="I89" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0550=比較失敗%dブック</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
       </c>
       <c r="J89" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0550=failed books:%d</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0480=Folder %s : </v>
       </c>
       <c r="K89" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0550=失败工作簿%d</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0480=文件夹%s : </v>
       </c>
     </row>
     <row r="90" spans="3:11">
       <c r="C90" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E90 &amp; " */ " &amp; D90 &amp; ","</f>
-        <v>/** 作業用フォルダ： */ APP_0580,</v>
+        <f t="shared" si="11"/>
+        <v>/** 差異発生%dブック */ APP_0530,</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>189</v>
+        <v>168</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="I90" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0580=作業用フォルダ：</v>
+        <f t="shared" si="8"/>
+        <v>APP_0530=差異発生%dブック</v>
       </c>
       <c r="J90" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0580=Working dir : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0530=diff books:%d</v>
       </c>
       <c r="K90" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0580=工作文件夹：</v>
+        <f t="shared" si="10"/>
+        <v>APP_0530=差异工作簿%d</v>
       </c>
     </row>
     <row r="91" spans="3:11">
       <c r="C91" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E91 &amp; " */ " &amp; D91 &amp; ","</f>
-        <v>/** 差分なし */ APP_0600,</v>
+        <f t="shared" si="11"/>
+        <v>/** 余剰%dブック */ APP_0540,</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>298</v>
+        <v>163</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>301</v>
+        <v>169</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="I91" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0600=差分なし</v>
+        <f t="shared" si="8"/>
+        <v>APP_0540=余剰%dブック</v>
       </c>
       <c r="J91" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0600=No Diffs</v>
+        <f t="shared" si="9"/>
+        <v>APP_0540=redundant books:%d</v>
       </c>
       <c r="K91" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0600=没有区别</v>
+        <f t="shared" si="10"/>
+        <v>APP_0540=冗余工作簿%d</v>
       </c>
     </row>
     <row r="92" spans="3:11">
       <c r="C92" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E92 &amp; " */ " &amp; D92 &amp; ","</f>
-        <v>/** 比較失敗 */ APP_0610,</v>
+        <f t="shared" si="11"/>
+        <v>/** 比較失敗%dブック */ APP_0550,</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>299</v>
+        <v>164</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>302</v>
+        <v>171</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="I92" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0610=比較失敗</v>
+        <f t="shared" si="8"/>
+        <v>APP_0550=比較失敗%dブック</v>
       </c>
       <c r="J92" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0610=Comparison Failed</v>
+        <f t="shared" si="9"/>
+        <v>APP_0550=failed books:%d</v>
       </c>
       <c r="K92" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0610=比较失败</v>
+        <f t="shared" si="10"/>
+        <v>APP_0550=失败工作簿%d</v>
       </c>
     </row>
     <row r="93" spans="3:11">
       <c r="C93" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E93 &amp; " */ " &amp; D93 &amp; ","</f>
-        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
+        <f t="shared" si="11"/>
+        <v>/** 作業用フォルダ： */ APP_0580,</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>317</v>
+        <v>178</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>325</v>
+        <v>286</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="I93" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0620=余剰行（A: %d, B: %d）</v>
+        <f t="shared" si="8"/>
+        <v>APP_0580=作業用フォルダ：</v>
       </c>
       <c r="J93" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0580=Working dir : </v>
       </c>
       <c r="K93" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0620=冗余行（A: %d, B: %d）</v>
+        <f t="shared" si="10"/>
+        <v>APP_0580=工作文件夹：</v>
       </c>
     </row>
     <row r="94" spans="3:11">
       <c r="C94" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E94 &amp; " */ " &amp; D94 &amp; ","</f>
-        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
+        <f t="shared" si="11"/>
+        <v>/** 差分なし */ APP_0600,</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>323</v>
+        <v>293</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>294</v>
       </c>
       <c r="I94" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0630=余剰列（A: %d, B: %d）</v>
+        <f t="shared" si="8"/>
+        <v>APP_0600=差分なし</v>
       </c>
       <c r="J94" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
+        <f t="shared" si="9"/>
+        <v>APP_0600=No Diffs</v>
       </c>
       <c r="K94" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0630=冗余列（A: %d, B: %d）</v>
+        <f t="shared" si="10"/>
+        <v>APP_0600=没有区别</v>
       </c>
     </row>
     <row r="95" spans="3:11">
       <c r="C95" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E95 &amp; " */ " &amp; D95 &amp; ","</f>
-        <v>/** 差分セル（%d） */ APP_0640,</v>
+        <f t="shared" si="11"/>
+        <v>/** 比較失敗 */ APP_0610,</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>324</v>
+        <v>296</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>295</v>
       </c>
       <c r="I95" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0640=差分セル（%d）</v>
+        <f t="shared" si="8"/>
+        <v>APP_0610=比較失敗</v>
       </c>
       <c r="J95" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0640=Diff Cells (%d)</v>
+        <f t="shared" si="9"/>
+        <v>APP_0610=Comparison Failed</v>
       </c>
       <c r="K95" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0640=差异单元格（%d）</v>
+        <f t="shared" si="10"/>
+        <v>APP_0610=比较失败</v>
       </c>
     </row>
     <row r="96" spans="3:11">
       <c r="C96" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E96 &amp; " */ " &amp; D96 &amp; ","</f>
-        <v>/** 比較フォルダ%s： */ APP_0660,</v>
+        <f t="shared" si="11"/>
+        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>180</v>
+        <v>306</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>221</v>
+        <v>307</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>314</v>
       </c>
       <c r="I96" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0660=比較フォルダ%s：</v>
+        <f t="shared" si="8"/>
+        <v>APP_0620=余剰行（A: %d, B: %d）</v>
       </c>
       <c r="J96" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0660=Folder %s : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
       </c>
       <c r="K96" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0660=文件夹%s：</v>
+        <f t="shared" si="10"/>
+        <v>APP_0620=冗余行（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="97" spans="3:11">
       <c r="C97" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E97 &amp; " */ " &amp; D97 &amp; ","</f>
-        <v>/** ワークシート */ APP_0680,</v>
+        <f t="shared" si="11"/>
+        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>50</v>
+        <v>463</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>109</v>
+        <v>310</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>312</v>
       </c>
       <c r="I97" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0680=ワークシート</v>
+        <f t="shared" si="8"/>
+        <v>APP_0630=余剰列（A: %d, B: %d）</v>
       </c>
       <c r="J97" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0680=Worksheet</v>
+        <f t="shared" si="9"/>
+        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
       </c>
       <c r="K97" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0680=工作表</v>
+        <f t="shared" si="10"/>
+        <v>APP_0630=冗余列（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="98" spans="3:11">
       <c r="C98" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E98 &amp; " */ " &amp; D98 &amp; ","</f>
-        <v>/** グラフシート */ APP_0690,</v>
+        <f t="shared" si="11"/>
+        <v>/** 差分セル（%d） */ APP_0640,</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>51</v>
+        <v>464</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>257</v>
+        <v>311</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I98" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0690=グラフシート</v>
+        <f t="shared" si="8"/>
+        <v>APP_0640=差分セル（%d）</v>
       </c>
       <c r="J98" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0690=Chart</v>
+        <f t="shared" si="9"/>
+        <v>APP_0640=Diff Cells (%d)</v>
       </c>
       <c r="K98" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0690=图表表</v>
+        <f t="shared" si="10"/>
+        <v>APP_0640=差异单元格（%d）</v>
       </c>
     </row>
     <row r="99" spans="3:11">
       <c r="C99" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E99 &amp; " */ " &amp; D99 &amp; ","</f>
-        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
+        <f t="shared" si="11"/>
+        <v>/** 比較フォルダ%s： */ APP_0660,</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>52</v>
+        <v>465</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>258</v>
+        <v>141</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="I99" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
+        <f t="shared" si="8"/>
+        <v>APP_0660=比較フォルダ%s：</v>
       </c>
       <c r="J99" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0700=MS Excel 5.0 Dialog</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0660=Folder %s : </v>
       </c>
       <c r="K99" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0700=MS Excel 5.0 对话表</v>
+        <f t="shared" si="10"/>
+        <v>APP_0660=文件夹%s：</v>
       </c>
     </row>
     <row r="100" spans="3:11">
       <c r="C100" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E100 &amp; " */ " &amp; D100 &amp; ","</f>
-        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
+        <f t="shared" si="11"/>
+        <v>/** ワークシート */ APP_0680,</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>110</v>
+        <v>90</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="I100" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0710=Excel 4.0 マクロシート</v>
+        <f t="shared" si="8"/>
+        <v>APP_0680=ワークシート</v>
       </c>
       <c r="J100" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0710=Excel 4.0 Macro</v>
+        <f t="shared" si="9"/>
+        <v>APP_0680=Worksheet</v>
       </c>
       <c r="K100" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0710=Excel 4.0 宏表</v>
+        <f t="shared" si="10"/>
+        <v>APP_0680=工作表</v>
       </c>
     </row>
     <row r="101" spans="3:11">
       <c r="C101" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E101 &amp; " */ " &amp; D101 &amp; ","</f>
-        <v>/** 余剰行%d */ APP_0730,</v>
+        <f t="shared" si="11"/>
+        <v>/** グラフシート */ APP_0690,</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>111</v>
+        <v>91</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="I101" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0730=余剰行%d</v>
+        <f t="shared" si="8"/>
+        <v>APP_0690=グラフシート</v>
       </c>
       <c r="J101" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0730=redundant rows:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0690=Chart</v>
       </c>
       <c r="K101" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0730=冗余行%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0690=图表表</v>
       </c>
     </row>
     <row r="102" spans="3:11">
       <c r="C102" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E102 &amp; " */ " &amp; D102 &amp; ","</f>
-        <v>/** 余剰列%d */ APP_0740,</v>
+        <f t="shared" si="11"/>
+        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>112</v>
+        <v>92</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="I102" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0740=余剰列%d</v>
+        <f t="shared" si="8"/>
+        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
       </c>
       <c r="J102" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0740=redundant columns:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0700=MS Excel 5.0 Dialog</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0740=冗余列%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0700=MS Excel 5.0 对话表</v>
       </c>
     </row>
     <row r="103" spans="3:11">
       <c r="C103" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E103 &amp; " */ " &amp; D103 &amp; ","</f>
-        <v>/** 差分セル%d */ APP_0750,</v>
+        <f t="shared" si="11"/>
+        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>259</v>
+        <v>93</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="I103" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0750=差分セル%d</v>
+        <f t="shared" si="8"/>
+        <v>APP_0710=Excel 4.0 マクロシート</v>
       </c>
       <c r="J103" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0750=diff cells:%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0710=Excel 4.0 Macro</v>
       </c>
       <c r="K103" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0750=差异单元格%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0710=Excel 4.0 宏表</v>
       </c>
     </row>
     <row r="104" spans="3:11">
       <c r="C104" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E104 &amp; " */ " &amp; D104 &amp; ","</f>
-        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
+        <f t="shared" si="11"/>
+        <v>/** 余剰行%d */ APP_0730,</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>194</v>
+        <v>52</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>148</v>
+        <v>94</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="I104" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
+        <f t="shared" si="8"/>
+        <v>APP_0730=余剰行%d</v>
       </c>
       <c r="J104" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0730=redundant rows:%d</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0730=冗余行%d</v>
       </c>
     </row>
     <row r="105" spans="3:11">
       <c r="C105" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E105 &amp; " */ " &amp; D105 &amp; ","</f>
-        <v>/** 行%d */ APP_0770,</v>
+        <f t="shared" si="11"/>
+        <v>/** 余剰列%d */ APP_0740,</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>57</v>
+        <v>95</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="I105" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="8"/>
+        <v>APP_0740=余剰列%d</v>
       </c>
       <c r="J105" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0770=Row %d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0740=redundant columns:%d</v>
       </c>
       <c r="K105" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0740=冗余列%d</v>
       </c>
     </row>
     <row r="106" spans="3:11">
       <c r="C106" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E106 &amp; " */ " &amp; D106 &amp; ","</f>
-        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
+        <f t="shared" si="11"/>
+        <v>/** 差分セル%d */ APP_0750,</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>195</v>
+        <v>54</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>149</v>
+        <v>96</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="I106" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
+        <f t="shared" si="8"/>
+        <v>APP_0750=差分セル%d</v>
       </c>
       <c r="J106" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0750=diff cells:%d</v>
       </c>
       <c r="K106" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0750=差异单元格%d</v>
       </c>
     </row>
     <row r="107" spans="3:11">
       <c r="C107" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E107 &amp; " */ " &amp; D107 &amp; ","</f>
-        <v>/** %s列 */ APP_0790,</v>
+        <f t="shared" si="11"/>
+        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>58</v>
+        <v>191</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>58</v>
+        <v>142</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="I107" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
       </c>
       <c r="J107" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0790=Column %s</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
       </c>
       <c r="K107" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
       </c>
     </row>
     <row r="108" spans="3:11">
       <c r="C108" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E108 &amp; " */ " &amp; D108 &amp; ","</f>
-        <v>/** 差分セル :  */ APP_0800,</v>
+        <f t="shared" si="11"/>
+        <v>/** 行%d */ APP_0770,</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>196</v>
+        <v>55</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>260</v>
+        <v>97</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="I108" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0800=差分セル : </v>
+        <f t="shared" si="8"/>
+        <v>APP_0770=行%d</v>
       </c>
       <c r="J108" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0800=Diff cells : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0770=Row %d</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0800=差异单元格 : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0770=行%d</v>
       </c>
     </row>
     <row r="109" spans="3:11">
       <c r="C109" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E109 &amp; " */ " &amp; D109 &amp; ","</f>
-        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
+        <f t="shared" si="11"/>
+        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>176</v>
+        <v>475</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>261</v>
+        <v>143</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="I109" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
       </c>
       <c r="J109" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">APP_0820=Root folder %s : </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
       </c>
     </row>
     <row r="110" spans="3:11">
       <c r="C110" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E110 &amp; " */ " &amp; D110 &amp; ","</f>
-        <v>/** 組み合わせ編集 */ APP_0860,</v>
+        <f t="shared" si="11"/>
+        <v>/** %s列 */ APP_0790,</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>276</v>
+        <v>476</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>278</v>
+        <v>98</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="I110" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0860=組み合わせ編集</v>
+        <f t="shared" si="8"/>
+        <v>APP_0790=%s列</v>
       </c>
       <c r="J110" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0860=Edit Pairing</v>
+        <f t="shared" si="9"/>
+        <v>APP_0790=Column %s</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0860=组合编辑</v>
+        <f t="shared" si="10"/>
+        <v>APP_0790=%s列</v>
       </c>
     </row>
     <row r="111" spans="3:11">
       <c r="C111" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E111 &amp; " */ " &amp; D111 &amp; ","</f>
-        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
+        <f t="shared" si="11"/>
+        <v>/** 差分セル :  */ APP_0800,</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>383</v>
+        <v>477</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>387</v>
+        <v>144</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="I111" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">APP_0800=差分セル : </v>
       </c>
       <c r="J111" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0800=Diff cells : </v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0800=差异单元格 : </v>
       </c>
     </row>
     <row r="112" spans="3:11">
       <c r="C112" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E112 &amp; " */ " &amp; D112 &amp; ","</f>
-        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
+        <f t="shared" si="11"/>
+        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>384</v>
+        <v>173</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>388</v>
+        <v>174</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="I112" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
       </c>
       <c r="J112" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0820=Root folder %s : </v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
       </c>
     </row>
     <row r="113" spans="3:11">
       <c r="C113" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E113 &amp; " */ " &amp; D113 &amp; ","</f>
-        <v>/** 共有ドライブ */ APP_0890,</v>
+        <f t="shared" si="11"/>
+        <v>/** 組み合わせ編集 */ APP_0860,</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>389</v>
+        <v>272</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G113" s="6" t="s">
-        <v>396</v>
+        <v>273</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="I113" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0890=共有ドライブ</v>
+        <f t="shared" si="8"/>
+        <v>APP_0860=組み合わせ編集</v>
       </c>
       <c r="J113" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0890=Shared drives</v>
+        <f t="shared" si="9"/>
+        <v>APP_0860=Edit Pairing</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0890=共享云端硬盘</v>
+        <f t="shared" si="10"/>
+        <v>APP_0860=组合编辑</v>
       </c>
     </row>
     <row r="114" spans="3:11">
       <c r="C114" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E114 &amp; " */ " &amp; D114 &amp; ","</f>
-        <v>/** すべてのファイル */ APP_0900,</v>
+        <f t="shared" si="11"/>
+        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>392</v>
+        <v>374</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="I114" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0900=すべてのファイル</v>
+        <f t="shared" si="8"/>
+        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
       </c>
       <c r="J114" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0900=All files</v>
+        <f t="shared" si="9"/>
+        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0900=所有文件</v>
+        <f t="shared" si="10"/>
+        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
       </c>
     </row>
     <row r="115" spans="3:11">
       <c r="C115" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E115 &amp; " */ " &amp; D115 &amp; ","</f>
-        <v>/** スター付き */ APP_0910,</v>
+        <f t="shared" si="11"/>
+        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="G115" s="6" t="s">
-        <v>397</v>
+        <v>375</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>377</v>
       </c>
       <c r="I115" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0910=スター付き</v>
+        <f t="shared" si="8"/>
+        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
       </c>
       <c r="J115" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0910=Starred</v>
+        <f t="shared" si="9"/>
+        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0910=已加星标</v>
+        <f t="shared" si="10"/>
+        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
       </c>
     </row>
     <row r="116" spans="3:11">
       <c r="C116" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E116 &amp; " */ " &amp; D116 &amp; ","</f>
-        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
+        <f t="shared" ref="C116:C147" si="12" xml:space="preserve"> "/** " &amp; E116 &amp; " */ " &amp; D116 &amp; ","</f>
+        <v>/** 共有ドライブ */ APP_0890,</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>399</v>
+        <v>379</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>385</v>
       </c>
       <c r="I116" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0890=共有ドライブ</v>
       </c>
       <c r="J116" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0920=Failed to download the file from Google Drive.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0890=Shared drives</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0890=共享云端硬盘</v>
       </c>
     </row>
     <row r="117" spans="3:11">
       <c r="C117" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E117 &amp; " */ " &amp; D117 &amp; ","</f>
-        <v>/** 更新者不明 */ APP_0930,</v>
+        <f t="shared" si="12"/>
+        <v>/** すべてのファイル */ APP_0900,</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>355</v>
+        <v>380</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="I117" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0930=更新者不明</v>
+        <f t="shared" si="8"/>
+        <v>APP_0900=すべてのファイル</v>
       </c>
       <c r="J117" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0930=Unknown</v>
+        <f t="shared" si="9"/>
+        <v>APP_0900=All files</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0930=更新者不明</v>
+        <f t="shared" si="10"/>
+        <v>APP_0900=所有文件</v>
       </c>
     </row>
     <row r="118" spans="3:11">
       <c r="C118" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E118 &amp; " */ " &amp; D118 &amp; ","</f>
-        <v>/** 最新版 */ APP_0940,</v>
+        <f t="shared" si="12"/>
+        <v>/** スター付き */ APP_0910,</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>357</v>
+        <v>384</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>386</v>
       </c>
       <c r="I118" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0940=最新版</v>
+        <f t="shared" si="8"/>
+        <v>APP_0910=スター付き</v>
       </c>
       <c r="J118" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0940=Latest</v>
+        <f t="shared" si="9"/>
+        <v>APP_0910=Starred</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0940=最新版</v>
+        <f t="shared" si="10"/>
+        <v>APP_0910=已加星标</v>
       </c>
     </row>
     <row r="119" spans="3:11">
       <c r="C119" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E119 &amp; " */ " &amp; D119 &amp; ","</f>
-        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
+        <f t="shared" si="12"/>
+        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>332</v>
+        <v>389</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="I119" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
+        <f t="shared" si="8"/>
+        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
       </c>
       <c r="J119" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
+        <f t="shared" si="9"/>
+        <v>APP_0920=Failed to download the file from Google Drive.</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
+        <f t="shared" si="10"/>
+        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
       </c>
     </row>
     <row r="120" spans="3:11">
       <c r="C120" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E120 &amp; " */ " &amp; D120 &amp; ","</f>
-        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
+        <f t="shared" si="12"/>
+        <v>/** 更新者不明 */ APP_0930,</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>335</v>
+        <v>345</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="I120" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0960=資格情報を削除しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0930=更新者不明</v>
       </c>
       <c r="J120" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0960=Credentials have been deleted.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0930=Unknown</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0960=已删除凭据。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0930=更新者不明</v>
       </c>
     </row>
     <row r="121" spans="3:11">
       <c r="C121" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E121 &amp; " */ " &amp; D121 &amp; ","</f>
-        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
+        <f t="shared" si="12"/>
+        <v>/** 最新版 */ APP_0940,</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>338</v>
+        <v>347</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="I121" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0940=最新版</v>
       </c>
       <c r="J121" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0940=Latest</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0940=最新版</v>
       </c>
     </row>
     <row r="122" spans="3:11">
       <c r="C122" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E122 &amp; " */ " &amp; D122 &amp; ","</f>
-        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
+        <f t="shared" si="12"/>
+        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>343</v>
+        <v>319</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="I122" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0980=資格情報の削除に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
       </c>
       <c r="J122" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0980=Failed to delete credentials.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0980=删除凭据失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
       </c>
     </row>
     <row r="123" spans="3:11">
       <c r="C123" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E123 &amp; " */ " &amp; D123 &amp; ","</f>
-        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
+        <f t="shared" si="12"/>
+        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>345</v>
+        <v>323</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="I123" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0960=資格情報を削除しました。</v>
       </c>
       <c r="J123" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0960=Credentials have been deleted.</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0960=已删除凭据。</v>
       </c>
     </row>
     <row r="124" spans="3:11">
       <c r="C124" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E124 &amp; " */ " &amp; D124 &amp; ","</f>
-        <v>/** Google連携エラー */ APP_1000,</v>
+        <f t="shared" si="12"/>
+        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>348</v>
+        <v>326</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>327</v>
       </c>
       <c r="I124" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1000=Google連携エラー</v>
+        <f t="shared" si="8"/>
+        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
       </c>
       <c r="J124" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1000=Google Integration Error</v>
+        <f t="shared" si="9"/>
+        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
       </c>
       <c r="K124" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1000=Google关联错误</v>
+        <f t="shared" si="10"/>
+        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
     </row>
     <row r="125" spans="3:11">
       <c r="C125" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E125 &amp; " */ " &amp; D125 &amp; ","</f>
-        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
+        <f t="shared" si="12"/>
+        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>351</v>
+        <v>331</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>332</v>
       </c>
       <c r="I125" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0980=資格情報の削除に失敗しました。</v>
       </c>
       <c r="J125" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1010=An error occurred during Google integration processing.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0980=Failed to delete credentials.</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1010=Google关联处理过程中发生错误。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0980=删除凭据失败。</v>
       </c>
     </row>
     <row r="126" spans="3:11">
       <c r="C126" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E126 &amp; " */ " &amp; D126 &amp; ","</f>
-        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
+        <f t="shared" si="12"/>
+        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>354</v>
+        <v>333</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="I126" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J126" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="9"/>
+        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K126" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="10"/>
+        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="127" spans="3:11">
       <c r="C127" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E127 &amp; " */ " &amp; D127 &amp; ","</f>
-        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
+        <f t="shared" si="12"/>
+        <v>/** Google連携エラー */ APP_1000,</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>374</v>
+        <v>493</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>380</v>
+        <v>336</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>337</v>
       </c>
       <c r="I127" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1000=Google連携エラー</v>
       </c>
       <c r="J127" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1030=File downloaded from Google Drive</v>
+        <f t="shared" si="9"/>
+        <v>APP_1000=Google Integration Error</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1030=已从Google云端硬盘下载文件</v>
+        <f t="shared" si="10"/>
+        <v>APP_1000=Google关联错误</v>
       </c>
     </row>
     <row r="128" spans="3:11">
       <c r="C128" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E128 &amp; " */ " &amp; D128 &amp; ","</f>
-        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
+        <f t="shared" si="12"/>
+        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>18</v>
+        <v>494</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>227</v>
+        <v>339</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="I128" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
       </c>
       <c r="J128" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1010=An error occurred during Google integration processing.</v>
       </c>
       <c r="K128" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1010=Google关联处理过程中发生错误。</v>
       </c>
     </row>
     <row r="129" spans="3:11">
       <c r="C129" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E129 &amp; " */ " &amp; D129 &amp; ","</f>
-        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
+        <f t="shared" si="12"/>
+        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>25</v>
+        <v>495</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>341</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G129" s="6" t="s">
-        <v>228</v>
+        <v>342</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="I129" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J129" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1050=Failed to open working directory.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1050=显示工作文件夹失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="130" spans="3:11">
       <c r="C130" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E130 &amp; " */ " &amp; D130 &amp; ","</f>
-        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
+        <f t="shared" si="12"/>
+        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>26</v>
+        <v>363</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>224</v>
+        <v>368</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>369</v>
       </c>
       <c r="I130" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>APP_1060=作業用フォルダの変更</v>
+        <f t="shared" si="8"/>
+        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
       </c>
       <c r="J130" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_1060=Change working directory</v>
+        <f t="shared" si="9"/>
+        <v>APP_1030=File downloaded from Google Drive</v>
       </c>
       <c r="K130" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1060=改变工作文件夹</v>
+        <f t="shared" si="10"/>
+        <v>APP_1030=已从Google云端硬盘下载文件</v>
       </c>
     </row>
     <row r="131" spans="3:11">
       <c r="C131" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E131 &amp; " */ " &amp; D131 &amp; ","</f>
-        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
+        <f t="shared" si="12"/>
+        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>229</v>
+        <v>65</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="I131" s="3" t="str">
-        <f t="shared" ref="I131:I154" si="6" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; E131)</f>
-        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
       </c>
       <c r="J131" s="4" t="str">
-        <f t="shared" ref="J131:J154" si="7" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; F131)</f>
-        <v>APP_1070=Failed to change working directory.</v>
+        <f t="shared" si="9"/>
+        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f t="shared" ref="K131:K154" si="8" xml:space="preserve"> IF($D131="", "", $D131 &amp; "=" &amp; G131)</f>
-        <v>APP_1070=更改工作文件夹失败。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
     </row>
     <row r="132" spans="3:11">
       <c r="C132" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E132 &amp; " */ " &amp; D132 &amp; ","</f>
-        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
+        <f t="shared" si="12"/>
+        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>230</v>
+        <v>68</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="I132" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
+        <f t="shared" si="8"/>
+        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
       </c>
       <c r="J132" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
+        <f t="shared" si="9"/>
+        <v>APP_1050=Failed to open working directory.</v>
       </c>
       <c r="K132" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
+        <f t="shared" si="10"/>
+        <v>APP_1050=显示工作文件夹失败。</v>
       </c>
     </row>
     <row r="133" spans="3:11">
       <c r="C133" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E133 &amp; " */ " &amp; D133 &amp; ","</f>
-        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
+        <f t="shared" si="12"/>
+        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="I133" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="8"/>
+        <v>APP_1060=作業用フォルダの変更</v>
       </c>
       <c r="J133" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="9"/>
+        <v>APP_1060=Change working directory</v>
       </c>
       <c r="K133" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="10"/>
+        <v>APP_1060=改变工作文件夹</v>
       </c>
     </row>
     <row r="134" spans="3:11">
       <c r="C134" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E134 &amp; " */ " &amp; D134 &amp; ","</f>
-        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
+        <f t="shared" si="12"/>
+        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="I134" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" ref="I134:I157" si="13" xml:space="preserve"> IF($D134="", "", $D134 &amp; "=" &amp; E134)</f>
+        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
       </c>
       <c r="J134" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" ref="J134:J157" si="14" xml:space="preserve"> IF($D134="", "", $D134 &amp; "=" &amp; F134)</f>
+        <v>APP_1070=Failed to change working directory.</v>
       </c>
       <c r="K134" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" ref="K134:K157" si="15" xml:space="preserve"> IF($D134="", "", $D134 &amp; "=" &amp; G134)</f>
+        <v>APP_1070=更改工作文件夹失败。</v>
       </c>
     </row>
     <row r="135" spans="3:11">
       <c r="C135" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E135 &amp; " */ " &amp; D135 &amp; ","</f>
-        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
+        <f t="shared" si="12"/>
+        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>24</v>
+        <v>71</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="I135" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
       </c>
       <c r="J135" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
       </c>
       <c r="K135" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
     </row>
     <row r="136" spans="3:11">
       <c r="C136" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E136 &amp; " */ " &amp; D136 &amp; ","</f>
-        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
+        <f t="shared" si="12"/>
+        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>404</v>
+        <v>502</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>599</v>
+        <v>22</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="I136" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1100=方眼Diff  -  詳細設定</v>
+        <f t="shared" si="13"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="J136" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
+        <f t="shared" si="14"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="K136" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1100=方眼Diff  -  详细设置</v>
+        <f t="shared" si="15"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
     </row>
     <row r="137" spans="3:11">
       <c r="C137" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E137 &amp; " */ " &amp; D137 &amp; ","</f>
-        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
+        <f t="shared" si="12"/>
+        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>121</v>
+        <v>503</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G137" s="6" t="s">
-        <v>231</v>
+        <v>23</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I137" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1110=比較対象フォルダの選択</v>
+        <f t="shared" si="13"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="J137" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1110=Select comparison folder</v>
+        <f t="shared" si="14"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="K137" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1110=选择用于比较的文件夹</v>
+        <f t="shared" si="15"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
     </row>
     <row r="138" spans="3:11">
       <c r="C138" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E138 &amp; " */ " &amp; D138 &amp; ","</f>
-        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
+        <f t="shared" si="12"/>
+        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>232</v>
+        <v>128</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="I138" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1120=比較対象ブックの選択</v>
+        <f t="shared" si="13"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="J138" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1120=Select comparison book</v>
+        <f t="shared" si="14"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="K138" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1120=选择用于比较的工作簿</v>
+        <f t="shared" si="15"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
     </row>
     <row r="139" spans="3:11">
       <c r="C139" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E139 &amp; " */ " &amp; D139 &amp; ","</f>
-        <v>/** Excel ブック */ APP_1130,</v>
+        <f t="shared" si="12"/>
+        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>21</v>
+        <v>505</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>393</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>106</v>
+        <v>394</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="I139" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1130=Excel ブック</v>
+        <f t="shared" si="13"/>
+        <v>APP_1100=方眼Diff  -  詳細設定</v>
       </c>
       <c r="J139" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1130=Excel book</v>
+        <f t="shared" si="14"/>
+        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
       </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1130=Excel工作簿</v>
+        <f t="shared" si="15"/>
+        <v>APP_1100=方眼Diff  -  详细设置</v>
       </c>
     </row>
     <row r="140" spans="3:11">
       <c r="C140" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E140 &amp; " */ " &amp; D140 &amp; ","</f>
-        <v>/** ファイルを読み込めません： */ APP_1140,</v>
+        <f t="shared" si="12"/>
+        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>190</v>
+        <v>506</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>233</v>
+        <v>127</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="I140" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1140=ファイルを読み込めません：</v>
+        <f t="shared" si="13"/>
+        <v>APP_1110=比較対象フォルダの選択</v>
       </c>
       <c r="J140" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_1140=Failed to open file : </v>
+        <f t="shared" si="14"/>
+        <v>APP_1110=Select comparison folder</v>
       </c>
       <c r="K140" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1140=无法读取文件：</v>
+        <f t="shared" si="15"/>
+        <v>APP_1110=选择用于比较的文件夹</v>
       </c>
     </row>
     <row r="141" spans="3:11">
       <c r="C141" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E141 &amp; " */ " &amp; D141 &amp; ","</f>
-        <v>/** シートが見つかりません： */ APP_1150,</v>
+        <f t="shared" si="12"/>
+        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>192</v>
+        <v>66</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="I141" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1150=シートが見つかりません：</v>
+        <f t="shared" si="13"/>
+        <v>APP_1120=比較対象ブックの選択</v>
       </c>
       <c r="J141" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_1150=No such sheet : </v>
+        <f t="shared" si="14"/>
+        <v>APP_1120=Select comparison book</v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1150=没有找到工作表：</v>
+        <f t="shared" si="15"/>
+        <v>APP_1120=选择用于比较的工作簿</v>
       </c>
     </row>
     <row r="142" spans="3:11">
       <c r="C142" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E142 &amp; " */ " &amp; D142 &amp; ","</f>
-        <v>/** フォルダを読み込めません： */ APP_1160,</v>
+        <f t="shared" si="12"/>
+        <v>/** Excel ブック */ APP_1130,</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>275</v>
+        <v>67</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="I142" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1160=フォルダを読み込めません：</v>
+        <f t="shared" si="13"/>
+        <v>APP_1130=Excel ブック</v>
       </c>
       <c r="J142" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
+        <f t="shared" si="14"/>
+        <v>APP_1130=Excel book</v>
       </c>
       <c r="K142" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1160=无法读取文件夹：</v>
+        <f t="shared" si="15"/>
+        <v>APP_1130=Excel工作簿</v>
       </c>
     </row>
     <row r="143" spans="3:11">
       <c r="C143" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E143 &amp; " */ " &amp; D143 &amp; ","</f>
-        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
+        <f t="shared" si="12"/>
+        <v>/** ファイルを読み込めません： */ APP_1140,</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>406</v>
+        <v>187</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>601</v>
+        <v>179</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="I143" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
+        <f t="shared" si="13"/>
+        <v>APP_1140=ファイルを読み込めません：</v>
       </c>
       <c r="J143" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">APP_1140=Failed to open file : </v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
+        <f t="shared" si="15"/>
+        <v>APP_1140=无法读取文件：</v>
       </c>
     </row>
     <row r="144" spans="3:11">
       <c r="C144" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E144 &amp; " */ " &amp; D144 &amp; ","</f>
-        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
+        <f t="shared" si="12"/>
+        <v>/** シートが見つかりません： */ APP_1150,</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>120</v>
+        <v>510</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>222</v>
+        <v>188</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="I144" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1150=シートが見つかりません：</v>
       </c>
       <c r="J144" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1180=Please specify different folders/books/sheets.</v>
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">APP_1150=No such sheet : </v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1150=没有找到工作表：</v>
       </c>
     </row>
     <row r="145" spans="3:11">
       <c r="C145" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E145 &amp; " */ " &amp; D145 &amp; ","</f>
-        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
+        <f t="shared" si="12"/>
+        <v>/** フォルダを読み込めません： */ APP_1160,</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>117</v>
+        <v>269</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>223</v>
+        <v>270</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="I145" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1160=フォルダを読み込めません：</v>
       </c>
       <c r="J145" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1160=无法读取文件夹：</v>
       </c>
     </row>
     <row r="146" spans="3:11">
       <c r="C146" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E146 &amp; " */ " &amp; D146 &amp; ","</f>
-        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
+        <f t="shared" si="12"/>
+        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>36</v>
+        <v>395</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>200</v>
+        <v>396</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>590</v>
       </c>
       <c r="I146" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
       </c>
       <c r="J146" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1210=Failed to create working directory.</v>
+        <f t="shared" si="14"/>
+        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
       </c>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1210=创建工作文件夹失败。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
     </row>
     <row r="147" spans="3:11">
       <c r="C147" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E147 &amp; " */ " &amp; D147 &amp; ","</f>
-        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
+        <f t="shared" si="12"/>
+        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>197</v>
+        <v>513</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>199</v>
+        <v>125</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I147" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1220=別の場所を指定してください。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
       </c>
       <c r="J147" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1220=Please specify another location.</v>
+        <f t="shared" si="14"/>
+        <v>APP_1180=Please specify different folders/books/sheets.</v>
       </c>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1220=请指定其他位置。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
     </row>
     <row r="148" spans="3:11">
       <c r="C148" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E148 &amp; " */ " &amp; D148 &amp; ","</f>
-        <v>/** 処理を中止しました。 */ APP_1240,</v>
+        <f t="shared" ref="C148:C157" si="16" xml:space="preserve"> "/** " &amp; E148 &amp; " */ " &amp; D148 &amp; ","</f>
+        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>202</v>
+        <v>115</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I148" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1240=処理を中止しました。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
       </c>
       <c r="J148" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1240=Processing has been canceled.</v>
+        <f t="shared" si="14"/>
+        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
       </c>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1240=处理已被取消。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
     </row>
     <row r="149" spans="3:11">
       <c r="C149" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E149 &amp; " */ " &amp; D149 &amp; ","</f>
-        <v>/** パスワード指定 */ APP_1250,</v>
+        <f t="shared" si="16"/>
+        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>225</v>
+        <v>77</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="I149" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1250=パスワード指定</v>
+        <f t="shared" si="13"/>
+        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
       </c>
       <c r="J149" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1250=Enter Password</v>
+        <f t="shared" si="14"/>
+        <v>APP_1210=Failed to create working directory.</v>
       </c>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1250=输入密码</v>
+        <f t="shared" si="15"/>
+        <v>APP_1210=创建工作文件夹失败。</v>
       </c>
     </row>
     <row r="150" spans="3:11">
       <c r="C150" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E150 &amp; " */ " &amp; D150 &amp; ","</f>
-        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
+        <f t="shared" si="16"/>
+        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>226</v>
+        <v>195</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="I150" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1260=%s はパスワードで保護されています。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1220=別の場所を指定してください。</v>
       </c>
       <c r="J150" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1260=The book [%s] is password protected.</v>
+        <f t="shared" si="14"/>
+        <v>APP_1220=Please specify another location.</v>
       </c>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1260=%s 是受密码保护的。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1220=请指定其他位置。</v>
       </c>
     </row>
     <row r="151" spans="3:11">
       <c r="C151" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E151 &amp; " */ " &amp; D151 &amp; ","</f>
-        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
+        <f t="shared" si="16"/>
+        <v>/** 処理を中止しました。 */ APP_1240,</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>401</v>
+        <v>198</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>403</v>
+        <v>200</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="I151" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1270=新しいバージョンが利用可能です。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1240=処理を中止しました。</v>
       </c>
       <c r="J151" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1270=A new version is available.</v>
+        <f t="shared" si="14"/>
+        <v>APP_1240=Processing has been canceled.</v>
       </c>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1270=有新版本可用。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1240=处理已被取消。</v>
       </c>
     </row>
     <row r="152" spans="3:11">
       <c r="C152" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E152 &amp; " */ " &amp; D152 &amp; ","</f>
-        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
+        <f t="shared" si="16"/>
+        <v>/** パスワード指定 */ APP_1250,</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>427</v>
+        <v>30</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>600</v>
+        <v>73</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="I152" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+        <f t="shared" si="13"/>
+        <v>APP_1250=パスワード指定</v>
       </c>
       <c r="J152" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+        <f t="shared" si="14"/>
+        <v>APP_1250=Enter Password</v>
       </c>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+        <f t="shared" si="15"/>
+        <v>APP_1250=输入密码</v>
       </c>
     </row>
     <row r="153" spans="3:11">
       <c r="C153" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E153 &amp; " */ " &amp; D153 &amp; ","</f>
-        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
+        <f t="shared" si="16"/>
+        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>425</v>
+        <v>519</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="G153" s="6" t="s">
-        <v>598</v>
+        <v>74</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="I153" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
+        <f t="shared" si="13"/>
+        <v>APP_1260=%s はパスワードで保護されています。</v>
       </c>
       <c r="J153" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
+        <f t="shared" si="14"/>
+        <v>APP_1260=The book [%s] is password protected.</v>
       </c>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
+        <f t="shared" si="15"/>
+        <v>APP_1260=%s 是受密码保护的。</v>
       </c>
     </row>
     <row r="154" spans="3:11">
       <c r="C154" s="1" t="str">
-        <f xml:space="preserve"> "/** " &amp; E154 &amp; " */ " &amp; D154 &amp; ","</f>
+        <f t="shared" si="16"/>
+        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="I154" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>APP_1270=新しいバージョンが利用可能です。</v>
+      </c>
+      <c r="J154" s="4" t="str">
+        <f t="shared" si="14"/>
+        <v>APP_1270=A new version is available.</v>
+      </c>
+      <c r="K154" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>APP_1270=有新版本可用。</v>
+      </c>
+    </row>
+    <row r="155" spans="3:11">
+      <c r="C155" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="I155" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+      </c>
+      <c r="J155" s="4" t="str">
+        <f t="shared" si="14"/>
+        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+      </c>
+      <c r="K155" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+      </c>
+    </row>
+    <row r="156" spans="3:11">
+      <c r="C156" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="I156" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
+      </c>
+      <c r="J156" s="4" t="str">
+        <f t="shared" si="14"/>
+        <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
+      </c>
+      <c r="K156" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
+      </c>
+    </row>
+    <row r="157" spans="3:11">
+      <c r="C157" s="1" t="str">
+        <f t="shared" si="16"/>
         <v>/** ★パスワード不明のためスキップ */ APP_1300,</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="I154" s="3" t="str">
-        <f t="shared" si="6"/>
+      <c r="D157" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="I157" s="3" t="str">
+        <f t="shared" si="13"/>
         <v>APP_1300=★パスワード不明のためスキップ</v>
       </c>
-      <c r="J154" s="4" t="str">
-        <f t="shared" si="7"/>
+      <c r="J157" s="4" t="str">
+        <f t="shared" si="14"/>
         <v>APP_1300=★Skipped due to unknown password</v>
       </c>
-      <c r="K154" s="5" t="str">
-        <f t="shared" si="8"/>
+      <c r="K157" s="5" t="str">
+        <f t="shared" si="15"/>
         <v>APP_1300=★因密码未知而跳过</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:K154">
-    <sortCondition ref="D49:D154"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A50:K157">
+    <sortCondition ref="D50:D157"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
+++ b/xyz.hotchpotch.hogandiff/messages.properties管理.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fdcf04b383bd82/workspace_202509/hogandiff4/xyz.hotchpotch.hogandiff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="6_{837EF89F-D38D-40BC-8B80-6986C3B731F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F597907-711F-4F5F-A2E5-6BC2E8C2DD68}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="6_{837EF89F-D38D-40BC-8B80-6986C3B731F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE45C8A9-E6C1-4850-974C-A429FD33872F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="(3)" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$C$1:$K$156</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="614">
   <si>
     <t>website</t>
   </si>
@@ -2517,8 +2517,107 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>FXML_0181</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストレポートを表示</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Display text report</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示文本报告</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）を保存しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）の保存に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Failed to save result text.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>对比结果文本保存失败。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_0041</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）を表示しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Opening result text...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示比较结果文本...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_0042</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（テキスト）の表示に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Failed to open result text.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示比较结果文本失败。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）を保存しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）の保存に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）を表示しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>比較結果レポート（Excel）の表示に失敗しました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APP_0181</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Oと%sのシートを比較しています...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Comparing sheets O and %s...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>显示Excel报告</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <r>
-      <t>显示</t>
+      <t>正在比较</t>
     </r>
     <r>
       <rPr>
@@ -2527,91 +2626,8 @@
         <rFont val="NSimSun"/>
         <family val="3"/>
       </rPr>
-      <t>Excel报告</t>
+      <t>O和%s的工作表...</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FXML_0181</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テキストレポートを表示</t>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Display text report</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>显示文本报告</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（テキスト）を保存しています...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（テキスト）の保存に失敗しました。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Failed to save result text.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>对比结果文本保存失败。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>APP_0041</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（テキスト）を表示しています...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Opening result text...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>显示比较结果文本...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>APP_0042</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（テキスト）の表示に失敗しました。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Failed to open result text.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>显示比较结果文本失败。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（Excel）を保存しています...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（Excel）の保存に失敗しました。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（Excel）を表示しています...</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>比較結果レポート（Excel）の表示に失敗しました。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2746,6 +2762,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3011,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:K156"/>
+  <dimension ref="C1:K157"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -3019,7 +3039,7 @@
     <col min="4" max="4" width="8.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="30.58203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="30.58203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.58203125" style="5" customWidth="1"/>
     <col min="8" max="8" width="2.58203125" style="1"/>
     <col min="9" max="9" width="2.58203125" style="3"/>
     <col min="10" max="10" width="2.58203125" style="4"/>
@@ -3040,7 +3060,7 @@
       <c r="F1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>110</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -3060,7 +3080,7 @@
       <c r="F2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>198</v>
       </c>
       <c r="I2" s="3" t="str">
@@ -3086,19 +3106,19 @@
       <c r="F3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I68" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
+        <f t="shared" ref="I3:I69" si="0" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; E3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="J3" s="4" t="str">
-        <f t="shared" ref="J3:J68" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
+        <f t="shared" ref="J3:J69" si="1" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; F3)</f>
         <v>FXML_0020=website</v>
       </c>
       <c r="K3" s="5" t="str">
-        <f t="shared" ref="K3:K68" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
+        <f t="shared" ref="K3:K69" si="2" xml:space="preserve"> IF($D3="", "", $D3 &amp; "=" &amp; G3)</f>
         <v>FXML_0020=website</v>
       </c>
     </row>
@@ -3112,7 +3132,7 @@
       <c r="F4" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>154</v>
       </c>
       <c r="I4" s="3" t="str">
@@ -3138,7 +3158,7 @@
       <c r="F5" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>155</v>
       </c>
       <c r="I5" s="3" t="str">
@@ -3164,7 +3184,7 @@
       <c r="F6" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>156</v>
       </c>
       <c r="I6" s="3" t="str">
@@ -3190,7 +3210,7 @@
       <c r="F7" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>199</v>
       </c>
       <c r="I7" s="3" t="str">
@@ -3216,7 +3236,7 @@
       <c r="F8" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>200</v>
       </c>
       <c r="I8" s="3" t="str">
@@ -3242,7 +3262,7 @@
       <c r="F9" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>201</v>
       </c>
       <c r="I9" s="3" t="str">
@@ -3268,7 +3288,7 @@
       <c r="F10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>202</v>
       </c>
       <c r="I10" s="3" t="str">
@@ -3294,7 +3314,7 @@
       <c r="F11" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>203</v>
       </c>
       <c r="I11" s="3" t="str">
@@ -3320,7 +3340,7 @@
       <c r="F12" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>204</v>
       </c>
       <c r="I12" s="3" t="str">
@@ -3346,7 +3366,7 @@
       <c r="F13" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>205</v>
       </c>
       <c r="I13" s="3" t="str">
@@ -3372,7 +3392,7 @@
       <c r="F14" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>206</v>
       </c>
       <c r="I14" s="3" t="str">
@@ -3398,7 +3418,7 @@
       <c r="F15" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>313</v>
       </c>
       <c r="I15" s="3" t="str">
@@ -3424,7 +3444,7 @@
       <c r="F16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>207</v>
       </c>
       <c r="I16" s="3" t="str">
@@ -3450,7 +3470,7 @@
       <c r="F17" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>273</v>
       </c>
       <c r="I17" s="3" t="str">
@@ -3476,8 +3496,8 @@
       <c r="F18" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>589</v>
+      <c r="G18" s="6" t="s">
+        <v>612</v>
       </c>
       <c r="I18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3494,16 +3514,16 @@
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>592</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>593</v>
       </c>
       <c r="I19" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3528,7 +3548,7 @@
       <c r="F20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>208</v>
       </c>
       <c r="I20" s="3" t="str">
@@ -3554,7 +3574,7 @@
       <c r="F21" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>209</v>
       </c>
       <c r="I21" s="3" t="str">
@@ -3580,7 +3600,7 @@
       <c r="F22" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>257</v>
       </c>
       <c r="I22" s="3" t="str">
@@ -3606,7 +3626,7 @@
       <c r="F23" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>258</v>
       </c>
       <c r="I23" s="3" t="str">
@@ -3632,7 +3652,7 @@
       <c r="F24" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>210</v>
       </c>
       <c r="I24" s="3" t="str">
@@ -3658,7 +3678,7 @@
       <c r="F25" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>211</v>
       </c>
       <c r="I25" s="3" t="str">
@@ -3684,7 +3704,7 @@
       <c r="F26" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>580</v>
       </c>
       <c r="I26" s="3" t="str">
@@ -3710,7 +3730,7 @@
       <c r="F27" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>102</v>
       </c>
       <c r="I27" s="3" t="str">
@@ -3736,7 +3756,7 @@
       <c r="F28" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>212</v>
       </c>
       <c r="I28" s="3" t="str">
@@ -3762,7 +3782,7 @@
       <c r="F29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>213</v>
       </c>
       <c r="I29" s="3" t="str">
@@ -3788,7 +3808,7 @@
       <c r="F30" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>180</v>
       </c>
       <c r="I30" s="3" t="str">
@@ -3814,7 +3834,7 @@
       <c r="F31" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="5" t="s">
         <v>182</v>
       </c>
       <c r="I31" s="3" t="str">
@@ -3840,7 +3860,7 @@
       <c r="F32" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>214</v>
       </c>
       <c r="I32" s="3" t="str">
@@ -3866,7 +3886,7 @@
       <c r="F33" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>348</v>
       </c>
       <c r="I33" s="3" t="str">
@@ -3892,7 +3912,7 @@
       <c r="F34" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>350</v>
       </c>
       <c r="I34" s="3" t="str">
@@ -3918,7 +3938,7 @@
       <c r="F35" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>353</v>
       </c>
       <c r="I35" s="3" t="str">
@@ -3944,7 +3964,7 @@
       <c r="F36" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="5" t="s">
         <v>358</v>
       </c>
       <c r="I36" s="3" t="str">
@@ -3970,7 +3990,7 @@
       <c r="F37" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="5" t="s">
         <v>359</v>
       </c>
       <c r="I37" s="3" t="str">
@@ -3996,7 +4016,7 @@
       <c r="F38" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="5" t="s">
         <v>398</v>
       </c>
       <c r="I38" s="3" t="str">
@@ -4022,7 +4042,7 @@
       <c r="F39" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="5" t="s">
         <v>399</v>
       </c>
       <c r="I39" s="3" t="str">
@@ -4048,7 +4068,7 @@
       <c r="F40" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="5" t="s">
         <v>404</v>
       </c>
       <c r="I40" s="3" t="str">
@@ -4074,7 +4094,7 @@
       <c r="F41" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="5" t="s">
         <v>564</v>
       </c>
       <c r="I41" s="3" t="str">
@@ -4100,7 +4120,7 @@
       <c r="F42" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="5" t="s">
         <v>406</v>
       </c>
       <c r="I42" s="3" t="str">
@@ -4126,7 +4146,7 @@
       <c r="F43" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="5" t="s">
         <v>581</v>
       </c>
       <c r="I43" s="3" t="str">
@@ -4152,7 +4172,7 @@
       <c r="F44" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="5" t="s">
         <v>367</v>
       </c>
       <c r="I44" s="3" t="str">
@@ -4178,7 +4198,7 @@
       <c r="F45" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="5" t="s">
         <v>364</v>
       </c>
       <c r="I45" s="3" t="str">
@@ -4204,7 +4224,7 @@
       <c r="F46" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="5" t="s">
         <v>568</v>
       </c>
       <c r="I46" s="3" t="str">
@@ -4230,7 +4250,7 @@
       <c r="F47" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="5" t="s">
         <v>572</v>
       </c>
       <c r="I47" s="3" t="str">
@@ -4263,7 +4283,7 @@
     </row>
     <row r="49" spans="3:11">
       <c r="C49" s="1" t="str">
-        <f t="shared" ref="C49:C82" si="3" xml:space="preserve"> "/** " &amp; E49 &amp; " */ " &amp; D49 &amp; ","</f>
+        <f t="shared" ref="C49:C83" si="3" xml:space="preserve"> "/** " &amp; E49 &amp; " */ " &amp; D49 &amp; ","</f>
         <v>/** 方眼Diff */ APP_0010,</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -4275,7 +4295,7 @@
       <c r="F49" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="5" t="s">
         <v>317</v>
       </c>
       <c r="I49" s="3" t="str">
@@ -4305,7 +4325,7 @@
       <c r="F50" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="5" t="s">
         <v>228</v>
       </c>
       <c r="I50" s="3" t="str">
@@ -4330,12 +4350,12 @@
         <v>417</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="6" t="s">
         <v>229</v>
       </c>
       <c r="I51" s="3" t="str">
@@ -4360,13 +4380,13 @@
         <v>418</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>596</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>597</v>
       </c>
       <c r="I52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4387,16 +4407,16 @@
         <v>/** 比較結果レポート（テキスト）を表示しています... */ APP_0041,</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>600</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>601</v>
       </c>
       <c r="I53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4417,16 +4437,16 @@
         <v>/** 比較結果レポート（テキスト）の表示に失敗しました。 */ APP_0042,</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>604</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>605</v>
       </c>
       <c r="I54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4455,7 +4475,7 @@
       <c r="F55" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="5" t="s">
         <v>230</v>
       </c>
       <c r="I55" s="3" t="str">
@@ -4485,7 +4505,7 @@
       <c r="F56" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="5" t="s">
         <v>231</v>
       </c>
       <c r="I56" s="3" t="str">
@@ -4515,7 +4535,7 @@
       <c r="F57" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="5" t="s">
         <v>232</v>
       </c>
       <c r="I57" s="3" t="str">
@@ -4545,7 +4565,7 @@
       <c r="F58" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="5" t="s">
         <v>233</v>
       </c>
       <c r="I58" s="3" t="str">
@@ -4575,7 +4595,7 @@
       <c r="F59" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="5" t="s">
         <v>582</v>
       </c>
       <c r="I59" s="3" t="str">
@@ -4605,7 +4625,7 @@
       <c r="F60" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="5" t="s">
         <v>234</v>
       </c>
       <c r="I60" s="3" t="str">
@@ -4635,7 +4655,7 @@
       <c r="F61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="G61" s="5" t="s">
         <v>235</v>
       </c>
       <c r="I61" s="3" t="str">
@@ -4665,7 +4685,7 @@
       <c r="F62" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="5" t="s">
         <v>173</v>
       </c>
       <c r="I62" s="3" t="str">
@@ -4695,7 +4715,7 @@
       <c r="F63" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G63" s="5" t="s">
         <v>325</v>
       </c>
       <c r="I63" s="3" t="str">
@@ -4725,7 +4745,7 @@
       <c r="F64" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="5" t="s">
         <v>104</v>
       </c>
       <c r="I64" s="3" t="str">
@@ -4755,7 +4775,7 @@
       <c r="F65" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="G65" s="6" t="s">
+      <c r="G65" s="5" t="s">
         <v>287</v>
       </c>
       <c r="I65" s="3" t="str">
@@ -4785,7 +4805,7 @@
       <c r="F66" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G66" s="5" t="s">
         <v>236</v>
       </c>
       <c r="I66" s="3" t="str">
@@ -4815,7 +4835,7 @@
       <c r="F67" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G67" s="5" t="s">
         <v>237</v>
       </c>
       <c r="I67" s="3" t="str">
@@ -4833,2677 +4853,2707 @@
     </row>
     <row r="68" spans="3:11">
       <c r="C68" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
+        <f t="shared" ref="C68" si="4" xml:space="preserve"> "/** " &amp; E68 &amp; " */ " &amp; D68 &amp; ","</f>
+        <v>/** Oと%sのシートを比較しています... */ APP_0181,</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>432</v>
+        <v>609</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>38</v>
+        <v>610</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>238</v>
+        <v>611</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>613</v>
       </c>
       <c r="I68" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>APP_0190=シートの比較に失敗しました。</v>
+        <f t="shared" ref="I68" si="5" xml:space="preserve"> IF($D68="", "", $D68 &amp; "=" &amp; E68)</f>
+        <v>APP_0181=Oと%sのシートを比較しています...</v>
       </c>
       <c r="J68" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>APP_0190=Failed to compare sheets.</v>
+        <f t="shared" ref="J68" si="6" xml:space="preserve"> IF($D68="", "", $D68 &amp; "=" &amp; F68)</f>
+        <v>APP_0181=Comparing sheets O and %s...</v>
       </c>
       <c r="K68" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>APP_0190=工作表比较失败。</v>
+        <f t="shared" ref="K68" si="7" xml:space="preserve"> IF($D68="", "", $D68 &amp; "=" &amp; G68)</f>
+        <v>APP_0181=正在比较O和%s的工作表...</v>
       </c>
     </row>
     <row r="69" spans="3:11">
       <c r="C69" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** 比較結果レポート（Excel）を保存しています... */ APP_0200,</v>
+        <v>/** シートの比較に失敗しました。 */ APP_0190,</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>606</v>
+        <v>38</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="I69" s="3" t="str">
-        <f t="shared" ref="I69:K72" si="4" xml:space="preserve"> IF($D69="", "", $D69 &amp; "=" &amp; E69)</f>
-        <v>APP_0200=比較結果レポート（Excel）を保存しています...</v>
+        <f t="shared" si="0"/>
+        <v>APP_0190=シートの比較に失敗しました。</v>
       </c>
       <c r="J69" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0200=Saving result report...</v>
+        <f t="shared" si="1"/>
+        <v>APP_0190=Failed to compare sheets.</v>
       </c>
       <c r="K69" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0200=保存比较结果报告...</v>
+        <f t="shared" si="2"/>
+        <v>APP_0190=工作表比较失败。</v>
       </c>
     </row>
     <row r="70" spans="3:11">
       <c r="C70" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** 比較結果レポート（Excel）の保存に失敗しました。 */ APP_0210,</v>
+        <v>/** 比較結果レポート（Excel）を保存しています... */ APP_0200,</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="I70" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0210=比較結果レポート（Excel）の保存に失敗しました。</v>
+        <f t="shared" ref="I70:K73" si="8" xml:space="preserve"> IF($D70="", "", $D70 &amp; "=" &amp; E70)</f>
+        <v>APP_0200=比較結果レポート（Excel）を保存しています...</v>
       </c>
       <c r="J70" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0210=Failed to save result report.</v>
+        <f t="shared" si="8"/>
+        <v>APP_0200=Saving result report...</v>
       </c>
       <c r="K70" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0210=保存比较结果报告失败。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0200=保存比较结果报告...</v>
       </c>
     </row>
     <row r="71" spans="3:11">
       <c r="C71" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** 比較結果レポート（Excel）を表示しています... */ APP_0220,</v>
+        <v>/** 比較結果レポート（Excel）の保存に失敗しました。 */ APP_0210,</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="I71" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0220=比較結果レポート（Excel）を表示しています...</v>
+        <f t="shared" si="8"/>
+        <v>APP_0210=比較結果レポート（Excel）の保存に失敗しました。</v>
       </c>
       <c r="J71" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0220=Opening result report...</v>
+        <f t="shared" si="8"/>
+        <v>APP_0210=Failed to save result report.</v>
       </c>
       <c r="K71" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0220=显示比较结果报告...</v>
+        <f t="shared" si="8"/>
+        <v>APP_0210=保存比较结果报告失败。</v>
       </c>
     </row>
     <row r="72" spans="3:11">
       <c r="C72" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** 比較結果レポート（Excel）の表示に失敗しました。 */ APP_0230,</v>
+        <v>/** 比較結果レポート（Excel）を表示しています... */ APP_0220,</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>300</v>
       </c>
       <c r="I72" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0230=比較結果レポート（Excel）の表示に失敗しました。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0220=比較結果レポート（Excel）を表示しています...</v>
       </c>
       <c r="J72" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0230=Failed to open result report.</v>
+        <f t="shared" si="8"/>
+        <v>APP_0220=Opening result report...</v>
       </c>
       <c r="K72" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>APP_0230=显示比较结果报告失败。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0220=显示比较结果报告...</v>
       </c>
     </row>
     <row r="73" spans="3:11">
       <c r="C73" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
+        <v>/** 比較結果レポート（Excel）の表示に失敗しました。 */ APP_0230,</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>119</v>
+        <v>436</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>608</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>131</v>
+        <v>302</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="I73" s="3" t="str">
-        <f t="shared" ref="I69:I132" si="5" xml:space="preserve"> IF($D73="", "", $D73 &amp; "=" &amp; E73)</f>
-        <v>APP_0240=フォルダ同士の比較を開始します。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0230=比較結果レポート（Excel）の表示に失敗しました。</v>
       </c>
       <c r="J73" s="4" t="str">
-        <f t="shared" ref="J69:J132" si="6" xml:space="preserve"> IF($D73="", "", $D73 &amp; "=" &amp; F73)</f>
-        <v>APP_0240=Starting comparing folders.</v>
+        <f t="shared" si="8"/>
+        <v>APP_0230=Failed to open result report.</v>
       </c>
       <c r="K73" s="5" t="str">
-        <f t="shared" ref="K69:K132" si="7" xml:space="preserve"> IF($D73="", "", $D73 &amp; "=" &amp; G73)</f>
-        <v>APP_0240=开始互相比较文件夹。</v>
+        <f t="shared" si="8"/>
+        <v>APP_0230=显示比较结果报告失败。</v>
       </c>
     </row>
     <row r="74" spans="3:11">
       <c r="C74" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
+        <v>/** フォルダ同士の比較を開始します。 */ APP_0240,</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="I74" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
+        <f t="shared" ref="I74:I133" si="9" xml:space="preserve"> IF($D74="", "", $D74 &amp; "=" &amp; E74)</f>
+        <v>APP_0240=フォルダ同士の比較を開始します。</v>
       </c>
       <c r="J74" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0250=Failed to create output directory.</v>
+        <f t="shared" ref="J74:J133" si="10" xml:space="preserve"> IF($D74="", "", $D74 &amp; "=" &amp; F74)</f>
+        <v>APP_0240=Starting comparing folders.</v>
       </c>
       <c r="K74" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0250=创建输出目的地文件夹失败。</v>
+        <f t="shared" ref="K74:K133" si="11" xml:space="preserve"> IF($D74="", "", $D74 &amp; "=" &amp; G74)</f>
+        <v>APP_0240=开始互相比较文件夹。</v>
       </c>
     </row>
     <row r="75" spans="3:11">
       <c r="C75" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** Excelブックを比較しています... */ APP_0260,</v>
+        <v>/** 出力フォルダの作成に失敗しました。 */ APP_0250,</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>240</v>
+        <v>132</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="I75" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0260=Excelブックを比較しています...</v>
+        <f t="shared" si="9"/>
+        <v>APP_0250=出力フォルダの作成に失敗しました。</v>
       </c>
       <c r="J75" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0260=Comparing books...</v>
+        <f t="shared" si="10"/>
+        <v>APP_0250=Failed to create output directory.</v>
       </c>
       <c r="K75" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0260=比较工作簿...</v>
+        <f t="shared" si="11"/>
+        <v>APP_0250=创建输出目的地文件夹失败。</v>
       </c>
     </row>
     <row r="76" spans="3:11">
       <c r="C76" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
+        <v>/** Excelブックを比較しています... */ APP_0260,</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>262</v>
+        <v>133</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="I76" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0280=フォルダの比較に失敗しました。</v>
+        <f t="shared" si="9"/>
+        <v>APP_0260=Excelブックを比較しています...</v>
       </c>
       <c r="J76" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0280=Failed to compare folders.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0260=Comparing books...</v>
       </c>
       <c r="K76" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0280=文件夹比较失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0260=比较工作簿...</v>
       </c>
     </row>
     <row r="77" spans="3:11">
       <c r="C77" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
+        <v>/** フォルダの比較に失敗しました。 */ APP_0280,</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>35</v>
+        <v>440</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>241</v>
+        <v>261</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>262</v>
       </c>
       <c r="I77" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0290=シート同士の比較を開始します。</v>
+        <f t="shared" si="9"/>
+        <v>APP_0280=フォルダの比較に失敗しました。</v>
       </c>
       <c r="J77" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0290=Starting comparing sheets.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0280=Failed to compare folders.</v>
       </c>
       <c r="K77" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0290=开始相互比较工作表。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0280=文件夹比较失败。</v>
       </c>
     </row>
     <row r="78" spans="3:11">
       <c r="C78" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
+        <v>/** シート同士の比較を開始します。 */ APP_0290,</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>163</v>
+        <v>441</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>242</v>
+        <v>130</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="I78" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
+        <f t="shared" si="9"/>
+        <v>APP_0290=シート同士の比較を開始します。</v>
       </c>
       <c r="J78" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0320=Starting comparing folder trees.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0290=Starting comparing sheets.</v>
       </c>
       <c r="K78" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0320=开始互相比较文件夹树。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0290=开始相互比较工作表。</v>
       </c>
     </row>
     <row r="79" spans="3:11">
       <c r="C79" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
+        <v>/** フォルダツリー同士の比較を開始します。 */ APP_0320,</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>243</v>
+        <v>162</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="I79" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0330=フォルダツリーを比較しています...</v>
+        <f t="shared" si="9"/>
+        <v>APP_0320=フォルダツリー同士の比較を開始します。</v>
       </c>
       <c r="J79" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0330=Comparing folders...</v>
+        <f t="shared" si="10"/>
+        <v>APP_0320=Starting comparing folder trees.</v>
       </c>
       <c r="K79" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0330=比较文件夹...</v>
+        <f t="shared" si="11"/>
+        <v>APP_0320=开始互相比较文件夹树。</v>
       </c>
     </row>
     <row r="80" spans="3:11">
       <c r="C80" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
+        <v>/** フォルダツリーを比較しています... */ APP_0330,</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>263</v>
+        <v>158</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>262</v>
+        <v>164</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="I80" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
+        <f t="shared" si="9"/>
+        <v>APP_0330=フォルダツリーを比較しています...</v>
       </c>
       <c r="J80" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0390=Failed to compare folder trees.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0330=Comparing folders...</v>
       </c>
       <c r="K80" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0390=文件夹比较失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0330=比较文件夹...</v>
       </c>
     </row>
     <row r="81" spans="3:11">
       <c r="C81" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** (比較相手なし) */ APP_0400,</v>
+        <v>/** フォルダツリーの比較に失敗しました。 */ APP_0390,</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>44</v>
+        <v>444</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>244</v>
+        <v>265</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>262</v>
       </c>
       <c r="I81" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0400=(比較相手なし)</v>
+        <f t="shared" si="9"/>
+        <v>APP_0390=フォルダツリーの比較に失敗しました。</v>
       </c>
       <c r="J81" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0400=(no opponent)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0390=Failed to compare folder trees.</v>
       </c>
       <c r="K81" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0400=(没有对比)</v>
+        <f t="shared" si="11"/>
+        <v>APP_0390=文件夹比较失败。</v>
       </c>
     </row>
     <row r="82" spans="3:11">
       <c r="C82" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>/** (差分なし) */ APP_0410,</v>
+        <v>/** (比較相手なし) */ APP_0400,</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>245</v>
+        <v>86</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="I82" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0410=(差分なし)</v>
+        <f t="shared" si="9"/>
+        <v>APP_0400=(比較相手なし)</v>
       </c>
       <c r="J82" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0410=(no diffs)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0400=(no opponent)</v>
       </c>
       <c r="K82" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0410=(没有区别)</v>
+        <f t="shared" si="11"/>
+        <v>APP_0400=(没有对比)</v>
       </c>
     </row>
     <row r="83" spans="3:11">
       <c r="C83" s="1" t="str">
-        <f t="shared" ref="C83:C114" si="8" xml:space="preserve"> "/** " &amp; E83 &amp; " */ " &amp; D83 &amp; ","</f>
-        <v>/** 差異発生%dシート */ APP_0420,</v>
+        <f t="shared" si="3"/>
+        <v>/** (差分なし) */ APP_0410,</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>123</v>
+        <v>446</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>246</v>
+        <v>87</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="I83" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0420=差異発生%dシート</v>
+        <f t="shared" si="9"/>
+        <v>APP_0410=(差分なし)</v>
       </c>
       <c r="J83" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0420=diff sheets:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0410=(no diffs)</v>
       </c>
       <c r="K83" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0420=差异工作表%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0410=(没有区别)</v>
       </c>
     </row>
     <row r="84" spans="3:11">
       <c r="C84" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 余剰%dシート */ APP_0430,</v>
+        <f t="shared" ref="C84:C115" si="12" xml:space="preserve"> "/** " &amp; E84 &amp; " */ " &amp; D84 &amp; ","</f>
+        <v>/** 差異発生%dシート */ APP_0420,</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="I84" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0430=余剰%dシート</v>
+        <f t="shared" si="9"/>
+        <v>APP_0420=差異発生%dシート</v>
       </c>
       <c r="J84" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0430=redundant sheets:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0420=diff sheets:%d</v>
       </c>
       <c r="K84" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0430=冗余工作表%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0420=差异工作表%d</v>
       </c>
     </row>
     <row r="85" spans="3:11">
       <c r="C85" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** ブック%s： */ APP_0440,</v>
+        <f t="shared" si="12"/>
+        <v>/** 余剰%dシート */ APP_0430,</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>285</v>
+        <v>124</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>187</v>
+        <v>137</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="I85" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0440=ブック%s：</v>
+        <f t="shared" si="9"/>
+        <v>APP_0430=余剰%dシート</v>
       </c>
       <c r="J85" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0440=Book %s : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0430=redundant sheets:%d</v>
       </c>
       <c r="K85" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0440=工作簿%s：</v>
+        <f t="shared" si="11"/>
+        <v>APP_0430=冗余工作表%d</v>
       </c>
     </row>
     <row r="86" spans="3:11">
       <c r="C86" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
+        <f t="shared" si="12"/>
+        <v>/** ブック%s： */ APP_0440,</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>46</v>
+        <v>449</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>105</v>
+        <v>138</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="I86" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
+        <f t="shared" si="9"/>
+        <v>APP_0440=ブック%s：</v>
       </c>
       <c r="J86" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0440=Book %s : </v>
       </c>
       <c r="K86" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
+        <f t="shared" si="11"/>
+        <v>APP_0440=工作簿%s：</v>
       </c>
     </row>
     <row r="87" spans="3:11">
       <c r="C87" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
+        <f t="shared" si="12"/>
+        <v>/** ■差分サマリ --------------------------------------------------- */ APP_0450,</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>247</v>
+        <v>88</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="I87" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
+        <f t="shared" si="9"/>
+        <v>APP_0450=■差分サマリ ---------------------------------------------------</v>
       </c>
       <c r="J87" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
+        <f t="shared" si="10"/>
+        <v>APP_0450=## SUMMARY -----------------------------------------------------</v>
       </c>
       <c r="K87" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
+        <f t="shared" si="11"/>
+        <v>APP_0450=■差异摘要 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="88" spans="3:11">
       <c r="C88" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** フォルダ%s :  */ APP_0480,</v>
+        <f t="shared" si="12"/>
+        <v>/** ■差分詳細 ----------------------------------------------------- */ APP_0460,</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>140</v>
+        <v>451</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>248</v>
+        <v>89</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="I88" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0460=■差分詳細 -----------------------------------------------------</v>
       </c>
       <c r="J88" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0480=Folder %s : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0460=## DETAIL ------------------------------------------------------</v>
       </c>
       <c r="K88" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0480=文件夹%s : </v>
+        <f t="shared" si="11"/>
+        <v>APP_0460=■差异细节 -----------------------------------------------------</v>
       </c>
     </row>
     <row r="89" spans="3:11">
       <c r="C89" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 差異発生%dブック */ APP_0530,</v>
+        <f t="shared" si="12"/>
+        <v>/** フォルダ%s :  */ APP_0480,</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>249</v>
+        <v>141</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="I89" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0530=差異発生%dブック</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0480=フォルダ%s : </v>
       </c>
       <c r="J89" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0530=diff books:%d</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0480=Folder %s : </v>
       </c>
       <c r="K89" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0530=差异工作簿%d</v>
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">APP_0480=文件夹%s : </v>
       </c>
     </row>
     <row r="90" spans="3:11">
       <c r="C90" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 余剰%dブック */ APP_0540,</v>
+        <f t="shared" si="12"/>
+        <v>/** 差異発生%dブック */ APP_0530,</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="I90" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0540=余剰%dブック</v>
+        <f t="shared" si="9"/>
+        <v>APP_0530=差異発生%dブック</v>
       </c>
       <c r="J90" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0540=redundant books:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0530=diff books:%d</v>
       </c>
       <c r="K90" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0540=冗余工作簿%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0530=差异工作簿%d</v>
       </c>
     </row>
     <row r="91" spans="3:11">
       <c r="C91" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 比較失敗%dブック */ APP_0550,</v>
+        <f t="shared" si="12"/>
+        <v>/** 余剰%dブック */ APP_0540,</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="I91" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0550=比較失敗%dブック</v>
+        <f t="shared" si="9"/>
+        <v>APP_0540=余剰%dブック</v>
       </c>
       <c r="J91" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0550=failed books:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0540=redundant books:%d</v>
       </c>
       <c r="K91" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0550=失败工作簿%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0540=冗余工作簿%d</v>
       </c>
     </row>
     <row r="92" spans="3:11">
       <c r="C92" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 作業用フォルダ： */ APP_0580,</v>
+        <f t="shared" si="12"/>
+        <v>/** 比較失敗%dブック */ APP_0550,</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>183</v>
+        <v>168</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="I92" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0580=作業用フォルダ：</v>
+        <f t="shared" si="9"/>
+        <v>APP_0550=比較失敗%dブック</v>
       </c>
       <c r="J92" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0580=Working dir : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0550=failed books:%d</v>
       </c>
       <c r="K92" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0580=工作文件夹：</v>
+        <f t="shared" si="11"/>
+        <v>APP_0550=失败工作簿%d</v>
       </c>
     </row>
     <row r="93" spans="3:11">
       <c r="C93" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 差分なし */ APP_0600,</v>
+        <f t="shared" si="12"/>
+        <v>/** 作業用フォルダ： */ APP_0580,</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>288</v>
+        <v>175</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>291</v>
+        <v>283</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="I93" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0600=差分なし</v>
+        <f t="shared" si="9"/>
+        <v>APP_0580=作業用フォルダ：</v>
       </c>
       <c r="J93" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0600=No Diffs</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0580=Working dir : </v>
       </c>
       <c r="K93" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0600=没有区别</v>
+        <f t="shared" si="11"/>
+        <v>APP_0580=工作文件夹：</v>
       </c>
     </row>
     <row r="94" spans="3:11">
       <c r="C94" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 比較失敗 */ APP_0610,</v>
+        <f t="shared" si="12"/>
+        <v>/** 差分なし */ APP_0600,</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="I94" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0610=比較失敗</v>
+        <f t="shared" si="9"/>
+        <v>APP_0600=差分なし</v>
       </c>
       <c r="J94" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0610=Comparison Failed</v>
+        <f t="shared" si="10"/>
+        <v>APP_0600=No Diffs</v>
       </c>
       <c r="K94" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0610=比较失败</v>
+        <f t="shared" si="11"/>
+        <v>APP_0600=没有区别</v>
       </c>
     </row>
     <row r="95" spans="3:11">
       <c r="C95" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
+        <f t="shared" si="12"/>
+        <v>/** 比較失敗 */ APP_0610,</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>311</v>
+        <v>293</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>292</v>
       </c>
       <c r="I95" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0620=余剰行（A: %d, B: %d）</v>
+        <f t="shared" si="9"/>
+        <v>APP_0610=比較失敗</v>
       </c>
       <c r="J95" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0610=Comparison Failed</v>
       </c>
       <c r="K95" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0620=冗余行（A: %d, B: %d）</v>
+        <f t="shared" si="11"/>
+        <v>APP_0610=比较失败</v>
       </c>
     </row>
     <row r="96" spans="3:11">
       <c r="C96" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
+        <f t="shared" si="12"/>
+        <v>/** 余剰行（A: %d, B: %d） */ APP_0620,</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>309</v>
+        <v>304</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>311</v>
       </c>
       <c r="I96" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0630=余剰列（A: %d, B: %d）</v>
+        <f t="shared" si="9"/>
+        <v>APP_0620=余剰行（A: %d, B: %d）</v>
       </c>
       <c r="J96" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0620=Redundant Rows (A: %d, B: %d)</v>
       </c>
       <c r="K96" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0630=冗余列（A: %d, B: %d）</v>
+        <f t="shared" si="11"/>
+        <v>APP_0620=冗余行（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="97" spans="3:11">
       <c r="C97" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 差分セル（%d） */ APP_0640,</v>
+        <f t="shared" si="12"/>
+        <v>/** 余剰列（A: %d, B: %d） */ APP_0630,</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>309</v>
       </c>
       <c r="I97" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0640=差分セル（%d）</v>
+        <f t="shared" si="9"/>
+        <v>APP_0630=余剰列（A: %d, B: %d）</v>
       </c>
       <c r="J97" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0640=Diff Cells (%d)</v>
+        <f t="shared" si="10"/>
+        <v>APP_0630=Redundant Columns (A: %d, B: %d)</v>
       </c>
       <c r="K97" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0640=差异单元格（%d）</v>
+        <f t="shared" si="11"/>
+        <v>APP_0630=冗余列（A: %d, B: %d）</v>
       </c>
     </row>
     <row r="98" spans="3:11">
       <c r="C98" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 比較フォルダ%s： */ APP_0660,</v>
+        <f t="shared" si="12"/>
+        <v>/** 差分セル（%d） */ APP_0640,</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>174</v>
+        <v>306</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>215</v>
+        <v>308</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="I98" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0660=比較フォルダ%s：</v>
+        <f t="shared" si="9"/>
+        <v>APP_0640=差分セル（%d）</v>
       </c>
       <c r="J98" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0660=Folder %s : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0640=Diff Cells (%d)</v>
       </c>
       <c r="K98" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0660=文件夹%s：</v>
+        <f t="shared" si="11"/>
+        <v>APP_0640=差异单元格（%d）</v>
       </c>
     </row>
     <row r="99" spans="3:11">
       <c r="C99" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** ワークシート */ APP_0680,</v>
+        <f t="shared" si="12"/>
+        <v>/** 比較フォルダ%s： */ APP_0660,</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>48</v>
+        <v>462</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>106</v>
+        <v>141</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="I99" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0680=ワークシート</v>
+        <f t="shared" si="9"/>
+        <v>APP_0660=比較フォルダ%s：</v>
       </c>
       <c r="J99" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0680=Worksheet</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0660=Folder %s : </v>
       </c>
       <c r="K99" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0680=工作表</v>
+        <f t="shared" si="11"/>
+        <v>APP_0660=文件夹%s：</v>
       </c>
     </row>
     <row r="100" spans="3:11">
       <c r="C100" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** グラフシート */ APP_0690,</v>
+        <f t="shared" si="12"/>
+        <v>/** ワークシート */ APP_0680,</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>250</v>
+        <v>90</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="I100" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0690=グラフシート</v>
+        <f t="shared" si="9"/>
+        <v>APP_0680=ワークシート</v>
       </c>
       <c r="J100" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0690=Chart</v>
+        <f t="shared" si="10"/>
+        <v>APP_0680=Worksheet</v>
       </c>
       <c r="K100" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0690=图表表</v>
+        <f t="shared" si="11"/>
+        <v>APP_0680=工作表</v>
       </c>
     </row>
     <row r="101" spans="3:11">
       <c r="C101" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
+        <f t="shared" si="12"/>
+        <v>/** グラフシート */ APP_0690,</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>251</v>
+        <v>91</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="I101" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
+        <f t="shared" si="9"/>
+        <v>APP_0690=グラフシート</v>
       </c>
       <c r="J101" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0700=MS Excel 5.0 Dialog</v>
+        <f t="shared" si="10"/>
+        <v>APP_0690=Chart</v>
       </c>
       <c r="K101" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0700=MS Excel 5.0 对话表</v>
+        <f t="shared" si="11"/>
+        <v>APP_0690=图表表</v>
       </c>
     </row>
     <row r="102" spans="3:11">
       <c r="C102" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
+        <f t="shared" si="12"/>
+        <v>/** MS Excel 5.0 ダイアログシート */ APP_0700,</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>107</v>
+        <v>92</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="I102" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0710=Excel 4.0 マクロシート</v>
+        <f t="shared" si="9"/>
+        <v>APP_0700=MS Excel 5.0 ダイアログシート</v>
       </c>
       <c r="J102" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0710=Excel 4.0 Macro</v>
+        <f t="shared" si="10"/>
+        <v>APP_0700=MS Excel 5.0 Dialog</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0710=Excel 4.0 宏表</v>
+        <f t="shared" si="11"/>
+        <v>APP_0700=MS Excel 5.0 对话表</v>
       </c>
     </row>
     <row r="103" spans="3:11">
       <c r="C103" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 余剰行%d */ APP_0730,</v>
+        <f t="shared" si="12"/>
+        <v>/** Excel 4.0 マクロシート */ APP_0710,</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>108</v>
+        <v>93</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="I103" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0730=余剰行%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0710=Excel 4.0 マクロシート</v>
       </c>
       <c r="J103" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0730=redundant rows:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0710=Excel 4.0 Macro</v>
       </c>
       <c r="K103" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0730=冗余行%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0710=Excel 4.0 宏表</v>
       </c>
     </row>
     <row r="104" spans="3:11">
       <c r="C104" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 余剰列%d */ APP_0740,</v>
+        <f t="shared" si="12"/>
+        <v>/** 余剰行%d */ APP_0730,</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>109</v>
+        <v>94</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="I104" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0740=余剰列%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0730=余剰行%d</v>
       </c>
       <c r="J104" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0740=redundant columns:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0730=redundant rows:%d</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0740=冗余列%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0730=冗余行%d</v>
       </c>
     </row>
     <row r="105" spans="3:11">
       <c r="C105" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 差分セル%d */ APP_0750,</v>
+        <f t="shared" si="12"/>
+        <v>/** 余剰列%d */ APP_0740,</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>252</v>
+        <v>95</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="I105" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0750=差分セル%d</v>
+        <f t="shared" si="9"/>
+        <v>APP_0740=余剰列%d</v>
       </c>
       <c r="J105" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0750=diff cells:%d</v>
+        <f t="shared" si="10"/>
+        <v>APP_0740=redundant columns:%d</v>
       </c>
       <c r="K105" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0750=差异单元格%d</v>
+        <f t="shared" si="11"/>
+        <v>APP_0740=冗余列%d</v>
       </c>
     </row>
     <row r="106" spans="3:11">
       <c r="C106" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
+        <f t="shared" si="12"/>
+        <v>/** 差分セル%d */ APP_0750,</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>145</v>
+        <v>96</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="I106" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0750=差分セル%d</v>
       </c>
       <c r="J106" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0750=diff cells:%d</v>
       </c>
       <c r="K106" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
+        <f t="shared" si="11"/>
+        <v>APP_0750=差异单元格%d</v>
       </c>
     </row>
     <row r="107" spans="3:11">
       <c r="C107" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 行%d */ APP_0770,</v>
+        <f t="shared" si="12"/>
+        <v>/** シート%s上の余剰行 :  */ APP_0760,</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>55</v>
+        <v>142</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="I107" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0760=シート%s上の余剰行 : </v>
       </c>
       <c r="J107" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0770=Row %d</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0760=Redundant rows on sheet %s : </v>
       </c>
       <c r="K107" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0770=行%d</v>
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">APP_0760=工作表%s的冗余行 : </v>
       </c>
     </row>
     <row r="108" spans="3:11">
       <c r="C108" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
+        <f t="shared" si="12"/>
+        <v>/** 行%d */ APP_0770,</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>146</v>
+        <v>97</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="I108" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0770=行%d</v>
       </c>
       <c r="J108" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0770=Row %d</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
+        <f t="shared" si="11"/>
+        <v>APP_0770=行%d</v>
       </c>
     </row>
     <row r="109" spans="3:11">
       <c r="C109" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** %s列 */ APP_0790,</v>
+        <f t="shared" si="12"/>
+        <v>/** シート%s上の余剰列 :  */ APP_0780,</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>56</v>
+        <v>143</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="I109" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0780=シート%s上の余剰列 : </v>
       </c>
       <c r="J109" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0790=Column %s</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0780=Redundant columns on sheet %s : </v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0790=%s列</v>
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">APP_0780=工作表%s的冗余列 : </v>
       </c>
     </row>
     <row r="110" spans="3:11">
       <c r="C110" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 差分セル :  */ APP_0800,</v>
+        <f t="shared" si="12"/>
+        <v>/** %s列 */ APP_0790,</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>253</v>
+        <v>98</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="I110" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0800=差分セル : </v>
+        <f t="shared" si="9"/>
+        <v>APP_0790=%s列</v>
       </c>
       <c r="J110" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0800=Diff cells : </v>
+        <f t="shared" si="10"/>
+        <v>APP_0790=Column %s</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0800=差异单元格 : </v>
+        <f t="shared" si="11"/>
+        <v>APP_0790=%s列</v>
       </c>
     </row>
     <row r="111" spans="3:11">
       <c r="C111" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
+        <f t="shared" si="12"/>
+        <v>/** 差分セル :  */ APP_0800,</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>170</v>
+        <v>474</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>254</v>
+        <v>144</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="I111" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0800=差分セル : </v>
       </c>
       <c r="J111" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">APP_0820=Root folder %s : </v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0800=Diff cells : </v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">APP_0800=差异单元格 : </v>
       </c>
     </row>
     <row r="112" spans="3:11">
       <c r="C112" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 組み合わせ編集 */ APP_0860,</v>
+        <f t="shared" si="12"/>
+        <v>/** ルートフォルダ%s :  */ APP_0820,</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>269</v>
+        <v>170</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>271</v>
+        <v>171</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="I112" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0860=組み合わせ編集</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">APP_0820=ルートフォルダ%s : </v>
       </c>
       <c r="J112" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0860=Edit Pairing</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">APP_0820=Root folder %s : </v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0860=组合编辑</v>
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">APP_0820=根文件夹%s : </v>
       </c>
     </row>
     <row r="113" spans="3:11">
       <c r="C113" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
+        <f t="shared" si="12"/>
+        <v>/** 組み合わせ編集 */ APP_0860,</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>369</v>
+        <v>269</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="G113" s="6" t="s">
-        <v>373</v>
+        <v>270</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="I113" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
+        <f t="shared" si="9"/>
+        <v>APP_0860=組み合わせ編集</v>
       </c>
       <c r="J113" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
+        <f t="shared" si="10"/>
+        <v>APP_0860=Edit Pairing</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
+        <f t="shared" si="11"/>
+        <v>APP_0860=组合编辑</v>
       </c>
     </row>
     <row r="114" spans="3:11">
       <c r="C114" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
+        <f t="shared" si="12"/>
+        <v>/** 方眼Diff  -  Googleドライブ リビジョン選択 */ APP_0870,</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>373</v>
       </c>
       <c r="I114" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
+        <f t="shared" si="9"/>
+        <v>APP_0870=方眼Diff  -  Googleドライブ リビジョン選択</v>
       </c>
       <c r="J114" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
+        <f t="shared" si="10"/>
+        <v>APP_0870=HoganDiff  -  Google Drive Revision Selection</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
+        <f t="shared" si="11"/>
+        <v>APP_0870=方眼Diff  -  Google Drive 版本选择</v>
       </c>
     </row>
     <row r="115" spans="3:11">
       <c r="C115" s="1" t="str">
-        <f t="shared" ref="C115:C146" si="9" xml:space="preserve"> "/** " &amp; E115 &amp; " */ " &amp; D115 &amp; ","</f>
-        <v>/** 共有ドライブ */ APP_0890,</v>
+        <f t="shared" si="12"/>
+        <v>/** 方眼Diff  -  Googleドライブ ファイル選択 */ APP_0880,</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="G115" s="6" t="s">
-        <v>382</v>
+        <v>372</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>374</v>
       </c>
       <c r="I115" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0890=共有ドライブ</v>
+        <f t="shared" si="9"/>
+        <v>APP_0880=方眼Diff  -  Googleドライブ ファイル選択</v>
       </c>
       <c r="J115" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0890=Shared drives</v>
+        <f t="shared" si="10"/>
+        <v>APP_0880=HoganDiff  -  Google Drive File Selection</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0890=共享云端硬盘</v>
+        <f t="shared" si="11"/>
+        <v>APP_0880=方眼Diff  -  Google Drive 文件选择</v>
       </c>
     </row>
     <row r="116" spans="3:11">
       <c r="C116" s="1" t="str">
+        <f t="shared" ref="C116:C147" si="13" xml:space="preserve"> "/** " &amp; E116 &amp; " */ " &amp; D116 &amp; ","</f>
+        <v>/** 共有ドライブ */ APP_0890,</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="I116" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** すべてのファイル */ APP_0900,</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="I116" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0900=すべてのファイル</v>
+        <v>APP_0890=共有ドライブ</v>
       </c>
       <c r="J116" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0900=All files</v>
+        <f t="shared" si="10"/>
+        <v>APP_0890=Shared drives</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0900=所有文件</v>
+        <f t="shared" si="11"/>
+        <v>APP_0890=共享云端硬盘</v>
       </c>
     </row>
     <row r="117" spans="3:11">
       <c r="C117" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** すべてのファイル */ APP_0900,</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="I117" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** スター付き */ APP_0910,</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="I117" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0910=スター付き</v>
+        <v>APP_0900=すべてのファイル</v>
       </c>
       <c r="J117" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0910=Starred</v>
+        <f t="shared" si="10"/>
+        <v>APP_0900=All files</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0910=已加星标</v>
+        <f t="shared" si="11"/>
+        <v>APP_0900=所有文件</v>
       </c>
     </row>
     <row r="118" spans="3:11">
       <c r="C118" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** スター付き */ APP_0910,</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="I118" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="I118" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
+        <v>APP_0910=スター付き</v>
       </c>
       <c r="J118" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0920=Failed to download the file from Google Drive.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0910=Starred</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0910=已加星标</v>
       </c>
     </row>
     <row r="119" spans="3:11">
       <c r="C119" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Googleドライブからのファイルダウンロードに失敗しました。 */ APP_0920,</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="I119" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 更新者不明 */ APP_0930,</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="I119" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0930=更新者不明</v>
+        <v>APP_0920=Googleドライブからのファイルダウンロードに失敗しました。</v>
       </c>
       <c r="J119" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0930=Unknown</v>
+        <f t="shared" si="10"/>
+        <v>APP_0920=Failed to download the file from Google Drive.</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0930=更新者不明</v>
+        <f t="shared" si="11"/>
+        <v>APP_0920=从Google云端硬盘下载文件失败。</v>
       </c>
     </row>
     <row r="120" spans="3:11">
       <c r="C120" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 更新者不明 */ APP_0930,</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="I120" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 最新版 */ APP_0940,</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="I120" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0940=最新版</v>
+        <v>APP_0930=更新者不明</v>
       </c>
       <c r="J120" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0940=Latest</v>
+        <f t="shared" si="10"/>
+        <v>APP_0930=Unknown</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0940=最新版</v>
+        <f t="shared" si="11"/>
+        <v>APP_0930=更新者不明</v>
       </c>
     </row>
     <row r="121" spans="3:11">
       <c r="C121" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 最新版 */ APP_0940,</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="I121" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="I121" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
+        <v>APP_0940=最新版</v>
       </c>
       <c r="J121" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
+        <f t="shared" si="10"/>
+        <v>APP_0940=Latest</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
+        <f t="shared" si="11"/>
+        <v>APP_0940=最新版</v>
       </c>
     </row>
     <row r="122" spans="3:11">
       <c r="C122" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？ */ APP_0950,</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I122" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="I122" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0960=資格情報を削除しました。</v>
+        <v>APP_0950=方眼DiffとGoogleドライブの連携を解除します。\nよろしいですか？</v>
       </c>
       <c r="J122" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0960=Credentials have been deleted.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0950=Disconnect HoganDiff from Google Drive. Are you sure?</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0960=已删除凭据。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0950=解除方眼Diff与Google Drive的关联。确定吗？</v>
       </c>
     </row>
     <row r="123" spans="3:11">
       <c r="C123" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 資格情報を削除しました。 */ APP_0960,</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="I123" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="I123" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
+        <v>APP_0960=資格情報を削除しました。</v>
       </c>
       <c r="J123" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0960=Credentials have been deleted.</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0960=已删除凭据。</v>
       </c>
     </row>
     <row r="124" spans="3:11">
       <c r="C124" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。 */ APP_0970,</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="I124" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="I124" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0980=資格情報の削除に失敗しました。</v>
+        <v>APP_0970=このPCに保存されていたGoogleアカウント連携のための資格情報を削除しました。\n\nGoogle側の設定では引き続き方眼Diffとの連携が許可されています。\n連携許可を完全に取り消したい場合はGoogleアカウントのサイトから設定を行ってください。</v>
       </c>
       <c r="J124" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0980=Failed to delete credentials.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0970=The credentials for Google account integration stored on this PC have been deleted.\n\nGoogle's settings still allow integration with Hougan Diff.\nIf you want to completely revoke the integration permission, please configure the settings from your Google account site.</v>
       </c>
       <c r="K124" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0980=删除凭据失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0970=已删除保存在此电脑上的Google账户关联凭据。\n\n在Google设置中仍允许与方眼Diff的关联。\n如要完全撤销关联权限，请从Google账户网站进行设置。</v>
       </c>
     </row>
     <row r="125" spans="3:11">
       <c r="C125" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 資格情報の削除に失敗しました。 */ APP_0980,</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="I125" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="I125" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <v>APP_0980=資格情報の削除に失敗しました。</v>
       </c>
       <c r="J125" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="10"/>
+        <v>APP_0980=Failed to delete credentials.</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="11"/>
+        <v>APP_0980=删除凭据失败。</v>
       </c>
     </row>
     <row r="126" spans="3:11">
       <c r="C126" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_0990,</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="I126" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** Google連携エラー */ APP_1000,</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I126" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1000=Google連携エラー</v>
+        <v>APP_0990=資格情報の削除に失敗しました。\n時間をおいてから再度お試しください。\n\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J126" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1000=Google Integration Error</v>
+        <f t="shared" si="10"/>
+        <v>APP_0990=Failed to delete credentials.\nPlease try again after waiting a moment.\n\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K126" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1000=Google关联错误</v>
+        <f t="shared" si="11"/>
+        <v>APP_0990=删除凭据失败。\n请稍后重试。\n\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="127" spans="3:11">
       <c r="C127" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Google連携エラー */ APP_1000,</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I127" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="I127" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
+        <v>APP_1000=Google連携エラー</v>
       </c>
       <c r="J127" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1010=An error occurred during Google integration processing.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1000=Google Integration Error</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1010=Google关联处理过程中发生错误。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1000=Google关联错误</v>
       </c>
     </row>
     <row r="128" spans="3:11">
       <c r="C128" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Google連携処理中にエラーが発生しました。 */ APP_1010,</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="I128" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="I128" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
+        <v>APP_1010=Google連携処理中にエラーが発生しました。</v>
       </c>
       <c r="J128" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1010=An error occurred during Google integration processing.</v>
       </c>
       <c r="K128" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1010=Google关联处理过程中发生错误。</v>
       </c>
     </row>
     <row r="129" spans="3:11">
       <c r="C129" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。 */ APP_1020,</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I129" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="G129" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="I129" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
+        <v>APP_1020=エラー：%s\n\n時間をおいてから再度お試しください。\n失敗し続ける場合はウェブサイトからお問い合わせください。</v>
       </c>
       <c r="J129" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1030=File downloaded from Google Drive</v>
+        <f t="shared" si="10"/>
+        <v>APP_1020=Error: %s\n\nPlease try again after waiting a moment.\nIf the failure continues, please contact us from our website.</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1030=已从Google云端硬盘下载文件</v>
+        <f t="shared" si="11"/>
+        <v>APP_1020=失败：%s\n\n请稍后重试。\n如持续失败，请通过网站联系我们。</v>
       </c>
     </row>
     <row r="130" spans="3:11">
       <c r="C130" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Googleドライブからファイルをダウンロードしました。 */ APP_1030,</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="I130" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="I130" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
+        <v>APP_1030=Googleドライブからファイルをダウンロードしました。</v>
       </c>
       <c r="J130" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1030=File downloaded from Google Drive</v>
       </c>
       <c r="K130" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1030=已从Google云端硬盘下载文件</v>
       </c>
     </row>
     <row r="131" spans="3:11">
       <c r="C131" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** Webページの表示に失敗しました。ご利用のブラウザでお試しください。 */ APP_1040,</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I131" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="I131" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
+        <v>APP_1040=Webページの表示に失敗しました。ご利用のブラウザでお試しください。</v>
       </c>
       <c r="J131" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1050=Failed to open working directory.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1040=Failed to open the website. Please try using your browser.</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1050=显示工作文件夹失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1040=网页未能显示。 请尝试使用你的浏览器。</v>
       </c>
     </row>
     <row r="132" spans="3:11">
       <c r="C132" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの表示に失敗しました。 */ APP_1050,</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="I132" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="I132" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>APP_1060=作業用フォルダの変更</v>
+        <v>APP_1050=作業用フォルダの表示に失敗しました。</v>
       </c>
       <c r="J132" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v>APP_1060=Change working directory</v>
+        <f t="shared" si="10"/>
+        <v>APP_1050=Failed to open working directory.</v>
       </c>
       <c r="K132" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>APP_1060=改变工作文件夹</v>
+        <f t="shared" si="11"/>
+        <v>APP_1050=显示工作文件夹失败。</v>
       </c>
     </row>
     <row r="133" spans="3:11">
       <c r="C133" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの変更 */ APP_1060,</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I133" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="I133" s="3" t="str">
-        <f t="shared" ref="I133:I156" si="10" xml:space="preserve"> IF($D133="", "", $D133 &amp; "=" &amp; E133)</f>
-        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
+        <v>APP_1060=作業用フォルダの変更</v>
       </c>
       <c r="J133" s="4" t="str">
-        <f t="shared" ref="J133:J156" si="11" xml:space="preserve"> IF($D133="", "", $D133 &amp; "=" &amp; F133)</f>
-        <v>APP_1070=Failed to change working directory.</v>
+        <f t="shared" si="10"/>
+        <v>APP_1060=Change working directory</v>
       </c>
       <c r="K133" s="5" t="str">
-        <f t="shared" ref="K133:K156" si="12" xml:space="preserve"> IF($D133="", "", $D133 &amp; "=" &amp; G133)</f>
-        <v>APP_1070=更改工作文件夹失败。</v>
+        <f t="shared" si="11"/>
+        <v>APP_1060=改变工作文件夹</v>
       </c>
     </row>
     <row r="134" spans="3:11">
       <c r="C134" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
+        <f t="shared" si="13"/>
+        <v>/** 作業用フォルダの変更に失敗しました。 */ APP_1070,</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>224</v>
+        <v>70</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="I134" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
+        <f t="shared" ref="I134:I157" si="14" xml:space="preserve"> IF($D134="", "", $D134 &amp; "=" &amp; E134)</f>
+        <v>APP_1070=作業用フォルダの変更に失敗しました。</v>
       </c>
       <c r="J134" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
+        <f t="shared" ref="J134:J157" si="15" xml:space="preserve"> IF($D134="", "", $D134 &amp; "=" &amp; F134)</f>
+        <v>APP_1070=Failed to change working directory.</v>
       </c>
       <c r="K134" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
+        <f t="shared" ref="K134:K157" si="16" xml:space="preserve"> IF($D134="", "", $D134 &amp; "=" &amp; G134)</f>
+        <v>APP_1070=更改工作文件夹失败。</v>
       </c>
     </row>
     <row r="135" spans="3:11">
       <c r="C135" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
+        <f t="shared" si="13"/>
+        <v>/** 次のフォルダの内容物を全て削除します。よろしいですか？ */ APP_1080,</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>22</v>
+        <v>71</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="I135" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1080=次のフォルダの内容物を全て削除します。よろしいですか？</v>
       </c>
       <c r="J135" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1080=Delete all contents of the following directory. Are you sure?</v>
       </c>
       <c r="K135" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1080=删除以下文件夹的所有内容。你确定吗？</v>
       </c>
     </row>
     <row r="136" spans="3:11">
       <c r="C136" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
+        <f t="shared" si="13"/>
+        <v>/** 表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。 */ APP_1091,</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="I136" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="14"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="J136" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
       <c r="K136" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
+        <f t="shared" si="16"/>
+        <v>APP_1091=表示言語の変更を保存しました。\nアプリケーションを再起動すると変更が反映されます。</v>
       </c>
     </row>
     <row r="137" spans="3:11">
       <c r="C137" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
+        <f t="shared" si="13"/>
+        <v>/** Display language change is saved. \nRestart the application to reflect the change. */ APP_1092,</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G137" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I137" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="J137" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="15"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
       <c r="K137" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1092=Display language change is saved. \nRestart the application to reflect the change.</v>
       </c>
     </row>
     <row r="138" spans="3:11">
       <c r="C138" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
+        <f t="shared" si="13"/>
+        <v>/** 对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。 */ APP_1093,</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>390</v>
+        <v>501</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>584</v>
+        <v>128</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="I138" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1100=方眼Diff  -  詳細設定</v>
+        <f t="shared" si="14"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="J138" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
+        <f t="shared" si="15"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
       <c r="K138" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1100=方眼Diff  -  详细设置</v>
+        <f t="shared" si="16"/>
+        <v>APP_1093=对显示语言的改变已经被保存。\n重新启动应用程序，这些变化就会生效。</v>
       </c>
     </row>
     <row r="139" spans="3:11">
       <c r="C139" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
+        <f t="shared" si="13"/>
+        <v>/** 方眼Diff  -  詳細設定 */ APP_1100,</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>118</v>
+        <v>502</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>225</v>
+        <v>391</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>584</v>
       </c>
       <c r="I139" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1110=比較対象フォルダの選択</v>
+        <f t="shared" si="14"/>
+        <v>APP_1100=方眼Diff  -  詳細設定</v>
       </c>
       <c r="J139" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1110=Select comparison folder</v>
+        <f t="shared" si="15"/>
+        <v>APP_1100=HoganDiff  -  Advanced Settings</v>
       </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1110=选择用于比较的文件夹</v>
+        <f t="shared" si="16"/>
+        <v>APP_1100=方眼Diff  -  详细设置</v>
       </c>
     </row>
     <row r="140" spans="3:11">
       <c r="C140" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
+        <f t="shared" si="13"/>
+        <v>/** 比較対象フォルダの選択 */ APP_1110,</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>20</v>
+        <v>503</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>226</v>
+        <v>127</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="I140" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1120=比較対象ブックの選択</v>
+        <f t="shared" si="14"/>
+        <v>APP_1110=比較対象フォルダの選択</v>
       </c>
       <c r="J140" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1120=Select comparison book</v>
+        <f t="shared" si="15"/>
+        <v>APP_1110=Select comparison folder</v>
       </c>
       <c r="K140" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1120=选择用于比较的工作簿</v>
+        <f t="shared" si="16"/>
+        <v>APP_1110=选择用于比较的文件夹</v>
       </c>
     </row>
     <row r="141" spans="3:11">
       <c r="C141" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** Excel ブック */ APP_1130,</v>
+        <f t="shared" si="13"/>
+        <v>/** 比較対象ブックの選択 */ APP_1120,</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>103</v>
+        <v>66</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="I141" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1130=Excel ブック</v>
+        <f t="shared" si="14"/>
+        <v>APP_1120=比較対象ブックの選択</v>
       </c>
       <c r="J141" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1130=Excel book</v>
+        <f t="shared" si="15"/>
+        <v>APP_1120=Select comparison book</v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1130=Excel工作簿</v>
+        <f t="shared" si="16"/>
+        <v>APP_1120=选择用于比较的工作簿</v>
       </c>
     </row>
     <row r="142" spans="3:11">
       <c r="C142" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** ファイルを読み込めません： */ APP_1140,</v>
+        <f t="shared" si="13"/>
+        <v>/** Excel ブック */ APP_1130,</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>227</v>
+        <v>67</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="I142" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1140=ファイルを読み込めません：</v>
+        <f t="shared" si="14"/>
+        <v>APP_1130=Excel ブック</v>
       </c>
       <c r="J142" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_1140=Failed to open file : </v>
+        <f t="shared" si="15"/>
+        <v>APP_1130=Excel book</v>
       </c>
       <c r="K142" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1140=无法读取文件：</v>
+        <f t="shared" si="16"/>
+        <v>APP_1130=Excel工作簿</v>
       </c>
     </row>
     <row r="143" spans="3:11">
       <c r="C143" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** シートが見つかりません： */ APP_1150,</v>
+        <f t="shared" si="13"/>
+        <v>/** ファイルを読み込めません： */ APP_1140,</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>186</v>
+        <v>176</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="I143" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1150=シートが見つかりません：</v>
+        <f t="shared" si="14"/>
+        <v>APP_1140=ファイルを読み込めません：</v>
       </c>
       <c r="J143" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_1150=No such sheet : </v>
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">APP_1140=Failed to open file : </v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1150=没有找到工作表：</v>
+        <f t="shared" si="16"/>
+        <v>APP_1140=无法读取文件：</v>
       </c>
     </row>
     <row r="144" spans="3:11">
       <c r="C144" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** フォルダを読み込めません： */ APP_1160,</v>
+        <f t="shared" si="13"/>
+        <v>/** シートが見つかりません： */ APP_1150,</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>268</v>
+        <v>185</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="I144" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1160=フォルダを読み込めません：</v>
+        <f t="shared" si="14"/>
+        <v>APP_1150=シートが見つかりません：</v>
       </c>
       <c r="J144" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">APP_1150=No such sheet : </v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1160=无法读取文件夹：</v>
+        <f t="shared" si="16"/>
+        <v>APP_1150=没有找到工作表：</v>
       </c>
     </row>
     <row r="145" spans="3:11">
       <c r="C145" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
+        <f t="shared" si="13"/>
+        <v>/** フォルダを読み込めません： */ APP_1160,</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>392</v>
+        <v>266</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>586</v>
+        <v>267</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="I145" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
+        <f t="shared" si="14"/>
+        <v>APP_1160=フォルダを読み込めません：</v>
       </c>
       <c r="J145" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">APP_1160=Failed to open folder : </v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
+        <f t="shared" si="16"/>
+        <v>APP_1160=无法读取文件夹：</v>
       </c>
     </row>
     <row r="146" spans="3:11">
       <c r="C146" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
+        <f t="shared" si="13"/>
+        <v>/** 設定を初期化しアプリケーションを終了します。\nよろしいですか？ */ APP_1170,</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>117</v>
+        <v>509</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>392</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>216</v>
+        <v>393</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>586</v>
       </c>
       <c r="I146" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1170=設定を初期化しアプリケーションを終了します。\nよろしいですか？</v>
       </c>
       <c r="J146" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1180=Please specify different folders/books/sheets.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1170=Initialize settings and exit the application.\nAre you sure?</v>
       </c>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1170=初始化设置并退出应用程序。\n确定吗？</v>
       </c>
     </row>
     <row r="147" spans="3:11">
       <c r="C147" s="1" t="str">
-        <f t="shared" ref="C147:C156" si="13" xml:space="preserve"> "/** " &amp; E147 &amp; " */ " &amp; D147 &amp; ","</f>
-        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
+        <f t="shared" si="13"/>
+        <v>/** 同じフォルダ同士／ブック同士／シート同士を比較することはできません。 */ APP_1180,</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>114</v>
+        <v>510</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>217</v>
+        <v>125</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="I147" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1180=同じフォルダ同士／ブック同士／シート同士を比較することはできません。</v>
       </c>
       <c r="J147" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1180=Please specify different folders/books/sheets.</v>
       </c>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1180=指定非相同的文件夹／工作簿／工作表。</v>
       </c>
     </row>
     <row r="148" spans="3:11">
       <c r="C148" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
+        <f t="shared" ref="C148:C157" si="17" xml:space="preserve"> "/** " &amp; E148 &amp; " */ " &amp; D148 &amp; ","</f>
+        <v>/** 比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。 */ APP_1190,</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>194</v>
+        <v>115</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="I148" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1190=比較が完了しました。\n比較結果Excelは ★パスワードが解除された状態で★ 作業用フォルダに保存されています。\nセキュリティ上の必要性に応じて、アプリ右下のボタンから作業用フォルダ内の比較結果Excelファイルをご自身で削除してください。</v>
       </c>
       <c r="J148" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1210=Failed to create working directory.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1190=Comparison is completed.\nThe result book(s) is saved in working directory with the password UNLOCKED.\nDepending on your security needs, you can delete the result book(s) in the working directory YOURSELF via the button in the lower right corner of the application.</v>
       </c>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1210=创建工作文件夹失败。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1190=比较已经完成。\n比较结果Excel被保存在工作文件夹中，★密码未被锁定★。\n根据你的安全需要，你可以通过应用程序右下方的按钮自行删除工作文件夹中的比较结果Excel文件。</v>
       </c>
     </row>
     <row r="149" spans="3:11">
       <c r="C149" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
+        <f t="shared" si="17"/>
+        <v>/** 作業用フォルダの作成に失敗しました。 */ APP_1210,</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>193</v>
+        <v>77</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="I149" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1220=別の場所を指定してください。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1210=作業用フォルダの作成に失敗しました。</v>
       </c>
       <c r="J149" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1220=Please specify another location.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1210=Failed to create working directory.</v>
       </c>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1220=请指定其他位置。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1210=创建工作文件夹失败。</v>
       </c>
     </row>
     <row r="150" spans="3:11">
       <c r="C150" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 処理を中止しました。 */ APP_1240,</v>
+        <f t="shared" si="17"/>
+        <v>/** 別の場所を指定してください。 */ APP_1220,</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="I150" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1240=処理を中止しました。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1220=別の場所を指定してください。</v>
       </c>
       <c r="J150" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1240=Processing has been canceled.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1220=Please specify another location.</v>
       </c>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1240=处理已被取消。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1220=请指定其他位置。</v>
       </c>
     </row>
     <row r="151" spans="3:11">
       <c r="C151" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** パスワード指定 */ APP_1250,</v>
+        <f t="shared" si="17"/>
+        <v>/** 処理を中止しました。 */ APP_1240,</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>219</v>
+        <v>197</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="I151" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1250=パスワード指定</v>
+        <f t="shared" si="14"/>
+        <v>APP_1240=処理を中止しました。</v>
       </c>
       <c r="J151" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1250=Enter Password</v>
+        <f t="shared" si="15"/>
+        <v>APP_1240=Processing has been canceled.</v>
       </c>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1250=输入密码</v>
+        <f t="shared" si="16"/>
+        <v>APP_1240=处理已被取消。</v>
       </c>
     </row>
     <row r="152" spans="3:11">
       <c r="C152" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
+        <f t="shared" si="17"/>
+        <v>/** パスワード指定 */ APP_1250,</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>220</v>
+        <v>73</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I152" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1260=%s はパスワードで保護されています。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1250=パスワード指定</v>
       </c>
       <c r="J152" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1260=The book [%s] is password protected.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1250=Enter Password</v>
       </c>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1260=%s 是受密码保护的。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1250=输入密码</v>
       </c>
     </row>
     <row r="153" spans="3:11">
       <c r="C153" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
+        <f t="shared" si="17"/>
+        <v>/** %s はパスワードで保護されています。 */ APP_1260,</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>387</v>
+        <v>31</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="G153" s="6" t="s">
-        <v>389</v>
+        <v>74</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I153" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1270=新しいバージョンが利用可能です。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1260=%s はパスワードで保護されています。</v>
       </c>
       <c r="J153" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1270=A new version is available.</v>
+        <f t="shared" si="15"/>
+        <v>APP_1260=The book [%s] is password protected.</v>
       </c>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1270=有新版本可用。</v>
+        <f t="shared" si="16"/>
+        <v>APP_1260=%s 是受密码保护的。</v>
       </c>
     </row>
     <row r="154" spans="3:11">
       <c r="C154" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
+        <f t="shared" si="17"/>
+        <v>/** 新しいバージョンが利用可能です。 */ APP_1270,</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>585</v>
+        <v>388</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>389</v>
       </c>
       <c r="I154" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
+        <f t="shared" si="14"/>
+        <v>APP_1270=新しいバージョンが利用可能です。</v>
       </c>
       <c r="J154" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
+        <f t="shared" si="15"/>
+        <v>APP_1270=A new version is available.</v>
       </c>
       <c r="K154" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
+        <f t="shared" si="16"/>
+        <v>APP_1270=有新版本可用。</v>
       </c>
     </row>
     <row r="155" spans="3:11">
       <c r="C155" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
+        <f t="shared" si="17"/>
+        <v>/** 新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。 */ APP_1280,</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>411</v>
+        <v>518</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="G155" s="6" t="s">
-        <v>583</v>
+        <v>410</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="I155" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
+        <f t="shared" si="14"/>
+        <v>APP_1280=新しいバージョンが利用可能です。\n\n    - 現在のバージョン : %s\n    - 最新のバージョン : %s\n\n最新バージョンをダウンロードするには、Webサイトをご確認ください。</v>
       </c>
       <c r="J155" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
+        <f t="shared" si="15"/>
+        <v>APP_1280=A new version is available.\n\n    - Current version : %s\n    - Latest version : %s\n\nTo download the latest version, please visit:</v>
       </c>
       <c r="K155" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
+        <f t="shared" si="16"/>
+        <v>APP_1280=有新版本可用。\n\n    - 当前版本 : %s\n    - 最新版本 : %s\n\n要下载最新版本，请访问：</v>
       </c>
     </row>
     <row r="156" spans="3:11">
       <c r="C156" s="1" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
+        <v>/** お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s */ APP_1290,</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="I156" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>APP_1290=お使いのアプリケーションは最新バージョンです。\n    - 現在のバージョン : %s</v>
+      </c>
+      <c r="J156" s="4" t="str">
+        <f t="shared" si="15"/>
+        <v>APP_1290=Your application is up to date.\n    - Current version : %s</v>
+      </c>
+      <c r="K156" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>APP_1290=您的应用程序已是最新版本。\n    - 当前版本 : %s</v>
+      </c>
+    </row>
+    <row r="157" spans="3:11">
+      <c r="C157" s="1" t="str">
+        <f t="shared" si="17"/>
         <v>/** ★パスワード不明のためスキップ */ APP_1300,</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="E156" s="3" t="s">
+      <c r="E157" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="F156" s="4" t="s">
+      <c r="F157" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="G156" s="6" t="s">
+      <c r="G157" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="I156" s="3" t="str">
-        <f t="shared" si="10"/>
+      <c r="I157" s="3" t="str">
+        <f t="shared" si="14"/>
         <v>APP_1300=★パスワード不明のためスキップ</v>
       </c>
-      <c r="J156" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="J157" s="4" t="str">
+        <f t="shared" si="15"/>
         <v>APP_1300=★Skipped due to unknown password</v>
       </c>
-      <c r="K156" s="5" t="str">
-        <f t="shared" si="12"/>
+      <c r="K157" s="5" t="str">
+        <f t="shared" si="16"/>
         <v>APP_1300=★因密码未知而跳过</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:K156">
-    <sortCondition ref="D49:D156"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:K157">
+    <sortCondition ref="D49:D157"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
